--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -695,6 +695,11 @@
       <c r="M3" s="24" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="N3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
         </is>
       </c>
     </row>
@@ -5362,6 +5367,11 @@
       <c r="M78" s="24" t="inlineStr">
         <is>
           <t>philosophe juif, mathématicien, astronome, médecin, exégète biblique, talmudiste et philosophe.</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juive</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>1175 – 1249</t>
+          <t xml:space="preserve">1175 – 1245</t>
         </is>
       </c>
       <c r="D37" s="31" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>1404 – 1457</t>
+          <t xml:space="preserve">1407 – 1457</t>
         </is>
       </c>
       <c r="D110" s="31" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -702,6 +702,16 @@
           <t xml:space="preserve">Traditions</t>
         </is>
       </c>
+      <c r="O3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Groupe</t>
+        </is>
+      </c>
+      <c r="P3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Importance</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="150.75" customHeight="1" s="25">
       <c r="A4" s="30" t="n">
@@ -787,6 +797,11 @@
           <t>anonyme qui tenta d'allier la pensée Platonicienne avec le Christianisme.</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="137.25" customHeight="1" s="25">
       <c r="A5" s="30" t="n">
@@ -852,6 +867,11 @@
           <t>philosophe érudit espagnol et l'un des plus influents de son temps.</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="126.75" customHeight="1" s="25">
       <c r="A6" s="30" t="n">
@@ -916,6 +936,14 @@
           <t>théologien byzantin qui approfondit la question de Dieu dans la nature.</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P6">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="97.5" customHeight="1" s="25">
       <c r="A7" s="30" t="n">
@@ -976,6 +1004,11 @@
       <c r="M7" s="24" t="inlineStr">
         <is>
           <t>philosophe et moine chrétien anglais célèbre pour son travail théologique.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1041,6 +1074,11 @@
       <c r="M8" s="24" t="inlineStr">
         <is>
           <t>religieux d'origine arabe et un des derniers Pères de l'Église.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -1109,6 +1147,11 @@
           <t>philosophe français qui a permis la transition de l'Antiquité vers le Moyen Âge.</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="174" customHeight="1" s="25">
       <c r="A10" s="30" t="n">
@@ -1170,6 +1213,11 @@
           <t>penseur religieux marquant le début de la traduction des textes grecs.</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="210" customHeight="1" s="25">
       <c r="A11" s="30" t="n">
@@ -1229,6 +1277,11 @@
       <c r="M11" s="24" t="inlineStr">
         <is>
           <t>philosophe qui incarna la fusion entre pouvoir ecclésiastique et gouvernance politique.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1297,6 +1350,11 @@
           <t>philosophe irlandais qui systématisa la connaissance en une vision cohérente de la réalité.</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="178.5" customHeight="1" s="25">
       <c r="A13" s="30" t="n">
@@ -1357,6 +1415,11 @@
       <c r="M13" s="24" t="inlineStr">
         <is>
           <t>religieux français qui contribua à l'essor de l'abaque.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1424,6 +1487,11 @@
           <t>religieux français qui réforma la vie monastique.</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="164.25" customHeight="1" s="25">
       <c r="A15" s="30" t="n">
@@ -1485,6 +1553,11 @@
           <t>philosophe français et figure intellectuelle des plus marquantes du tournant de l'an mil.</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="116.25" customHeight="1" s="25">
       <c r="A16" s="30" t="n">
@@ -1544,6 +1617,11 @@
       <c r="M16" s="24" t="inlineStr">
         <is>
           <t>religieux et théologien français condamné pour hérésie.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -1614,6 +1692,11 @@
           <t>religieux italien qui participa à la réforme grégorienne de l'église.</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="231.75" customHeight="1" s="25">
       <c r="A18" s="30" t="n">
@@ -1679,6 +1762,11 @@
           <t>religieux italien qui œuvra à l'assouplissement de la réforme grégorienne.</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="150" customHeight="1" s="25">
       <c r="A19" s="30" t="n">
@@ -1744,6 +1832,11 @@
           <t>philosophe médiéval qui explique pourquoi Dieu s'est fait homme.</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="137.25" customHeight="1" s="25">
       <c r="A20" s="30" t="n">
@@ -1801,6 +1894,11 @@
           <t>philosophe religieux français défenseur courageux des principes réformateurs.</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="158.25" customHeight="1" s="25">
       <c r="A21" s="30" t="n">
@@ -1862,6 +1960,11 @@
           <t>philosophe zélandais l'une des figures les plus énigmatiques du mouvement réformateur du XIIe siècle.</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="182.25" customHeight="1" s="25">
       <c r="A22" s="30" t="n">
@@ -1923,6 +2026,11 @@
           <t>philosophe scolastique français fondateur du nominalisme.</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="180.75" customHeight="1" s="25">
       <c r="A23" s="30" t="n">
@@ -1984,6 +2092,11 @@
           <t>philosophe anglais et un important passeur de savoir de l'Occident médiéval.</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="174" customHeight="1" s="25">
       <c r="A24" s="30" t="n">
@@ -2044,6 +2157,11 @@
           <t>Philosophe français au réalisme modéré dans le débat sur les universaux.</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="174" customHeight="1" s="25">
       <c r="A25" s="30" t="n">
@@ -2105,6 +2223,11 @@
       <c r="M25" s="24" t="inlineStr">
         <is>
           <t>religieux français qui a joué un rôle crucial dans la pensée médiévale.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -2172,6 +2295,14 @@
           <t>réformateur religieux français qui dénonça les richesses de l'église.</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P26">
+        <v>2</v>
+      </c>
     </row>
     <row r="27" ht="217.5" customHeight="1" s="25">
       <c r="A27" s="30" t="n">
@@ -2233,6 +2364,11 @@
           <t>abbesse et intellectuelle française connue pour sa relation avec Pierre Abélard.</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="217.5" customHeight="1" s="25">
       <c r="A28" s="30" t="n">
@@ -2293,6 +2429,11 @@
           <t>philosophe français qui organisa tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu.</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="179.25" customHeight="1" s="25">
       <c r="A29" s="30" t="n">
@@ -2352,6 +2493,11 @@
           <t>abbesse, mystique et visionnaire du Moyen Âge.</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="157.5" customHeight="1" s="25">
       <c r="A30" s="30" t="n">
@@ -2414,6 +2560,14 @@
           <t>philosophe &amp; théologien scolastique majeur connu pour "les 4 Livres des Sentences".</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P30">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" ht="152.25" customHeight="1" s="25">
       <c r="A31" s="30" t="n">
@@ -2475,6 +2629,11 @@
           <t>philosophe et intellectuel anglais adepte de la perspective cicéronienne.</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="153" customHeight="1" s="25">
       <c r="A32" s="30" t="n">
@@ -2536,6 +2695,11 @@
           <t>philosophe français surnommé Doctor Universalis pour son savoir encyclopédique.</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="158.25" customHeight="1" s="25">
       <c r="A33" s="30" t="n">
@@ -2596,6 +2760,11 @@
           <t>philosophe scolastique français médiéval qui a travaillé sur l’interprétation de la Bible.</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="210" customHeight="1" s="25">
       <c r="A34" s="30" t="n">
@@ -2657,6 +2826,11 @@
           <t>philosophe français figure clé de la première scolastique parisienne.</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="184.5" customHeight="1" s="25">
       <c r="A35" s="30" t="n">
@@ -2718,6 +2892,11 @@
           <t>philosophe italien au sommet de la hiérarchie ecclésiastique de son temps.</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="116.25" customHeight="1" s="25">
       <c r="A36" s="30" t="n">
@@ -2779,6 +2958,11 @@
           <t>philosophe  et érudit anglais et l'un des précurseurs de la science moderne.</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="137.25" customHeight="1" s="25">
       <c r="A37" s="30" t="n">
@@ -2840,6 +3024,11 @@
           <t>philosophe scolastique anglais &amp; grand maître franciscain.</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="126.75" customHeight="1" s="25">
       <c r="A38" s="30" t="n">
@@ -2902,6 +3091,11 @@
           <t>philosophe scolastique français et 1er à intégrer la philosophie d'Aristote.</t>
         </is>
       </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="157.5" customHeight="1" s="25">
       <c r="A39" s="30" t="n">
@@ -2962,6 +3156,11 @@
       <c r="M39" s="24" t="inlineStr">
         <is>
           <t>philosophe franciscain français figure clé de la scolastique parisienne précoce.</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -3028,6 +3227,14 @@
           <t>religieux érudit germanique qui unit science et foi.</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P40">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" ht="105.75" customHeight="1" s="25">
       <c r="A41" s="30" t="n">
@@ -3089,6 +3296,11 @@
           <t>philosophe scolastique français qui incarne les figures obscures des écoles médiévales .</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="147.75" customHeight="1" s="25">
       <c r="A42" s="30" t="n">
@@ -3151,6 +3363,11 @@
           <t>philosophe dominicain anglais membre d'un ordre mendiant &amp; reconnu par l'église.</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="112.5" customHeight="1" s="25">
       <c r="A43" s="30" t="n">
@@ -3212,6 +3429,14 @@
           <t>philosophe espagnol auteur des "Summulae logicales", manuel scolastique.</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P43">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" ht="123" customHeight="1" s="25">
       <c r="A44" s="30" t="n">
@@ -3273,6 +3498,11 @@
           <t>religieux italien et pilier de la théologie chrétienne du Moyen Âge.</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="126" customHeight="1" s="25">
       <c r="A45" s="30" t="n">
@@ -3335,6 +3565,11 @@
           <t>philosophe scolastique néerlandais épistémologue centré sur l'illumination divine.</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="128.25" customHeight="1" s="25">
       <c r="A46" s="30" t="n">
@@ -3397,6 +3632,11 @@
           <t>philosophe anglais qui fut l'un des inventeurs de la méthode scientifique.</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="114" customHeight="1" s="25">
       <c r="A47" s="30" t="n">
@@ -3454,6 +3694,14 @@
           <t>philosophe dominicain français élève d'Albert le Grand.</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P47">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" ht="183.75" customHeight="1" s="25">
       <c r="A48" s="30" t="n">
@@ -3515,6 +3763,11 @@
           <t>philosophe italien et personnalité intellectuelle des plus marquantes de la Florence du XIIIe siècle.</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="187.5" customHeight="1" s="25">
       <c r="A49" s="30" t="n">
@@ -3576,6 +3829,14 @@
           <t>philosophe chrétien italien qui a fondé l'école de pensée Scolastique.</t>
         </is>
       </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P49">
+        <v>3</v>
+      </c>
     </row>
     <row r="50" ht="116.25" customHeight="1" s="25">
       <c r="A50" s="30" t="n">
@@ -3638,6 +3899,11 @@
           <t>philosophe franciscain et théologien conservateur en conflit avec Thomas d'Aquin.</t>
         </is>
       </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="90" customHeight="1" s="25">
       <c r="A51" s="30" t="n">
@@ -3695,6 +3961,11 @@
           <t>philosophe dominicain anglais éminent défenseur du thomisme.</t>
         </is>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="78" customHeight="1" s="25">
       <c r="A52" s="30" t="n">
@@ -3756,6 +4027,11 @@
           <t>philosophe scolastique belge et astronome dominicain.</t>
         </is>
       </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="123.75" customHeight="1" s="25">
       <c r="A53" s="30" t="n">
@@ -3817,6 +4093,11 @@
           <t>philosophe catalan précurseur de la logique symbolique par sa méthode nommée 'Art'.</t>
         </is>
       </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="105.75" customHeight="1" s="25">
       <c r="A54" s="30" t="n">
@@ -3879,6 +4160,11 @@
           <t>philosophe français &amp; figure centrale de l'aristotélisme radical.</t>
         </is>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="91.5" customHeight="1" s="25">
       <c r="A55" s="30" t="n">
@@ -3941,6 +4227,11 @@
           <t>philosophe franciscain italien qui a contribué à forger de nombreux concepts.</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="114.75" customHeight="1" s="25">
       <c r="A56" s="30" t="n">
@@ -4003,6 +4294,11 @@
           <t>philosophe &amp; théologien français grand commentateur médiéval d’Aristote.</t>
         </is>
       </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="141.75" customHeight="1" s="25">
       <c r="A57" s="30" t="n">
@@ -4064,6 +4360,11 @@
           <t>Philosophe danois, figure majeure du courant averroïste de l’Université de Paris.</t>
         </is>
       </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="132.75" customHeight="1" s="25">
       <c r="A58" s="30" t="n">
@@ -4125,6 +4426,11 @@
           <t>philosophe dominicain allemand connu pour son opposition au thomisme.</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="126.75" customHeight="1" s="25">
       <c r="A59" s="30" t="n">
@@ -4186,6 +4492,11 @@
           <t>philosophe &amp; théologien scolastique belge contributeur en métaphysique.</t>
         </is>
       </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="126.75" customHeight="1" s="25">
       <c r="A60" s="30" t="n">
@@ -4247,6 +4558,11 @@
           <t>philosophe italien théoricien du pouvoir princier &amp; défenseur de l'église.</t>
         </is>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="95.25" customHeight="1" s="25">
       <c r="A61" s="30" t="n">
@@ -4308,6 +4624,11 @@
           <t>philosophe franciscain français figure majeure des franciscains du Languedoc.</t>
         </is>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="116.25" customHeight="1" s="25">
       <c r="A62" s="30" t="n">
@@ -4371,6 +4692,11 @@
           <t>philosophe surnommé "doctor solidus" pour la solidité de sa pensée.</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="125.25" customHeight="1" s="25">
       <c r="A63" s="30" t="n">
@@ -4433,6 +4759,11 @@
           <t>philosophe italien célèbre pour son ouvrage sur le "gouvernement chrétien".</t>
         </is>
       </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="102" customHeight="1" s="25">
       <c r="A64" s="30" t="n">
@@ -4494,6 +4825,11 @@
           <t>philosophe dominicain breton qui appartient au milieu universitaire parisien.</t>
         </is>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="95.25" customHeight="1" s="25">
       <c r="A65" s="30" t="n">
@@ -4557,6 +4893,11 @@
           <t>théologien &amp; chroniqueur anglais de l'oeuvre littéraire du 13ème siècle.</t>
         </is>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="238.5" customHeight="1" s="25">
       <c r="A66" s="30" t="n">
@@ -4619,6 +4960,11 @@
           <t>philosophe et théologien allemand chrétien d'influence mystique.</t>
         </is>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="137.25" customHeight="1" s="25">
       <c r="A67" s="30" t="n">
@@ -4680,6 +5026,11 @@
       <c r="M67" s="24" t="inlineStr">
         <is>
           <t>philosophe scolastique français &amp; cardinal franciscain qui illustre la place des ordres mendiants.</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4744,6 +5095,11 @@
       <c r="M68" s="24" t="inlineStr">
         <is>
           <t>poète italien du Moyen Âge qui donna une vision des cieux dans la Divine Comédie.</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4812,6 +5168,14 @@
           <t>philosophe écossais qui joua un rôle important dans la pensée Scolastique.</t>
         </is>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" ht="201" customHeight="1" s="25">
       <c r="A70" s="30" t="n">
@@ -4869,6 +5233,11 @@
           <t>philosophe français le plus grand exégète biblique du Moyen Âge tardif.</t>
         </is>
       </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="137.25" customHeight="1" s="25">
       <c r="A71" s="30" t="n">
@@ -4924,6 +5293,11 @@
       <c r="M71" s="24" t="inlineStr">
         <is>
           <t>philosophe français connu pour son rejet de certaines thèses thomistes.</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -4998,6 +5372,11 @@
           <t>philosophe italien précurseur de la séparation de l'Église et de l'État.</t>
         </is>
       </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="184.5" customHeight="1" s="25">
       <c r="A73" s="30" t="n">
@@ -5059,6 +5438,11 @@
           <t>philosophe anglais champion du réalisme philosophique face à la révolution nominaliste.</t>
         </is>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="116.25" customHeight="1" s="25">
       <c r="A74" s="30" t="n">
@@ -5120,6 +5504,11 @@
           <t>philosophe &amp; théologien franciscain français de la scolastique tardive.</t>
         </is>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="95.25" customHeight="1" s="25">
       <c r="A75" s="30" t="n">
@@ -5179,6 +5568,11 @@
       <c r="M75" s="24" t="inlineStr">
         <is>
           <t>philosophe français et représentant de l'Aristotélisme.</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -5246,6 +5640,14 @@
           <t>philosophe anglais connu pour sa formulation du rasoir d'Ockham.</t>
         </is>
       </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P76">
+        <v>3</v>
+      </c>
     </row>
     <row r="77" ht="139.5" customHeight="1" s="25">
       <c r="A77" s="30" t="n">
@@ -5307,6 +5709,11 @@
           <t>philosophe franciscain français grand représentant du courant Scotiste.</t>
         </is>
       </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="139.5" customHeight="1" s="25">
       <c r="A78" s="36" t="n">
@@ -5371,7 +5778,12 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t xml:space="preserve">juive</t>
+          <t xml:space="preserve">juive;occident</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">islam-juif</t>
         </is>
       </c>
     </row>
@@ -5435,6 +5847,11 @@
           <t>philosophe dominicain anglais figure du nominalisme oxonien et disciple d’Ockham.</t>
         </is>
       </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="172.5" customHeight="1" s="25">
       <c r="A80" s="30" t="n">
@@ -5496,6 +5913,11 @@
           <t>philosophe anglais qui contribua à la théologie augustinienne &amp; aux sciences naturelles.</t>
         </is>
       </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="214.5" customHeight="1" s="25">
       <c r="A81" s="30" t="n">
@@ -5558,6 +5980,11 @@
           <t>philosophe français instigateur du scepticisme religieux en Europe.</t>
         </is>
       </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="214.5" customHeight="1" s="25">
       <c r="A82" s="30" t="n">
@@ -5614,6 +6041,11 @@
           <t xml:space="preserve"> philosophe naturel, logicien et mathématicien anglais figure centrale des « Calculateurs d’Oxford ».</t>
         </is>
       </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="222" customHeight="1" s="25">
       <c r="A83" s="30" t="n">
@@ -5675,6 +6107,11 @@
           <t>philosophe français au contact direct de la spéculation mystique la plus audacieuse de son temps.</t>
         </is>
       </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="183" customHeight="1" s="25">
       <c r="A84" s="30" t="n">
@@ -5736,6 +6173,11 @@
           <t>religieux anglais et l'un des transmetteurs essentiels de la révolution ockhamiste.</t>
         </is>
       </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="155.25" customHeight="1" s="25">
       <c r="A85" s="30" t="n">
@@ -5797,6 +6239,11 @@
           <t>philosophe et théologien médiéval , précurseur du scepticisme.</t>
         </is>
       </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="117.75" customHeight="1" s="25">
       <c r="A86" s="30" t="n">
@@ -5858,6 +6305,11 @@
           <t>philosophe cistercien français connu pour ses positions nominalistes radicales.</t>
         </is>
       </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="108" customHeight="1" s="25">
       <c r="A87" s="30" t="n">
@@ -5919,6 +6371,11 @@
           <t>philosophe italien et un des derniers grands scolastiques du Moyen Âge.</t>
         </is>
       </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="108" customHeight="1" s="25">
       <c r="A88" s="30" t="n">
@@ -5978,6 +6435,11 @@
           <t>philosophe et logicien anglais proche du Merton College à Oxford.</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="193.5" customHeight="1" s="25">
       <c r="A89" s="30" t="n">
@@ -6039,6 +6501,11 @@
           <t>philosophe anglais qui appartient au groupe brillant des Calculatores de Merton.</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="95.25" customHeight="1" s="25">
       <c r="A90" s="30" t="n">
@@ -6100,6 +6567,11 @@
           <t>philosophe allemand représentant du nominalisme tardif.</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="105.75" customHeight="1" s="25">
       <c r="A91" s="30" t="n">
@@ -6161,6 +6633,11 @@
           <t>théologien anglais précurseur de la réforme protestante anglaise.</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="105.75" customHeight="1" s="25">
       <c r="A92" s="30" t="n">
@@ -6222,6 +6699,11 @@
           <t>philosophe français penseur le plus polyvalent du Moyen Âge tardif.</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="99.75" customHeight="1" s="25">
       <c r="A93" s="30" t="n">
@@ -6283,6 +6765,11 @@
           <t>philosophe italien célèbre pour ses commentaires sur le "Liber Sententiarum".</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="144" customHeight="1" s="25">
       <c r="A94" s="30" t="n">
@@ -6344,6 +6831,11 @@
           <t>philosophe italien à la croisée de la philosophie naturelle, de l'astronomie et de la mécanique.</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="100.5" customHeight="1" s="25">
       <c r="A95" s="30" t="n">
@@ -6407,6 +6899,11 @@
           <t>philosophe italien et figure de référence de la Renaissance culturelle florentine.</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="93.75" customHeight="1" s="25">
       <c r="A96" s="30" t="n">
@@ -6467,6 +6964,11 @@
       <c r="M96" s="24" t="inlineStr">
         <is>
           <t>philosophe néerlandais et figure majeure du nominalisme scolastique.</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -6533,6 +7035,11 @@
           <t>philosophe et homme d’Église français, acteur clé du Grand Schisme d’Occident.</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="122.25" customHeight="1" s="25">
       <c r="A98" s="30" t="n">
@@ -6595,6 +7102,11 @@
           <t>philosophe byzantin fervent défenseur du néoplatonisme contre l'aristotélisme scolastique.</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="183.75" customHeight="1" s="25">
       <c r="A99" s="30" t="n">
@@ -6654,6 +7166,11 @@
       <c r="M99" s="24" t="inlineStr">
         <is>
           <t>théologien français qui contribua à réformer l'église par une spiritualité plus personnelle.</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>
@@ -6721,6 +7238,11 @@
           <t>philosophe et poétesse française considérée comme la première femme de lettres.</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="138.75" customHeight="1" s="25">
       <c r="A101" s="30" t="n">
@@ -6784,6 +7306,11 @@
           <t>philosophe et humaniste italien considéré comme le créateur de la forme renaissance .</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="111.75" customHeight="1" s="25">
       <c r="A102" s="30" t="n">
@@ -6847,6 +7374,11 @@
           <t>philosophe tchèque précurseur de la Réforme protestante, influencé par John Wyclif.</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="117.75" customHeight="1" s="25">
       <c r="A103" s="30" t="n">
@@ -6908,6 +7440,11 @@
           <t>humaniste italien qui a rendu les textes grecs accessibles aux lettrés de la renaissance.</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="117" customHeight="1" s="25">
       <c r="A104" s="30" t="n">
@@ -6971,6 +7508,11 @@
           <t>philosophe italien connu pour son rôle dans la redécouverte de textes anciens perdus.</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="136.5" customHeight="1" s="25">
       <c r="A105" s="30" t="n">
@@ -7032,6 +7574,11 @@
           <t>philosophe néerlandais auteur de "L'Imitation de Jésus-Christ", livre de spiritualité chrétienne.</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="80.25" customHeight="1" s="25">
       <c r="A106" s="30" t="n">
@@ -7093,6 +7640,11 @@
           <t>philosophe tchèque  redoutable dans les disputes académiques.</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="155.25" customHeight="1" s="25">
       <c r="A107" s="30" t="n">
@@ -7155,6 +7707,11 @@
           <t>philosophe catalan célèbre pour son ouvrage "Theologia naturalis sive Liber creaturarum".</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="165.75" customHeight="1" s="25">
       <c r="A108" s="30" t="n">
@@ -7218,6 +7775,11 @@
           <t>philosophe allemand précurseur de la pensée moderne en raison de ses idées novatrices.</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="98.25" customHeight="1" s="25">
       <c r="A109" s="30" t="n">
@@ -7282,6 +7844,11 @@
           <t>philosophe italien de la renaissance et humaniste convaincu.</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="147.75" customHeight="1" s="25">
       <c r="A110" s="30" t="n">
@@ -7343,6 +7910,11 @@
           <t>philosophe et humaniste italien qui remit en question les traditions médiévales.</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="147.75" customHeight="1" s="25">
       <c r="A111" s="30" t="n">
@@ -7403,6 +7975,11 @@
           <t>philosophe nominaliste allemand considéré comme l’un des derniers grands scolastiques médiévaux.</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="147" customHeight="1" s="25">
       <c r="A112" s="30" t="n">
@@ -7465,6 +8042,11 @@
           <t>philosophe italien qui joua un rôle clé dans la diffusion du néoplatonisme en Europe.</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="159" customHeight="1" s="25">
       <c r="A113" s="30" t="n">
@@ -7526,6 +8108,11 @@
           <t>philosophe français qui incarne la réforme évangélique par l'intérieur de l'Église.</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="149.25" customHeight="1" s="25">
       <c r="A114" s="30" t="n">
@@ -7589,6 +8176,11 @@
           <t>philosophe italien connu pour ses réflexions audacieuses sur l'âme humaine.</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="177" customHeight="1" s="25">
       <c r="A115" s="30" t="n">
@@ -7648,6 +8240,11 @@
       <c r="M115" s="24" t="inlineStr">
         <is>
           <t>philosophe écossais qui plaida pour l'union de l'Écosse et de l'Angleterre.</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
         </is>
       </c>
     </row>

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2364,6 +2364,11 @@
           <t>abbesse et intellectuelle française connue pour sa relation avec Pierre Abélard.</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">occident</t>
@@ -2491,6 +2496,11 @@
       <c r="M29" s="24" t="inlineStr">
         <is>
           <t>abbesse, mystique et visionnaire du Moyen Âge.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -7236,6 +7246,11 @@
       <c r="M100" s="24" t="inlineStr">
         <is>
           <t>philosophe et poétesse française considérée comme la première femme de lettres.</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -5778,7 +5778,7 @@
       </c>
       <c r="L78" s="24" t="inlineStr">
         <is>
-          <t>Herméneutique juive</t>
+          <t xml:space="preserve">Herméneutique juive ; Philosophie juive médiévale</t>
         </is>
       </c>
       <c r="M78" s="24" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -8263,7 +8263,64 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="76.5" customHeight="1" s="25"/>
+    <row r="116" ht="76.5" customHeight="1" s="25">
+      <c r="A116" s="30">
+        <v>1060</v>
+      </c>
+      <c r="B116" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1130</t>
+        </is>
+      </c>
+      <c r="C116" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">XIe – XIIe siècle</t>
+        </is>
+      </c>
+      <c r="D116" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ioane PETRITSI</t>
+        </is>
+      </c>
+      <c r="E116" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ioane_Petritsi" title=" Wikipedia (en)"&gt;Ioane PETRITSI&lt;/a&gt; est le plus important philosophe géorgien du Moyen Âge. Né dans une famille aristocratique de la province de Samtskhé, dans le sud de la Géorgie, il étudie à Constantinople auprès des plus grands maîtres byzantins de son temps, Michel Psellos et Jean Italos, qui renouvellent l’étude de Platon et des néoplatoniciens. Après la condamnation de Jean Italos pour hérésie, il se réfugie, semble-t-il, au monastère géorgien de Petritsoni, en Bulgarie, dont il tire son surnom.&lt;/p&gt; &lt;p&gt;Traducteur infatigable, il fait passer en géorgien des œuvres d’Aristote, de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title=" Wikipedia"&gt;Proclus&lt;/a&gt;, de Némésius et d’Ammonius, ainsi que des textes bibliques et des vies de saints. Il veut montrer que la philosophie grecque et la foi chrétienne peuvent s’accorder. Son œuvre maîtresse est sa traduction des &lt;em&gt;Éléments de théologie&lt;/em&gt; de Proclus, accompagnée d’un long commentaire : l’Un, principe premier au-delà de tout ce qui existe, y est rapproché du Dieu chrétien, et la procession des êtres à partir de l’Un est relue à la lumière de la Création.&lt;/p&gt; &lt;p&gt;Ses idées le mettent en conflit avec les gardiens de l’orthodoxie géorgienne, jusqu’à ce que le roi David IV le Bâtisseur l’installe à l’académie de Gelati, grand centre d’enseignement fondé par le souverain. Il compose aussi des hymnes et de la poésie mystique. Son influence sur la pensée et la langue philosophique géorgiennes a été durable, et elle connaît un renouveau au XVIIIe siècle. Il est aujourd’hui considéré comme le philosophe géorgien le plus lu.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H116" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/petritsi-mini.webp</t>
+        </is>
+      </c>
+      <c r="J116" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Géorgienne</t>
+        </is>
+      </c>
+      <c r="K116" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L116" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme</t>
+        </is>
+      </c>
+      <c r="M116" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe néoplatonicien géorgien, traducteur et commentateur de Proclus.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P116">
+        <v>2</v>
+      </c>
+    </row>
     <row r="117" ht="99.75" customHeight="1" s="25"/>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="L66" s="24" t="inlineStr">
         <is>
-          <t>Mysticisme ; Néoplatonisme</t>
+          <t xml:space="preserve">Mysticisme ; Néoplatonisme ; Mystique rhénane</t>
         </is>
       </c>
       <c r="M66" s="24" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="L83" s="24" t="inlineStr">
         <is>
-          <t>Mysticisme</t>
+          <t xml:space="preserve">Mysticisme ; Mystique rhénane</t>
         </is>
       </c>
       <c r="M83" s="24" t="inlineStr">
@@ -8321,7 +8321,118 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" ht="99.75" customHeight="1" s="25"/>
+    <row r="117" ht="99.75" customHeight="1" s="25">
+      <c r="A117" s="30">
+        <v>1295</v>
+      </c>
+      <c r="B117" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1366</t>
+        </is>
+      </c>
+      <c r="C117" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1295 – 1366</t>
+        </is>
+      </c>
+      <c r="D117" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Henri SUSO</t>
+        </is>
+      </c>
+      <c r="E117" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Suso" title=" Wikipedia"&gt;Henri SUSO&lt;/a&gt; (Heinrich Seuse en allemand) est un religieux dominicain allemand, l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Mystique_rh%C3%A9nane" title=" Wikipedia"&gt;mystique rhénane&lt;/a&gt;. Né vers 1295 au bord du lac de Constance, il entre à treize ans au couvent des dominicains de Constance. Vers dix-huit ans, une expérience intérieure le convertit : il se livre alors pendant des années à des pénitences extrêmes, avant de comprendre qu’il doit renoncer à ces mortifications extérieures pour une ascèse tout intérieure.&lt;/p&gt; &lt;p&gt;Envoyé étudier à Cologne en 1323, il y suit l’enseignement de &lt;a href="https://fr.wikipedia.org/wiki/Ma%C3%AEtre_Eckhart" title=" Wikipedia"&gt;Maître Eckhart&lt;/a&gt;, dont il devient l’un des disciples les plus fidèles. Après la condamnation de son maître, il écrit pour le défendre le &lt;em&gt;Petit Livre de la vérité&lt;/em&gt;, ce qui lui vaut des ennuis avec son ordre. Mais là où Eckhart pense en métaphysicien, Suso parle en poète et en amoureux. Dans le &lt;em&gt;Petit Livre de la Sagesse éternelle&lt;/em&gt;, sous forme de dialogue, il célèbre la Sagesse divine, qu’il aime comme un chevalier aime sa dame. Sa version latine, l’&lt;em&gt;Horloge de la Sagesse&lt;/em&gt;, devient l’un des livres de dévotion les plus lus de la fin du Moyen Âge. Le détachement eckhartien devient chez lui un chemin de l’âme qui passe par la souffrance acceptée, l’imitation du Christ et la tendresse.&lt;/p&gt; &lt;p&gt;Prédicateur et directeur spirituel de nombreuses religieuses, il raconte sa vie à l’une d’elles, Elsbeth Stagel, qui la met par écrit : c’est l’une des premières autobiographies spirituelles en langue allemande, illustrée de dessins symboliques. Il meurt à Ulm en 1366. Il a été proclamé bienheureux en 1831.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H117" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/suso-mini.webp</t>
+        </is>
+      </c>
+      <c r="J117" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allemande</t>
+        </is>
+      </c>
+      <c r="K117" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; esthetique</t>
+        </is>
+      </c>
+      <c r="L117" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mystique rhénane ; Mysticisme</t>
+        </is>
+      </c>
+      <c r="M117" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dominicain allemand, disciple de Maître Eckhart et poète de la Sagesse éternelle.</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P117"/>
+    </row>
+    <row r="118" ht="99.75" customHeight="1" s="25">
+      <c r="A118" s="30">
+        <v>1293</v>
+      </c>
+      <c r="B118" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1381</t>
+        </is>
+      </c>
+      <c r="C118" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1293 – 1381</t>
+        </is>
+      </c>
+      <c r="D118" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jan van RUUSBROEC</t>
+        </is>
+      </c>
+      <c r="E118" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Van_Ruysbroeck_%28religieux%29" title=" Wikipedia"&gt;Jan van RUUSBROEC&lt;/a&gt; (ou Ruysbroeck, dit « l’Admirable ») est un prêtre et mystique brabançon, le grand maître de la mystique flamande, branche de la &lt;a href="https://fr.wikipedia.org/wiki/Mystique_rh%C3%A9nane" title=" Wikipedia"&gt;mystique rhénane&lt;/a&gt;. Né en 1293 près de Bruxelles, il étudie auprès d’un oncle chanoine, devient prêtre et chapelain de la collégiale Sainte-Gudule, où il reste jusqu’à cinquante ans. Il écrit en moyen néerlandais, la langue du peuple, et non en latin.&lt;/p&gt; &lt;p&gt;En 1343, il se retire avec quelques compagnons dans la forêt de Soignes, à Groenendael, la « vallée verte », où il fonde une communauté qui adopte la règle des chanoines de saint Augustin. Son chef-d’œuvre, &lt;em&gt;Les Noces spirituelles&lt;/em&gt;, décrit l’ascension de l’âme vers Dieu en trois étapes : la vie active, faite de vertus et de charité ; la vie intérieure, où l’âme se recueille et désire Dieu ; enfin la vie contemplative, où elle s’unit à Dieu sans se confondre avec lui. Car, à la différence de certains mystiques de son temps, Ruusbroec maintient toujours la distinction entre la créature et le Créateur, et ne sépare jamais la contemplation des sacrements de l’Église ni de l’amour du prochain. Il s’oppose vivement aux « Frères du libre esprit », qui prétendaient qu’une âme unie à Dieu n’était plus tenue par aucune loi morale.&lt;/p&gt; &lt;p&gt;Sa renommée dépasse vite le Brabant. Gérard Groote, le fondateur de la &lt;a href="https://fr.wikipedia.org/wiki/Devotio_moderna" title=" Wikipedia"&gt;Devotio moderna&lt;/a&gt;, lui rend visite, et ce mouvement, d’où sortira l’&lt;em&gt;Imitation de Jésus-Christ&lt;/em&gt;, prolonge son esprit. Il meurt à Groenendael en 1381, presque nonagénaire. Maurice Maeterlinck a traduit et fait connaître son œuvre en France. Il a été proclamé bienheureux en 1908.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H118" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/ruusbroec-mini.webp</t>
+        </is>
+      </c>
+      <c r="J118" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Belge</t>
+        </is>
+      </c>
+      <c r="K118" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L118" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mystique rhénane ; Mysticisme</t>
+        </is>
+      </c>
+      <c r="M118" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mystique brabançon, auteur des Noces spirituelles, le grand maître de la mystique flamande.</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P118"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="G4" s="33" t="inlineStr">
         <is>
-          <t>"Parution des œuvres intégrales du Pseudo-Denys l'Aréopagite" par la caverne du pélerin</t>
+          <t xml:space="preserve">"Parution des œuvres intégrales du Pseudo-Denys l'Aréopagite" par La caverne du pèlerin</t>
         </is>
       </c>
       <c r="H4" s="33" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>"St Pierre DAMIEN" par radio Salve Regina</t>
+          <t xml:space="preserve">"St Pierre DAMIEN" par Radio Salve Regina</t>
         </is>
       </c>
       <c r="H17" s="33" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G33" s="33" t="inlineStr">
         <is>
-          <t>Pierre le Chantre par filosofia Tierra</t>
+          <t xml:space="preserve">Pierre le Chantre par Filosofia Tierra</t>
         </is>
       </c>
       <c r="H33" s="32" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="G34" s="33" t="inlineStr">
         <is>
-          <t>la querelle des universaux ‘ par Philosophie analytique</t>
+          <t xml:space="preserve">la querelle des universaux ‘ par Philosophie Analytique</t>
         </is>
       </c>
       <c r="H34" s="33" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G35" s="33" t="inlineStr">
         <is>
-          <t>"Peter of Capua" par WikiAudio</t>
+          <t xml:space="preserve">"Peter of Capua" par Wikiaudio</t>
         </is>
       </c>
       <c r="H35" s="33" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="G43" s="33" t="inlineStr">
         <is>
-          <t>l’europe m édiévale’ par voyage endormis</t>
+          <t xml:space="preserve">l’europe m édiévale’ par Voyages Endormis</t>
         </is>
       </c>
       <c r="H43" s="33" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G74" s="33" t="inlineStr">
         <is>
-          <t>la querelle des universaux par philosophie analytique</t>
+          <t xml:space="preserve">la querelle des universaux par Philosophie Analytique</t>
         </is>
       </c>
       <c r="H74" s="33" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2185,7 +2185,7 @@
       <c r="E25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Ab%C3%A9lard"   title=" Wikipedia"&gt; Pierre ABÉLARD&lt;/a&gt; était un philosophe, théologien français considéré comme l'un des penseurs les plus importants de son époque et a joué un rôle crucial dans le développement de la pensée médiévale. &lt;/p&gt; &lt;p&gt;
-Il est connu pour sa quête de la vérité et son approche critique de la pensée traditionnelle. Il était particulièrement intéressé par la logique et la philosophie du langage, et il a fait d'importantes contributions à ces domaines. Il était un enseignant influent et charismatique, qui a attiré de nombreux étudiants avides de connaissances car ses méthodes d'enseignement étaient novatrices pour l'époque, mettant l'accent sur le raisonnement logique et l'analyse rationnelle plutôt que sur une simple acceptation des autorités traditionnelles. &lt;/p&gt; &lt;p&gt; Il était un  &lt;a href="https://youtu.be/chy00QiFJF0"  title="qu'est ce qu'un concept? par La Sociothèque"&gt;conceptialiste&lt;/a&gt;  convaincu et soutenait que les universaux, c'est-à-dire les concepts généraux tels que l'humanité ou la bonté, ne sont que des mots et n'ont pas d'existence réelle. Selon lui, seules les choses individuelles et concrètes ont une existence réelle. Cette position allait à l'encontre de la pensée traditionnelle de l'époque, qui soutenait le réalisme, c'est-à-dire la croyance en l'existence réelle des universaux. &lt;/p&gt; &lt;p&gt;  Il est aussi connu pour sa liaison tumultueuse avec  &lt;a href="https://www.youtube.com/watch?v=tLTjrrLxg_Q&amp;ab_channel=Jean-LucDubart"  title="Héloîse et Abélard par Jean Luc Dubart "&gt;Héloïse&lt;/a&gt; , une jeune femme brillante et érudite qui était sa disciple. Leur relation a provoqué un scandale à l'époque, car elle était considérée comme contraire aux normes sociales et religieuses de l'époque. Ils ont fini par se marier secrètement, mais ont été séparés de force par la famille d'Héloïse. Leur correspondance ultérieure, dans laquelle ils expriment leurs sentiments et leurs réflexions philosophiques, est devenue célèbre et est toujours étudiée aujourd'hui. &lt;/p&gt;
+Il est connu pour sa quête de la vérité et son approche critique de la pensée traditionnelle. Il était particulièrement intéressé par la logique et la philosophie du langage, et il a fait d'importantes contributions à ces domaines. Il était un enseignant influent et charismatique, qui a attiré de nombreux étudiants avides de connaissances car ses méthodes d'enseignement étaient novatrices pour l'époque, mettant l'accent sur le raisonnement logique et l'analyse rationnelle plutôt que sur une simple acceptation des autorités traditionnelles. &lt;/p&gt; &lt;p&gt; Il était un  &lt;a href="https://youtu.be/chy00QiFJF0"  title="qu'est ce qu'un concept? par La Sociothèque"&gt;conceptialiste&lt;/a&gt;  convaincu et soutenait que les universaux, c'est-à-dire les concepts généraux tels que l'humanité ou la bonté, ne sont que des mots et n'ont pas d'existence réelle. Selon lui, seules les choses individuelles et concrètes ont une existence réelle. Cette position allait à l'encontre de la pensée traditionnelle de l'époque, qui soutenait le réalisme, c'est-à-dire la croyance en l'existence réelle des universaux. &lt;/p&gt; &lt;p&gt;  Il est aussi connu pour sa liaison tumultueuse avec  &lt;a href="https://www.youtube.com/watch?v=tLTjrrLxg_Q&amp;ab_channel=Jean-LucDubart"  title="Héloîse et Abélard par Jean Luc Dubart "&gt;Héloïse&lt;/a&gt;, une jeune femme brillante et érudite qui était sa disciple. Leur relation a provoqué un scandale à l'époque, car elle était considérée comme contraire aux normes sociales et religieuses de l'époque. Ils ont fini par se marier secrètement, mais ont été séparés de force par la famille d'Héloïse. Leur correspondance ultérieure, dans laquelle ils expriment leurs sentiments et leurs réflexions philosophiques, est devenue célèbre et est toujours étudiée aujourd'hui. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -2254,9 +2254,9 @@
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_de_Clairvaux"  style=  title=" Wikipedia"&gt;BERNARD de Clairvaux&lt;/a&gt; est une figure marquante du XIIe siècle, tant sur le plan religieux que politique. Moine cistercien, mystique, réformateur, théologien et conseiller influent, il a joué un rôle central dans l'Église catholique et dans la société médiévale. &lt;/p&gt; &lt;p&gt; Il est un ardent et très influent défenseur de la réforme Grégorienne de l'Église et il s'oppose fermement à la corruption et à l'accumulation de richesses par le clergé. Il critique également les excès de la scolastique naissante, privilégiant une approche plus mystique et contemplative de la foi. &lt;/p&gt; &lt;p&gt; Il est l'auteur de nombreux traités théologiques et spirituels, dont les plus célèbres sont : &lt;/p&gt;
 &lt;dd&gt;"De l'amour de Dieu" (De diligendo Deo), où il explore la nature de l'amour divin et son rôle dans la vie spirituelle. &lt;/dd&gt;
-&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=uo94zAU5RnU"  title="Sermons sur le Cantique par Sanctus"&gt;"Sermons sur le Cantique des Cantiques" &lt;/a&gt;, une œuvre mystique qui interprète ce livre biblique comme une allégorie de l'union de l'âme avec Dieu.&lt;/dd&gt;
+&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=uo94zAU5RnU"  title="Sermons sur le Cantique par Sanctus"&gt;"Sermons sur le Cantique des Cantiques"&lt;/a&gt;, une œuvre mystique qui interprète ce livre biblique comme une allégorie de l'union de l'âme avec Dieu.&lt;/dd&gt;
 &lt;dd&gt;"De la grâce et du libre arbitre", où il aborde les questions de la prédestination et de la liberté humaine.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt;
-&lt;p&gt; Il fut co-fondateur de l'ordre des Templiers et le premier investigateur du le lancement de la &lt;a href="https://www.youtube.com/watch?v=jvRDaQ81vZc" title="Bernard de Clairvaux , la 2ème croisade par Coursitou "&gt;deuxième croissade . &lt;/a&gt; &lt;/p&gt;  &lt;p&gt; Canonisé en 1174, il est déclaré docteur de l'Église en 1830. Il a contribué à l'expansion de l'ordre cistercien et ses écrits ont profondément marqué la spiritualité chrétienne, inspirant des figures comme saint François d'Assise et saint Thomas d'Aquin.  Il est considéré comme l'un des grands mystiques du christianisme, ayant approfondi la compréhension de l'amour divin et de la relation entre l'homme et Dieu. &lt;/p&gt;    &lt;audio controls title="Saint Bertrand de Clairvaux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22636-10.04.2022-ITEMA_22990601-2022B45498S0100-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+&lt;p&gt; Il fut co-fondateur de l'ordre des Templiers et le premier investigateur du le lancement de la &lt;a href="https://www.youtube.com/watch?v=jvRDaQ81vZc" title="Bernard de Clairvaux , la 2ème croisade par Coursitou "&gt;deuxième croissade. &lt;/a&gt; &lt;/p&gt;  &lt;p&gt; Canonisé en 1174, il est déclaré docteur de l'Église en 1830. Il a contribué à l'expansion de l'ordre cistercien et ses écrits ont profondément marqué la spiritualité chrétienne, inspirant des figures comme saint François d'Assise et saint Thomas d'Aquin.  Il est considéré comme l'un des grands mystiques du christianisme, ayant approfondi la compréhension de l'amour divin et de la relation entre l'homme et Dieu. &lt;/p&gt;    &lt;audio controls title="Saint Bertrand de Clairvaux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22636-10.04.2022-ITEMA_22990601-2022B45498S0100-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugues_de_Saint-Victor"  style=  title=" Wikipedia"&gt;HUGUES de Saint Victor&lt;/a&gt; était à la fois philosophe, théologien et pédagogue, souvent présenté comme une figure majeure de l’école   &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1960_num_34_1_2248" title="les origines de huges de st victor par persée  "&gt;de Saint-Victor à Paris &lt;/a&gt; . Sa philosophie cherche à organiser tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance n’est pas une fin en soi : elle prépare l’âme à une vie spirituelle plus haute. C’est pourquoi il accorde une grande importance aux arts libéraux, à la lecture, à l’étude méthodique et à l’éducation intellectuelle, dans &lt;a href="https://www.youtube.com/watch?v=A65kiTkbMNU" title="hugh of st victor’s Didascalicon par Cut the Fluff "&gt;son Didascalicon. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Un point central de sa pensée est l’union entre raison et foi. Il ne méprise pas la raison, mais il estime qu’elle a ses limites et qu’elle doit servir à comprendre ce que la foi révèle. Il se méfie d’une dialectique trop querelleuse et préfère une démarche plus ordonnée, plus humble et plus tournée vers l’édification intérieure. &lt;/p&gt; &lt;p&gt; Sa philosophie est aussi profondément spirituelle et mystique. Il décrit l’ascension de l’âme vers Dieu à travers un mouvement en plusieurs étapes, souvent résumé par la progression de la pensée, de la méditation et de la contemplation. Chez lui, la contemplation n’est pas une fuite du monde, mais l’aboutissement d’un travail patient sur soi, sur le savoir et sur la prière. &lt;/p&gt; &lt;p&gt; Il a marqué durablement la pensée médiévale parce qu’il veut tout relier : savoirs, morale, vie intérieure et histoire du salut. On peut dire qu’il incarne une philosophie de l’ordre, de l’apprentissage total et de la montée graduelle vers la vérité, ce qui lui a valu une grande influence au Moyen Âge. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugues_de_Saint-Victor"  style=  title=" Wikipedia"&gt;HUGUES de Saint Victor&lt;/a&gt; était à la fois philosophe, théologien et pédagogue, souvent présenté comme une figure majeure de l’école   &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1960_num_34_1_2248" title="les origines de huges de st victor par persée  "&gt;de Saint-Victor à Paris&lt;/a&gt;. Sa philosophie cherche à organiser tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance n’est pas une fin en soi : elle prépare l’âme à une vie spirituelle plus haute. C’est pourquoi il accorde une grande importance aux arts libéraux, à la lecture, à l’étude méthodique et à l’éducation intellectuelle, dans &lt;a href="https://www.youtube.com/watch?v=A65kiTkbMNU" title="hugh of st victor’s Didascalicon par Cut the Fluff "&gt;son Didascalicon. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Un point central de sa pensée est l’union entre raison et foi. Il ne méprise pas la raison, mais il estime qu’elle a ses limites et qu’elle doit servir à comprendre ce que la foi révèle. Il se méfie d’une dialectique trop querelleuse et préfère une démarche plus ordonnée, plus humble et plus tournée vers l’édification intérieure. &lt;/p&gt; &lt;p&gt; Sa philosophie est aussi profondément spirituelle et mystique. Il décrit l’ascension de l’âme vers Dieu à travers un mouvement en plusieurs étapes, souvent résumé par la progression de la pensée, de la méditation et de la contemplation. Chez lui, la contemplation n’est pas une fuite du monde, mais l’aboutissement d’un travail patient sur soi, sur le savoir et sur la prière. &lt;/p&gt; &lt;p&gt; Il a marqué durablement la pensée médiévale parce qu’il veut tout relier : savoirs, morale, vie intérieure et histoire du salut. On peut dire qu’il incarne une philosophie de l’ordre, de l’apprentissage total et de la montée graduelle vers la vérité, ce qui lui a valu une grande influence au Moyen Âge. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hildegarde_de_Bingen"  style=  title=" Wikipedia"&gt;HILDEGARDE de Bingen&lt;/a&gt; était une grande figure du Moyen Âge,originaire du Saint Empire germanique et à la fois mystique, abbesse, musicienne, médecin et penseuse.  &lt;a href="https://www.youtube.com/watch?v=-kf9N7UKzvA" title="hildegarde de bingen une vie une œuvre par Eclair Brut  "&gt;Sa philosophie &lt;/a&gt;  ne se présente pas comme un système abstrait, mais comme une vision du monde unifiée, où Dieu, la nature, le corps et l’âme forment un tout cohérent. &lt;/p&gt; &lt;p&gt; Pour elle, l’univers est vivant et ordonné par une harmonie profonde. L’être humain y occupe une place centrale, comme un microcosme qui reflète le macrocosme : ce qui se passe dans l’âme répond aux mouvements du monde, et inversement. &lt;/p&gt; &lt;p&gt; Un concept essentiel chez elle est la viriditas, souvent traduite par « verdeur » ou « force de vie ». Cette idée désigne l’énergie vitale, la fécondité, la santé spirituelle et corporelle, ainsi que la capacité de croître dans le bien et dans la foi. La nature n’est donc pas seulement un décor, mais un signe de la présence divine. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=AoQE_GQGZK4" title="hildegarde de bingen guérisseuse par France Culture "&gt;Sa pensée insiste &lt;/a&gt;  aussi sur l’unité entre le corps et l’âme. Elle ne les oppose pas radicalement : elle considère qu’une vie juste suppose un équilibre entre la dimension spirituelle, les émotions, la santé physique et la relation à Dieu. C’est ce qui explique son intérêt pour la médecine, les plantes, les remèdes et les rythmes de vie. &lt;/p&gt; &lt;p&gt; Sa philosophie a une forte dimension morale et spirituelle. elle invite à la conversion, à la simplicité, à l’écoute intérieure et à la responsabilité envers la création. Elle voit le monde comme une symphonie où chaque être a sa place, et où l’être humain est appelé à retrouver l’harmonie perdue. &lt;/p&gt;  &lt;audio controls title="Hildegarde de Bingen, l’insoumise par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-22.12.2013-ITEMA_20564951-2013C14958E0046-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hildegarde_de_Bingen"  style=  title=" Wikipedia"&gt;HILDEGARDE de Bingen&lt;/a&gt; était une grande figure du Moyen Âge,originaire du Saint Empire germanique et à la fois mystique, abbesse, musicienne, médecin et penseuse.  &lt;a href="https://www.youtube.com/watch?v=-kf9N7UKzvA" title="hildegarde de bingen une vie une œuvre par Eclair Brut  "&gt;Sa philosophie &lt;/a&gt;  ne se présente pas comme un système abstrait, mais comme une vision du monde unifiée, où Dieu, la nature, le corps et l’âme forment un tout cohérent. &lt;/p&gt; &lt;p&gt; Pour elle, l’univers est vivant et ordonné par une harmonie profonde. L’être humain y occupe une place centrale, comme un microcosme qui reflète le macrocosme : ce qui se passe dans l’âme répond aux mouvements du monde, et inversement. &lt;/p&gt; &lt;p&gt; Un concept essentiel chez elle est la viriditas, souvent traduite par « verdeur » ou « force de vie ». Cette idée désigne l’énergie vitale, la fécondité, la santé spirituelle et corporelle, ainsi que la capacité de croître dans le bien et dans la foi. La nature n’est donc pas seulement un décor, mais un signe de la présence divine. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=AoQE_GQGZK4" title="hildegarde de bingen guérisseuse par France Culture "&gt;Sa pensée insiste &lt;/a&gt;  aussi sur l’unité entre le corps et l’âme. Elle ne les oppose pas radicalement : elle considère qu’une vie juste suppose un équilibre entre la dimension spirituelle, les émotions, la santé physique et la relation à Dieu. C’est ce qui explique son intérêt pour la médecine, les plantes, les remèdes et les rythmes de vie. &lt;/p&gt; &lt;p&gt; Sa philosophie a une forte dimension morale et spirituelle. Elle invite à la conversion, à la simplicité, à l’écoute intérieure et à la responsabilité envers la création. Elle voit le monde comme une symphonie où chaque être a sa place, et où l’être humain est appelé à retrouver l’harmonie perdue. &lt;/p&gt;  &lt;audio controls title="Hildegarde de Bingen, l’insoumise par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-22.12.2013-ITEMA_20564951-2013C14958E0046-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F29" s="30" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E31" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Salisbury"   title=" Wikipedia"&gt;JEAN de Salisbery&lt;/a&gt; était un philosophe, écrivain et  diplomate  anglais au service de l'Église, secrétaire de l'archevêque de Cantorbéry puis évêque de Chartres. &lt;/p&gt; &lt;p&gt; Il  était un adepte de la &lt;a href="https://www.youtube.com/watch?v=MnQ1n5vmlEA"  title="La pensée de Cicéron par Le Prisme Humain"&gt; perspective cicéronienne&lt;/a&gt;, croyant que les choses pouvaient être prouvées de manière définitive tout en restant ouvertes à la remise en question. Il défendait un scepticisme modéré, où la connaissance peut être basée sur certaines certitudes. Il souligna l'importance des études historiques en philosophie et dans toutes les autres branches du savoir, et fut parmi les premiers à formuler clairement la solution du "réalisme modéré" face au problème philosophique des idées universelles. &lt;/p&gt; &lt;p&gt; Il publia vers 1159  &lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1994_num_72_4_7422_t1_0966_0000_5" style="color:#88A1E9" title=" Jean de Salisbury (Ioannis Saresberiensis). Metalogicon  par Persée"&gt;  "Metalogicon"&lt;/a&gt;, un traité exhaustif sur la logique et l'épistémologie où il défend l'étude de la logique et des arts libéraux comme essentiels pour comprendre le monde et acquérir des connaissances. Il est considéré comme une défense importante du trivium (grammaire, rhétorique et logique). Il publia ensuite &lt;a href="https://fr.wikipedia.org/wiki/Policraticus"  title="Policraticus par Wikipedia"&gt;"Policraticus, sive de nugis curialium et de vestigiis philosophorum"&lt;/a&gt; , une œuvre majeure de la théorie politique médiévale où il développe une vision nuancée de la société idéale, arguant que l'État doit être guidé par la raison, la justice et la vertu. Il y aborde des concepts tels que le "corps politique" (où le souverain est la tête et les sujets le corps) et la relation entre l'Église et l'État, soulignant la suprématie de l'Église sur le pouvoir royal. &lt;/p&gt; &lt;p&gt; Il  est considéré comme l'un des intellectuels les plus cultivés de son temps et un écrivain latin d'une grande élégance où le "Le Policraticus" a été une œuvre politique très influente tout au long du Moyen Âge, souvent citée et étudiée pour ses idées sur le gouvernement et le droit. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Salisbury"   title=" Wikipedia"&gt;JEAN de Salisbery&lt;/a&gt; était un philosophe, écrivain et  diplomate  anglais au service de l'Église, secrétaire de l'archevêque de Cantorbéry puis évêque de Chartres. &lt;/p&gt; &lt;p&gt; Il  était un adepte de la &lt;a href="https://www.youtube.com/watch?v=MnQ1n5vmlEA"  title="La pensée de Cicéron par Le Prisme Humain"&gt; perspective cicéronienne&lt;/a&gt;, croyant que les choses pouvaient être prouvées de manière définitive tout en restant ouvertes à la remise en question. Il défendait un scepticisme modéré, où la connaissance peut être basée sur certaines certitudes. Il souligna l'importance des études historiques en philosophie et dans toutes les autres branches du savoir, et fut parmi les premiers à formuler clairement la solution du "réalisme modéré" face au problème philosophique des idées universelles. &lt;/p&gt; &lt;p&gt; Il publia vers 1159  &lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1994_num_72_4_7422_t1_0966_0000_5" style="color:#88A1E9" title=" Jean de Salisbury (Ioannis Saresberiensis). Metalogicon  par Persée"&gt;  "Metalogicon"&lt;/a&gt;, un traité exhaustif sur la logique et l'épistémologie où il défend l'étude de la logique et des arts libéraux comme essentiels pour comprendre le monde et acquérir des connaissances. Il est considéré comme une défense importante du trivium (grammaire, rhétorique et logique). Il publia ensuite &lt;a href="https://fr.wikipedia.org/wiki/Policraticus"  title="Policraticus par Wikipedia"&gt;"Policraticus, sive de nugis curialium et de vestigiis philosophorum"&lt;/a&gt;, une œuvre majeure de la théorie politique médiévale où il développe une vision nuancée de la société idéale, arguant que l'État doit être guidé par la raison, la justice et la vertu. Il y aborde des concepts tels que le "corps politique" (où le souverain est la tête et les sujets le corps) et la relation entre l'Église et l'État, soulignant la suprématie de l'Église sur le pouvoir royal. &lt;/p&gt; &lt;p&gt; Il  est considéré comme l'un des intellectuels les plus cultivés de son temps et un écrivain latin d'une grande élégance où le "Le Policraticus" a été une œuvre politique très influente tout au long du Moyen Âge, souvent citée et étudiée pour ses idées sur le gouvernement et le droit. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F31" s="30" t="inlineStr">
@@ -3196,7 +3196,7 @@
       <c r="E40" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_le_Grand"   title=" Wikipedia"&gt;ALBERT le Grand&lt;/a&gt; était un érudit, philosophe, théologien, et scientifique dont les travaux ont eu une influence profonde sur la pensée médiévale et moderne. Il est souvent considéré comme le &lt;a href="https://www.youtube.com/watch?v=DvQXZaFwB5k" title=Albert le Grand par Pier Aujourd'hui "&gt;précurseur&lt;/a&gt; de la synthèse entre la philosophie aristotélicienne et la théologie chrétienne, les rendant accessibles au monde chrétien. Ses travaux ont jeté les bases pour la synthèse philosophico-théologique que Thomas d'Aquin développera plus tard. Il était également un scientifique passionné et a écrit des traités sur une variété de sujets, y compris la biologie, la zoologie, la botanique, la minéralogie, et l'alchimie. Ses observations empiriques et ses expériences ont marqué un tournant dans l'approche médiévale des sciences naturelles. &lt;/p&gt; &lt;p&gt; Ses Œuvres Majeures : &lt;/p&gt;
-&lt;p&gt; De Mineralibus (Sur les Minéraux)  ,  De Animalibus (Sur les Animaux)  , &lt;a href="https://www.youtube.com/watch?v=PwYmEVkmqlo&amp;t=27s" style="color:#88A1E9" title=Le silence :Albert le Grand par la caverne du pelerins "&gt;Summa Theologiae&lt;/a&gt; (une synthèse de théologie)  , Commentaires sur Aristote (y compris sur la Physique, la Métaphysique, et l'Éthique à Nicomaque)  ,  Canonisation et Héritage &lt;/p&gt; 
+&lt;p&gt; De Mineralibus (Sur les Minéraux),  De Animalibus (Sur les Animaux), &lt;a href="https://www.youtube.com/watch?v=PwYmEVkmqlo&amp;t=27s" style="color:#88A1E9" title=Le silence :Albert le Grand par la caverne du pelerins "&gt;Summa Theologiae&lt;/a&gt; (une synthèse de théologie), Commentaires sur Aristote (y compris sur la Physique, la Métaphysique, et l'Éthique à Nicomaque),  Canonisation et Héritage &lt;/p&gt; 
 &lt;p&gt; Il  a été canonisé par le pape Pie XI en 1931 et déclaré Docteur de l'Église. Son héritage intellectuel est immense, influençant non seulement la théologie et la philosophie, mais aussi les sciences naturelles. Il est souvent considéré comme un modèle de l'érudition médiévale, capable de synthétiser la foi et la raison. &lt;/p&gt; 
 </t>
         </is>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_d%27Espagne"   title=" Wikipedia"&gt;Pierre D'ESPAGNE&lt;/a&gt;   était un philosophe espagno  également connu sous le nom de Petrus Hispanus, désigne plusieurs figures médiévales du XIIIe siècle, dont certaines sont associées à la philosophie et à la logique à Paris autour de 1215. Le plus notable est l'auteur présumé des "Summulae logicales", un manuel fondamental de logique scolastique. &lt;/p&gt; &lt;p&gt; Il systématise  &lt;a href="https://www.persee.fr/doc/crai_0065-0536_1864_num_8_1_66876"  title="la logique de Pierre d’espagne par Persee"&gt; la logique aristotélicienne &lt;/a&gt;, Porphyre et les premiers scolastiques comme Jean Pagus. Ces textes traitent des propriétés des termes, des propositions et des syllogismes, influençant l'enseignement jusqu'à la Renaissance et servant de base aux débats anti-averroïstes. &lt;/p&gt; &lt;p&gt; Actif durant l'introduction clandestine d'Aristote malgré les interdits de 1210-1215, il participe à la tension entre raison profane et théologie, appuyant en 1277 la condamnation des averroïstes par Étienne Tempier. Son œuvre, éditée au XXe siècle par L.M. de Rijk, marque la maturation de la scolastique dialectique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_d%27Espagne"   title=" Wikipedia"&gt;Pierre D'ESPAGNE&lt;/a&gt;   était un philosophe espagno  également connu sous le nom de Petrus Hispanus, désigne plusieurs figures médiévales du XIIIe siècle, dont certaines sont associées à la philosophie et à la logique à Paris autour de 1215. Le plus notable est l'auteur présumé des "Summulae logicales", un manuel fondamental de logique scolastique. &lt;/p&gt; &lt;p&gt; Il systématise  &lt;a href="https://www.persee.fr/doc/crai_0065-0536_1864_num_8_1_66876"  title="la logique de Pierre d’espagne par Persee"&gt; la logique aristotélicienne&lt;/a&gt;, Porphyre et les premiers scolastiques comme Jean Pagus. Ces textes traitent des propriétés des termes, des propositions et des syllogismes, influençant l'enseignement jusqu'à la Renaissance et servant de base aux débats anti-averroïstes. &lt;/p&gt; &lt;p&gt; Actif durant l'introduction clandestine d'Aristote malgré les interdits de 1210-1215, il participe à la tension entre raison profane et théologie, appuyant en 1277 la condamnation des averroïstes par Étienne Tempier. Son œuvre, éditée au XXe siècle par L.M. de Rijk, marque la maturation de la scolastique dialectique. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F43" s="30" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="E44" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bonaventure_de_Bagnoregio"  title=" Wikipedia"&gt;BONAVENTURE de Bagnorea&lt;/a&gt; de son vrai nom Giovanni di Fidanza, était un philosophe scolastique, théologien franciscain et cardinal italien. Il est souvent surnommé le "Docteur séraphique", un titre honorifique dans la tradition chrétienne, à cause de la chaleur mystique et affective de sa pensée. Il a été Ministre général de l’Ordre franciscain et a joué un rôle central dans la structuration intellectuelle et spirituelle de cet ordre, notamment en synthétisant la pensée de saint François d’Assise avec les outils intellectuels de son temps. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance commence par les sens, passe par la raison, mais atteint son sommet par &lt;a href="https://www.youtube.com/watch?v=Anl-a-pLAEA"  title="Divines  Illuminations par City of the Immaculata"&gt;l'illumination divine &lt;/a&gt;. Il suit ici une ligne néo-platonicienne et contrairement à Thomas d’Aquin, qui accorde une grande autonomie à la raison naturelle, il insiste sur le fait que toute vraie connaissance vient de Dieu. Il développe une théorie de l’illumination intellectuelle (héritée de saint Augustin) : l’âme humaine ne peut accéder à la vérité sans une lumière intérieure donnée par Dieu. Il voit dans l’esprit humain un reflet de la Trinité : mémoire, intelligence, volonté. &lt;/p&gt; &lt;p&gt; Il développe l'idée que l’univers est une "échelle vers Dieu"dans son œuvre mystique majeure, le  &lt;a href="https://www.clerus.org/bibliaclerusonline/fr/v3.htm"  title="Itinéraire de l'âme par Clerus.org"&gt; "Itinerarium mentis in Deum" &lt;/a&gt; (L’itinéraire de l’âme vers Dieu), où il décrit les étapes de l’ascension spirituelle de l’âme jusqu’à l’union avec Dieu. &lt;/p&gt; &lt;p&gt; Il était  un mystique autant qu’un intellectuel et opposait parfois la science froide des universitaires à la sagesse humble du croyant animé d’amour. Il a fortement influencé la spiritualité franciscaine, mais aussi toute la tradition chrétienne occidentale.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bonaventure_de_Bagnoregio"  title=" Wikipedia"&gt;BONAVENTURE de Bagnorea&lt;/a&gt; de son vrai nom Giovanni di Fidanza, était un philosophe scolastique, théologien franciscain et cardinal italien. Il est souvent surnommé le "Docteur séraphique", un titre honorifique dans la tradition chrétienne, à cause de la chaleur mystique et affective de sa pensée. Il a été Ministre général de l’Ordre franciscain et a joué un rôle central dans la structuration intellectuelle et spirituelle de cet ordre, notamment en synthétisant la pensée de saint François d’Assise avec les outils intellectuels de son temps. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance commence par les sens, passe par la raison, mais atteint son sommet par &lt;a href="https://www.youtube.com/watch?v=Anl-a-pLAEA"  title="Divines  Illuminations par City of the Immaculata"&gt;l'illumination divine&lt;/a&gt;. Il suit ici une ligne néo-platonicienne et contrairement à Thomas d’Aquin, qui accorde une grande autonomie à la raison naturelle, il insiste sur le fait que toute vraie connaissance vient de Dieu. Il développe une théorie de l’illumination intellectuelle (héritée de saint Augustin) : l’âme humaine ne peut accéder à la vérité sans une lumière intérieure donnée par Dieu. Il voit dans l’esprit humain un reflet de la Trinité : mémoire, intelligence, volonté. &lt;/p&gt; &lt;p&gt; Il développe l'idée que l’univers est une "échelle vers Dieu"dans son œuvre mystique majeure, le  &lt;a href="https://www.clerus.org/bibliaclerusonline/fr/v3.htm"  title="Itinéraire de l'âme par Clerus.org"&gt; "Itinerarium mentis in Deum" &lt;/a&gt; (L’itinéraire de l’âme vers Dieu), où il décrit les étapes de l’ascension spirituelle de l’âme jusqu’à l’union avec Dieu. &lt;/p&gt; &lt;p&gt; Il était  un mystique autant qu’un intellectuel et opposait parfois la science froide des universitaires à la sagesse humble du croyant animé d’amour. Il a fortement influencé la spiritualité franciscaine, mais aussi toute la tradition chrétienne occidentale.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F44" s="30" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E80" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Bradwardine"  title=" Wikipedia"&gt;Thomas BRADWARDINE&lt;/a&gt;  était un philosophe anglais surnommé "le Docteur Profond". Archevêque de Canterbury et confesseur du roi Édouard III, il a marqué son époque par ses contributions à la théologie augustinienne et aux sciences naturelles. &lt;/p&gt; &lt;p&gt; Né probablement à Hartfield dans le Sussex, il étudie à Oxford puis au Merton College, où il excelle en  &lt;a href="https://www.youtube.com/watch?v=G05snIT5bRo&amp;t=58s" title="Thomas Bradwardine: The Mathematician-Philosopher Who Bridged Medieval Thought and Early Science  par Math Mystique"&gt;théologie et en mathématiques &lt;/a&gt; . Il devient chancelier de l'université d'Oxford, chanoine de Lincoln, chancelier de la cathédrale Saint-Paul de Londres, et suit Édouard III lors de ses campagnes en France en tant que chapelain. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "De causa Dei contra Pelagium" paru vers 1344, combat le pélagianisme en défendant la toute-puissance divine et la prédestination, tout en intégrant une approche mathématique à la théologie.   &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1960_num_40_2_3617"  title="Thomas Bradwardine, un précurseur de Luther ?  par Persée"&gt;Thomiste rigoureux, &lt;/a&gt;  il insiste sur la concurrence divine avec la volonté humaine, influençant plus tard des réformateurs comme Wycliffe. &lt;/p&gt; &lt;p&gt; Dans "Tractatus de proportionibus velocitatum in motibus" paru en  1328, il développe une théorie des proportions géométriques pour les vitesses, anticipant la croissance exponentielle et critiquant les idées aristotéliciennes sur le mouvement. Associé aux "Calculateurs d'Oxford", il contribue au théorème de la vitesse moyenne et à la cinématique, préfigurant des découvertes comme la loi des corps tombants. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Bradwardine"  title=" Wikipedia"&gt;Thomas BRADWARDINE&lt;/a&gt;  était un philosophe anglais surnommé "le Docteur Profond". Archevêque de Canterbury et confesseur du roi Édouard III, il a marqué son époque par ses contributions à la théologie augustinienne et aux sciences naturelles. &lt;/p&gt; &lt;p&gt; Né probablement à Hartfield dans le Sussex, il étudie à Oxford puis au Merton College, où il excelle en  &lt;a href="https://www.youtube.com/watch?v=G05snIT5bRo&amp;t=58s" title="Thomas Bradwardine: The Mathematician-Philosopher Who Bridged Medieval Thought and Early Science  par Math Mystique"&gt;théologie et en mathématiques&lt;/a&gt;. Il devient chancelier de l'université d'Oxford, chanoine de Lincoln, chancelier de la cathédrale Saint-Paul de Londres, et suit Édouard III lors de ses campagnes en France en tant que chapelain. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "De causa Dei contra Pelagium" paru vers 1344, combat le pélagianisme en défendant la toute-puissance divine et la prédestination, tout en intégrant une approche mathématique à la théologie.   &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1960_num_40_2_3617"  title="Thomas Bradwardine, un précurseur de Luther ?  par Persée"&gt;Thomiste rigoureux, &lt;/a&gt;  il insiste sur la concurrence divine avec la volonté humaine, influençant plus tard des réformateurs comme Wycliffe. &lt;/p&gt; &lt;p&gt; Dans "Tractatus de proportionibus velocitatum in motibus" paru en  1328, il développe une théorie des proportions géométriques pour les vitesses, anticipant la croissance exponentielle et critiquant les idées aristotéliciennes sur le mouvement. Associé aux "Calculateurs d'Oxford", il contribue au théorème de la vitesse moyenne et à la cinématique, préfigurant des découvertes comme la loi des corps tombants. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="E82" s="41" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Swineshead"  title=" Wikipedia"&gt;Richard SWINESHEAD&lt;/a&gt; , aussi orthographié Swyneshed ou Suiseth, était un philosophe naturel, logicien et mathématicien anglais, membre du Merton College d’Oxford et figure centrale des « Calculateurs d’Oxford ». Surnommé « le Calculateur », il est surtout connu pour son Liber calculationum (« Livre des calculs », vers 1350), œuvre majeure de physique quantitative médiévale qui lui valut une renommée européenne durable. &lt;/p&gt; &lt;p&gt; Il appartient au groupe des Oxford Calculators (ou « école de Merton »), un cercle de penseurs – avec Thomas Bradwardine, William Heytesbury, John Dumbleton – qui, dans la première moitié du XIVe siècle, appliquent des techniques logiques et mathématiques à des problèmes de physique aristotélicienne. Leur projet n’est pas de faire des mathématiques pures, mais de quantifier des grandeurs physiques (mouvement, vitesse, force, chaleur, lumière, densité, etc.) et de résoudre des sophismes portant sur ces grandeurs. Dans ce cadre, il apparaît souvent comme le dernier et le plus abouti des calculateurs, poussant à l’extrême la méthode de « calcul » des variations qualitatives et quantitatives. &lt;/p&gt; &lt;p&gt; Le Liber calculationum est une série de traités rédigés vers 1340–1350, organisés en chapitres thématiques traitant du mouvement local, des proportions, des qualités intenses et remises, de la raréfaction et condensation, de la lumière, des puissances naturelles, etc. L’ouvrage ne se présente pas comme un traité de métaphysique ou de physique fondamentale, mais comme un manuel de techniques logico-mathématiques permettant de calculer les valeurs et les changements de variables physiques, ou de résoudre des sophismes sur ces changements. Swineshead y développe, entre autres, plus de cinquante variations de la loi dynamique de Bradwardine (qui relie force, résistance et vitesse), montrant une maîtrise exceptionnelle des proportions et des raisonnements infinitésimaux rudimentaires. &lt;/p&gt; &lt;p&gt; Sur le plan philosophique et scientifique, il contribue à déplacer la physique médiévale d’une approche purement qualitative vers une physique de plus en plus quantitative, préparant ainsi, à très long terme, des développements qui mèneront à la cinématique moderne et, indirectement, au calcul infinitésimal. Il est admiré par des auteurs de la Renaissance et de l’époque moderne (Cardan le classe parmi les plus grands savants ; Leibniz le mentionne avec estime) et reste, jusqu’au XVIe siècle, une autorité majeure en physique quantitative dans les universités italiennes et européennes. Historiquement, on le situe donc à la croisée de la logique médiévale, de la philosophie naturelle aristotélicienne et des premières formes de mathématisation de la physique. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_Swineshead"  title=" Wikipedia"&gt;Richard SWINESHEAD&lt;/a&gt;, aussi orthographié Swyneshed ou Suiseth, était un philosophe naturel, logicien et mathématicien anglais, membre du Merton College d’Oxford et figure centrale des « Calculateurs d’Oxford ». Surnommé « le Calculateur », il est surtout connu pour son Liber calculationum (« Livre des calculs », vers 1350), œuvre majeure de physique quantitative médiévale qui lui valut une renommée européenne durable. &lt;/p&gt; &lt;p&gt; Il appartient au groupe des Oxford Calculators (ou « école de Merton »), un cercle de penseurs – avec Thomas Bradwardine, William Heytesbury, John Dumbleton – qui, dans la première moitié du XIVe siècle, appliquent des techniques logiques et mathématiques à des problèmes de physique aristotélicienne. Leur projet n’est pas de faire des mathématiques pures, mais de quantifier des grandeurs physiques (mouvement, vitesse, force, chaleur, lumière, densité, etc.) et de résoudre des sophismes portant sur ces grandeurs. Dans ce cadre, il apparaît souvent comme le dernier et le plus abouti des calculateurs, poussant à l’extrême la méthode de « calcul » des variations qualitatives et quantitatives. &lt;/p&gt; &lt;p&gt; Le Liber calculationum est une série de traités rédigés vers 1340–1350, organisés en chapitres thématiques traitant du mouvement local, des proportions, des qualités intenses et remises, de la raréfaction et condensation, de la lumière, des puissances naturelles, etc. L’ouvrage ne se présente pas comme un traité de métaphysique ou de physique fondamentale, mais comme un manuel de techniques logico-mathématiques permettant de calculer les valeurs et les changements de variables physiques, ou de résoudre des sophismes sur ces changements. Swineshead y développe, entre autres, plus de cinquante variations de la loi dynamique de Bradwardine (qui relie force, résistance et vitesse), montrant une maîtrise exceptionnelle des proportions et des raisonnements infinitésimaux rudimentaires. &lt;/p&gt; &lt;p&gt; Sur le plan philosophique et scientifique, il contribue à déplacer la physique médiévale d’une approche purement qualitative vers une physique de plus en plus quantitative, préparant ainsi, à très long terme, des développements qui mèneront à la cinématique moderne et, indirectement, au calcul infinitésimal. Il est admiré par des auteurs de la Renaissance et de l’époque moderne (Cardan le classe parmi les plus grands savants ; Leibniz le mentionne avec estime) et reste, jusqu’au XVIe siècle, une autorité majeure en physique quantitative dans les universités italiennes et européennes. Historiquement, on le situe donc à la croisée de la logique médiévale, de la philosophie naturelle aristotélicienne et des premières formes de mathématisation de la physique. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="E85" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_d%27Autr%C3%A9court"   title=" Wikipedia"&gt;Nicolas D'AUTRECOURT&lt;/a&gt; était un philosophe et théologien médiéval souvent considéré comme l'un des précurseurs du &lt;a href="https://www.philomag.com/lexique/scepticisme" title="Le septicisme  par Philomag "&gt;scepticisme moderne&lt;/a&gt;. et de la pensée critique. Bien que moins connu que d'autres figures de la scolastique médiévale, comme Thomas d'Aquin ou Jean Duns Scot, il a joué un rôle important dans l'histoire de la philosophie en remettant en question certaines des certitudes de son époque. &lt;/p&gt; &lt;p&gt;  Il est surtout connu pour son scepticisme radical, qui l'a amené à remettre en question les fondements de la connaissance et de la métaphysique. Il a critiqué les arguments traditionnels de la scolastique, en particulier ceux basés sur la causalité et la substance. Selon lui, il est impossible de connaître avec certitude les causes des phénomènes ou la nature des substances.&lt;/p&gt; &lt;p&gt;  En 1346, il a été condamné par le pape Clément VI pour ses positions philosophiques jugées dangereuses pour la foi chrétienne. Ses écrits ont été brûlés, et il a été contraint de se rétracter publiquement. Après sa condamnation, il a disparu des archives historiques, et on sait peu de choses sur les dernières années de sa vie.&lt;/p&gt; &lt;p&gt; Malgré la destruction de la plupart de ses écrits, quelques lettres et fragments de ses travaux ont survécu. Parmi ceux-ci, ses Lettres à Bernard d'Arezzo sont particulièrement importantes, car elles exposent ses critiques de la causalité et de la connaissance métaphysique. &lt;/p&gt; &lt;p&gt; Il reste une figure fascinante de l'histoire de la philosophie, car il incarne une rupture avec les certitudes de la &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1911_num_18_70_1977" style="color:#88A1E9" title="La scolastique médiévale" par Persée "&gt;scolastique médiévale &lt;/a&gt;. Son scepticisme radical et sa critique de la causalité préfigurent des débats philosophiques qui prendront toute leur importance à l'époque moderne. Bien que marginalisé de son vivant, il est aujourd'hui reconnu comme un penseur original et audacieux. &lt;/p&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_d%27Autr%C3%A9court"   title=" Wikipedia"&gt;Nicolas D'AUTRECOURT&lt;/a&gt; était un philosophe et théologien médiéval souvent considéré comme l'un des précurseurs du &lt;a href="https://www.philomag.com/lexique/scepticisme" title="Le septicisme  par Philomag "&gt;scepticisme moderne&lt;/a&gt; et de la pensée critique. Bien que moins connu que d'autres figures de la scolastique médiévale, comme Thomas d'Aquin ou Jean Duns Scot, il a joué un rôle important dans l'histoire de la philosophie en remettant en question certaines des certitudes de son époque. &lt;/p&gt; &lt;p&gt;  Il est surtout connu pour son scepticisme radical, qui l'a amené à remettre en question les fondements de la connaissance et de la métaphysique. Il a critiqué les arguments traditionnels de la scolastique, en particulier ceux basés sur la causalité et la substance. Selon lui, il est impossible de connaître avec certitude les causes des phénomènes ou la nature des substances.&lt;/p&gt; &lt;p&gt;  En 1346, il a été condamné par le pape Clément VI pour ses positions philosophiques jugées dangereuses pour la foi chrétienne. Ses écrits ont été brûlés, et il a été contraint de se rétracter publiquement. Après sa condamnation, il a disparu des archives historiques, et on sait peu de choses sur les dernières années de sa vie.&lt;/p&gt; &lt;p&gt; Malgré la destruction de la plupart de ses écrits, quelques lettres et fragments de ses travaux ont survécu. Parmi ceux-ci, ses Lettres à Bernard d'Arezzo sont particulièrement importantes, car elles exposent ses critiques de la causalité et de la connaissance métaphysique. &lt;/p&gt; &lt;p&gt; Il reste une figure fascinante de l'histoire de la philosophie, car il incarne une rupture avec les certitudes de la &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1911_num_18_70_1977" style="color:#88A1E9" title="La scolastique médiévale" par Persée "&gt;scolastique médiévale&lt;/a&gt;. Son scepticisme radical et sa critique de la causalité préfigurent des débats philosophiques qui prendront toute leur importance à l'époque moderne. Bien que marginalisé de son vivant, il est aujourd'hui reconnu comme un penseur original et audacieux. &lt;/p&gt;  </t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="E99" s="43" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Gerson"   title=" Wikipedia"&gt;Jean GERSON&lt;/a&gt;,  de son nom complet Jean Charlier de Gerson, est principalement connu pour son rôle de théologien, mystique, réformateur et chancelier de l'Université de Paris. Il a vécu pendant une période tumultueuse de l'histoire européenne, marquée par le &lt;a href="https://www.persee.fr/doc/cafan_0575-061x_2004_act_39_1_1831" style="color:#88A1E9" title="Le grand Schisme par Persée"&gt;Grand Schisme&lt;/a&gt; d'Occident (1378-1417), qui a divisé la chrétienté entre plusieurs papes rivaux. Cette crise a profondément influencé sa pensée et ses actions, notamment son engagement pour l'unité de l'Église et la réforme des institutions ecclésiastiques. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un représentant de la &lt;a href="https://www.universalis.fr/encyclopedie/devotio-moderna/" title="&lt;devotio moderna par Universalis"&gt;devotio moderna&lt;/a&gt; , un mouvement spirituel qui mettait l'accent sur la &lt;a href="https://www.universalis.fr/encyclopedie/piete/"  title="&lt;piété par Universalis"&gt;piété&lt;/a&gt; personnelle et la relation intime avec Dieu. Il a écrit abondamment sur des sujets théologiques et mystiques, cherchant à concilier la rigueur intellectuelle de la scolastique avec une spiritualité plus personnelle et affective. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus célèbres, on trouve: &lt;/p&gt; &lt;dd&gt; -  De mystica theologia, où il explore les voies de la contemplation mystique. &lt;/dd&gt; &lt;dd&gt; - De consolatione theologiae, qui traite de la consolation spirituelle face aux épreuves de la vie.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt;  &lt;p&gt; Il a été un ardent défenseur de la conciliarité, une doctrine qui soutenait que les conciles généraux de l'Église avaient autorité sur le pape, notamment en période de crise comme le Grand Schisme. Il a participé activement au &lt;a href="https://www.youtube.com/watch?v=LzxjFDsma3Y" title="&lt;consille de Constance’occident par Pierre de laurier »&gt;consille de Constance &lt;/a&gt;,  où il a plaidé pour la résolution du schisme et la réforme de l'Église. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Gerson"   title=" Wikipedia"&gt;Jean GERSON&lt;/a&gt;,  de son nom complet Jean Charlier de Gerson, est principalement connu pour son rôle de théologien, mystique, réformateur et chancelier de l'Université de Paris. Il a vécu pendant une période tumultueuse de l'histoire européenne, marquée par le &lt;a href="https://www.persee.fr/doc/cafan_0575-061x_2004_act_39_1_1831" style="color:#88A1E9" title="Le grand Schisme par Persée"&gt;Grand Schisme&lt;/a&gt; d'Occident (1378-1417), qui a divisé la chrétienté entre plusieurs papes rivaux. Cette crise a profondément influencé sa pensée et ses actions, notamment son engagement pour l'unité de l'Église et la réforme des institutions ecclésiastiques. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un représentant de la &lt;a href="https://www.universalis.fr/encyclopedie/devotio-moderna/" title="&lt;devotio moderna par Universalis"&gt;devotio moderna&lt;/a&gt;, un mouvement spirituel qui mettait l'accent sur la &lt;a href="https://www.universalis.fr/encyclopedie/piete/"  title="&lt;piété par Universalis"&gt;piété&lt;/a&gt; personnelle et la relation intime avec Dieu. Il a écrit abondamment sur des sujets théologiques et mystiques, cherchant à concilier la rigueur intellectuelle de la scolastique avec une spiritualité plus personnelle et affective. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus célèbres, on trouve: &lt;/p&gt; &lt;dd&gt; -  De mystica theologia, où il explore les voies de la contemplation mystique. &lt;/dd&gt; &lt;dd&gt; - De consolatione theologiae, qui traite de la consolation spirituelle face aux épreuves de la vie.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt;  &lt;p&gt; Il a été un ardent défenseur de la conciliarité, une doctrine qui soutenait que les conciles généraux de l'Église avaient autorité sur le pape, notamment en période de crise comme le Grand Schisme. Il a participé activement au &lt;a href="https://www.youtube.com/watch?v=LzxjFDsma3Y" title="&lt;consille de Constance’occident par Pierre de laurier »&gt;consille de Constance&lt;/a&gt;,  où il a plaidé pour la résolution du schisme et la réforme de l'Église. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F99" s="30" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -3203,12 +3203,12 @@
       </c>
       <c r="F40" s="30" t="inlineStr">
         <is>
-          <t>iY2q1nMwvIo</t>
+          <t xml:space="preserve">6AsBsbIfktQ</t>
         </is>
       </c>
       <c r="G40" s="33" t="inlineStr">
         <is>
-          <t>"St albert le Grand" par Chemin des saints</t>
+          <t xml:space="preserve">"Albert le Grand, entre science et théologie" par Prométhée moi</t>
         </is>
       </c>
       <c r="H40" s="33" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="L6" s="24" t="inlineStr">
         <is>
-          <t>Patristique ; Monothélisme</t>
+          <t xml:space="preserve">Patristique</t>
         </is>
       </c>
       <c r="M6" s="24" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="L25" s="24" t="inlineStr">
         <is>
-          <t>Nominalisme ; Scolastique</t>
+          <t xml:space="preserve">Nominalisme ; Scolastique ; Conceptualisme</t>
         </is>
       </c>
       <c r="M25" s="24" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="L76" s="24" t="inlineStr">
         <is>
-          <t>Nominalisme</t>
+          <t xml:space="preserve">Nominalisme ; Conceptualisme</t>
         </is>
       </c>
       <c r="M76" s="24" t="inlineStr">
@@ -8432,6 +8432,62 @@
         </is>
       </c>
       <c r="P118"/>
+    </row>
+    <row r="119" ht="99.75" customHeight="1" s="25">
+      <c r="A119" s="30">
+        <v>575</v>
+      </c>
+      <c r="B119" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">638</t>
+        </is>
+      </c>
+      <c r="C119" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 575 – 638</t>
+        </is>
+      </c>
+      <c r="D119" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SERGE Ier de Constantinople</t>
+        </is>
+      </c>
+      <c r="E119" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Serge_Ier_de_Constantinople" title=" Wikipedia"&gt;SERGE Ier de Constantinople&lt;/a&gt; est patriarche de Constantinople de 610 à sa mort, en 638, sous le règne de l’empereur Héraclius. Selon des sources byzantines, il serait d’origine syrienne, né dans une famille monophysite. Il gouverne l’Église de la capitale à une époque dramatique : les Perses prennent Jérusalem en 614 et emportent la Vraie Croix ; en 626, les Avars et les Perses assiègent Constantinople en l’absence de l’empereur. Serge conduit les processions qui soutiennent les défenseurs, et une tradition lui attribue l’hymne acathiste à la Vierge, chanté pour célébrer la délivrance de la ville.&lt;/p&gt; &lt;p&gt;Héraclius veut refaire l’unité de l’Empire, divisé depuis le concile de Chalcédoine (451) entre ceux qui confessent deux natures dans le Christ, divine et humaine, et les monophysites d’Égypte et de Syrie, qui n’en reconnaissent qu’une. Serge cherche un compromis : on garderait les deux natures, mais on affirmerait dans le Christ une seule « énergie », une seule activité, puis une seule volonté. C’est d’abord le monoénergisme, accepté en 633 par une partie des monophysites d’Alexandrie, puis le &lt;a href="https://fr.wikipedia.org/wiki/Monoth%C3%A9lisme" title=" Wikipedia"&gt;monothélisme&lt;/a&gt;, formulé dans l’&lt;em&gt;Ecthèse&lt;/em&gt;, l’édit qu’il rédige et qu’Héraclius publie en 638. Le pape Honorius, consulté, approuve la formule d’« une seule volonté ».&lt;/p&gt; &lt;p&gt;Mais le compromis échoue. Le moine Sophrone de Jérusalem, puis &lt;a href="https://fr.wikipedia.org/wiki/Maxime_le_Confesseur" title=" Wikipedia"&gt;Maxime le Confesseur&lt;/a&gt;, objectent qu’un Christ sans volonté humaine ne serait pas pleinement homme : ce qui n’est pas assumé n’est pas sauvé. Les conquêtes arabes privent bientôt l’Empire des provinces qu’on voulait réconcilier. En 681, le troisième concile de Constantinople condamne le monothélisme, et Serge, comme le pape Honorius, est anathématisé. Le débat a pourtant fait avancer une question philosophique : qu’est-ce qu’une volonté, et peut-on être une seule personne avec deux volontés ?&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H119" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/serge-mini.webp</t>
+        </is>
+      </c>
+      <c r="J119" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Byzantine</t>
+        </is>
+      </c>
+      <c r="K119" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite</t>
+        </is>
+      </c>
+      <c r="L119" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monothélisme</t>
+        </is>
+      </c>
+      <c r="M119" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patriarche de Constantinople, auteur du monothélisme pour réconcilier les chrétiens d’Orient.</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P119"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -3195,10 +3195,7 @@
       </c>
       <c r="E40" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_le_Grand"   title=" Wikipedia"&gt;ALBERT le Grand&lt;/a&gt; était un érudit, philosophe, théologien, et scientifique dont les travaux ont eu une influence profonde sur la pensée médiévale et moderne. Il est souvent considéré comme le &lt;a href="https://www.youtube.com/watch?v=DvQXZaFwB5k" title=Albert le Grand par Pier Aujourd'hui "&gt;précurseur&lt;/a&gt; de la synthèse entre la philosophie aristotélicienne et la théologie chrétienne, les rendant accessibles au monde chrétien. Ses travaux ont jeté les bases pour la synthèse philosophico-théologique que Thomas d'Aquin développera plus tard. Il était également un scientifique passionné et a écrit des traités sur une variété de sujets, y compris la biologie, la zoologie, la botanique, la minéralogie, et l'alchimie. Ses observations empiriques et ses expériences ont marqué un tournant dans l'approche médiévale des sciences naturelles. &lt;/p&gt; &lt;p&gt; Ses Œuvres Majeures : &lt;/p&gt;
-&lt;p&gt; De Mineralibus (Sur les Minéraux),  De Animalibus (Sur les Animaux), &lt;a href="https://www.youtube.com/watch?v=PwYmEVkmqlo&amp;t=27s" style="color:#88A1E9" title=Le silence :Albert le Grand par la caverne du pelerins "&gt;Summa Theologiae&lt;/a&gt; (une synthèse de théologie), Commentaires sur Aristote (y compris sur la Physique, la Métaphysique, et l'Éthique à Nicomaque),  Canonisation et Héritage &lt;/p&gt; 
-&lt;p&gt; Il  a été canonisé par le pape Pie XI en 1931 et déclaré Docteur de l'Église. Son héritage intellectuel est immense, influençant non seulement la théologie et la philosophie, mais aussi les sciences naturelles. Il est souvent considéré comme un modèle de l'érudition médiévale, capable de synthétiser la foi et la raison. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_le_Grand"   title=" Wikipedia"&gt;ALBERT le Grand&lt;/a&gt; (vers 1200-1280) est un théologien, philosophe et savant allemand de l’ordre dominicain, surnommé le « Docteur universel » pour l’étendue de son savoir. Né en Souabe, il étudie à Padoue, entre chez les dominicains, enseigne à Paris, où il a pour élève Thomas d’Aquin, puis fonde à Cologne en 1248 un centre d’études qui forme toute une génération. Il est un temps évêque de Ratisbonne, mais renonce vite à cette charge pour revenir à l’enseignement.&lt;/p&gt; &lt;p&gt;Albert se donne un programme immense : rendre Aristote intelligible aux Latins, en paraphrasant et en commentant toutes ses œuvres, logique, physique, métaphysique, éthique et politique. Il distingue nettement la philosophie, qui procède par la raison, de la théologie, fondée sur la révélation, et revendique pour la première une réelle autonomie : il est le &lt;a href="https://www.youtube.com/watch?v=DvQXZaFwB5k" title="Albert le Grand par Pier Aujourd'hui"&gt;précurseur&lt;/a&gt; de la synthèse que réalisera Thomas d’Aquin. Il écrit aussi une &lt;a href="https://www.youtube.com/watch?v=PwYmEVkmqlo&amp;t=27s" style="color:#88A1E9" title="Le silence :Albert le Grand par la caverne du pelerins"&gt;&lt;em&gt;Somme de théologie&lt;/em&gt;&lt;/a&gt;. Mais il est surtout un naturaliste passionné, qui observe lui-même les plantes, les animaux et les minéraux : ses traités &lt;em&gt;Sur les animaux&lt;/em&gt;, &lt;em&gt;Sur les végétaux&lt;/em&gt; et &lt;em&gt;Sur les minéraux&lt;/em&gt; mêlent l’héritage d’Aristote à de nombreuses observations personnelles, ce qui en fait l’un des premiers savants de l’Occident médiéval. Par ailleurs, son intérêt pour le néoplatonisme du Pseudo-Denys et du &lt;em&gt;Livre des causes&lt;/em&gt; inspire ses disciples allemands, d’Ulrich de Strasbourg à Maître Eckhart.&lt;/p&gt; &lt;p&gt;On lui attribua plus tard des livres de magie et d’alchimie, comme le &lt;em&gt;Grand Albert&lt;/em&gt;, qui ne sont pas de lui. Canonisé et proclamé docteur de l’Église en 1931, il est le patron des scientifiques.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F40" s="30" t="inlineStr">
@@ -3400,7 +3397,7 @@
       </c>
       <c r="E43" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_d%27Espagne"   title=" Wikipedia"&gt;Pierre D'ESPAGNE&lt;/a&gt;   était un philosophe espagno  également connu sous le nom de Petrus Hispanus, désigne plusieurs figures médiévales du XIIIe siècle, dont certaines sont associées à la philosophie et à la logique à Paris autour de 1215. Le plus notable est l'auteur présumé des "Summulae logicales", un manuel fondamental de logique scolastique. &lt;/p&gt; &lt;p&gt; Il systématise  &lt;a href="https://www.persee.fr/doc/crai_0065-0536_1864_num_8_1_66876"  title="la logique de Pierre d’espagne par Persee"&gt; la logique aristotélicienne&lt;/a&gt;, Porphyre et les premiers scolastiques comme Jean Pagus. Ces textes traitent des propriétés des termes, des propositions et des syllogismes, influençant l'enseignement jusqu'à la Renaissance et servant de base aux débats anti-averroïstes. &lt;/p&gt; &lt;p&gt; Actif durant l'introduction clandestine d'Aristote malgré les interdits de 1210-1215, il participe à la tension entre raison profane et théologie, appuyant en 1277 la condamnation des averroïstes par Étienne Tempier. Son œuvre, éditée au XXe siècle par L.M. de Rijk, marque la maturation de la scolastique dialectique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_d%27Espagne"   title=" Wikipedia"&gt;Pierre D’ESPAGNE&lt;/a&gt;, en latin Petrus Hispanus, est l’auteur d’un des manuels de logique les plus lus du Moyen Âge, les &lt;em&gt;Tractatus&lt;/em&gt;, appelés plus tard &lt;em&gt;Summulae logicales&lt;/em&gt;, composés vers le milieu du XIIIe siècle. Son identité reste discutée. La tradition l’identifie à Pierre Julien, médecin et savant portugais, auteur d’un célèbre recueil de remèdes, le &lt;em&gt;Trésor des pauvres&lt;/em&gt;, devenu pape en 1276 sous le nom de Jean XXI et mort l’année suivante à Viterbe, écrasé par l’effondrement d’un plafond. Des historiens pensent plutôt à un dominicain castillan du même nom.&lt;/p&gt; &lt;p&gt;Son manuel expose en douze traités &lt;a href="https://www.persee.fr/doc/crai_0065-0536_1864_num_8_1_66876"  title="la logique de Pierre d’espagne par Persee"&gt;la logique aristotélicienne&lt;/a&gt; telle qu’on l’enseignait alors dans les facultés des arts, à partir d’Aristote et de Porphyre : les termes, les propositions, les syllogismes, les arguments probables et les sophismes. Il y ajoute ce que les médiévaux appelaient la « logique des modernes », leur invention propre : la théorie des propriétés des termes, en particulier la « supposition », qui étudie ce qu’un mot désigne dans une phrase donnée. Dans « l’homme est une espèce », « homme » ne désigne pas un individu, mais un concept. Le livre popularise aussi les vers mnémotechniques qui servaient à retenir les figures du syllogisme, comme &lt;em&gt;Barbara&lt;/em&gt; ou &lt;em&gt;Celarent&lt;/em&gt;.&lt;/p&gt; &lt;p&gt;Copié et commenté pendant trois siècles, imprimé plus de cent fois, il a formé des générations d’étudiants jusqu’à la Renaissance. Devenu pape, Jean XXI demanda en 1277 à l’évêque de Paris d’enquêter sur les erreurs enseignées à l’université, ce qui conduisit à la condamnation de 219 thèses. Dante le place au Paradis.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F43" s="30" t="inlineStr">
@@ -3669,7 +3666,7 @@
       </c>
       <c r="E47" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ulrich_de_Strasbourg"  title=" Wikipedia"&gt;Ulrich de STRASBOURG&lt;/a&gt; était un philosophe dominicain français, élève d'Albert le Grand.  Il enseigne la théologie à Strasbourg, devient provincial de Teutonie en 1272, puis est envoyé à Paris pour lire les Sentences et obtenir la maîtrise en théologie, où il meurt en 1277. &lt;p&gt; &lt;p&gt; Son oeuvre  "Summa de bono" rédigée entre 1262 et 1272, est une somme théologique majeure influencée par le néoplatonisme albertinien, intégrant des sources comme le Liber de causis et Avicenne. Elle synthétise théologie et philosophie, faisant le lien entre aristotélisme et mysticisme rhénan ultérieur. &lt;/p&gt; &lt;p&gt;Il  met l'accent sur l'être comme première émanation divine, lumière primordiale de toutes choses, et sur une connaissance naturelle de Dieu comme vérité suprême. Anti-thomiste sur certains points, il privilégie une approche néoplatonicienne où Dieu est cause de toute vérité, accessible par la raison avant la foi. Ses idées sur la connaissance de Dieu et les vertus influencent l'école dominicaine rhénane. &lt;/p&gt; &lt;p&gt; Contemporaine de la "Somme théologique" de Thomas d'Aquin, son œuvre reste peu éditée mais clé pour comprendre la transition vers les mystiques comme Maître Eckhart et Tauler. Elle fut largement diffusée et étudiée au Moyen Âge. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ulrich_de_Strasbourg"  title=" Wikipedia"&gt;Ulrich de STRASBOURG&lt;/a&gt; (vers 1225-1277) est un théologien et philosophe dominicain allemand, l’un des meilleurs disciples d’&lt;a href="https://fr.wikipedia.org/wiki/Albert_le_Grand" title=" Wikipedia"&gt;Albert le Grand&lt;/a&gt;. Il suit son enseignement à Cologne, en même temps que Thomas d’Aquin, puis enseigne lui-même la théologie au couvent dominicain de Strasbourg. En 1272, il devient provincial de Teutonie, c’est-à-dire supérieur des dominicains de l’Allemagne. Envoyé à Paris en 1277 pour y obtenir la maîtrise en théologie, il y meurt peu après son arrivée.&lt;/p&gt; &lt;p&gt;Son grand ouvrage, la &lt;em&gt;Somme du souverain bien&lt;/em&gt; (&lt;em&gt;Summa de summo bono&lt;/em&gt;), rédigée entre 1262 et 1272 et restée inachevée, est une vaste synthèse de théologie et de philosophie. Fidèle à Albert, Ulrich y combine Aristote avec la tradition néoplatonicienne du Pseudo-Denys, du &lt;em&gt;Livre des causes&lt;/em&gt; et d’Avicenne. Dieu y est pensé comme intellect et lumière, source de toute vérité. La première des réalités créées est l’être, qui procède de Dieu comme une lumière, et toutes les autres choses en découlent selon un ordre de perfection décroissante. L’homme peut connaître Dieu naturellement par la raison, avant même la foi, et l’intellect humain, en s’unissant à cette lumière, s’élève vers la contemplation. Ulrich y insère aussi un célèbre traité sur la beauté, l’un des textes les plus importants de l’esthétique médiévale : la beauté naît de la forme qui fait resplendir la matière, comme la lumière illumine les couleurs.&lt;/p&gt; &lt;p&gt;Contemporaine de la &lt;em&gt;Somme théologique&lt;/em&gt; de Thomas d’Aquin, son œuvre a été lue par Dietrich de Freiberg et Berthold de Moosburg. Elle prépare la mystique rhénane de Maître Eckhart et de Tauler.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F47" s="30" t="n"/>
@@ -5607,11 +5604,7 @@
       </c>
       <c r="E76" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_d%27Ockham"  title=" Wikipedia"&gt; Guillaume d'OCKHAM&lt;/a&gt; était un philosophe et théologien &lt;a  href="https://www.persee.fr/doc/phlou_0776-555x_1921_num_23_89_2264"  title="Le nominalisme d'Ockham  par Persée"&gt; Nominaliste&lt;/a&gt; Anglais connu pour ses contributions à la philosophie médiévale  et a été un critique important des positions dominantes de son époque, en particulier de la &lt;a  href="https://www.persee.fr/doc/phlou_0776-5541_1898_num_5_19_1610"  title="La Scolastique  par Persée"&gt; scolastique&lt;/a&gt;. &lt;/p&gt; &lt;p&gt; Il a également été un défenseur de la liberté individuelle et a soutenu que les croyances religieuses ne devraient pas être imposées par la force. Il a également été critique à l'égard de l'autorité papale et a défendu l'idée que les pouvoirs temporel et spirituel devraient être séparés.&lt;/p&gt; &lt;p&gt;
-Cependant, c'est sa formulation du &lt;a  href="https://www.youtube.com/watch?v=mjzR8Bx6D8ct"  title="Le rasoir d'Ockham  par El Khader"&gt;rasoir d'Ockham&lt;/a&gt;  qui est peut-être sa contribution la plus célèbre à la philosophie. C'est un principe méthodologique qui stipule que lorsqu'on a plusieurs explications possibles à un phénomène, la plus simple est généralement la meilleure. Autrement dit, il ne faut pas multiplier les entités ou les hypothèses sans nécessité.&lt;/p&gt; &lt;p&gt; 
-Le rasoir d'Ockham a eu une grande influence sur la philosophie, la science et la pensée en général et a contribué à la révolution scientifique en encourageant les scientifiques à se concentrer sur des explications simples et empiriques plutôt que sur des théories complexes et spéculatives. De plus, il est également utilisé dans le domaine de la logique et de l'épistémologie pour évaluer les arguments et les théories.&lt;/p&gt;
- &lt;audio controls title="Le rasoir d'Ockham par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2013/04/s17/NET_FI_3b7dff03-d4dd-4b03-8d48-bef7d8510fb5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
-&lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_d%27Ockham"  title=" Wikipedia"&gt;Guillaume d’OCKHAM&lt;/a&gt; (vers 1285-1347) est un théologien et philosophe anglais de l’ordre franciscain, la grande figure du &lt;a  href="https://www.persee.fr/doc/phlou_0776-555x_1921_num_23_89_2264"  title="Le nominalisme d'Ockham  par Persée"&gt;nominalisme&lt;/a&gt;. Né au village d’Ockham, près de Londres, il étudie et enseigne à Oxford. Soupçonné d’hérésie, il est convoqué en 1324 à Avignon, auprès du pape, et y prend le parti des franciscains qui défendent la pauvreté du Christ contre Jean XXII. Excommunié, il s’enfuit en 1328 et trouve refuge à Munich, auprès de l’empereur Louis de Bavière, où il meurt.&lt;/p&gt; &lt;p&gt;Ockham rompt avec les grandes synthèses de la &lt;a  href="https://www.persee.fr/doc/phlou_0776-5541_1898_num_5_19_1610"  title="La Scolastique  par Persée"&gt;scolastique&lt;/a&gt;. Seuls existent les individus, cet homme, ce cheval ; les universaux, comme « l’humanité » ou « l’animal », ne sont pas des réalités présentes dans les choses, mais des signes, des concepts de l’esprit qui désignent plusieurs individus semblables. Notre connaissance part de l’intuition directe des choses singulières. Son principe d’économie, appelé plus tard le &lt;a  href="https://www.youtube.com/watch?v=mjzR8Bx6D8c"  title="Le rasoir d'Ockham  par El Khader"&gt;rasoir d’Ockham&lt;/a&gt;, recommande de ne pas multiplier les êtres sans nécessité : entre deux explications, on retient celle qui suppose le moins d’entités. Ockham insiste aussi sur la toute-puissance de Dieu, qui peut faire tout ce qui n’est pas contradictoire : le monde n’est pas nécessaire, et les vérités de la foi ne se démontrent pas par la raison. En politique, il conteste la toute-puissance du pape, défend l’indépendance du pouvoir temporel et parle des droits des individus.&lt;/p&gt; &lt;p&gt;Sa pensée inaugure la « voie moderne », qui domine les universités à la fin du Moyen Âge. Elle annonce l’empirisme anglais et l’esprit de la science moderne.&lt;/p&gt;  &lt;audio controls title="Le rasoir d'Ockham par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/inter/sons/2013/04/s17/NET_FI_3b7dff03-d4dd-4b03-8d48-bef7d8510fb5.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F76" s="30" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -966,8 +966,7 @@
       </c>
       <c r="E7" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/B%C3%A8de_le_V%C3%A9n%C3%A9rable"  style="color:#6A142A"  title=" Wikipedia"&gt;BÈDE le Vénérable&lt;/a&gt; (en latin: Beda Venerabilis) était un moine chrétien anglais célèbre pour son travail en tant que théologien, linguiste et philosophe  sur la nature de Dieu, la liberté humaine et la nature de l'âme. &lt;/p&gt; &lt;p&gt; Son ouvrage le plus célèbre est &lt;a href="https://books.openedition.org/irhis/334?lang=fr"  style="color:#88A1E9"  title="Histoire ecclésiastique par Open Edition"&gt; "Histoire ecclésiastique du peuple anglais"&lt;/a&gt;  (ou "Historia ecclesiastica gentis Anglorum" en latin), qui est considéré comme la première histoire complète de l'Église d'Angleterre. &lt;/p&gt; &lt;p&gt; En tant que savant, Bède était réputé pour son érudition et sa connaissance des langues anciennes, comme le latin, le grec et l'hébreu. Son œuvre sur le calcul du temps "De Temporum Ratione", dans laquelle il a développé un système pour calculer la date de Pâques a eu une grande importante pour la compréhension de la chronologie chrétienne et a été largement utilisée dans toute l'Europe médiévale. &lt;/p&gt; &lt;p&gt;  Il a été canonisé en 1899 et est aujourd'hui considéré comme un saint dans l'Église catholique romaine et dans l'Église anglicane. &lt;/p&gt;
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/B%C3%A8de_le_V%C3%A9n%C3%A9rable"  style="color:#6A142A"  title=" Wikipedia"&gt;BÈDE le Vénérable&lt;/a&gt; (672-735), en latin &lt;em&gt;Beda Venerabilis&lt;/em&gt;, est un moine et savant anglais, l’un des plus grands érudits du haut Moyen Âge. Confié à sept ans au monastère de Wearmouth, puis à celui de Jarrow, en Northumbrie, il y passe toute sa vie, consacrée, dit-il, à « apprendre, enseigner et écrire ». Il n’a presque jamais voyagé, mais il dispose d’une des plus riches bibliothèques de l’Europe de son temps.&lt;/p&gt; &lt;p&gt;Son œuvre est immense : commentaires de la Bible, vies de saints, traités de grammaire, de poésie, de sciences de la nature. Son livre le plus célèbre, l’&lt;a href="https://books.openedition.org/irhis/334?lang=fr"  style="color:#88A1E9"  title="Histoire ecclésiastique par Open Edition"&gt;&lt;em&gt;Histoire ecclésiastique du peuple anglais&lt;/em&gt;&lt;/a&gt; (731), raconte la christianisation de l’Angleterre depuis l’époque romaine. C’est une source essentielle pour l’histoire de ce pays, et un modèle de méthode : Bède cite ses sources, reproduit des documents, distingue ce qu’il a lu de ce qu’on lui a raconté. Dans &lt;em&gt;Le Calcul du temps&lt;/em&gt; (725), il expose comment calculer la date de Pâques, question qui divisait alors les Églises, et étudie les mouvements du soleil et de la lune ainsi que les marées, qu’il relie aux phases de la lune. Il contribue surtout à répandre l’usage de compter les années à partir de la naissance du Christ, l’« ère chrétienne », que nous utilisons encore aujourd’hui. Pour lui, l’étude de la nature et de l’histoire conduit à mieux comprendre l’œuvre de Dieu.&lt;/p&gt; &lt;p&gt;On raconte qu’il mourut en dictant les dernières lignes d’une traduction de l’Évangile de Jean en vieil anglais. Il est proclamé docteur de l’Église en 1899 ; Dante le place au Paradis.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F7" s="30" t="inlineStr">
@@ -3128,7 +3127,7 @@
       </c>
       <c r="E39" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_La_Rochelle"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean de La Rochelle&lt;/a&gt; était un philosophe franciscain français disciple direct d'Alexandre de Hales et figure clé de la scolastique parisienne précoce. Il collabore étroitement avec lui à la "Summa theologica", qu'il contribue à achever après la mort de son maître en 1245. &lt;/p&gt; &lt;p&gt; Précurseur du franciscanisme intellectuel, il défend la théologie comme sagesse unissant connaissance, sainteté et enseignement, incarnant une approche augustinienne face à l'aristotélisme naissant. &lt;/p&gt; &lt;p&gt;  Innovant en philosophie de l'âme, il organise les  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1964_num_38_4_2400_t1_0422_0000_2" style="color:#88A1E9" title=" Jean de la Rochelle, Tractatus de divisione multiplici potentiarum animae. Texte critique avec introduction, notes et tables, par Pierre Michaud-Quantin, Textes philosophiques du moyen âge XI, 1964 par Persée"&gt;textes autoritaires &lt;/a&gt; en analysant leurs vocabulaires concurrents, posant les bases pour Bonaventure et influençant la scolastique. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - "Summa de anima" écrit vers  1235 : Traite de l'âme selon les quatre causes aristotéliciennes, distinguant une âme supérieure (spirituelle) et inférieure (corporelle), en débat avec les théories matérialistes. - "Tractatus de divisione potentiarum animae" écrit vers 1233  : Analyse détaillée des divisions de l'âme, intégrant Platon, Aristote, Avicenne et Augustin pour clarifier les sources philosophiques nouvelles. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_La_Rochelle"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean de La Rochelle&lt;/a&gt; était un philosophe franciscain français disciple direct d'Alexandre de Hales et figure clé de la scolastique parisienne précoce. Il collabore étroitement avec lui à la "Summa theologica", à laquelle il contribue ; maître et disciple meurent tous deux en 1245, et l'ouvrage sera achevé par d'autres franciscains. &lt;/p&gt; &lt;p&gt; Précurseur du franciscanisme intellectuel, il défend la théologie comme sagesse unissant connaissance, sainteté et enseignement, incarnant une approche augustinienne face à l'aristotélisme naissant. &lt;/p&gt; &lt;p&gt;  Innovant en philosophie de l'âme, il organise les  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1964_num_38_4_2400_t1_0422_0000_2" style="color:#88A1E9" title=" Jean de la Rochelle, Tractatus de divisione multiplici potentiarum animae. Texte critique avec introduction, notes et tables, par Pierre Michaud-Quantin, Textes philosophiques du moyen âge XI, 1964 par Persée"&gt;autorités&lt;/a&gt;, c'est-à-dire les textes de référence, en analysant leurs vocabulaires concurrents, posant les bases pour Bonaventure et influençant la scolastique. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - "Summa de anima" écrit vers  1235 : Traite de l'âme selon les quatre causes aristotéliciennes, distinguant une âme supérieure (spirituelle) et inférieure (corporelle), en débat avec les théories matérialistes. - "Tractatus de divisione potentiarum animae" écrit vers 1233  : Analyse détaillée des divisions de l'âme, intégrant Platon, Aristote, Avicenne et Augustin pour clarifier les sources philosophiques nouvelles. Jean de La Rochelle est en effet l’un des premiers, à Paris, à intégrer dans la théologie la psychologie d’Avicenne, récemment traduite de l’arabe : il distingue avec lui les sens externes, les sens internes, comme l’imagination et la mémoire, et les puissances de l’intellect. Il enseigne avec Alexandre de Hales, dès 1238, la première école franciscaine de l’université de Paris. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -3599,8 +3598,7 @@
       </c>
       <c r="E46" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Roger_Bacon"  title=" Wikipedia"&gt; Roger BACON&lt;/a&gt; était un philosophe, théologien et scientifique anglais qui,en tant que chrétien,  a cherché à harmoniser la science et la religion. Il a soutenu que la science et la religion ne devaient pas être en conflit, mais plutôt travailler ensemble pour atteindre la vérité. Il a également plaidé pour une réforme de l'éducation, encourageant l'étude des langues, des mathématiques et des sciences naturelles. &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1913_num_20_77_2047"   title="Opus par Persée.fr "&gt;L'"Opus Majus" &lt;/a&gt; est un recueil des idées et des théories de Bacon sur un large éventail de sujets, notamment la grammaire, la logique, les mathématiques, la physique et la métaphysique.  &lt;/p&gt; &lt;p&gt; Il a été écrit comme un argument en faveur de la nécessité de réformer l'éducation à l'époque médiévale et de promouvoir l'utilisation de méthodes expérimentales dans la recherche scientifique. &lt;/p&gt; &lt;p&gt; 
-Dans l'ensemble, la philosophie de Roger Bacon a été un catalyseur important pour le développement de la méthode scientifique moderne, et &lt;a href="https://www.youtube.com/watch?v=VWyIWIJDR-A"  style="color:#88A1E9"  title="R Bacon par Sir Talkalot Doolittle"&gt;son travail&lt;/a&gt; a influencé de nombreux scientifiques et philosophes des siècles suivants. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Roger_Bacon"  title=" Wikipedia"&gt;Roger BACON&lt;/a&gt; (vers 1220-1292) est un philosophe et savant anglais, de l’ordre franciscain, surnommé le « Docteur admirable ». Après avoir étudié à Oxford, il enseigne à Paris, où il est l’un des premiers à commenter les œuvres d’Aristote. Influencé par Robert Grosseteste, il se passionne ensuite pour les langues, les mathématiques et l’optique, et entre vers 1257 chez les Franciscains.&lt;/p&gt; &lt;p&gt;En 1266, le pape Clément IV lui demande de lui envoyer en secret un exposé de ses idées. Bacon rédige alors en quelques mois l’&lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1913_num_20_77_2047"   title="Opus par Persée.fr "&gt;&lt;em&gt;Opus majus&lt;/em&gt;&lt;/a&gt;, « l’œuvre majeure », complété par l’&lt;em&gt;Opus minus&lt;/em&gt; et l’&lt;em&gt;Opus tertium&lt;/em&gt;. Il y propose une réforme complète du savoir. Il commence par dénoncer les quatre causes de l’erreur : la soumission à une autorité indigne, la coutume, l’opinion de la foule, et la tendance à cacher son ignorance sous un faux savoir. Il plaide pour l’étude du grec et de l’hébreu, afin de lire la Bible et les philosophes dans le texte, et pour les mathématiques, « porte et clef » de toutes les sciences. Il consacre une longue partie à l’optique, étudie l’arc-en-ciel et décrit l’usage des lentilles pour grossir les objets. Il insiste surtout sur la « science expérimentale », qui vérifie par l’expérience les conclusions du raisonnement et découvre des vérités nouvelles. Il imagine des machines volantes, des navires sans rameurs et des voitures sans chevaux. Mais pour lui, tout ce savoir doit servir la théologie et le bien de la chrétienté.&lt;/p&gt; &lt;p&gt;Ses idées hardies lui valent des difficultés au sein de son ordre. &lt;a href="https://www.youtube.com/watch?v=VWyIWIJDR-A"  style="color:#88A1E9"  title="R Bacon par Sir Talkalot Doolittle"&gt;Son œuvre&lt;/a&gt; a fait de lui, à la Renaissance, une figure légendaire de savant et de magicien.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F46" s="30" t="inlineStr">
@@ -3866,7 +3864,7 @@
       </c>
       <c r="E50" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Peckham"  title=" Wikipedia"&gt;John PECKHAM&lt;/a&gt;  était un philosophe franciscain britannique disciple de Bonaventure à l'université de Paris ou il enseigne la théologie et s'oppose au thomisme, notamment sur l'âme et l'unité de la forme. Influencé par Roger Bacon en optique et astronomie, il retourne en Angleterre vers 1270 pour enseigner à Oxford. &lt;/p&gt; &lt;p&gt; Élu ministre provincial des Franciscains en Angleterre en 1275, il devient archevêque de Cantorbéry en 1279. Il réforme le clergé, combat le pluralisme et l'usure, et convoque des conciles comme celui de Lambeth (1281) pour imposer une catéchèse minimale aux laïcs. &lt;/p&gt; &lt;p&gt;  Ses écrits incluent des traités d'optique (Perspectiva), Tractatus de anima, Quodlibeta, des commentaires bibliques et Philomena, un poème notable. Il rédige aussi Expositio super Regulam Fratrum Minorum sur la prédication. Défenseur d'une théologie augustinienne conservatrice, il critique l'aristotélisme radical, insiste sur la pauvreté franciscaine et explore l'existence de Dieu, la perspective et les tensions entre foi et raison dans un cadre anti-thomiste. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/John_Peckham"  title=" Wikipedia"&gt;John PECKHAM&lt;/a&gt;  était un philosophe franciscain britannique disciple de Bonaventure à l'université de Paris où il enseigne la théologie et s'oppose au thomisme, notamment sur l'âme et l'unité de la forme. Influencé par Roger Bacon en optique et astronomie, il retourne en Angleterre vers 1270 pour enseigner à Oxford. &lt;/p&gt; &lt;p&gt; Élu ministre provincial des Franciscains en Angleterre en 1275, il devient archevêque de Cantorbéry en 1279. Il réforme le clergé, combat le pluralisme et l'usure, et convoque des conciles comme celui de Lambeth (1281) pour imposer une catéchèse minimale aux laïcs. &lt;/p&gt; &lt;p&gt;  Ses écrits incluent des traités d'optique (Perspectiva), Tractatus de anima, Quodlibeta, des commentaires bibliques et Philomena, un poème notable. Il rédige aussi Expositio super Regulam Fratrum Minorum sur la prédication. Défenseur d'une théologie augustinienne conservatrice, il critique l'aristotélisme radical, insiste sur la pauvreté franciscaine et explore l'existence de Dieu, la perspective et les tensions entre foi et raison dans un cadre anti-thomiste. Vers 1270, à Paris, il s’oppose publiquement à Thomas d’Aquin sur l’unité de la forme substantielle dans l’homme ; devenu archevêque, il fait condamner en 1284 et en 1286 plusieurs thèses thomistes enseignées à Oxford. Sa &lt;em&gt;Perspective commune&lt;/em&gt;, manuel d’optique inspiré du savant arabe Alhazen, est restée en usage dans les universités jusqu’au XVIIe siècle. Dans son poème &lt;em&gt;Philomena&lt;/em&gt;, le chant du rossignol figure l’âme qui médite la Passion du Christ. &lt;/p&gt; 
  </t>
         </is>
       </c>
@@ -3933,7 +3931,7 @@
       </c>
       <c r="E51" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_de_Sutton"   title=" Wikipedia"&gt;Thomas de SUTTON&lt;/a&gt;  était un théologien et philosophe dominicain anglais, l'un des premiers et plus éminents défenseurs du thomisme contre ses détracteurs contemporains. Ordonné diacre en 1274 par l'archevêque de York, il rejoint les dominicains dans les années 1270, possiblement après un passage comme fellow au Merton College d'Oxford. Il obtient son doctorat en théologie en 1282 et enseigne activement à Oxford, où il devient une figure clé de l'école thomiste anglaise. &lt;/p&gt; &lt;p&gt; Il est célèbre pour sa réfutation des critiques anti-thomistes, notamment dans son "Contra pluralitatem formarum" et "De productione formae substantialis". Il défend l'unicité de la forme substantiale par individu contre les pluralistes comme Henri de Gand, arguant que l'âme intellectuelle unifie le corps sans multiplier les formes. &lt;/p&gt; &lt;p&gt; Dans ses  &lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1980_num_34_1_1168_t1_0162_0000_1" style="color:#88A1E9" title="Thomas von Sutton. Quaestiones ordinariae. Hrsg. von Johannes Schneider par Persée"&gt;"Quaestiones Ordinariae" &lt;/a&gt; et sur l'âme intellective, il rejette l'averroïsme et insiste sur la distinction essence-existence. Il affirme que l'âme est forme substantiale unique, individuée par la matière, et combat les vues spiritualistes excessives en s'appuyant sur Aristote et Thomas. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_de_Sutton"   title=" Wikipedia"&gt;Thomas de SUTTON&lt;/a&gt;  était un théologien et philosophe dominicain anglais, l'un des premiers et plus éminents défenseurs du thomisme contre ses détracteurs contemporains. Ordonné diacre en 1274 par l'archevêque de York, il rejoint les dominicains dans les années 1270, possiblement après un passage comme fellow au Merton College d'Oxford. Il obtient son doctorat en théologie en 1282 et enseigne activement à Oxford, où il devient une figure clé de l'école thomiste anglaise. &lt;/p&gt; &lt;p&gt; Il est célèbre pour sa réfutation des critiques anti-thomistes, notamment dans son "Contra pluralitatem formarum" et "De productione formae substantialis". Il défend l'unicité de la forme substantiale par individu contre les pluralistes comme Henri de Gand, arguant que l'âme intellectuelle unifie le corps sans multiplier les formes. &lt;/p&gt; &lt;p&gt; Dans ses  &lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1980_num_34_1_1168_t1_0162_0000_1" style="color:#88A1E9" title="Thomas von Sutton. Quaestiones ordinariae. Hrsg. von Johannes Schneider par Persée"&gt;"Quaestiones Ordinariae" &lt;/a&gt; et sur l'âme intellective, il rejette l'averroïsme et insiste sur la distinction essence-existence. Il affirme que l'âme est forme substantiale unique, individuée par la matière, et combat les vues spiritualistes excessives en s'appuyant sur Aristote et Thomas. Il est aussi l’un des premiers à répondre à Jean Duns Scot, dont la pensée s’impose à Oxford au début du XIVe siècle, en défendant contre lui la doctrine thomiste de la connaissance et de l’individuation. Ses questions disputées et quodlibétiques, longtemps oubliées, ont été éditées au XXe siècle et montrent un penseur original, qui ne se contente pas de répéter Thomas d’Aquin mais en prolonge la pensée. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F51" s="30" t="n"/>
@@ -3995,7 +3993,7 @@
       </c>
       <c r="E52" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_de_Lessines"   title=" Wikipedia"&gt;Gilles de LESSINES&lt;/a&gt;  né dans le Hainaut (actuelle Belgique), est un philosophe scolastique et astronome dominicain,  Membre de l'ordre des Prêcheurs. Élève d'Albert le Grand à Paris, il devint bachelier en théologie et fut lié à Thomas d'Aquin, défendant ses idées après la condamnation de 1277 par l'évêque de Paris. &lt;/p&gt; &lt;p&gt; Il rédigea en 1278 le traité &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1920_num_22_86_2243"  title="Gilles de Lessines et son « Tractatus de Crepusculis » [ par Persée"&gt;"De unitate formae", &lt;/a&gt;  soutenant l'unité de la forme substantielle contre les pluralistes, en lien avec les débats thomistes. Il s'intéressa aussi à l'astronomie, écrivant Sur l'essence, le mouvement et la signification des comètes, où il adopta la vision aristotélicienne des comètes comme phénomènes météorologiques. &lt;/p&gt; &lt;p&gt; Ses travaux portent sur la métaphysique (unité des formes), l'optique et l'astronomie, influencés par Alhazen et Aristote via Guillaume de Moerbeke. Il illustre la scolastique belge médiévale, entre averroïsme et thomisme. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_de_Lessines"   title=" Wikipedia"&gt;Gilles de LESSINES&lt;/a&gt; (vers 1230-après 1304) est un philosophe et savant dominicain, né à Lessines, dans le Hainaut, dans l’actuelle Belgique. Disciple d’&lt;a href="https://fr.wikipedia.org/wiki/Albert_le_Grand" title=" Wikipedia"&gt;Albert le Grand&lt;/a&gt; et proche de Thomas d’Aquin, il participe aux grands débats qui agitent l’université de Paris dans la seconde moitié du XIIIe siècle, et défend fidèlement la pensée thomiste.&lt;/p&gt; &lt;p&gt;Vers 1270, il envoie à Albert le Grand la liste de quinze thèses enseignées à Paris par les maîtres averroïstes, comme l’éternité du monde ou l’unité de l’intellect pour tous les hommes, et lui demande son avis : la réponse d’Albert, le traité &lt;em&gt;Sur les quinze problèmes&lt;/em&gt;, est un document majeur sur ces controverses. Après la mort de Thomas d’Aquin, plusieurs de ses thèses sont condamnées en 1277 à Oxford. Gilles prend sa défense en 1278 dans le traité &lt;em&gt;De l’unité de la forme&lt;/em&gt; : chaque être n’a qu’une seule forme substantielle, qui fait de lui ce qu’il est, et l’âme humaine est la forme unique du corps, contre ceux qui en multiplient les formes. Il s’intéresse aussi à la nature : dans un traité sur la comète de 1264, il explique, à la suite d’Aristote, que les comètes sont des phénomènes de l’atmosphère, et non des astres, et discute de leur signification. &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1920_num_22_86_2243"  title="Gilles de Lessines et son « Tractatus de Crepusculis » [ par Persée"&gt;Son traité sur le crépuscule&lt;/a&gt; étudie, à partir de l’opticien arabe Alhazen, la lumière du soir et du matin et la hauteur de l’atmosphère. On lui attribue enfin un traité sur l’usure, qui examine le prêt à intérêt.&lt;/p&gt; &lt;p&gt;Son œuvre montre la diversité de la scolastique du XIIIe siècle, où la théologie côtoie l’astronomie et l’optique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F52" s="30" t="inlineStr">
@@ -4194,8 +4192,7 @@
       </c>
       <c r="E55" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Matteo_d%27Acquasparta"  style="color:#6A142A"  title=" Wikipedia"&gt;Matteo d'ACQUASPARTA&lt;/a&gt; était un philosophe,  théologien  italien majeur du XIIIe siècle tardif. Né en Ombrie près de Terni, il s'est distingué comme &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1972_num_70_7_5687_t1_0438_0000_2" style="color:#88A1E9" title="Pasquale Mazzarella, La dottrina dell'anima e della conoscenza in Matteo d'Acquasparta par Persée"&gt;maître en théologie &lt;/a&gt; à l'université de Paris lors de la censure de 1277, avant d'occuper des postes élevés dans l'Église. Franciscain originaire d'Acquasparta, il étudie à Paris, Bologne et Oxford, enseigne la théologie et devient ministre général des Frères mineurs en 1287 et fut nommé cardinal-évêque de Porto en 1291 par Nicolas IV. &lt;/p&gt; &lt;p&gt; Ses écrits incluent des Quaestiones disputatae et quodlibétiques, traitant de la connaissance de soi, de l'âme et de la théologie. Des éditions récentes analysent ses quodlibets parisiens, soulignant son rôle dans le genre quodlibétique. &lt;/p&gt; &lt;p&gt; Il intègre l'héritage agostinien et bonaventurien avec des éléments aristotéliciens, explorant la connaissance de l'intellect et la certitude volontaire dans la foi. Sa pensée marque les débats sur l'épistémologie médiévale et la théologie franciscaine. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Matteo_d%27Acquasparta"  style="color:#6A142A"  title=" Wikipedia"&gt;Matteo d’ACQUASPARTA&lt;/a&gt; (vers 1240-1302) est un théologien et philosophe franciscain italien. Né en Ombrie, il entre très jeune chez les Frères mineurs, étudie à Paris et y devient &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1972_num_70_7_5687_t1_0438_0000_2" style="color:#88A1E9" title="Pasquale Mazzarella, La dottrina dell'anima e della conoscenza in Matteo d'Acquasparta par Persée"&gt;maître en théologie&lt;/a&gt; vers 1277, au moment où l’université est secouée par la condamnation de 219 thèses philosophiques. Il enseigne ensuite à la cour pontificale, à Rome, avant de devenir ministre général de son ordre en 1287, puis cardinal en 1288.&lt;/p&gt; &lt;p&gt;Matteo est l’un des principaux représentants de l’école franciscaine après saint Bonaventure, dont il reprend l’inspiration augustinienne tout en tenant compte d’Aristote. Ses &lt;em&gt;Questions disputées sur la foi et sur la connaissance&lt;/em&gt; examinent comment l’intellect humain atteint la vérité. Pour Aristote et Thomas d’Aquin, l’intellect tire ses idées des choses sensibles par abstraction. Matteo l’admet, mais il juge que cela ne suffit pas : une connaissance certaine et immuable exige, selon la tradition d’Augustin, une illumination de l’esprit par la lumière divine. Cette lumière ne remplace pas l’intellect humain, elle agit avec lui. Il défend aussi une connaissance directe des choses singulières et de l’âme par elle-même, et souligne le rôle de la volonté dans l’assentiment de la foi. Ses questions quodlibétiques, débats publics où le maître répondait à toute question posée par l’assistance, témoignent de la vitalité de la vie universitaire.&lt;/p&gt; &lt;p&gt;Légat du pape Boniface VIII, il tente en 1300 de réconcilier les factions qui déchirent Florence, sans succès. Dante le mentionne au Paradis, en lui reprochant d’avoir relâché la règle franciscaine.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F55" s="30" t="inlineStr">
@@ -5267,7 +5264,7 @@
       </c>
       <c r="E71" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_Durand_de_Saint-Pour%C3%A7ain"  style="color:#6A142A"  title=" Wikipedia"&gt;Guillaume DURAND de St Pourçain&lt;/a&gt;   fut un philosophe scolastique et théologien dominicain français surnommé le "Doctor resolutissimus" pour ses idées novatrices et son rejet de certaines thèses thomistes. &lt;/p&gt; &lt;p&gt;Il  s'opposa au réalisme aristotélicien de Thomas d'Aquin en adoptant un nominalisme précurseur de celui de Guillaume d'Occam, niant l'existence réelle des universaux au profit d'une appréhension directe du réel. Il défendit la  &lt;a href="https://www.persee.fr/doc/cafan_0575-061x_2012_act_45_1_2095" style="color:#88A1E9" title="        Le studium de la Curie pontificale et ses maîtres au temps de Jean XXII   par Persée"&gt;primauté de la raison &lt;/a&gt; sur l'autorité humaine, y compris celle d'Aristote, et rejeta des concepts scolastiques comme les espèces intelligibles ou un intellect agent séparé. Sa noétique met l'accent sur l'adéquation subjective entre l'objet perçu et l'expérience, inaugurant une période moderne de la scolastique. &lt;/p&gt; &lt;p&gt; Son œuvre majeure est un commentaire en trois recensions des Sentences de Pierre Lombard, édité à plusieurs reprises mais sans version critique moderne. Il rédigea aussi des quodlibeta et un traité sur la puissance temporelle des rois. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_Durand_de_Saint-Pour%C3%A7ain"  style="color:#6A142A"  title=" Wikipedia"&gt;Guillaume DURAND de St Pourçain&lt;/a&gt; (vers 1275-1334) est un théologien et philosophe dominicain français, né à Saint-Pourçain, en Auvergne. Surnommé le « docteur très résolu » (&lt;em&gt;Doctor resolutissimus&lt;/em&gt;), il est connu pour sa liberté d’esprit envers Thomas d’Aquin, pourtant devenu le maître officiel de son ordre.&lt;/p&gt; &lt;p&gt;Dans son commentaire des &lt;em&gt;Sentences&lt;/em&gt; de Pierre Lombard, le grand manuel de théologie de l’époque, il affirme qu’en tout ce qui ne touche pas à la foi, il vaut mieux suivre la raison que l’autorité d’un docteur, aussi célèbre soit-il. Il critique plusieurs thèses thomistes, ce qui lui vaut d’être censuré par son ordre en 1314 et 1316 ; il remanie son ouvrage à plusieurs reprises, si bien qu’il en existe trois versions. Selon lui, seuls existent réellement les individus : l’universel n’est qu’une manière dont l’intellect conçoit plusieurs choses semblables. Il rejette les « espèces intelligibles », ces images intermédiaires que les thomistes plaçaient entre l’objet et l’esprit : l’intellect connaît directement les choses. Ces thèses, proches du nominalisme, annoncent celles de Guillaume d’Ockham. Appelé à enseigner à la cour pontificale d’Avignon, au &lt;a href="https://www.persee.fr/doc/cafan_0575-061x_2012_act_45_1_2095" style="color:#88A1E9" title="        Le studium de la Curie pontificale et ses maîtres au temps de Jean XXII   par Persée"&gt;studium de la curie de Jean XXII&lt;/a&gt;, il devient ensuite évêque de Limoux, du Puy, puis de Meaux.&lt;/p&gt; &lt;p&gt;En 1329, il intervient dans le débat sur le pouvoir de l’Église et celui du roi de France, et il s’oppose en 1333 au pape Jean XXII sur la question de la vision de Dieu après la mort. Son indépendance d’esprit en fait l’une des figures de la fin de la scolastique.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F71" s="30" t="n"/>

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P119"/>
+  <dimension ref="A1:P120"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -1376,8 +1376,8 @@
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sylvestre_II"  style="color:#6A142A"  title=" Wikipedia"&gt; GERBERT d'Aurillac&lt;/a&gt;, également connu sous le nom du pape Sylvestre II, est une figure majeure du Moyen Âge, reconnu pour son érudition, ses contributions scientifiques et son influence politique. &lt;/p&gt;  &lt;p&gt; Il devient un enseignant renommé et attire des étudiants de toute l’Europe. Ses cours portent sur les arts libéraux &lt;a href="https://manuel-de-methodologie-historique.blog.tudchentil.org/trivium-et-quadrivium/" style="color:#88A1E9" title="Trivium et quadrivium par sfha "&gt;(le trivium et le quadrivium)&lt;/a&gt;, avec une attention particulière aux mathématiques, à l’astronomie et à la musique. &lt;/p&gt; 
-&lt;p&gt;Il est également connu pour avoir introduit en Europe l’usage de &lt;a href="https://alainbusser.github.io/primaire/html/gerbert1.html"  title="Abaque de Gebert "&gt;l’abaque de Gerbert&lt;/a&gt;, un outil de calcul inspiré des méthodes arabes, ainsi que pour avoir popularisé le chiffrement arabe (les chiffres dits "arabes", bien que leur adoption généralisée en Europe ait pris plusieurs siècles). &lt;/p&gt; &lt;p&gt; En 999, il est élu pape sous le nom de Sylvestre II. Il cherche à renforcer l’autorité papale et à réformer l’Église, soutient les efforts d’Otton III pour unifier l’Europe sous un empire chrétien et encourage les études scientifiques et la diffusion des connaissances. &lt;/p&gt;  &lt;p&gt; Il est souvent surnommé le &lt;a href="https://www.youtube.com/watch?v=onfmvvXjk08" title="Gebert d'Aurrillac par palacky "&gt;"pape savant" &lt;/a&gt;ou le "pape mathématicien". Son œuvre a joué un rôle clé dans la transmission des connaissances antiques et arabes à l’Europe médiévale, préparant le terrain pour la Renaissance du XIIe siècle. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sylvestre_II"  style="color:#6A142A"  title=" Wikipedia"&gt; GERBERT d'Aurillac&lt;/a&gt;, également connu sous le nom du pape Sylvestre II, est une figure majeure du Moyen Âge, reconnu pour son érudition, ses contributions scientifiques et son influence politique. &lt;/p&gt;  &lt;p&gt; Il devient un enseignant renommé et attire des étudiants de toute l’Europe. Ses cours portent sur les arts libéraux &lt;a href="https://manuel-de-methodologie-historique.blog.tudchentil.org/trivium-et-quadrivium/" style="color:#88A1E9" title="Trivium et quadrivium par sfha "&gt;(le trivium et le quadrivium)&lt;/a&gt;, avec une attention particulière aux mathématiques, à l’astronomie et à la musique. &lt;/p&gt; 
+&lt;p&gt;Il est également connu pour avoir introduit en Europe l’usage de &lt;a href="https://alainbusser.github.io/primaire/html/gerbert1.html"  title="Abaque de Gebert "&gt;l’abaque de Gerbert&lt;/a&gt;, un outil de calcul inspiré des méthodes arabes, ainsi que pour avoir popularisé le chiffrement arabe (les chiffres dits "arabes", bien que leur adoption généralisée en Europe ait pris plusieurs siècles). &lt;/p&gt; &lt;p&gt; En 999, il est élu pape sous le nom de Sylvestre II. Il cherche à renforcer l’autorité papale et à réformer l’Église, soutient les efforts d’Otton III pour unifier l’Europe sous un empire chrétien et encourage les études scientifiques et la diffusion des connaissances. &lt;/p&gt;  &lt;p&gt; Il est souvent surnommé le &lt;a href="https://www.youtube.com/watch?v=onfmvvXjk08" title="Gebert d'Aurrillac par palacky "&gt;"pape savant" &lt;/a&gt;ou le "pape mathématicien". Son œuvre a joué un rôle clé dans la transmission des connaissances antiques et arabes à l’Europe médiévale, préparant le terrain pour la Renaissance du XIIe siècle. Né en Auvergne vers 945, moine au monastère d’Aurillac, il part étudier en Catalogne, proche des savoirs de l’Espagne musulmane. Maître de l’école de la cathédrale de Reims, il enseigne la logique d’Aristote et de Boèce. Précepteur du futur empereur Otton III, il devient archevêque de Reims, puis de Ravenne, avant d’être le premier pape français. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="E41" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Pagus"  title=" Wikipedia"&gt;Jean PAGUS&lt;/a&gt;   était un philosophe scolastique français maître ès arts parisien, actif dans les premières décennies de l'université de Paris. Peu documenté, il incarne les figures obscures des écoles médiévales qui ont contribué à l'essor des arts libéraux avant la pleine structuration universitère. Il enseigne à Paris durant la période de genèse de l'université (1200-1231), marquée par l'arrivée de l'aristote latin et les tensions avec l'Église. Il fait partie d'une cohorte de magistri internationaux favorisant la méritocratie scolaire et la diffusion du savoir profane. &lt;/p&gt; &lt;p&gt; Ses écrits exacts restent mal connus, mais il est cité dans des contextes doctrinaux mêlant théologie et philosophie, notamment sur l'autorité des Écritures et de la tradition. Associé à des débats scolastiques précoces, il préfigure les querelles entre averroïstes et thomistes. &lt;/p&gt; &lt;p&gt; Malgré sa notoriété éphémère, il illustre le foisonnement des maîtres parisiens avant 1231, reliant les écoles du XIIe siècle à l'âge d'or de la scolastique. Son obscurity relative contraste avec des contemporains comme Pierre de Capoue ou les Anglais influents. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Pagus"  title=" Wikipedia"&gt;Jean PAGUS&lt;/a&gt;, en latin Johannes Pagus (vers 1205-vers 1265), est un maître de l’université de Paris, l’un des logiciens les plus importants de la première moitié du XIIIe siècle. Maître ès arts vers 1230-1240, il enseigne la logique à la faculté des arts, avant de devenir maître en théologie et de commenter, comme tous les théologiens de son temps, les &lt;em&gt;Sentences&lt;/em&gt; de Pierre Lombard.&lt;/p&gt; &lt;p&gt;Son époque est celle où les œuvres d’Aristote, récemment traduites du grec et de l’arabe, entrent dans l’enseignement parisien, malgré les interdictions qui frappent d’abord ses livres sur la nature. La logique, elle, est au cœur des études : tout étudiant doit apprendre à définir, à distinguer et à argumenter. Jean Pagus commente l’&lt;em&gt;Isagoge&lt;/em&gt; de Porphyre et les &lt;em&gt;Catégories&lt;/em&gt; d’Aristote, mais il est surtout connu pour ses traités sur les propriétés des termes, en particulier l’« appellation », qui étudie à quels objets existants un mot s’applique dans une phrase donnée. Ces recherches font partie de la « logique des modernes », l’invention propre des logiciens médiévaux, qui analysent finement le langage, bien au-delà de ce qu’avait fait Aristote. Elles posent des questions encore discutées aujourd’hui : un nom désigne-t-il les choses présentes seulement, ou aussi les choses passées et futures ? De quoi parle une phrase sur un être qui n’existe plus ?&lt;/p&gt; &lt;p&gt;Ses travaux ont nourri ceux de ses successeurs, comme Pierre d’Espagne, dont le manuel de logique deviendra un classique pour trois siècles. Jean Pagus illustre ainsi la vitalité de l’université de Paris à ses débuts.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F41" s="30" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="E42" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Kilwardby"   title=" Wikipedia"&gt;Robert KILWARDBY&lt;/a&gt;  était un philosophe dominicain britanique, étudiant à l'université de Paris dès 1231, il devient magister artium en 1237, réputé en grammaire et logique. Il rejoint les dominicains vers 1245, enseigne la théologie à Oxford et obtient le titre de &lt;a href="https://www.youtube.com/watch?v=OnrD7r4BLqc" title="Robert Kilwardby par See Hear Say Learn"&gt;magister regens &lt;/a&gt; en 1256. &lt;/p&gt; &lt;p&gt; Prieur provincial des dominicains en Angleterre de 1261 à 1272, il est nommé archevêque de Cantorbéry en 1273 par le pape Grégoire X. En 1277, il émet des condamnations contre 30 propositions philosophiques à Oxford. Élevé cardinal-évêque de Porto en 1278, il meurt l'année suivante en Italie. &lt;/p&gt; &lt;p&gt; Conservateur éclectique, il défend l'unité augustinienne contre l'aristotélisme radical, notamment l'unité de la forme chez l'homme. Ses travaux portent sur la logique, l'épistémologie, la théologie trinitaire et la résolution des tensions entre Aristote et les Pères de l'Église. Auteur prolifique, ses écrits incluent &lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1981_num_35_1_1210_t1_0147_0000_3" style="color:#88A1E9" title="Robert Kilwardby, O.P. De Ortu scientiarum edited by Albert G par Persée"&gt;"De ortu scientiarum"&lt;/a&gt; sur la classification des sciences, "De tempore", des commentaires sur Aristote, Boèce et les Sentences de Pierre Lombard, ainsi que des abrégés patristiques comme "Tabulae super Originalia Patrum". &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Kilwardby"   title=" Wikipedia"&gt;Robert KILWARDBY&lt;/a&gt;  était un philosophe dominicain anglais, étudiant à l'université de Paris dès 1231, il devient magister artium en 1237, réputé en grammaire et logique. Il rejoint les dominicains vers 1245, enseigne la théologie à Oxford et obtient le titre de &lt;a href="https://www.youtube.com/watch?v=OnrD7r4BLqc" title="Robert Kilwardby par See Hear Say Learn"&gt;magister regens &lt;/a&gt; en 1256. &lt;/p&gt; &lt;p&gt; Prieur provincial des dominicains en Angleterre de 1261 à 1272, il est nommé archevêque de Cantorbéry en 1273 par le pape Grégoire X. En 1277, il émet des condamnations contre 30 propositions philosophiques à Oxford. Élevé cardinal-évêque de Porto en 1278, il meurt l'année suivante en Italie. &lt;/p&gt; &lt;p&gt; Conservateur éclectique, il défend l'unité augustinienne contre l'aristotélisme radical, notamment l'unité de la forme chez l'homme. Ses travaux portent sur la logique, l'épistémologie, la théologie trinitaire et la résolution des tensions entre Aristote et les Pères de l'Église. Auteur prolifique, ses écrits incluent &lt;a href="https://www.persee.fr/doc/scrip_0036-9772_1981_num_35_1_1210_t1_0147_0000_3" style="color:#88A1E9" title="Robert Kilwardby, O.P. De Ortu scientiarum edited by Albert G par Persée"&gt;"De ortu scientiarum"&lt;/a&gt; sur la classification des sciences, "De tempore", des commentaires sur Aristote, Boèce et les Sentences de Pierre Lombard, ainsi que des abrégés patristiques comme "Tabulae super Originalia Patrum". Archevêque de Cantorbéry, il fait condamner à Oxford, le 18 mars 1277, trente propositions parmi lesquelles la thèse thomiste de l’unité de la forme substantielle : un dominicain condamnait ainsi une doctrine de Thomas d’Aquin ce qui fit grand bruit dans l’ordre. Dans un traité sur l’imagination, il défend aussi une théorie active de la perception : l’âme n’est pas passivement marquée par les objets, elle produit elle-même ses images à leur occasion. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4125,7 +4125,7 @@
       </c>
       <c r="E54" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Siger_de_Brabant"  style="color:#6A142A"  title=" Wikipedia"&gt;Siger de BRABANT&lt;/a&gt; était un philosophe français,  figure centrale de l'aristotélisme radical ou averroïsme latin. Leader d'un groupe enseignant un aristotélisme pur, sans compromis avec la foi chrétienne, il défendit des  &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1931_num_33_30_2612" style="color:#88A1E9" title="Siger de Brabant et la doctrine de la double vérité  par Persée"&gt;thèses controversées &lt;/a&gt; comme l'éternité du monde et l'unicité de l'intellect pour toute l'humanité. Condamné en 1270 et 1277 par l'évêque Étienne Tempier pour hérésie, il incarna la tension entre raison philosophique et théologie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Il posa la primauté de la raison philosophique sur la révélation, affirmant l'unité de l'intellect agent pour l'humanité, rendant l'individu mortel mais l'espèce éternelle. Il défendit &lt;a href="https://www.youtube.com/watch?v=P6i1aYrQQ9c" style="color:#88A1E9" title="L'esprit médiéval  par HvT"&gt;l'autonomie &lt;/a&gt; de la philosophie, l'éternité du monde et le déterminisme, rejetant la création ex nihilo et la Providence totale. Critiquant l'infaillibilité papale en affaires temporelles, il privilégiait les bonnes lois aux bons rulers. &lt;/p&gt; &lt;p&gt; Ses écrits incluent "De anima intellectiva"  paru en 1270 sur l'âme intellective unique et éternelle, "Quaestiones in metaphysicam", "Impossibilia" (exercices de sophisme) et des questions sur la logique, la physique et l'éternité du monde. Ces textes, publiés par Pierre Mandonnet en 1899, explorent la métaphysique aristotélicienne influencée par Averroès, Avicenne et Proclus. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Siger_de_Brabant"  style="color:#6A142A"  title=" Wikipedia"&gt;Siger de BRABANT&lt;/a&gt; était un philosophe brabançon, maître à la faculté des arts de Paris,  figure centrale de l'aristotélisme radical ou averroïsme latin. Leader d'un groupe enseignant un aristotélisme pur, sans compromis avec la foi chrétienne, il défendit des  &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1931_num_33_30_2612" style="color:#88A1E9" title="Siger de Brabant et la doctrine de la double vérité  par Persée"&gt;thèses controversées &lt;/a&gt; comme l'éternité du monde et l'unicité de l'intellect pour toute l'humanité. Condamné en 1270 et 1277 par l'évêque Étienne Tempier pour hérésie, il incarna la tension entre raison philosophique et théologie au XIIIe siècle. &lt;/p&gt; &lt;p&gt; Il posa la primauté de la raison philosophique sur la révélation, affirmant l'unité de l'intellect agent pour l'humanité, rendant l'individu mortel mais l'espèce éternelle. Il défendit &lt;a href="https://www.youtube.com/watch?v=P6i1aYrQQ9c" style="color:#88A1E9" title="L'esprit médiéval  par HvT"&gt;l'autonomie &lt;/a&gt; de la philosophie, l'éternité du monde et le déterminisme, rejetant la création ex nihilo et la Providence totale. En politique, il se demandait s'il vaut mieux être gouverné par un bon roi ou par de bonnes lois. &lt;/p&gt; &lt;p&gt; Ses écrits incluent "De anima intellectiva"  paru en 1270 sur l'âme intellective unique et éternelle, "Quaestiones in metaphysicam", "Impossibilia" (exercices de sophisme) et des questions sur la logique, la physique et l'éternité du monde. Ces textes, publiés par Pierre Mandonnet en 1899, explorent la métaphysique aristotélicienne influencée par Averroès, Avicenne et Proclus. &lt;/p&gt; Cité devant l’inquisiteur de France en 1276, il se réfugie auprès de la cour pontificale et meurt à Orvieto vers 1284, poignardé par son secrétaire devenu fou. Dante le place au Paradis, aux côtés de Thomas d’Aquin : il y voit le symbole de la liberté de la raison. 
 </t>
         </is>
       </c>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E64" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herv%C3%A9_N%C3%A9dellec"   title=" Wikipedia"&gt;Hervé NÉDELLEC&lt;/a&gt;   était un théologien et philosophe breton et  appartient à la haute scolastique, au moment où les débats sur Aristote, l’averroïsme latin, Thomas d’Aquin et les rapports entre raison et foi sont particulièrement vifs. &lt;/p&gt; &lt;p&gt; Il intervient dans les grandes controverses universitaires parisiennes (notamment autour des ordres mendiants, de l’autorité pontificale et de la théologie comme science), aux côtés de maîtres séculiers comme Henri de Gand ou Godefroid de Fontaines. &lt;/p&gt; &lt;p&gt; Dominical et thomiste, il se présente comme un défenseur de la pensée de Thomas d’Aquin face à ses critiques, cherchant à préciser et systématiser le thomisme naissant. Sa réflexion sur des notions comme intentio (tension ou orientation vers un objet) et sur la nature de l’intellect montre une attention fine à la psychologie philosophique et à la théorie de la connaissance dans le cadre aristotélicien christianisé. &lt;/p&gt; &lt;p&gt; Les notices modernes recensent une quinzaine de textes, principalement des commentaires théologiques et des questions disputées, typiques de la méthode scolastique. Il reste une référence pour l’histoire du thomisme primitif et pour l’étude des débats médiévaux sur l’intellect, la volonté et l’autorité ecclésiale, mais demeure peu connu du grand public. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Herv%C3%A9_N%C3%A9dellec"   title=" Wikipedia"&gt;Hervé NÉDELLEC&lt;/a&gt;   était un théologien et philosophe breton et  appartient à la haute scolastique, au moment où les débats sur Aristote, l’averroïsme latin, Thomas d’Aquin et les rapports entre raison et foi sont particulièrement vifs. &lt;/p&gt; &lt;p&gt; Il intervient dans les grandes controverses universitaires parisiennes (notamment autour des ordres mendiants, de l’autorité pontificale et de la théologie comme science), face à des maîtres séculiers comme Henri de Gand ou Godefroid de Fontaines. &lt;/p&gt; &lt;p&gt; Dominicain et thomiste, il se présente comme un défenseur de la pensée de Thomas d’Aquin face à ses critiques, cherchant à préciser et systématiser le thomisme naissant. Sa réflexion sur des notions comme intentio (tension ou orientation vers un objet) et sur la nature de l’intellect montre une attention fine à la psychologie philosophique et à la théorie de la connaissance dans le cadre aristotélicien christianisé. &lt;/p&gt; &lt;p&gt; Les notices modernes recensent une quinzaine de textes, principalement des commentaires théologiques et des questions disputées, typiques de la méthode scolastique. Il reste une référence pour l’histoire du thomisme primitif et pour l’étude des débats médiévaux sur l’intellect, la volonté et l’autorité ecclésiale, mais demeure peu connu du grand public. &lt;/p&gt; Maître en théologie à Paris vers 1307, il devient en 1318 maître général de l’ordre dominicain et œuvre activement pour la canonisation de Thomas d’Aquin, prononcée en 1323, l’année de sa mort. Il s’oppose aussi à son confrère Durand de Saint-Pourçain, dont il fait censurer les thèses antithomistes. </t>
         </is>
       </c>
       <c r="F64" s="30" t="inlineStr">
@@ -5059,10 +5059,7 @@
       </c>
       <c r="E68" s="32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dante_Alighieri"  title=" Wikipedia"&gt;DANDE Alighieri&lt;/a&gt; est un poète, écrivain et homme politique florentin, considéré comme le père de la langue italienne et l'un des plus grands auteurs de la littérature mondiale. &lt;/p&gt; &lt;p&gt;Son œuvre majeure, &lt;a href="https://www.youtube.com/watch?v=TkG-Pw47J-s"  title="La Divine Comedie par Histoire et Mythologie en BD"&gt;La Divine Comédie&lt;/a&gt;, est un poème épique allégorique qui raconte le voyage de Dante à travers l'Enfer, &lt;a href="https://www.youtube.com/watch?v=c9DtM28fJUM"  title="Le Purgatoire Angoissant de Dante par Histoire et Mythologie en BD"&gt;le Purgatoire&lt;/a&gt; et &lt;a href="https://www.youtube.com/watch?v=lZDbNpP1wVw" title="Le Paradis de Dante par See Uin History"&gt;le Paradis&lt;/a&gt;. Ce poème, écrit en tercets enchaînés, est une œuvre monumentale qui aborde les thèmes de l'amour, de la mort, du péché, de la rédemption et de la justice divine. Dante y décrit sa vision de l'au-delà, inspirée par la théologie chrétienne et la philosophie antique. &lt;/p&gt;
-&lt;p&gt; L'Enfer est un lieu de souffrance éternelle où les âmes des damnés sont punies pour leurs péchés. Le Purgatoire est un lieu de purification où les âmes des pécheurs repentis se préparent à entrer au Paradis. Le Paradis est le lieu de béatitude éternelle où les âmes des justes contemplent la gloire de Dieu.  Il est également l'auteur d'autres œuvres importantes, notamment : &lt;/p&gt; &lt;dd&gt; Vita Nuova: un recueil de poèmes et de prose qui célèbre l'amour de Dante pour Béatrice. &lt;/dd&gt; &lt;dd&gt;
-Convivio: un traité philosophique inachevé. &lt;/dd&gt; &lt;dd&gt;
-De Vulgari Eloquentia: un essai sur la langue vulgaire italienne. &lt;/dd&gt;  &lt;p&gt; &lt;/p&gt;  &lt;audio controls title=""Quelques foulés au Purgatoire par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14484-11.03.2019-ITEMA_22005109-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Dante_Alighieri"  title=" Wikipedia"&gt;DANTE Alighieri&lt;/a&gt; (1265-1321) est un poète, philosophe et homme politique florentin, considéré comme le père de la langue italienne et l’un des plus grands écrivains de tous les temps. Jeune homme, il voue un amour idéal à Béatrice, qu’il célèbre dans la &lt;em&gt;Vie nouvelle&lt;/em&gt;. Engagé dans la vie politique de Florence, il est exilé en 1302 par la faction adverse et ne reverra jamais sa ville ; il meurt à Ravenne.&lt;/p&gt; &lt;p&gt;Nourri d’Aristote, de Thomas d’Aquin et des philosophes arabes, Dante est aussi un penseur. Dans le &lt;em&gt;Banquet&lt;/em&gt; (&lt;em&gt;Convivio&lt;/em&gt;), il veut offrir en langue italienne, et non en latin, la nourriture de la philosophie à ceux qui n’ont pas pu étudier. Dans &lt;em&gt;De l’éloquence en langue vulgaire&lt;/em&gt;, il défend la dignité de la langue parlée. Dans la &lt;em&gt;Monarchie&lt;/em&gt;, il soutient que l’humanité a besoin d’un empereur universel pour garantir la paix, et que son pouvoir vient directement de Dieu, non du pape : l’Église et l’Empire ont deux missions distinctes, le salut éternel et le bonheur terrestre. Son chef-d’œuvre, &lt;a href="https://www.youtube.com/watch?v=TkG-Pw47J-s"  title="La Divine Comedie par Histoire et Mythologie en BD"&gt;&lt;em&gt;La Divine Comédie&lt;/em&gt;&lt;/a&gt;, raconte son voyage à travers l’Enfer, &lt;a href="https://www.youtube.com/watch?v=c9DtM28fJUM"  title="Le Purgatoire Angoissant de Dante par Histoire et Mythologie en BD"&gt;le Purgatoire&lt;/a&gt; et &lt;a href="https://www.youtube.com/watch?v=lZDbNpP1wVw" title="Le Paradis de Dante par See Uin History"&gt;le Paradis&lt;/a&gt;, guidé par le poète Virgile, figure de la raison, puis par Béatrice, figure de la grâce. Le poème est une somme du savoir de son temps. Dante y place les grands philosophes païens, Aristote, « le maître de ceux qui savent », Socrate et Platon, dans les limbes, et fait parler au Paradis Thomas d’Aquin et Siger de Brabant. Le poème s’achève sur « l’amour qui meut le soleil et les autres étoiles ».&lt;/p&gt; &lt;p&gt;Son œuvre a fixé la langue italienne et inspiré poètes, peintres et penseurs jusqu’à nos jours.&lt;/p&gt;  &lt;audio controls title="Quelques foulées au Purgatoire par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/14484-11.03.2019-ITEMA_22005109-0.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;</t>
         </is>
       </c>
       <c r="F68" s="30" t="inlineStr">
@@ -6332,7 +6329,7 @@
       </c>
       <c r="E87" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Rimini"  title=" Wikipedia"&gt;Grégoire de RIMINI&lt;/a&gt;  était un  théologien et philosophe scolastique italien, figure majeure de l'augustinianisme et du nominalisme modéré.  Il fut un ermite de saint Augustin influent, surnommé Doctor Acutus pour son esprit pénétrant. &lt;/p&gt; &lt;p&gt; Fidèle à saint Augustin, il défend une prédestination divine stricte et critique le semi-pélagianisme de Pierre Auriol. Il développe une théorie des phrases complexes, ni extra-mentales ni purement propositionnelles, pour fonder la connaissance scientifique sans objets abstraits réels. Nominaliste, il rejette les universaux comme entités physiques et nie l'infini en acte dans le réel, réservant les abstractions à la convention mentale. &lt;/p&gt; &lt;p&gt; Son commentaire sur les deux premiers livres des Sentences (1342-1344) reste son  &lt;a href="https://www.youtube.com/watch?v=C4UsF2baXQI" title="Gregory of Rimini: The Last Great Scholastic  par Philosopher Friends"&gt;œuvre majeure, &lt;/a&gt;  mêlant théologie, métaphysique et épistémologie. Il rédige aussi des tables analytiques sur Augustin et des écrits sur l'usure, influençant la pensée tardomédiévale jusqu'à la Réforme. &lt;/p&gt; &lt;p&gt; Il  unit les traditions oxonienne et parisienne, impactant des penseurs ultérieurs comme Luther, qui le cita favorablement. Son œuvre illustre les tensions entre toute-puissance divine, connaissance humaine et réalité physique au cœur de la scolastique du XIVᵉ siècle. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Rimini"  title=" Wikipedia"&gt;Grégoire de RIMINI&lt;/a&gt;  était un  théologien et philosophe scolastique italien, figure majeure de l'augustinianisme et du nominalisme modéré.  Il fut un ermite de saint Augustin influent, surnommé Doctor Acutus pour son esprit pénétrant. &lt;/p&gt; &lt;p&gt; Fidèle à saint Augustin, il défend une prédestination divine stricte et critique le semi-pélagianisme de Pierre Auriol. Il développe la théorie du « complexe signifiable » : ce que l'on sait n'est ni une chose extérieure ni une phrase de l'esprit, mais ce que signifie la proposition vraie, par exemple « que l'homme est un animal », pour fonder la connaissance scientifique sans objets abstraits réels. Nominaliste, il rejette les universaux comme entités physiques et nie l'infini en acte dans le réel, réservant les abstractions à la convention mentale. &lt;/p&gt; &lt;p&gt; Son commentaire sur les deux premiers livres des Sentences (1342-1344) reste son  &lt;a href="https://www.youtube.com/watch?v=C4UsF2baXQI" title="Gregory of Rimini: The Last Great Scholastic  par Philosopher Friends"&gt;œuvre majeure, &lt;/a&gt;  mêlant théologie, métaphysique et épistémologie. Il rédige aussi des tables analytiques sur Augustin et des écrits sur l'usure, influençant la pensée tardomédiévale jusqu'à la Réforme. &lt;/p&gt; &lt;p&gt; Il  unit les traditions oxonienne et parisienne, impactant des penseurs ultérieurs comme Luther, qui le cita favorablement. Son œuvre illustre les tensions entre toute-puissance divine, connaissance humaine et réalité physique au cœur de la scolastique du XIVᵉ siècle. Prieur général de son ordre en 1357, il meurt l’année suivante. Sa rigueur augustinienne lui valut un surnom terrible, « le bourreau des enfants », parce qu’il soutenait que les enfants morts sans baptême étaient damnés. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F87" s="30" t="inlineStr">
@@ -6858,8 +6855,8 @@
       </c>
       <c r="E95" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Coluccio_Salutati"  title=" Wikipedia"&gt;Coluccio SALUTATI&lt;/a&gt; était un philosophe et homme politique italien considéré comme une figure de référence de la Renaissance culturelle florentine. Il avécu pendant une période de transition entre le Moyen Âge et la Renaissance, marquée par un regain d'intérêt pour les textes antiques et les valeurs civiques. Il a contribué à poser les bases de l'humanisme florentin. &lt;/p&gt; &lt;p&gt; Il a encouragé la traduction et l'étude des œuvres de Cicéron, Sénèque et d'autres auteurs antiques et a promu l'étude de la grammaire, de la rhétorique, de l'histoire et de la philosophie morale, fondements de l'éducation humaniste. Contrairement à Pétrarque, qui privilégiait la retraite studieuse, il a défendu l'engagement civique et l'action politique comme voie vers la vertu et a toujours cherché à concilier philosophie antique et théologie, préfigurant des penseurs comme Marsile Ficin.  Ses oeuvres majeures : &lt;/p&gt; &lt;p&gt;-  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1956_num_54_44_4898_t1_0629_0000_2" title="Coluccio Salutati, De nobilitate legum et medicinae, De verecundia par Persée"&gt;De nobilitate legum et medicinae &lt;/a&gt; : Défend la supériorité du droit sur la médecine. &lt;/p&gt; 
-&lt;p&gt; - De fato, fortuna et casu : Réflexion sur le libre arbitre. &lt;/p&gt; &lt;p&gt;Il incarne le passage de la culture médiévale à  &lt;a href="https://www.youtube.com/watch?v=UCODGnN8Vck"  title=" Coluccio Salutati: El Humanista que Forjó el Renacimiento en Italia par Revista Literaria"&gt;l'humanisme renaissant&lt;/a&gt;, en mêlant érudition classique, engagement politique et  &lt;a href="https://www.persee.fr/doc/efr_0223-5099_2009_act_423_1_9790#:~:text=%C3%94%20hommes%20au%20milieu%20desquels,peut%20trouver%20la%20vie%20solitaire!" title=" Coluccio Salutati et Santa Maria degli Angeli par Persée"&gt;foi chrétienne&lt;/a&gt;. Son rôle administratif et intellectuel a fait de Florence un foyer culturel essentiel. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Coluccio_Salutati"  title=" Wikipedia"&gt;Coluccio SALUTATI&lt;/a&gt; était un philosophe et homme politique italien considéré comme une figure de référence de la Renaissance culturelle florentine. Il a vécu pendant une période de transition entre le Moyen Âge et la Renaissance, marquée par un regain d'intérêt pour les textes antiques et les valeurs civiques. Il a contribué à poser les bases de l'humanisme florentin. &lt;/p&gt; &lt;p&gt; Il a encouragé la traduction et l'étude des œuvres de Cicéron, Sénèque et d'autres auteurs antiques et a promu l'étude de la grammaire, de la rhétorique, de l'histoire et de la philosophie morale, fondements de l'éducation humaniste. Contrairement à Pétrarque, qui privilégiait la retraite studieuse, il a défendu l'engagement civique et l'action politique comme voie vers la vertu et a toujours cherché à concilier philosophie antique et théologie, préfigurant des penseurs comme Marsile Ficin.  Ses oeuvres majeures : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1956_num_54_44_4898_t1_0629_0000_2" title="Coluccio Salutati, De nobilitate legum et medicinae, De verecundia par Persée"&gt;De nobilitate legum et medicinae &lt;/a&gt; : Défend la supériorité du droit sur la médecine. &lt;/p&gt; 
+&lt;p&gt;&lt;em&gt;De fato, fortuna et casu&lt;/em&gt; : Réflexion sur le libre arbitre. &lt;/p&gt; &lt;p&gt;Il incarne le passage de la culture médiévale à  &lt;a href="https://www.youtube.com/watch?v=UCODGnN8Vck"  title=" Coluccio Salutati: El Humanista que Forjó el Renacimiento en Italia par Revista Literaria"&gt;l'humanisme renaissant&lt;/a&gt;, en mêlant érudition classique, engagement politique et  &lt;a href="https://www.persee.fr/doc/efr_0223-5099_2009_act_423_1_9790#:~:text=%C3%94%20hommes%20au%20milieu%20desquels,peut%20trouver%20la%20vie%20solitaire!" title=" Coluccio Salutati et Santa Maria degli Angeli par Persée"&gt;foi chrétienne&lt;/a&gt;. Son rôle administratif et intellectuel a fait de Florence un foyer culturel essentiel. &lt;/p&gt; Chancelier de la république de Florence de 1375 à sa mort, il rédige des lettres officielles d’une telle éloquence que le duc de Milan les disait plus redoutables qu’un corps de cavalerie. Il fait venir à Florence, en 1397, le savant byzantin Manuel Chrysoloras pour y enseigner le grec. 
 </t>
         </is>
       </c>
@@ -6926,7 +6923,7 @@
       </c>
       <c r="E96" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_d%27Inghen"  title=" Wikipedia"&gt;MARSILLEd'Inghen&lt;/a&gt;  était un philosophe néerlandais du bas Moyen Âge, figure majeure du nominalisme scolastique, élève de Jean Buridan, Albert de Saxe et Nicole Oresme à l'université de Paris. Chassé de Paris en 1379 en raison du Grand Schisme d'Occident, il fonde en 1386 l'université de Heidelberg, dont il est recteur à neuf reprises jusqu'à sa mort en 1396. &lt;/p&gt; &lt;p&gt; Nominaliste arriéré, il affirme que les universaux n'existent que dans l'esprit humain, seule existe la réalité des individus sensibles et la connaissance scientifique porte sur des propositions mentales universelles et nécessaires. &lt;/p&gt; &lt;p&gt; Prolifique en traités sur la supposition des termes, les conséquences, les insolubles et l'épistémologie, il suit Buridan dans une méthode logico-sémantique rigoureuse. &lt;/p&gt; &lt;p&gt; En physique, il développe la théorie de l'impetus contre Aristote, voyant les forces comme des qualités transférées d'un objet à un autre. Il traite des idées divines comme objectivement distinctes en Dieu, sans distinction formelle, influencé par les franciscains. &lt;/p&gt; &lt;p&gt; Sa théologie, mêlant Ockham, Buridan, Thomas d'Aquin et Bonaventure, insiste sur la simplicité divine et une connaissance partielle de Dieu via la philosophie naturelle. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_d%27Inghen"  title=" Wikipedia"&gt;MARSILE d'Inghen&lt;/a&gt;  était un philosophe néerlandais du bas Moyen Âge, figure majeure du nominalisme scolastique, élève de Jean Buridan, Albert de Saxe et Nicole Oresme à l'université de Paris. Chassé de Paris en 1379 en raison du Grand Schisme d'Occident, il devient en 1386 le premier recteur de la nouvelle université de Heidelberg, dont il est recteur à neuf reprises jusqu'à sa mort en 1396. &lt;/p&gt; &lt;p&gt; Nominaliste modéré, il affirme que les universaux n'existent que dans l'esprit humain, seule existe la réalité des individus sensibles et la connaissance scientifique porte sur des propositions mentales universelles et nécessaires. &lt;/p&gt; &lt;p&gt; Prolifique en traités sur la supposition des termes, les conséquences, les insolubles et l'épistémologie, il suit Buridan dans une méthode logico-sémantique rigoureuse. &lt;/p&gt; &lt;p&gt; En physique, il développe la théorie de l'impetus contre Aristote, voyant les forces comme des qualités transférées d'un objet à un autre. Il traite des idées divines comme objectivement distinctes en Dieu, sans distinction formelle, influencé par les franciscains. &lt;/p&gt; &lt;p&gt; Sa théologie, mêlant Ockham, Buridan, Thomas d'Aquin et Bonaventure, insiste sur la simplicité divine et une connaissance partielle de Dieu via la philosophie naturelle. Recteur de l’université de Paris à deux reprises avant son départ, il fait de Heidelberg un foyer de la « voie moderne », la logique et la philosophie naturelle issues d’Ockham et de Buridan. Ses manuels de logique sont enseignés dans les universités d’Europe centrale jusqu’au XVIe siècle. Il distingue clairement ce que la raison peut démontrer et ce que seule la foi enseigne. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -7472,9 +7469,7 @@
       </c>
       <c r="E104" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Poggio_Bracciolini"  title=" Wikipedia"&gt;Poggio BRACCIOLINI&lt;/a&gt; était un philosophe humaniste, écrivain et homme politique italien principalement connu pour son rôle dans la redécouverte de &lt;a href="https://essentiels.bnf.fr/fr/extrait/a1bd507f-5631-4eb6-a966-107ea642dd9d-poggio-bracciolini-sauveur-livres-oublies" style="color:#88A1E9" title=" Poggio Bracciolini, sauveur de livres oubliés ? par BnF"&gt;textes anciens&lt;/a&gt; perdus. Il est célèbre pour avoir exhumé des œuvres majeures de l'Antiquité, notamment : &lt;/p&gt; 
-&lt;p&gt; - "De rerum natura" de Lucrèce ainsi que des discours de Cicéron, perdus depuis des siècles et des ouvrages de Quintilien, Vitruve et d'autres auteurs classiques.  &lt;a href="https://www.youtube.com/watch?v=6zg6zhBsJf4" style="color:#88A1E9" title=" Poggio Bracciolini: Travel and Treasure Hunting in the Age of Humanism par TheBiflorence"&gt;Ses découvertes &lt;/a&gt; ont eu un impact immense sur la philosophie, la science et la littérature de la Renaissance, en particulier en diffusant des idées épicuriennes et stoïciennes.  Il a aussi écrit différents textes dont : &lt;/p&gt; &lt;p&gt; -"De l’avarice" ("De avaritia") : Un dialogue critique sur la cupidité dans la société de son temps. &lt;/p&gt; &lt;p&gt; - "Facéties" ("Liber facetiarum") : Un recueil d'histoires satiriques et grivoises, souvent critiques envers le clergé. &lt;/p&gt; &lt;p&gt; - "De la noblesse" : Une réflexion sur la vraie nature de la noblesse (mérite vs. naissance). &lt;/p&gt; &lt;p&gt; Il était connu pour son esprit vif et ses controverses, notamment avec d'autres humanistes comme Lorenzo Valla.  Ses écrits mêlaient érudition, ironie et parfois une morale ambiguë, reflétant les tensions entre christianisme et pensée antique. &lt;/p&gt; 
-</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Poggio_Bracciolini"  title=" Wikipedia"&gt;Poggio BRACCIOLINI&lt;/a&gt;, dit le Pogge (1380-1459), est un humaniste italien, célèbre pour avoir retrouvé de nombreux &lt;a href="https://essentiels.bnf.fr/fr/extrait/a1bd507f-5631-4eb6-a966-107ea642dd9d-poggio-bracciolini-sauveur-livres-oublies" style="color:#88A1E9" title=" Poggio Bracciolini, sauveur de livres oubliés ? par BnF"&gt;textes anciens&lt;/a&gt; que l’on croyait perdus. Né en Toscane, il entre au service de la cour pontificale, où il est secrétaire de plusieurs papes pendant près de cinquante ans. À la fin de sa vie, il devient chancelier de la république de Florence et en écrit l’histoire.&lt;/p&gt; &lt;p&gt;Pendant le concile de Constance (1414-1418), qui doit mettre fin au Grand Schisme, il profite de ses loisirs pour explorer les bibliothèques des monastères de Suisse, d’Allemagne et de France. Il y découvre des manuscrits oubliés depuis des siècles : un texte complet de l’&lt;em&gt;Institution oratoire&lt;/em&gt; de Quintilien, à Saint-Gall, plusieurs discours de Cicéron, et surtout, en 1417, le poème de Lucrèce, &lt;em&gt;De la nature des choses&lt;/em&gt;, qui fait connaître à l’Europe la physique atomiste et la morale d’Épicure. &lt;a href="https://www.youtube.com/watch?v=6zg6zhBsJf4" style="color:#88A1E9" title=" Poggio Bracciolini: Travel and Treasure Hunting in the Age of Humanism par TheBiflorence"&gt;Ses découvertes&lt;/a&gt; nourrissent toute la Renaissance. Pogge les copie lui-même dans une belle écriture régulière, imitée des manuscrits anciens, qui est à l’origine de nos caractères romains. Écrivain, il compose des dialogues moraux : &lt;em&gt;Sur l’avarice&lt;/em&gt;, où il défend en partie l’intérêt et le goût du gain, &lt;em&gt;Sur la noblesse&lt;/em&gt;, qui la fonde sur le mérite plutôt que sur la naissance, ou &lt;em&gt;Sur la misère de la condition humaine&lt;/em&gt;. Ses &lt;em&gt;Facéties&lt;/em&gt;, recueil d’histoires drôles et grivoises, souvent dirigées contre le clergé, connaissent un immense succès.&lt;/p&gt; &lt;p&gt;Polémiste redoutable, il échange avec l’humaniste Lorenzo Valla des invectives restées célèbres. Il illustre l’esprit de la Renaissance : l’amour des textes antiques et une liberté de ton nouvelle.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F104" s="30" t="inlineStr">
@@ -7807,8 +7802,8 @@
       </c>
       <c r="E109" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leon_Battista_Alberti" title=" Wikipedia"&gt;Léon Battista ALBERTI&lt;/a&gt; était un penseur et un artiste Italien de la Renaissance. Il était un polymathe, c'est-à-dire un savant qui excelle dans de nombreux domaines, y compris l'architecture, la sculpture, les mathématiques, la philosophie et la littérature. &lt;p&gt; &lt;p&gt; Il était un humaniste convaincu, qui croyait que la culture et la connaissance étaient des éléments clés pour améliorer la vie des individus et de la société dans son ensemble. Il a  écrit sur la politique et la société, dans lesquels il a prôné la vertu et la responsabilité civique et a été un défenseur de l'éducation pour tous, y compris les femmes.&lt;/p&gt; &lt;p&gt;  Il est aussi connu pour son traité sur l'architecture, intitulé De re aedificatoria (De la construction), publié en 1452. Ce livre est considéré comme l'un des premiers traités d'architecture modernes et a eu une influence considérable sur l'architecture européenne pendant des siècles.&lt;/p&gt; &lt;p&gt;
-Il a également écrit des traités sur la peinture et la sculpture, dans lesquels il a souligné l'importance de &lt;a href="https://www.youtube.com/watch?v=JnCiwh75D_k&amp;ab_channel=MassimoBrandolini"  title="Leon Battista Alberti par Massimo Brandolini"&gt; la perspective &lt;/a&gt; et de la proportion dans l'art. Il a été l'un des premiers à utiliser la perspective linéaire de manière systématique dans ses peintures et ses dessins, ce qui a permis de donner une impression de profondeur et de réalisme. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leon_Battista_Alberti" title=" Wikipedia"&gt;Léon Battista ALBERTI&lt;/a&gt; était un penseur et un artiste Italien de la Renaissance. Il était un polymathe, c'est-à-dire un savant qui excelle dans de nombreux domaines, y compris l'architecture, la sculpture, les mathématiques, la philosophie et la littérature. &lt;p&gt; &lt;p&gt; Il était un humaniste convaincu, qui croyait que la culture et la connaissance étaient des éléments clés pour améliorer la vie des individus et de la société dans son ensemble. Dans ses dialogues &lt;em&gt;Sur la famille&lt;/em&gt;, il réfléchit à l'éducation des enfants, à l'économie domestique et à l'amitié, et défend la vertu et la responsabilité civique.&lt;/p&gt; &lt;p&gt;  Il est aussi connu pour son traité sur l'architecture, intitulé De re aedificatoria (De la construction), publié en 1452. Ce livre est considéré comme l'un des premiers traités d'architecture modernes et a eu une influence considérable sur l'architecture européenne pendant des siècles.&lt;/p&gt; &lt;p&gt;
+Il a également écrit des traités sur la peinture et la sculpture, dans lesquels il a souligné l'importance de &lt;a href="https://www.youtube.com/watch?v=JnCiwh75D_k&amp;ab_channel=MassimoBrandolini"  title="Leon Battista Alberti par Massimo Brandolini"&gt; la perspective &lt;/a&gt; et de la proportion dans l'art. Il a été l'un des premiers à utiliser la perspective linéaire de manière systématique dans ses peintures et ses dessins, ce qui a permis de donner une impression de profondeur et de réalisme. &lt;/p&gt; Dans &lt;em&gt;De la peinture&lt;/em&gt; (1435) il donne la première théorie de la perspective : le tableau est comme « une fenêtre ouverte » sur le monde. Architecte, il dessine la façade de Santa Maria Novella à Florence et l’église Sant’Andrea de Mantoue. Il incarne l’idéal de l’« homme universel » de la Renaissance, pour qui « les hommes peuvent tout par eux-mêmes, pourvu qu’ils le veuillent ». 
 &lt;p&gt; &lt;/p&gt;</t>
         </is>
       </c>
@@ -8478,6 +8473,71 @@
         </is>
       </c>
       <c r="P119"/>
+    </row>
+    <row r="120" ht="99.75" customHeight="1" s="25">
+      <c r="A120" s="30">
+        <v>724</v>
+      </c>
+      <c r="B120" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804</t>
+        </is>
+      </c>
+      <c r="C120" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">724 - 804</t>
+        </is>
+      </c>
+      <c r="D120" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ALCUIN</t>
+        </is>
+      </c>
+      <c r="E120" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alcuin"  title=" Wikipedia"&gt;ALCUIN&lt;/a&gt; (vers 735-804) est un savant et pédagogue anglais, le principal artisan de la renaissance culturelle voulue par Charlemagne. Né en Northumbrie, il est formé à l’école de la cathédrale d’York, l’une des plus réputées d’Europe, qu’il finit par diriger. En 781, il rencontre en Italie Charlemagne, roi des Francs, qui l’invite à sa cour.&lt;/p&gt; &lt;p&gt;Il prend alors la tête de l’école du palais, où il enseigne au roi lui-même, à ses enfants et aux jeunes nobles la grammaire, la rhétorique, la dialectique et l’astronomie. Il écrit pour eux des manuels sous forme de dialogues entre maître et élève, dont l’un met en scène le jeune Pépin, fils du roi. Conseiller écouté, il inspire la politique d’éducation de Charlemagne, qui demande aux évêchés et aux monastères d’ouvrir des écoles pour former le clergé, dans tout l’&lt;a href="https://www.youtube.com/watch?v=yqIEe4nptPI&amp;ab_channel=PierrickAuger"  title="L'Empire carolingien par Pierrick Auger"&gt;Empire carolingien&lt;/a&gt;. Il participe à la révision du texte de la Bible latine et à l’unification de la liturgie, et combat les doctrines jugées hérétiques. Philosophe, il compose un traité sur l’âme, dans la tradition de saint Augustin, ainsi qu’un traité sur les vertus et les vices destiné à un laïc. Ses quelque trois cents lettres sont une source précieuse sur son temps. En 796, il devient abbé de Saint-Martin de Tours, dont le scriptorium copie et diffuse de nombreux manuscrits, dans la nouvelle écriture claire et lisible appelée « minuscule caroline », ancêtre de nos lettres minuscules.&lt;/p&gt; &lt;p&gt;Il meurt à Tours en 804. Ses élèves, comme Raban Maur, poursuivent son œuvre, et la plupart des textes antiques que nous lisons encore nous sont parvenus grâce à des copies carolingiennes.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A3P2E6ljEUU</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Alcium ou la renaissance carolingienne" par Storiavoce</t>
+        </is>
+      </c>
+      <c r="H120" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/alcuin-mini.webp</t>
+        </is>
+      </c>
+      <c r="J120" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Britannique</t>
+        </is>
+      </c>
+      <c r="K120" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L120" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patristique</t>
+        </is>
+      </c>
+      <c r="M120" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe érudit anglais qui a eu une grande influence sur l'éducation en Europe.</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -734,31 +734,22 @@
       </c>
       <c r="E4" s="32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pseudo-Denys_l%27Ar%C3%A9opagite"  style="color:#6A142A"  title=" Wikipedia"&gt; Pseudo-DENYS l'Aréopagite&lt;/a&gt;, souvent simplement appelé "Pseudo-Denys," est un auteur chrétien mystique a qui on a longtemps attribué l'identité de Denys l'Aréopagite, un converti de l'apôtre Paul mentionné dans les Actes des Apôtres (Actes 17:34). Cependant, les recherches historiques ont montré que ces écrits ne pouvaient pas provenir de cette époque, et l'auteur reste anonyme. &lt;/p&gt;  &lt;p&gt; Il représente une des tentatives les plus radicales de réconcilier le message évangélique et &lt;a href="https://www.persee.fr/doc/dha_0755-7256_1981_num_7_1_1438"  title="Denys, précurseurs et postérité par Persée  "&gt;la tradition néoplatonicienne&lt;/a&gt;.  Ses œuvres principales sont regroupées sous le titre de "Corpus dionysien." Elles incluent : &lt;/p&gt;
-&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=IcAgXi8g-_s" title="La hiérarchie celeste par Source Chrétienne "&gt; - La Hiérarchie céleste (De Caelesti Hierarchia)&lt;/a&gt;&lt;dd&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pseudo-Denys_l%27Ar%C3%A9opagite"  style="color:#6A142A"  title=" Wikipedia"&gt; Pseudo-DENYS l'Aréopagite&lt;/a&gt;, souvent simplement appelé "Pseudo-Denys," est un auteur chrétien mystique a qui on a longtemps attribué l'identité de Denys l'Aréopagite, un converti de l'apôtre Paul mentionné dans les Actes des Apôtres (Actes 17:34). Cependant, les recherches historiques ont montré que ces écrits ne pouvaient pas provenir de cette époque, et l'auteur reste anonyme. &lt;/p&gt; &lt;p&gt; Il représente une des tentatives les plus radicales de réconcilier le message évangélique et &lt;a href="https://www.persee.fr/doc/dha_0755-7256_1981_num_7_1_1438"  title="Denys, précurseurs et postérité par Persée  "&gt;la tradition néoplatonicienne&lt;/a&gt;.  Ses œuvres principales sont regroupées sous le titre de "Corpus dionysien." Elles incluent : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=IcAgXi8g-_s" title="La hiérarchie celeste par Source Chrétienne "&gt; - La Hiérarchie céleste (De Caelesti Hierarchia)&lt;/a&gt;&lt;p&gt;
 &lt;p&gt;Ce traité décrit les neuf ordres angéliques, organisés en trois triades : Séraphins, Chérubins, Trônes ; Dominations, Vertus, Puissances ; et Principautés, Archanges, Anges.
 Il explore la manière dont les anges médiatisent entre Dieu et le monde.&lt;/p&gt;
-&lt;dd&gt; - La Hiérarchie ecclésiastique (De Ecclesiastica Hierarchia) &lt;/dd&gt;
-&lt;p&gt;Ce texte examine la structure et les rites de l'Église chrétienne, en mettant en parallèle la hiérarchie ecclésiastique avec celle des anges.
+&lt;p&gt;La Hiérarchie ecclésiastique (De Ecclesiastica Hierarchia) &lt;/p&gt; &lt;p&gt;Ce texte examine la structure et les rites de l'Église chrétienne, en mettant en parallèle la hiérarchie ecclésiastique avec celle des anges.
 Il propose une vision sacramentelle et symbolique des liturgies.&lt;/p&gt;
-&lt;dd&gt; - Les Noms divins (De Divinis Nominibus)&lt;/dd&gt;
-&lt;p&gt;Ce traité traite des noms attribués à Dieu dans les Écritures, comme le Bien, l’Amour, la Lumière, etc.
+&lt;p&gt;Les Noms divins (De Divinis Nominibus)&lt;/p&gt; &lt;p&gt;Ce traité traite des noms attribués à Dieu dans les Écritures, comme le Bien, l’Amour, la Lumière, etc.
 Il développe une théologie apophatique, affirmant que Dieu dépasse tout langage humain et ne peut être pleinement décrit. &lt;/p&gt;
-&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=qZMwuQQj-Xk&amp;t=7s"  title="La théologie mystique par Source Chrétienne "&gt; - La Théologie mystique (De Mystica Theologia) &lt;/a&gt;&lt;/dd&gt;
-&lt;p&gt;Un court texte qui explore la voie de l'union mystique avec Dieu par la négation (via negativa).
-L'accent est mis sur la transcendance absolue de Dieu, atteinte en dépassant toutes les affirmations positives et les images mentales. &lt;/p&gt;
-&lt;dd&gt;Dix lettres qui développent certains points théologiques ou mystiques des autres œuvres. &lt;/dd&gt;   
-&lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=AU_WTuu3W6Q&amp;t=37s" title="La théologie négative par raisonnances "&gt;Théologie apophatique (ou négative)&lt;/a&gt; : 
-L'auteur insiste sur le fait que Dieu transcende toute compréhension humaine. On ne peut parler de Dieu qu’en termes négatifs, c'est-à-dire en disant ce qu'Il n’est pas, plutôt qu’en essayant de définir ce qu’Il est. &lt;/p&gt;
-&lt;p&gt;Symbolisme hiérarchique : 
-Le monde est organisé de manière hiérarchique, avec une descente des réalités divines à travers des intermédiaires comme les anges et les prêtres, et une remontée de l’âme humaine vers Dieu. &lt;/p&gt;
-&lt;p&gt;Union mystique : 
-L’objectif ultime de la vie spirituelle est l’union avec Dieu, qui s’obtient par la purification, l’illumination et la perfection, processus décrits dans les œuvres. &lt;/p&gt;
-&lt;p&gt;Influence : 
+&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=qZMwuQQj-Xk&amp;t=7s"  title="La théologie mystique par Source Chrétienne "&gt; - La Théologie mystique (De Mystica Theologia) &lt;/a&gt;&lt;/p&gt; &lt;p&gt;Un court texte qui explore la voie de l'union mystique avec Dieu par la négation (via negativa).
+L'accent est mis sur la transcendance absolue de Dieu, atteinte en dépassant toutes les affirmations positives et les images mentales. &lt;/p&gt; &lt;p&gt;Dix lettres qui développent certains points théologiques ou mystiques des autres œuvres. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=AU_WTuu3W6Q&amp;t=37s" title="La théologie négative par raisonnances "&gt;Théologie apophatique (ou négative)&lt;/a&gt; : 
+L'auteur insiste sur le fait que Dieu transcende toute compréhension humaine. On ne peut parler de Dieu qu’en termes négatifs, c'est-à-dire en disant ce qu'Il n’est pas, plutôt qu’en essayant de définir ce qu’Il est. &lt;/p&gt; &lt;p&gt;Symbolisme hiérarchique : 
+Le monde est organisé de manière hiérarchique, avec une descente des réalités divines à travers des intermédiaires comme les anges et les prêtres, et une remontée de l’âme humaine vers Dieu. &lt;/p&gt; &lt;p&gt;Union mystique : 
+L’objectif ultime de la vie spirituelle est l’union avec Dieu, qui s’obtient par la purification, l’illumination et la perfection, processus décrits dans les œuvres. &lt;/p&gt; &lt;p&gt;Influence : 
 Les écrits de Pseudo-Denys ont marqué la théologie chrétienne. 
 En Orient, ils ont influencé des penseurs comme Maxime le Confesseur et Grégoire Palamas.
 En Occident, ils ont été traduits par Jean Scot Érigène au IXe siècle et ont profondément influencé des figures médiévales comme Thomas d’Aquin, Bonaventure et Maître Eckhart.&lt;/p&gt;
-&lt;p&gt;Pseudo-Denys est donc une figure clé pour comprendre le développement de la mystique chrétienne et de la théologie médiévale. &lt;/p&gt;   &lt;p&gt;   &lt;/p&gt;</t>
+&lt;p&gt;Pseudo-Denys est donc une figure clé pour comprendre le développement de la mystique chrétienne et de la théologie médiévale. &lt;/p&gt;   </t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
@@ -824,11 +815,11 @@
       </c>
       <c r="E5" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_S%C3%A9ville"  title=" Wikipedia"&gt; ISIDORE de Seville&lt;/a&gt;  également connu sous le nom d'Isidore Hispalensis ou Isidore de Hispalis, était un éminent philosophe, théologien et érudit espagnol considéré comme l'un des derniers grands penseurs de la période de l'Antiquité tardive et l'un des savants les plus influents de son temps. &lt;/p&gt; &lt;p&gt;
+          <t xml:space="preserve">&lt;p&gt; &lt;a href="https://fr.wikipedia.org/wiki/Isidore_de_S%C3%A9ville"  title=" Wikipedia"&gt; ISIDORE de Seville&lt;/a&gt;  également connu sous le nom d'Isidore Hispalensis ou Isidore de Hispalis, était un éminent philosophe, théologien et érudit espagnol considéré comme l'un des derniers grands penseurs de la période de l'Antiquité tardive et l'un des savants les plus influents de son temps. &lt;/p&gt; &lt;p&gt;
 Il est surtout connu pour son œuvre majeure, &lt;a href="https://www.persee.fr/doc/ista_0000-0000_2004_edc_938_1"  style="color:#88A1E9"  title="Etymologies de Isidore de seville par Persée"&gt;"Etymologiae"&lt;/a&gt; (ou "Étymologies"), une encyclopédie en vingt livres qui couvre une vaste gamme de sujets, de la théologie et de la philosophie à la grammaire, la médecine, l'histoire, la zoologie, l'astronomie et bien d'autres encore. L'ouvrage était destiné à rassembler et à préserver les connaissances de l'époque et a eu une influence durable sur les savants médiévaux. &lt;/p&gt; &lt;p&gt; 
 "Etymologiae" était structuré selon un modèle encyclopédique basé sur l'idée d'étymologie, c'est-à-dire la recherche des origines et des significations des mots. Il a établi une classification systématique des arts libéraux (le quadrivium et le trivium) et a contribué à préserver de nombreux textes anciens en les citant dans son œuvre. Il a également introduit des concepts tels que la distinction entre les sept arts mécaniques et les sept arts libéraux. &lt;/p&gt; &lt;p&gt; 
 Isidore était également préoccupé par les questions de foi et d'orthodoxie, et il a participé activement aux débats théologiques de son époque. Il a été nommé archevêque de Séville en 601 et a joué un rôle important dans l'organisation de l'Église en Espagne. Il a également contribué à la conversion des Wisigoths à la foi catholique et a promu l'éducation et la formation des prêtres. &lt;/p&gt; 
-&lt;p&gt; &lt;/p&gt;</t>
+</t>
         </is>
       </c>
       <c r="F5" s="30" t="inlineStr">
@@ -894,10 +885,9 @@
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_le_Confesseur"  title=" Wikipedia"&gt;MAXIME le Confesseur&lt;/a&gt; est une figure majeure de la théologie chrétienne byzantine et un ardent défenseur de l'orthodoxie face aux controverses christologiques de son époque. Moine, philosophe et théologien, il a joué un rôle central dans la lutte contre l'hérésie du  &lt;a href="https://fr.wikipedia.org/wiki/Monoth%C3%A9lisme" style="color:#88A1E9" title="monotheisme par Wikipedia "&gt;monothélisme&lt;/a&gt;, ce qui lui valut d'être persécuté et mutilé avant de mourir en exil. &lt;/p&gt; &lt;p&gt; Il a produit de &lt;a href="https://fr.orthodoxwiki.org/Maxime_le_Confesseur" style="color:#88A1E9" title="Maxime le Confesseur par Orthodoxwiki "&gt;nombreuses œuvres&lt;/a&gt; théologiques d'une profondeur immense, mêlant philosophie néoplatonicienne et tradition chrétienne dont la défense de la  &lt;a href="https://www.youtube.com/watch?v=P789srH_Bvw&amp;t=53s" style="color:#88A1E9" title="Saint Maxime par Le Verbe media "&gt;doctrine des deux volontés&lt;/a&gt; (dyothélisme) ou il insiste sur le fait que l’humanité du Christ est complète, y compris une volonté humaine libre qui choisit d’obéir à la volonté divine.&lt;/p&gt; &lt;p&gt;  Il développe une vision profonde de l’être humain : &lt;/p&gt; 
-&lt;dd&gt; - L’homme est créé pour la déification (théosis), c’est-à-dire une participation à la nature divine.&lt;/dd&gt;
-&lt;dd&gt; - Le péché est une rupture de l’harmonie entre l’homme et Dieu, mais la grâce permet le retour à cette union.&lt;/dd&gt;
-&lt;dd&gt; - L’ascèse et la contemplation sont essentielles pour progresser vers Dieu.&lt;/dd&gt;  &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il a une vision cosmologique impressionnante : tout l’univers est ordonné vers Dieu. Il propose une lecture symbolique de l’histoire et de la création, où le Christ est le centre du cosmos et de l’histoire. L’univers est appelé à s’unir en Dieu dans une harmonie finale. &lt;/p&gt;  &lt;p&gt; Il  est un penseur incontournable du christianisme, ayant marqué son époque par son courage face aux persécutions et par la profondeur de sa réflexion. Son engagement pour la vérité théologique a façonné l’orthodoxie chrétienne telle que nous la connaissons aujourd’hui. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;  &lt;p&gt; &lt;/p&gt;  &lt;audio controls title="Maxime le Confesseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10491-03.07.2011-ITEMA_20295046-2011C3184E0012-ITE_00043801_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;/p&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Maxime_le_Confesseur"  title=" Wikipedia"&gt;MAXIME le Confesseur&lt;/a&gt; est une figure majeure de la théologie chrétienne byzantine et un ardent défenseur de l'orthodoxie face aux controverses christologiques de son époque. Moine, philosophe et théologien, il a joué un rôle central dans la lutte contre l'hérésie du  &lt;a href="https://fr.wikipedia.org/wiki/Monoth%C3%A9lisme" style="color:#88A1E9" title="monotheisme par Wikipedia "&gt;monothélisme&lt;/a&gt;, ce qui lui valut d'être persécuté et mutilé avant de mourir en exil. &lt;/p&gt; &lt;p&gt; Il a produit de &lt;a href="https://fr.orthodoxwiki.org/Maxime_le_Confesseur" style="color:#88A1E9" title="Maxime le Confesseur par Orthodoxwiki "&gt;nombreuses œuvres&lt;/a&gt; théologiques d'une profondeur immense, mêlant philosophie néoplatonicienne et tradition chrétienne dont la défense de la  &lt;a href="https://www.youtube.com/watch?v=P789srH_Bvw&amp;t=53s" style="color:#88A1E9" title="Saint Maxime par Le Verbe media "&gt;doctrine des deux volontés&lt;/a&gt; (dyothélisme) ou il insiste sur le fait que l’humanité du Christ est complète, y compris une volonté humaine libre qui choisit d’obéir à la volonté divine.&lt;/p&gt; &lt;p&gt;  Il développe une vision profonde de l’être humain : &lt;/p&gt; &lt;p&gt;L’homme est créé pour la déification (théosis), c’est-à-dire une participation à la nature divine.&lt;/p&gt;
+&lt;p&gt;Le péché est une rupture de l’harmonie entre l’homme et Dieu, mais la grâce permet le retour à cette union.&lt;/p&gt;
+&lt;p&gt;L’ascèse et la contemplation sont essentielles pour progresser vers Dieu.&lt;/p&gt; &lt;p&gt; Il a une vision cosmologique impressionnante : tout l’univers est ordonné vers Dieu. Il propose une lecture symbolique de l’histoire et de la création, où le Christ est le centre du cosmos et de l’histoire. L’univers est appelé à s’unir en Dieu dans une harmonie finale. &lt;/p&gt; &lt;p&gt; Il  est un penseur incontournable du christianisme, ayant marqué son époque par son courage face aux persécutions et par la profondeur de sa réflexion. Son engagement pour la vérité théologique a façonné l’orthodoxie chrétienne telle que nous la connaissons aujourd’hui. &lt;/p&gt;     &lt;audio controls title="Maxime le Confesseur par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10491-03.07.2011-ITEMA_20295046-2011C3184E0012-ITE_00043801_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;/p&gt;  </t>
         </is>
       </c>
       <c r="F6" s="30" t="inlineStr">
@@ -1032,11 +1022,7 @@
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Damasc%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean DAMASCÈNE&lt;/a&gt; était un prètre théologien d'origine  &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1994_num_211_3_1376" title="Jean Damascène. Ecrits sur l'Islam par Persée"&gt; arabe &lt;/a&gt;vénéré comme saint par l'Église catholique et l'Église orthodoxe. Il est considéré comme l'un des derniers  &lt;a href="https://www.youtube.com/watch?v=0805ye1styI" style="color:#88A1E9" title="La vie de saint Jean Damascène, Docteur de l'Église défenseur des icônes et des reliques  par Chaine catholique"&gt; Pères de l'Église.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Connu pour ses contributions théologiques et philosophiques dont les plus importantes  : &lt;/p&gt; 
-&lt;p&gt; - "La Foi orthodoxe" : Synthèse systématique de la théologie chrétienne, basée sur les enseignements des Pères de l'Église et des conciles œcuméniques. Il a eu une influence considérable sur la théologie byzantine et médiévale. &lt;/p&gt; 
-&lt;p&gt; - "Contre les iconoclastes" : Ardent défenseur de la vénération des icônes, s'opposant à l'iconoclasme, un mouvement qui rejetait l'utilisation des images religieuses. Ses trois traités "Contre ceux qui rejettent les saintes images" sont des textes fondateurs de la théologie des icônes. &lt;/p&gt; 
-&lt;p&gt; - "Dialectique" : Cet ouvrage est une introduction à la philosophie aristotélicienne, montrant l'influence de la pensée grecque sur sa théologie. &lt;/p&gt; 
-&lt;p&gt; - "Hymnes et poèmes" : Il a également composé des hymnes liturgiques, dont certains sont encore utilisés dans la liturgie orthodoxe. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Il  a joué un rôle crucial dans la défense et l'explication de la doctrine chrétienne, en particulier face aux hérésies de son temps. Il a insisté sur l'importance de la tradition et des conciles œcuméniques, et a contribué à la formulation de la doctrine de l'Incarnation et de la nature du Christ. &lt;/p&gt; &lt;p&gt; Sa défense des icônes a été particulièrement influente. Il a argumenté que  &lt;a href="https://www.youtube.com/watch?v=C5hADqvgHOI" style="color:#88A1E9" title="Jean Damascène Homélie sur le culte des Icônes par La Chaine d'Or"&gt; les icônes&lt;/a&gt; ne sont pas adorées mais vénérées, et qu'elles servent de fenêtres vers le divin, aidant les fidèles à se concentrer sur Dieu et les saints. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Damasc%C3%A8ne"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean DAMASCÈNE&lt;/a&gt; était un prètre théologien d'origine  &lt;a href="https://www.persee.fr/doc/rhr_0035-1423_1994_num_211_3_1376" title="Jean Damascène. Ecrits sur l'Islam par Persée"&gt; arabe &lt;/a&gt;vénéré comme saint par l'Église catholique et l'Église orthodoxe. Il est considéré comme l'un des derniers  &lt;a href="https://www.youtube.com/watch?v=0805ye1styI" style="color:#88A1E9" title="La vie de saint Jean Damascène, Docteur de l'Église défenseur des icônes et des reliques  par Chaine catholique"&gt; Pères de l'Église.&lt;/a&gt;  &lt;/p&gt; &lt;p&gt;Connu pour ses contributions théologiques et philosophiques dont les plus importantes  : &lt;/p&gt; &lt;p&gt;"La Foi orthodoxe" : Synthèse systématique de la théologie chrétienne, basée sur les enseignements des Pères de l'Église et des conciles œcuméniques. Il a eu une influence considérable sur la théologie byzantine et médiévale. &lt;/p&gt; &lt;p&gt;"Contre les iconoclastes" : Ardent défenseur de la vénération des icônes, s'opposant à l'iconoclasme, un mouvement qui rejetait l'utilisation des images religieuses. Ses trois traités "Contre ceux qui rejettent les saintes images" sont des textes fondateurs de la théologie des icônes. &lt;/p&gt; &lt;p&gt;"Dialectique" : Cet ouvrage est une introduction à la philosophie aristotélicienne, montrant l'influence de la pensée grecque sur sa théologie. &lt;/p&gt; &lt;p&gt;"Hymnes et poèmes" : Il a également composé des hymnes liturgiques, dont certains sont encore utilisés dans la liturgie orthodoxe. &lt;/p&gt; &lt;p&gt; Il  a joué un rôle crucial dans la défense et l'explication de la doctrine chrétienne, en particulier face aux hérésies de son temps. Il a insisté sur l'importance de la tradition et des conciles œcuméniques, et a contribué à la formulation de la doctrine de l'Incarnation et de la nature du Christ. &lt;/p&gt; &lt;p&gt; Sa défense des icônes a été particulièrement influente. Il a argumenté que  &lt;a href="https://www.youtube.com/watch?v=C5hADqvgHOI" style="color:#88A1E9" title="Jean Damascène Homélie sur le culte des Icônes par La Chaine d'Or"&gt; les icônes&lt;/a&gt; ne sont pas adorées mais vénérées, et qu'elles servent de fenêtres vers le divin, aidant les fidèles à se concentrer sur Dieu et les saints. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F8" s="30" t="inlineStr">
@@ -1102,15 +1088,10 @@
       </c>
       <c r="E9" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fr%C3%A9degis_de_Tours"  style="color:#6A142A"  title=" Wikipedia"&gt;FRÉDÉGISE&lt;/a&gt;, qui fût l'élève d' Alcuin, est un personnage connu pour être l'auteur ou le compilateur de la Chronique de Frédégise, un texte historique et non un ouvrage philosophique. C'est une source précieuse pour comprendre la transition du monde antique vers le Moyen Âge. Son rôle dans l'histoire intellectuelle mérovingienne, avec un focus sur son importance et ses écrits.  La Chronique de Frédégaire se divise en plusieurs livres :&lt;/p&gt;
- &lt;dd&gt;Livre I et II : Ces parties reprennent des récits tirés de sources classiques et bibliques. Elles incluent des récits sur la création du monde, les histoires de l'Ancien Testament, et des extraits de chroniques antérieures comme celles d'Eusèbe de Césarée et d'Orose. &lt;/dd&gt;
- &lt;dd&gt; Livre III : Il aborde l’histoire de Rome, incluant les conquêtes de Jules César et des empereurs. Il s’inspire des écrits de Grégoire de Tours (auteur de l’Histoire des Francs). &lt;/dd&gt;
- &lt;dd&gt;Livre IV : C'est la partie la plus originale. Elle relate les événements contemporains, notamment les règnes de Clotaire II, Dagobert Ier, et la montée en puissance des maires du palais comme Pépin de Herstal. &lt;/dd&gt;
-&lt;p&gt; La chronique est remarquable pour son mélange de mythologie, de récits historiques, et de théologie chrétienne. Le style est parfois naïf et reflète une vision chrétienne du monde, mais elle conserve des récits précieux sur les rois francs, leurs relations avec leurs voisins (notamment les Saxons, les Burgondes, et les Byzantins), et les évolutions internes du royaume. Bien que Frédégaire ne soit pas un philosophe dans le sens classique du terme, il appartient à un courant de pensée médiéval influencé par la synthèse chrétienne du savoir antique et biblique. Son travail reflète plusieurs aspects de la pensée mérovingienne comme l’idée de Providence Divine. &lt;/p&gt;
- &lt;p&gt;Sa réflexion sur le néant et les ténèbres est fascinante, mais elle demande une mise au point : Il n'est pas connu comme un philosophe systématique, et ses écrits n’offrent pas de réflexion explicite ou approfondie sur des concepts abstraits tels que le néant ou les ténèbres au sens philosophique. Cependant, son œuvre peut être analysée dans le cadre de la pensée chrétienne médiévale, où ces notions sont souvent imbriquées dans des récits théologiques et cosmologiques. Il inscrit son œuvre dans une tradition chrétienne qui a beaucoup emprunté à la théologie de saint Augustin et à la Genèse biblique. Dans ce cadre, les concepts de néant (nihil) et de ténèbres (tenebrae) ont une portée symbolique et théologique.&lt;/p&gt; 
-&lt;p&gt; Les ténèbres symbolisent l'absence de Dieu, souvent associées au péché et au chaos. Cette conception trouve son origine dans la Genèse : « Au commencement, les ténèbres couvraient l’abîme, et l’Esprit de Dieu planait au-dessus des eaux. » (Genèse 1:2).
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Fr%C3%A9degis_de_Tours"  style="color:#6A142A"  title=" Wikipedia"&gt;FRÉDÉGISE&lt;/a&gt;, qui fût l'élève d' Alcuin, est un personnage connu pour être l'auteur ou le compilateur de la Chronique de Frédégise, un texte historique et non un ouvrage philosophique. C'est une source précieuse pour comprendre la transition du monde antique vers le Moyen Âge. Son rôle dans l'histoire intellectuelle mérovingienne, avec un focus sur son importance et ses écrits.  La Chronique de Frédégaire se divise en plusieurs livres :&lt;/p&gt; &lt;p&gt;Livre I et II : Ces parties reprennent des récits tirés de sources classiques et bibliques. Elles incluent des récits sur la création du monde, les histoires de l'Ancien Testament, et des extraits de chroniques antérieures comme celles d'Eusèbe de Césarée et d'Orose. &lt;/p&gt; &lt;p&gt; Livre III : Il aborde l’histoire de Rome, incluant les conquêtes de Jules César et des empereurs. Il s’inspire des écrits de Grégoire de Tours (auteur de l’Histoire des Francs). &lt;/p&gt; &lt;p&gt;Livre IV : C'est la partie la plus originale. Elle relate les événements contemporains, notamment les règnes de Clotaire II, Dagobert Ier, et la montée en puissance des maires du palais comme Pépin de Herstal. &lt;/p&gt;
+&lt;p&gt; La chronique est remarquable pour son mélange de mythologie, de récits historiques, et de théologie chrétienne. Le style est parfois naïf et reflète une vision chrétienne du monde, mais elle conserve des récits précieux sur les rois francs, leurs relations avec leurs voisins (notamment les Saxons, les Burgondes, et les Byzantins), et les évolutions internes du royaume. Bien que Frédégaire ne soit pas un philosophe dans le sens classique du terme, il appartient à un courant de pensée médiéval influencé par la synthèse chrétienne du savoir antique et biblique. Son travail reflète plusieurs aspects de la pensée mérovingienne comme l’idée de Providence Divine. &lt;/p&gt; &lt;p&gt;Sa réflexion sur le néant et les ténèbres est fascinante, mais elle demande une mise au point : Il n'est pas connu comme un philosophe systématique, et ses écrits n’offrent pas de réflexion explicite ou approfondie sur des concepts abstraits tels que le néant ou les ténèbres au sens philosophique. Cependant, son œuvre peut être analysée dans le cadre de la pensée chrétienne médiévale, où ces notions sont souvent imbriquées dans des récits théologiques et cosmologiques. Il inscrit son œuvre dans une tradition chrétienne qui a beaucoup emprunté à la théologie de saint Augustin et à la Genèse biblique. Dans ce cadre, les concepts de néant (nihil) et de ténèbres (tenebrae) ont une portée symbolique et théologique.&lt;/p&gt; &lt;p&gt; Les ténèbres symbolisent l'absence de Dieu, souvent associées au péché et au chaos. Cette conception trouve son origine dans la Genèse : « Au commencement, les ténèbres couvraient l’abîme, et l’Esprit de Dieu planait au-dessus des eaux. » (Genèse 1:2).
 Chez Frédégise, bien que les références explicites soient rares, les ténèbres peuvent être perçues comme une métaphore pour les moments de déclin et de confusion dans l'histoire des Francs, interprétés comme un éloignement de Dieu. &lt;/p&gt;
-Les Ténèbres comme le Désordre Historique - Le Néant comme Absence de Sens -  Le néant est l’état antérieur à la création divine, transcendu par l’intervention de Dieu.
+Les Ténèbres comme le Désordre Historique ; Le Néant comme Absence de Sens ; Le néant est l’état antérieur à la création divine, transcendu par l’intervention de Dieu.
 Les ténèbres, souvent métaphoriques, représentent le péché, le désordre, ou l’éloignement de la lumière divine.. &lt;/p&gt;</t>
         </is>
       </c>
@@ -1173,8 +1154,8 @@
       </c>
       <c r="E10" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hilduin_de_Saint-Denis"   title=" Wikipedia"&gt;HILDUIN&lt;/a&gt; ou Hilduin de Saint-Denis est une Figure Clé et influente du Haut Moyen à l'époque carolingienne, connu pour son rôle d'ecclésiastique,  &lt;a href="https://www.persee.fr/doc/rhef_0300-9505_1923_num_9_42_2260" style="color:#88A1E9" title="Trouble dans le genre par Persée  "&gt;d'écrivain &lt;/a&gt; et de conseiller de l'empereur Louis le Pieux. Il a contribué au développement intellectuel et spirituel du royaume franc, ainsi qu'à la promotion du culte de saint Denis, le patron des Francs.  &lt;/p&gt;
-&lt;p&gt; Il joue un rôle crucial dans l’introduction des écrits attribués à &lt;a href="https://fr.wikipedia.org/wiki/Denys_l%27Ar%C3%A9opagite" style="color:#88A1E9" title="Denys l’Aréopagite par Wikipedia  "&gt;Denys l’Aréopagite&lt;/a&gt; (le Corpus Dionysiacum) en Occident. Ces textes, traduits du grec en latin par lui ou son entourage, marquent le début de leur réception en Europe médiévale. Le néoplatonisme de ces écrits influencera profondément la pensée médiévale, notamment chez Jean Scot Érigène. &lt;/p&gt;  &lt;p&gt; Il voit l’histoire comme un processus ordonné par Dieu, où les saints jouent un rôle central dans le destin des peuples.                                        
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hilduin_de_Saint-Denis"   title=" Wikipedia"&gt;HILDUIN&lt;/a&gt; ou Hilduin de Saint-Denis est une Figure Clé et influente du Haut Moyen à l'époque carolingienne, connu pour son rôle d'ecclésiastique,  &lt;a href="https://www.persee.fr/doc/rhef_0300-9505_1923_num_9_42_2260" style="color:#88A1E9" title="Trouble dans le genre par Persée  "&gt;d'écrivain &lt;/a&gt; et de conseiller de l'empereur Louis le Pieux. Il a contribué au développement intellectuel et spirituel du royaume franc, ainsi qu'à la promotion du culte de saint Denis, le patron des Francs.  &lt;/p&gt;
+&lt;p&gt; Il joue un rôle crucial dans l’introduction des écrits attribués à &lt;a href="https://fr.wikipedia.org/wiki/Denys_l%27Ar%C3%A9opagite" style="color:#88A1E9" title="Denys l’Aréopagite par Wikipedia  "&gt;Denys l’Aréopagite&lt;/a&gt; (le Corpus Dionysiacum) en Occident. Ces textes, traduits du grec en latin par lui ou son entourage, marquent le début de leur réception en Europe médiévale. Le néoplatonisme de ces écrits influencera profondément la pensée médiévale, notamment chez Jean Scot Érigène. &lt;/p&gt; &lt;p&gt; Il voit l’histoire comme un processus ordonné par Dieu, où les saints jouent un rôle central dans le destin des peuples.                                        
 Dans son travail sur saint Denis, il inscrit la mission évangélique de ce dernier dans un contexte universel, reliant les origines du christianisme en Gaule au projet divin. Son travail de réforme a contribué à modeler l’institution monastique carolingienne. &lt;/p&gt;
 &lt;p&gt; Il est l'auteur d’un ouvrage intitulé "Passio sancti Dionysii" (La Passion de saint Denis), qui associe saint Denis, premier évêque de Paris, à Denys l’Aréopagite, un personnage mentionné dans les Actes des Apôtres et à qui étaient attribués des écrits néo-platoniciens.
 Ce lien, bien que historiquement douteux, a permis de magnifier l’aura spirituelle de Saint-Denis, tout en conférant à l’abbaye un prestige international.&lt;/p&gt;</t>
@@ -1305,11 +1286,7 @@
       </c>
       <c r="E12" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Scot_%C3%89rig%C3%A8ne"   title=" Wikipedia"&gt;Jean Scot ERIGÈNE&lt;/a&gt; était un philosophe et théologien irlandais du IXe siècle. Son œuvre la plus célèbre est  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1997_num_71_1_3394_t1_0128_0000_1" style="color:#88A1E9" title="de la division de la nature par Persée"&gt; "De divisione naturae"&lt;/a&gt; (Sur la division de la nature), qui est l'une des œuvres philosophiques les plus importantes du Moyen Âge latin et où il tente de systématiser la connaissance en une seule vision cohérente de la réalité. Il divise la nature en quatre divisions : la nature créée (qui existe et peut être comprise), la nature non créée (qui existe mais ne peut pas être comprise, c'est-à-dire Dieu), la nature qui crée et n'est pas créée (le processus de création lui-même, ou le Logos), et la nature qui n'est ni créée ni crée (le non-être absolu).&lt;/p&gt;
-&lt;p&gt;Il était influencé par la pensée de Platon, Plotin et Denys l'Aréopagite, ainsi que par les Pères de l'Église et la tradition néo-platonicienne et était également fortement imprégné de la philosophie grecque et arabe, ce qui était assez inhabituel pour un penseur occidental de cette époque.&lt;/p&gt;
-&lt;p&gt;Adepte de la tradition de &lt;a href="https://www.youtube.com/watch?v=90H26hzj4AY&amp;ab_channel=Napo" style="color:#88A1E9" title="la théologie négative par Napo"&gt; Théologie Négative&lt;/a&gt;, qui enseigne que Dieu est au-delà de toute conceptualisation humaine. Cela signifie que la connaissance de Dieu ne peut être obtenue que par la négation des attributs limités qui lui sont attribués par les êtres humains.&lt;/p&gt;
-&lt;p&gt;Bien qu'il soit un théologien chrétien, il a développé une vision panthéiste modérée dans laquelle Dieu est présent en toutes choses. Pour lui, la création est une manifestation de la volonté divine et une participation à la nature divine, mettant l'accent sur la participation de l'homme à la connaissance divine. Il croyait que la raison humaine est capable de comprendre certaines vérités divines, bien que de manière limitée, et que la véritable connaissance est atteinte par une participation active à la nature divine. &lt;/p&gt;
-&lt;p&gt;Il était également connu pour son approche audacieuse des questions théologiques et philosophiques. Par exemple, il était en avance sur son temps en soutenant l'idée de la prédestination universelle, qui affirme que Dieu veut le salut de tous les êtres humains. Cette vision a été controversée à son époque et a même été condamnée comme hérétique après sa mort.&lt;/p&gt;
+          <t xml:space="preserve"> &lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Scot_%C3%89rig%C3%A8ne"   title=" Wikipedia"&gt;Jean Scot ERIGÈNE&lt;/a&gt; était un philosophe et théologien irlandais du IXe siècle. Son œuvre la plus célèbre est  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1997_num_71_1_3394_t1_0128_0000_1" style="color:#88A1E9" title="de la division de la nature par Persée"&gt; "De divisione naturae"&lt;/a&gt; (Sur la division de la nature), qui est l'une des œuvres philosophiques les plus importantes du Moyen Âge latin et où il tente de systématiser la connaissance en une seule vision cohérente de la réalité. Il divise la nature en quatre divisions : la nature créée (qui existe et peut être comprise), la nature non créée (qui existe mais ne peut pas être comprise, c'est-à-dire Dieu), la nature qui crée et n'est pas créée (le processus de création lui-même, ou le Logos), et la nature qui n'est ni créée ni crée (le non-être absolu).&lt;/p&gt; &lt;p&gt;Il était influencé par la pensée de Platon, Plotin et Denys l'Aréopagite, ainsi que par les Pères de l'Église et la tradition néo-platonicienne et était également fortement imprégné de la philosophie grecque et arabe, ce qui était assez inhabituel pour un penseur occidental de cette époque.&lt;/p&gt; &lt;p&gt;Adepte de la tradition de &lt;a href="https://www.youtube.com/watch?v=90H26hzj4AY&amp;ab_channel=Napo" style="color:#88A1E9" title="la théologie négative par Napo"&gt; Théologie Négative&lt;/a&gt;, qui enseigne que Dieu est au-delà de toute conceptualisation humaine. Cela signifie que la connaissance de Dieu ne peut être obtenue que par la négation des attributs limités qui lui sont attribués par les êtres humains.&lt;/p&gt; &lt;p&gt;Bien qu'il soit un théologien chrétien, il a développé une vision panthéiste modérée dans laquelle Dieu est présent en toutes choses. Pour lui, la création est une manifestation de la volonté divine et une participation à la nature divine, mettant l'accent sur la participation de l'homme à la connaissance divine. Il croyait que la raison humaine est capable de comprendre certaines vérités divines, bien que de manière limitée, et que la véritable connaissance est atteinte par une participation active à la nature divine. &lt;/p&gt; &lt;p&gt;Il était également connu pour son approche audacieuse des questions théologiques et philosophiques. Par exemple, il était en avance sur son temps en soutenant l'idée de la prédestination universelle, qui affirme que Dieu veut le salut de tous les êtres humains. Cette vision a été controversée à son époque et a même été condamnée comme hérétique après sa mort.&lt;/p&gt;
 </t>
         </is>
       </c>
@@ -1376,8 +1353,7 @@
       </c>
       <c r="E13" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sylvestre_II"  style="color:#6A142A"  title=" Wikipedia"&gt; GERBERT d'Aurillac&lt;/a&gt;, également connu sous le nom du pape Sylvestre II, est une figure majeure du Moyen Âge, reconnu pour son érudition, ses contributions scientifiques et son influence politique. &lt;/p&gt;  &lt;p&gt; Il devient un enseignant renommé et attire des étudiants de toute l’Europe. Ses cours portent sur les arts libéraux &lt;a href="https://manuel-de-methodologie-historique.blog.tudchentil.org/trivium-et-quadrivium/" style="color:#88A1E9" title="Trivium et quadrivium par sfha "&gt;(le trivium et le quadrivium)&lt;/a&gt;, avec une attention particulière aux mathématiques, à l’astronomie et à la musique. &lt;/p&gt; 
-&lt;p&gt;Il est également connu pour avoir introduit en Europe l’usage de &lt;a href="https://alainbusser.github.io/primaire/html/gerbert1.html"  title="Abaque de Gebert "&gt;l’abaque de Gerbert&lt;/a&gt;, un outil de calcul inspiré des méthodes arabes, ainsi que pour avoir popularisé le chiffrement arabe (les chiffres dits "arabes", bien que leur adoption généralisée en Europe ait pris plusieurs siècles). &lt;/p&gt; &lt;p&gt; En 999, il est élu pape sous le nom de Sylvestre II. Il cherche à renforcer l’autorité papale et à réformer l’Église, soutient les efforts d’Otton III pour unifier l’Europe sous un empire chrétien et encourage les études scientifiques et la diffusion des connaissances. &lt;/p&gt;  &lt;p&gt; Il est souvent surnommé le &lt;a href="https://www.youtube.com/watch?v=onfmvvXjk08" title="Gebert d'Aurrillac par palacky "&gt;"pape savant" &lt;/a&gt;ou le "pape mathématicien". Son œuvre a joué un rôle clé dans la transmission des connaissances antiques et arabes à l’Europe médiévale, préparant le terrain pour la Renaissance du XIIe siècle. Né en Auvergne vers 945, moine au monastère d’Aurillac, il part étudier en Catalogne, proche des savoirs de l’Espagne musulmane. Maître de l’école de la cathédrale de Reims, il enseigne la logique d’Aristote et de Boèce. Précepteur du futur empereur Otton III, il devient archevêque de Reims, puis de Ravenne, avant d’être le premier pape français. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Sylvestre_II"  style="color:#6A142A"  title=" Wikipedia"&gt; GERBERT d'Aurillac&lt;/a&gt;, également connu sous le nom du pape Sylvestre II, est une figure majeure du Moyen Âge, reconnu pour son érudition, ses contributions scientifiques et son influence politique. &lt;/p&gt; &lt;p&gt; Il devient un enseignant renommé et attire des étudiants de toute l’Europe. Ses cours portent sur les arts libéraux &lt;a href="https://manuel-de-methodologie-historique.blog.tudchentil.org/trivium-et-quadrivium/" style="color:#88A1E9" title="Trivium et quadrivium par sfha "&gt;(le trivium et le quadrivium)&lt;/a&gt;, avec une attention particulière aux mathématiques, à l’astronomie et à la musique. &lt;/p&gt; &lt;p&gt;Il est également connu pour avoir introduit en Europe l’usage de &lt;a href="https://alainbusser.github.io/primaire/html/gerbert1.html"  title="Abaque de Gebert "&gt;l’abaque de Gerbert&lt;/a&gt;, un outil de calcul inspiré des méthodes arabes, ainsi que pour avoir popularisé le chiffrement arabe (les chiffres dits "arabes", bien que leur adoption généralisée en Europe ait pris plusieurs siècles). &lt;/p&gt; &lt;p&gt; En 999, il est élu pape sous le nom de Sylvestre II. Il cherche à renforcer l’autorité papale et à réformer l’Église, soutient les efforts d’Otton III pour unifier l’Europe sous un empire chrétien et encourage les études scientifiques et la diffusion des connaissances. &lt;/p&gt; &lt;p&gt; Il est souvent surnommé le &lt;a href="https://www.youtube.com/watch?v=onfmvvXjk08" title="Gebert d'Aurrillac par palacky "&gt;"pape savant" &lt;/a&gt;ou le "pape mathématicien". Son œuvre a joué un rôle clé dans la transmission des connaissances antiques et arabes à l’Europe médiévale, préparant le terrain pour la Renaissance du XIIe siècle. Né en Auvergne vers 945, moine au monastère d’Aurillac, il part étudier en Catalogne, proche des savoirs de l’Espagne musulmane. Maître de l’école de la cathédrale de Reims, il enseigne la logique d’Aristote et de Boèce. Précepteur du futur empereur Otton III, il devient archevêque de Reims, puis de Ravenne, avant d’être le premier pape français. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -1444,10 +1420,10 @@
       <c r="E14" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Abbon_de_Fleury"   title=" Wikipedia"&gt; ABBON de Fleury&lt;/a&gt;, également connu sous le nom d'Abbon de Saint-Benoît, est une figure intellectuelle et religieuse majeure du Xe siècle. Moine, érudit, enseignant et réformateur, il a joué un rôle important dans le renouveau culturel et spirituel de son époque. &lt;/p&gt; &lt;p&gt; Il se distingue rapidement par son intelligence et étudie &lt;a href="https://fr.wikipedia.org/wiki/Arts_lib%C3%A9raux" title="Les arts Liberaux par Wikipedia "&gt;les arts libéraux &lt;/a&gt; (le trivium et le quadrivium),  l’astronomie et les mathématiques ainsi que des textes sacrés et des œuvres des Pères de l’Église. &lt;/p&gt; &lt;p&gt; En 988, il est élu abbé de Fleury et, sous sa direction, l’abbaye connaît un âge d’or intellectuel et spirituel. Il renforce la bibliothèque, encourage la copie des manuscrits et attire des érudits de toute l’Europe. Il est également un médiateur habile dans les conflits politiques et religieux de l’époque. &lt;/p&gt; &lt;p&gt;  Ses œuvres reflètent sa vaste culture et son engagement pour la réforme. Parmi ses écrits les plus importants, on trouve : &lt;/p&gt;
-&lt;dd&gt; "Collectio canonum" : Un recueil de textes canoniques visant à renforcer l’autorité de l’Église et à promouvoir la réforme. &lt;/dd&gt;
-&lt;dd&gt;"Apologeticus" : Une défense des droits et des privilèges des moines face aux empiètements des évêques et des seigneurs.&lt;/dd&gt;
-&lt;dd&gt; &lt;a href="https://www.persee.fr/doc/alma_0994-8090_1979_num_42_1_1876"  title="Quaestiones grammaticales par Persée "&gt;"Quaestiones grammaticales"  &lt;/a&gt;: Un traité de grammaire qui témoigne de son intérêt pour les arts libéraux.&lt;/dd&gt;
-&lt;dd&gt;"Vie de saint Edmond" : Une hagiographie du roi martyr Edmond d’East Anglie, qui reflète son engagement spirituel et moral.&lt;/dd&gt;   &lt;p&gt; Abbon a contribué à préserver et à transmettre les connaissances antiques et médiévales, tout en promouvant la réforme de l’Église et des monastères. Son engagement pour l’éducation et la rigueur morale a influencé des générations de moines et d’érudits.&lt;/p&gt; </t>
+&lt;p&gt; "Collectio canonum" : Un recueil de textes canoniques visant à renforcer l’autorité de l’Église et à promouvoir la réforme. &lt;/p&gt;
+&lt;p&gt;"Apologeticus" : Une défense des droits et des privilèges des moines face aux empiètements des évêques et des seigneurs.&lt;/p&gt;
+&lt;p&gt; &lt;a href="https://www.persee.fr/doc/alma_0994-8090_1979_num_42_1_1876"  title="Quaestiones grammaticales par Persée "&gt;"Quaestiones grammaticales"  &lt;/a&gt;: Un traité de grammaire qui témoigne de son intérêt pour les arts libéraux.&lt;/p&gt;
+&lt;p&gt;"Vie de saint Edmond" : Une hagiographie du roi martyr Edmond d’East Anglie, qui reflète son engagement spirituel et moral.&lt;/p&gt; &lt;p&gt; Abbon a contribué à préserver et à transmettre les connaissances antiques et médiévales, tout en promouvant la réforme de l’Église et des monastères. Son engagement pour l’éducation et la rigueur morale a influencé des générations de moines et d’érudits.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F14" s="30" t="inlineStr">
@@ -1579,7 +1555,7 @@
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/B%C3%A9renger_de_Tours"   title=" Wikipedia"&gt; BERENGER de Tours&lt;/a&gt;  est une figure importante de l'histoire intellectuelle et religieuse du Moyen Âge surtout connu pour ses positions théologiques controversées, en particulier sur la question de la présence réelle du Christ dans &lt;a href="https://shs.cairn.info/revue-des-sciences-philosophiques-et-theologiques-2011-2-page-303?lang=fr"  title="Querelle eucharistique par Cairn "&gt;l'Eucharistie.  &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Au XIe siècle, la doctrine de la transsubstantiation, qui affirme que le pain et le vin deviennent réellement le corps et le sang du Christ lors de la consécration, commençait à se formaliser. Pour lui, le pain et le vin conservaient leur substance matérielle après la consécration, et la présence du Christ était spirituelle plutôt que physique. &lt;/p&gt;   &lt;p&gt; Il est considéré comme un précurseur du rationalisme théologique, un courant qui cherche à concilier la foi chrétienne avec la raison et la logique. Il s'appuie sur des arguments rationnels pour interpréter les Écritures et les doctrines de l'Église, plutôt que de se contenter d'une acceptation littérale ou traditionnelle. &lt;/p&gt;&lt;p&gt;Bérenger utilise la dialectique, une méthode de raisonnement et de débat, pour défendre ses positions théologiques. Cette approche méthodique et logique préfigure la méthode scolastique, qui deviendra dominante dans les universités médiévales à partir du XIIe siècle. La scolastique cherche à résoudre les contradictions apparentes entre la foi et la raison en utilisant des arguments logiques et philosophiques. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/B%C3%A9renger_de_Tours"   title=" Wikipedia"&gt; BERENGER de Tours&lt;/a&gt;  est une figure importante de l'histoire intellectuelle et religieuse du Moyen Âge surtout connu pour ses positions théologiques controversées, en particulier sur la question de la présence réelle du Christ dans &lt;a href="https://shs.cairn.info/revue-des-sciences-philosophiques-et-theologiques-2011-2-page-303?lang=fr"  title="Querelle eucharistique par Cairn "&gt;l'Eucharistie.  &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Au XIe siècle, la doctrine de la transsubstantiation, qui affirme que le pain et le vin deviennent réellement le corps et le sang du Christ lors de la consécration, commençait à se formaliser. Pour lui, le pain et le vin conservaient leur substance matérielle après la consécration, et la présence du Christ était spirituelle plutôt que physique. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur du rationalisme théologique, un courant qui cherche à concilier la foi chrétienne avec la raison et la logique. Il s'appuie sur des arguments rationnels pour interpréter les Écritures et les doctrines de l'Église, plutôt que de se contenter d'une acceptation littérale ou traditionnelle. &lt;/p&gt;&lt;p&gt;Bérenger utilise la dialectique, une méthode de raisonnement et de débat, pour défendre ses positions théologiques. Cette approche méthodique et logique préfigure la méthode scolastique, qui deviendra dominante dans les universités médiévales à partir du XIIe siècle. La scolastique cherche à résoudre les contradictions apparentes entre la foi et la raison en utilisant des arguments logiques et philosophiques. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
@@ -1645,13 +1621,10 @@
       </c>
       <c r="E17" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Damien"  style="color:#6A142A"  title=" Wikipedia"&gt; Saint Pierre DAMIEN&lt;/a&gt;, était un moine, cardinal, théologien italien et réformateur de l'Église catholique. Il est l'une des figures majeures de &lt;a href="https://www.persee.fr/doc/rhef_0300-9505_1926_num_12_55_2390" style="color:#88A1E9" title="Réforme grégorienne par Presée "&gt;la réforme grégorienne&lt;/a&gt;,  aux côtés de figures comme le pape Grégoire VII et saint Hugues de Cluny. Un mouvement visant à purifier l'Église de ses abus et à renforcer la discipline ecclésiastique. Canonisé en 1828, il est également reconnu comme &lt;a href="https://nominis.cef.fr/contenus/saint/681/Saint-Pierre-Damien.html" style="color:#88A1E9" title="Pierre Damien Docteur de l'église par Omminis "&gt;Docteur de l'Église&lt;/a&gt; depuis 1828. &lt;/p&gt; &lt;p&gt; Il est un ardent défenseur de l'ascèse et de la pénitence et croit que la purification personnelle est essentielle pour atteindre la sainteté et réformer l'Église. Il est l'un des principaux promoteurs du célibat des prêtres, qu'il considère comme un moyen de préserver la pureté et l'intégrité du clergé et prône un retour à une observance stricte de la Règle de saint Benoît et à une vie de pauvreté, de prière et de solitude. &lt;/p&gt; &lt;p&gt; Ses œuvres reflètent ses préoccupations spirituelles, théologiques et réformatrices. Parmi ses écrits les plus importants, on trouve : &lt;/p&gt;
-&lt;dd&gt;"Liber Gomorrhianus"  &lt;a href="https://journals.openedition.org/ccm/13758"  title="Infos Livre des Gomorrhe de l'église par Open editions "&gt;(Livre de Gomorrhe)&lt;/a&gt; :
-Un traité sévère dénonçant les vices du clergé, en particulier la sodomie et d'autres pratiques immorales. Ce texte a suscité des controverses mais a contribué à la réforme des mœurs ecclésiastiques. &lt;/dd&gt;
-&lt;dd&gt;"De la Divine Toute-Puissance" :
-Une réflexion théologique sur la puissance de Dieu et les limites de la raison humaine. Il y défend l'idée que Dieu peut accomplir des choses qui semblent impossibles aux hommes. &lt;/dd&gt;
-&lt;dd&gt;"Vie de saint Romuald" :
-Une biographie de saint Romuald, fondateur des Camaldules, qui met en avant les idéaux de la vie érémitique et de la réforme monastique. &lt;/dd&gt;   &lt;p&gt; Saint Pierre Damien est une figure majeure de l'histoire de l'Église médiévale. &lt;a href="https://www.youtube.com/watch?v=j6Cc5BVq--s&amp;list=PLlJpcv8AbXH3FSwxMejZmFK-j3IojD0Dw&amp;index=10" style="color:#88A1E9" title="Pierre Damien, sa vie par La Sapiniere "&gt;Son engagement&lt;/a&gt; pour la réforme, sa profonde spiritualité et ses écrits théologiques en font un modèle de sainteté et un défenseur infatigable de la pureté de l'Église. Son héritage continue d'inspirer les chrétiens, en particulier ceux engagés dans la vie monastique et la réforme ecclésiastique. &lt;/p&gt;     &lt;audio controls title="Saint Pierre Damien: le livre de gomorrhe par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11739-22.02.2021-ITEMA_22581586-2021F53451E0035-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_Damien"  style="color:#6A142A"  title=" Wikipedia"&gt; Saint Pierre DAMIEN&lt;/a&gt;, était un moine, cardinal, théologien italien et réformateur de l'Église catholique. Il est l'une des figures majeures de &lt;a href="https://www.persee.fr/doc/rhef_0300-9505_1926_num_12_55_2390" style="color:#88A1E9" title="Réforme grégorienne par Presée "&gt;la réforme grégorienne&lt;/a&gt;,  aux côtés de figures comme le pape Grégoire VII et saint Hugues de Cluny. Un mouvement visant à purifier l'Église de ses abus et à renforcer la discipline ecclésiastique. Canonisé en 1828, il est également reconnu comme &lt;a href="https://nominis.cef.fr/contenus/saint/681/Saint-Pierre-Damien.html" style="color:#88A1E9" title="Pierre Damien Docteur de l'église par Omminis "&gt;Docteur de l'Église&lt;/a&gt; depuis 1828. &lt;/p&gt; &lt;p&gt; Il est un ardent défenseur de l'ascèse et de la pénitence et croit que la purification personnelle est essentielle pour atteindre la sainteté et réformer l'Église. Il est l'un des principaux promoteurs du célibat des prêtres, qu'il considère comme un moyen de préserver la pureté et l'intégrité du clergé et prône un retour à une observance stricte de la Règle de saint Benoît et à une vie de pauvreté, de prière et de solitude. &lt;/p&gt; &lt;p&gt; Ses œuvres reflètent ses préoccupations spirituelles, théologiques et réformatrices. Parmi ses écrits les plus importants, on trouve : &lt;/p&gt; &lt;p&gt;"Liber Gomorrhianus"  &lt;a href="https://journals.openedition.org/ccm/13758"  title="Infos Livre des Gomorrhe de l'église par Open editions "&gt;(Livre de Gomorrhe)&lt;/a&gt; :
+Un traité sévère dénonçant les vices du clergé, en particulier la sodomie et d'autres pratiques immorales. Ce texte a suscité des controverses mais a contribué à la réforme des mœurs ecclésiastiques. &lt;/p&gt; &lt;p&gt;"De la Divine Toute-Puissance" :
+Une réflexion théologique sur la puissance de Dieu et les limites de la raison humaine. Il y défend l'idée que Dieu peut accomplir des choses qui semblent impossibles aux hommes. &lt;/p&gt; &lt;p&gt;"Vie de saint Romuald" :
+Une biographie de saint Romuald, fondateur des Camaldules, qui met en avant les idéaux de la vie érémitique et de la réforme monastique. &lt;/p&gt; &lt;p&gt; Saint Pierre Damien est une figure majeure de l'histoire de l'Église médiévale. &lt;a href="https://www.youtube.com/watch?v=j6Cc5BVq--s&amp;list=PLlJpcv8AbXH3FSwxMejZmFK-j3IojD0Dw&amp;index=10" style="color:#88A1E9" title="Pierre Damien, sa vie par La Sapiniere "&gt;Son engagement&lt;/a&gt; pour la réforme, sa profonde spiritualité et ses écrits théologiques en font un modèle de sainteté et un défenseur infatigable de la pureté de l'Église. Son héritage continue d'inspirer les chrétiens, en particulier ceux engagés dans la vie monastique et la réforme ecclésiastique. &lt;/p&gt;     &lt;audio controls title="Saint Pierre Damien: le livre de gomorrhe par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11739-22.02.2021-ITEMA_22581586-2021F53451E0035-22.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
@@ -1718,11 +1691,11 @@
       </c>
       <c r="E18" s="32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Otloh_de_Saint-Emmeram"  title=" Wikipedia"&gt; OTLOH  de St Emmeran&lt;/a&gt;, était un moine bénédictin Italien, écrivain et théologien,  principalement connu pour ses écrits spirituels et théologiques, ainsi que pour son engagement dans la réforme monastique de son époque. &lt;/p&gt;  &lt;p&gt;  Il vécu à une époque de grands bouleversements dans l'Église médiévale, marquée par &lt;a href="https://www.persee.fr/doc/rhef_0300-9505_1926_num_12_55_2390"  title="Réforme grégorienne par Presée "&gt;la réforme grégorienne&lt;/a&gt;, qui visait à renforcer la discipline ecclésiastique et à lutter contre la simonie (la vente des charges ecclésiastiques) et le nicolaïsme (le non-respect du célibat des clercs). Ces réformes ont également touché les monastères, où l'on cherchait à restaurer une observance stricte de la Règle de saint Benoît. &lt;/p&gt;  &lt;p&gt; Il est profondément influencé par la tradition bénédictine et par les écrits des Pères de l'Église, en particulier saint Augustin. Sa spiritualité est centrée sur la recherche de Dieu à travers la prière, la méditation des Écritures et l'ascèse. Il insiste sur l'importance de la conversion intérieure et de la lutte contre les péchés et les tentations. &lt;/p&gt; &lt;p&gt; Otloh est un auteur prolifique, et ses écrits reflètent ses préoccupations spirituelles et théologiques. Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt;
-&lt;dd&gt;"Liber visionum" (Livre des visions) : Un recueil de visions et de révélations mystiques, qui témoigne de la spiritualité intense d'Otloh et de son intérêt pour l'expérience religieuse personnelle.&lt;/dd&gt;  &lt;dd&gt;"De doctrina spirituali" (De la doctrine spirituelle) : Un traité sur la vie spirituelle, qui insiste sur l'importance de la prière, de la méditation et de l'ascèse pour atteindre la perfection spirituelle. &lt;/dd&gt;
-&lt;dd&gt;"Vita sancti Wolfgangi" (Vie de saint Wolfgang) : Une hagiographie de saint Wolfgang, évêque de Ratisbonne, qui reflète l'idéal de sainteté et de réforme ecclésiastique d'Otloh. &lt;/dd&gt;
-&lt;dd&gt;"Dialogus de tribus quaestionibus" (Dialogue sur trois questions) : Un dialogue théologique qui aborde des questions complexes sur la nature de Dieu, la grâce et le libre arbitre.&lt;/dd&gt;
-&lt;dd&gt;"Liber de temptatione cuiusdam monachi" &lt;a href="https://www.persee.fr/doc/bsnaf_0081-1181_2015_num_2013_1_12128"  title="Les visions de Otloh par Persée "&gt;(Livre sur la tentation d'un certain moine)&lt;/a&gt;  : Un texte autobiographique dans lequel Otloh décrit ses propres luttes spirituelles et ses tentations, offrant un aperçu rare de la vie intérieure d'un moine médiéval.&lt;/dd&gt;   &lt;p&gt; Il est une des figures importantes de la réforme monastique du XIe siècle. Ses écrits ont eu une influence durable sur la spiritualité monastique et ont contribué à façonner la pensée religieuse de son époque. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Otloh_de_Saint-Emmeram"  title=" Wikipedia"&gt; OTLOH  de St Emmeran&lt;/a&gt;, était un moine bénédictin Italien, écrivain et théologien,  principalement connu pour ses écrits spirituels et théologiques, ainsi que pour son engagement dans la réforme monastique de son époque. &lt;/p&gt; &lt;p&gt;  Il vécu à une époque de grands bouleversements dans l'Église médiévale, marquée par &lt;a href="https://www.persee.fr/doc/rhef_0300-9505_1926_num_12_55_2390"  title="Réforme grégorienne par Presée "&gt;la réforme grégorienne&lt;/a&gt;, qui visait à renforcer la discipline ecclésiastique et à lutter contre la simonie (la vente des charges ecclésiastiques) et le nicolaïsme (le non-respect du célibat des clercs). Ces réformes ont également touché les monastères, où l'on cherchait à restaurer une observance stricte de la Règle de saint Benoît. &lt;/p&gt; &lt;p&gt; Il est profondément influencé par la tradition bénédictine et par les écrits des Pères de l'Église, en particulier saint Augustin. Sa spiritualité est centrée sur la recherche de Dieu à travers la prière, la méditation des Écritures et l'ascèse. Il insiste sur l'importance de la conversion intérieure et de la lutte contre les péchés et les tentations. &lt;/p&gt; &lt;p&gt; Otloh est un auteur prolifique, et ses écrits reflètent ses préoccupations spirituelles et théologiques. Parmi ses œuvres les plus importantes, on peut citer : &lt;/p&gt;
+&lt;p&gt;"Liber visionum" (Livre des visions) : Un recueil de visions et de révélations mystiques, qui témoigne de la spiritualité intense d'Otloh et de son intérêt pour l'expérience religieuse personnelle.&lt;/p&gt; &lt;p&gt;"De doctrina spirituali" (De la doctrine spirituelle) : Un traité sur la vie spirituelle, qui insiste sur l'importance de la prière, de la méditation et de l'ascèse pour atteindre la perfection spirituelle. &lt;/p&gt;
+&lt;p&gt;"Vita sancti Wolfgangi" (Vie de saint Wolfgang) : Une hagiographie de saint Wolfgang, évêque de Ratisbonne, qui reflète l'idéal de sainteté et de réforme ecclésiastique d'Otloh. &lt;/p&gt;
+&lt;p&gt;"Dialogus de tribus quaestionibus" (Dialogue sur trois questions) : Un dialogue théologique qui aborde des questions complexes sur la nature de Dieu, la grâce et le libre arbitre.&lt;/p&gt;
+&lt;p&gt;"Liber de temptatione cuiusdam monachi" &lt;a href="https://www.persee.fr/doc/bsnaf_0081-1181_2015_num_2013_1_12128"  title="Les visions de Otloh par Persée "&gt;(Livre sur la tentation d'un certain moine)&lt;/a&gt;  : Un texte autobiographique dans lequel Otloh décrit ses propres luttes spirituelles et ses tentations, offrant un aperçu rare de la vie intérieure d'un moine médiéval.&lt;/p&gt; &lt;p&gt; Il est une des figures importantes de la réforme monastique du XIe siècle. Ses écrits ont eu une influence durable sur la spiritualité monastique et ont contribué à façonner la pensée religieuse de son époque. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F18" s="30" t="inlineStr">
@@ -2252,10 +2225,9 @@
       <c r="E26" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Bernard_de_Clairvaux"  style=  title=" Wikipedia"&gt;BERNARD de Clairvaux&lt;/a&gt; est une figure marquante du XIIe siècle, tant sur le plan religieux que politique. Moine cistercien, mystique, réformateur, théologien et conseiller influent, il a joué un rôle central dans l'Église catholique et dans la société médiévale. &lt;/p&gt; &lt;p&gt; Il est un ardent et très influent défenseur de la réforme Grégorienne de l'Église et il s'oppose fermement à la corruption et à l'accumulation de richesses par le clergé. Il critique également les excès de la scolastique naissante, privilégiant une approche plus mystique et contemplative de la foi. &lt;/p&gt; &lt;p&gt; Il est l'auteur de nombreux traités théologiques et spirituels, dont les plus célèbres sont : &lt;/p&gt;
-&lt;dd&gt;"De l'amour de Dieu" (De diligendo Deo), où il explore la nature de l'amour divin et son rôle dans la vie spirituelle. &lt;/dd&gt;
-&lt;dd&gt;&lt;a href="https://www.youtube.com/watch?v=uo94zAU5RnU"  title="Sermons sur le Cantique par Sanctus"&gt;"Sermons sur le Cantique des Cantiques"&lt;/a&gt;, une œuvre mystique qui interprète ce livre biblique comme une allégorie de l'union de l'âme avec Dieu.&lt;/dd&gt;
-&lt;dd&gt;"De la grâce et du libre arbitre", où il aborde les questions de la prédestination et de la liberté humaine.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt;
-&lt;p&gt; Il fut co-fondateur de l'ordre des Templiers et le premier investigateur du le lancement de la &lt;a href="https://www.youtube.com/watch?v=jvRDaQ81vZc" title="Bernard de Clairvaux , la 2ème croisade par Coursitou "&gt;deuxième croissade. &lt;/a&gt; &lt;/p&gt;  &lt;p&gt; Canonisé en 1174, il est déclaré docteur de l'Église en 1830. Il a contribué à l'expansion de l'ordre cistercien et ses écrits ont profondément marqué la spiritualité chrétienne, inspirant des figures comme saint François d'Assise et saint Thomas d'Aquin.  Il est considéré comme l'un des grands mystiques du christianisme, ayant approfondi la compréhension de l'amour divin et de la relation entre l'homme et Dieu. &lt;/p&gt;    &lt;audio controls title="Saint Bertrand de Clairvaux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22636-10.04.2022-ITEMA_22990601-2022B45498S0100-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+&lt;p&gt;"De l'amour de Dieu" (De diligendo Deo), où il explore la nature de l'amour divin et son rôle dans la vie spirituelle. &lt;/p&gt;
+&lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=uo94zAU5RnU"  title="Sermons sur le Cantique par Sanctus"&gt;"Sermons sur le Cantique des Cantiques"&lt;/a&gt;, une œuvre mystique qui interprète ce livre biblique comme une allégorie de l'union de l'âme avec Dieu.&lt;/p&gt;
+&lt;p&gt;"De la grâce et du libre arbitre", où il aborde les questions de la prédestination et de la liberté humaine.&lt;/p&gt; &lt;p&gt; Il fut co-fondateur de l'ordre des Templiers et le premier investigateur du le lancement de la &lt;a href="https://www.youtube.com/watch?v=jvRDaQ81vZc" title="Bernard de Clairvaux , la 2ème croisade par Coursitou "&gt;deuxième croissade. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Canonisé en 1174, il est déclaré docteur de l'Église en 1830. Il a contribué à l'expansion de l'ordre cistercien et ses écrits ont profondément marqué la spiritualité chrétienne, inspirant des figures comme saint François d'Assise et saint Thomas d'Aquin.  Il est considéré comme l'un des grands mystiques du christianisme, ayant approfondi la compréhension de l'amour divin et de la relation entre l'homme et Dieu. &lt;/p&gt;    &lt;audio controls title="Saint Bertrand de Clairvaux par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/22636-10.04.2022-ITEMA_22990601-2022B45498S0100-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F26" s="30" t="inlineStr">
@@ -2393,7 +2365,7 @@
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugues_de_Saint-Victor"  style=  title=" Wikipedia"&gt;HUGUES de Saint Victor&lt;/a&gt; était à la fois philosophe, théologien et pédagogue, souvent présenté comme une figure majeure de l’école   &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1960_num_34_1_2248" title="les origines de huges de st victor par persée  "&gt;de Saint-Victor à Paris&lt;/a&gt;. Sa philosophie cherche à organiser tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance n’est pas une fin en soi : elle prépare l’âme à une vie spirituelle plus haute. C’est pourquoi il accorde une grande importance aux arts libéraux, à la lecture, à l’étude méthodique et à l’éducation intellectuelle, dans &lt;a href="https://www.youtube.com/watch?v=A65kiTkbMNU" title="hugh of st victor’s Didascalicon par Cut the Fluff "&gt;son Didascalicon. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Un point central de sa pensée est l’union entre raison et foi. Il ne méprise pas la raison, mais il estime qu’elle a ses limites et qu’elle doit servir à comprendre ce que la foi révèle. Il se méfie d’une dialectique trop querelleuse et préfère une démarche plus ordonnée, plus humble et plus tournée vers l’édification intérieure. &lt;/p&gt; &lt;p&gt; Sa philosophie est aussi profondément spirituelle et mystique. Il décrit l’ascension de l’âme vers Dieu à travers un mouvement en plusieurs étapes, souvent résumé par la progression de la pensée, de la méditation et de la contemplation. Chez lui, la contemplation n’est pas une fuite du monde, mais l’aboutissement d’un travail patient sur soi, sur le savoir et sur la prière. &lt;/p&gt; &lt;p&gt; Il a marqué durablement la pensée médiévale parce qu’il veut tout relier : savoirs, morale, vie intérieure et histoire du salut. On peut dire qu’il incarne une philosophie de l’ordre, de l’apprentissage total et de la montée graduelle vers la vérité, ce qui lui a valu une grande influence au Moyen Âge. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugues_de_Saint-Victor"  style=  title=" Wikipedia"&gt;HUGUES de Saint Victor&lt;/a&gt; était à la fois philosophe, théologien et pédagogue, souvent présenté comme une figure majeure de l’école   &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1960_num_34_1_2248" title="les origines de huges de st victor par persée  "&gt;de Saint-Victor à Paris&lt;/a&gt;. Sa philosophie cherche à organiser tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance n’est pas une fin en soi : elle prépare l’âme à une vie spirituelle plus haute. C’est pourquoi il accorde une grande importance aux arts libéraux, à la lecture, à l’étude méthodique et à l’éducation intellectuelle, dans &lt;a href="https://www.youtube.com/watch?v=A65kiTkbMNU" title="hugh of st victor’s Didascalicon par Cut the Fluff "&gt;son Didascalicon. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Un point central de sa pensée est l’union entre raison et foi. Il ne méprise pas la raison, mais il estime qu’elle a ses limites et qu’elle doit servir à comprendre ce que la foi révèle. Il se méfie d’une dialectique trop querelleuse et préfère une démarche plus ordonnée, plus humble et plus tournée vers l’édification intérieure. &lt;/p&gt; &lt;p&gt; Sa philosophie est aussi profondément spirituelle et mystique. Il décrit l’ascension de l’âme vers Dieu à travers un mouvement en plusieurs étapes, souvent résumé par la progression de la pensée, de la méditation et de la contemplation. Chez lui, la contemplation n’est pas une fuite du monde, mais l’aboutissement d’un travail patient sur soi, sur le savoir et sur la prière. &lt;/p&gt; &lt;p&gt; Il a marqué durablement la pensée médiévale parce qu’il veut tout relier : savoirs, morale, vie intérieure et histoire du salut. Il incarne une philosophie de l’ordre, de l’apprentissage total et de la montée graduelle vers la vérité, ce qui lui a valu une grande influence au Moyen Âge. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -2994,7 +2966,7 @@
       </c>
       <c r="E37" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_de_Hales"    title=" Wikipedia"&gt;Alexandre de HALES&lt;/a&gt; était un philosophe scolastique anglais considéré comme le premier grand maître franciscain à l'Université de Paris et surnommé "Doctor irrefragabilis admodum". Maître des arts dès 1209-1210 à Paris, il enseigne la philosophie avant les interdictions temporaires des textes aristotéliciens. &lt;/p&gt; &lt;p&gt; Précurseur du scotisme et du  &lt;a href="https://fr.wikipedia.org/wiki/Histoire_des_ordres_franciscains" title=" ordres des franciscains  par Wikipedia"&gt;franciscanisme &lt;/a&gt; intellectuel, il intègre Aristote avec Augustin, développant des doctrines comme le caractère indélébile des sacrements et le trésor des mérites des saints. Il défend une vision augustinienne de l'illumination divine et pose les bases théologiques pour l'ordre franciscain, notamment dans l'interprétation de la règle de saint François. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=lfzyS3RdRl0&amp;t=174s"  title=" Alexandre de Hales Biographies Fr par Christopher Santos Côté"&gt;Ses oeuvres  &lt;/a&gt; principales sont : - "Sa Summa theologica"  achevée par ses élèves comme Jean de la Rochelle et Guillaume de Melitona, est la première somme théologique systématique franciscaine, structurée en thèse-antithèse-synthèse avec citations variées (Bible, Pères, philosophes arabes et grecs). Elle traite de Dieu et ses attributs (livre I), de la Création et du péché (II), de la rédemption (III), et des sacrements (IV), influençant profondément la scolastique. &lt;/p&gt; &lt;p&gt; Son œuvre, imprimée dès 1475, marque la transition vers la grande scolastique du XIIIe siècle et reste une référence pour la théologie franciscaine. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_de_Hales"    title=" Wikipedia"&gt;Alexandre de HALES&lt;/a&gt; était un philosophe scolastique anglais considéré comme le premier grand maître franciscain à l'Université de Paris et surnommé "Doctor irrefragabilis admodum". Maître des arts dès 1209-1210 à Paris, il enseigne la philosophie avant les interdictions temporaires des textes aristotéliciens. &lt;/p&gt; &lt;p&gt; Précurseur du scotisme et du  &lt;a href="https://fr.wikipedia.org/wiki/Histoire_des_ordres_franciscains" title=" ordres des franciscains  par Wikipedia"&gt;franciscanisme &lt;/a&gt; intellectuel, il intègre Aristote avec Augustin, développant des doctrines comme le caractère indélébile des sacrements et le trésor des mérites des saints. Il défend une vision augustinienne de l'illumination divine et pose les bases théologiques pour l'ordre franciscain, notamment dans l'interprétation de la règle de saint François. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=lfzyS3RdRl0&amp;t=174s"  title=" Alexandre de Hales Biographies Fr par Christopher Santos Côté"&gt;Ses oeuvres  &lt;/a&gt; principales sont : "Sa Summa theologica"  achevée par ses élèves comme Jean de la Rochelle et Guillaume de Melitona, est la première somme théologique systématique franciscaine, structurée en thèse-antithèse-synthèse avec citations variées (Bible, Pères, philosophes arabes et grecs). Elle traite de Dieu et ses attributs (livre I), de la Création et du péché (II), de la rédemption (III), et des sacrements (IV), influençant profondément la scolastique. &lt;/p&gt; &lt;p&gt; Son œuvre, imprimée dès 1475, marque la transition vers la grande scolastique du XIIIe siècle et reste une référence pour la théologie franciscaine. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F37" s="30" t="inlineStr">
@@ -3060,7 +3032,7 @@
       </c>
       <c r="E38" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_d%27Auvergne"  style="color:#6A142A"  title=" Wikipedia"&gt;Guillaume D'AUVERGNE&lt;/a&gt; était un philosophe scolastique français, évêque de Paris et conseiller de saint Louis. Il est l’un des premiers &lt;a href="https://www.persee.fr/doc/rjuiv_0484-8616_1880_num_1_1_6298_t2_0140_0000_5" style="color:#88A1E9" title="Guillaume d'Auvergne, évêque de Paris (1228-1249), sa vie et ses ouvrages ; thèse de doctorat présentée à la Faculté des lettres de Paris, par M. Noël Valois, licencié ès lettres et en droit, archiviste-paléographe, 1880  par Persée"&gt;maîtres parisiens &lt;/a&gt; à intégrer de manière systématique la philosophie d’Aristote dans une synthèse encore très marquée par saint Augustin, ce qui en fait une figure de transition entre l’augustinisme ancien et la scolastique "aristotélisée". &lt;/p&gt; &lt;p&gt;  Il est souvent décrite comme une tentative de synthèse entre l’augustinisme théologique et une ontologie aristotélicienne passée par le filtre néoplatonicien d’Avicenne : cette intégration des sources arabes et antiques est encore intuitive et parfois ambiguë, mais elle prépare la grande scolastique (Albert le Grand, Thomas d’Aquin). Sa réflexion sur magie et religion est particulièrement originale : en opposant signe magique et signe sacramentel comme deux usages symétriques du signe, il lie la question de la causalité spirituelle aux notions de pacte, de volonté et d’agentivité, ce qui a attiré l’attention de recherches récentes sur l’histoire de la magie et des sciences "secrètes". &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - "De legibus" écrit vers 1228‑1230, examine la loi divine, naturelle et humaine et propose une théorie originale des sacrements : le signe sacramentel fonctionne comme le contraire exact d’un signe magique, celui‑ci reposant sur un pacte avec le diable alors que le sacrement repose sur un pacte avec le Christ. - "De primo principio" traite du "premier principe", c’est‑à‑dire de Dieu comme Trinité, en articulant arguments philosophiques et dogme trinitaire chrétien. - "De anima" écrit en 1230 aborde la nature de l’âme humaine et de ses puissances, dans le cadre de la réception d’Aristote, tandis que "De universo creaturarum" paru en 1231 propose une vaste cosmologie de l’univers des créatures. &lt;/p&gt; &lt;p&gt; En tant qu’évêque de Paris et maître en théologie, Guillaume se trouve au centre de la première phase de la scolastique parisienne "aristotélisante" et fournit un cadre doctrinal qui influencera des auteurs comme Bonaventure ou Thomas d’Aquin, même lorsqu’ils s’en démarquent. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Guillaume_d%27Auvergne"  style="color:#6A142A"  title=" Wikipedia"&gt;Guillaume D'AUVERGNE&lt;/a&gt; était un philosophe scolastique français, évêque de Paris et conseiller de saint Louis. Il est l’un des premiers &lt;a href="https://www.persee.fr/doc/rjuiv_0484-8616_1880_num_1_1_6298_t2_0140_0000_5" style="color:#88A1E9" title="Guillaume d'Auvergne, évêque de Paris (1228-1249), sa vie et ses ouvrages ; thèse de doctorat présentée à la Faculté des lettres de Paris, par M. Noël Valois, licencié ès lettres et en droit, archiviste-paléographe, 1880  par Persée"&gt;maîtres parisiens &lt;/a&gt; à intégrer de manière systématique la philosophie d’Aristote dans une synthèse encore très marquée par saint Augustin, ce qui en fait une figure de transition entre l’augustinisme ancien et la scolastique "aristotélisée". &lt;/p&gt; &lt;p&gt;  Il est souvent décrite comme une tentative de synthèse entre l’augustinisme théologique et une ontologie aristotélicienne passée par le filtre néoplatonicien d’Avicenne : cette intégration des sources arabes et antiques est encore intuitive et parfois ambiguë, mais elle prépare la grande scolastique (Albert le Grand, Thomas d’Aquin). Sa réflexion sur magie et religion est particulièrement originale : en opposant signe magique et signe sacramentel comme deux usages symétriques du signe, il lie la question de la causalité spirituelle aux notions de pacte, de volonté et d’agentivité, ce qui a attiré l’attention de recherches récentes sur l’histoire de la magie et des sciences "secrètes". &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "De legibus" écrit vers 1228‑1230, examine la loi divine, naturelle et humaine et propose une théorie originale des sacrements : le signe sacramentel fonctionne comme le contraire exact d’un signe magique, celui‑ci reposant sur un pacte avec le diable alors que le sacrement repose sur un pacte avec le Christ. "De primo principio" traite du "premier principe", c’est‑à‑dire de Dieu comme Trinité, en articulant arguments philosophiques et dogme trinitaire chrétien. "De anima" écrit en 1230 aborde la nature de l’âme humaine et de ses puissances, dans le cadre de la réception d’Aristote, tandis que "De universo creaturarum" paru en 1231 propose une vaste cosmologie de l’univers des créatures. &lt;/p&gt; &lt;p&gt; En tant qu’évêque de Paris et maître en théologie, Guillaume se trouve au centre de la première phase de la scolastique parisienne "aristotélisante" et fournit un cadre doctrinal qui influencera des auteurs comme Bonaventure ou Thomas d’Aquin, même lorsqu’ils s’en démarquent. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F38" s="30" t="inlineStr">
@@ -3127,7 +3099,7 @@
       </c>
       <c r="E39" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_La_Rochelle"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean de La Rochelle&lt;/a&gt; était un philosophe franciscain français disciple direct d'Alexandre de Hales et figure clé de la scolastique parisienne précoce. Il collabore étroitement avec lui à la "Summa theologica", à laquelle il contribue ; maître et disciple meurent tous deux en 1245, et l'ouvrage sera achevé par d'autres franciscains. &lt;/p&gt; &lt;p&gt; Précurseur du franciscanisme intellectuel, il défend la théologie comme sagesse unissant connaissance, sainteté et enseignement, incarnant une approche augustinienne face à l'aristotélisme naissant. &lt;/p&gt; &lt;p&gt;  Innovant en philosophie de l'âme, il organise les  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1964_num_38_4_2400_t1_0422_0000_2" style="color:#88A1E9" title=" Jean de la Rochelle, Tractatus de divisione multiplici potentiarum animae. Texte critique avec introduction, notes et tables, par Pierre Michaud-Quantin, Textes philosophiques du moyen âge XI, 1964 par Persée"&gt;autorités&lt;/a&gt;, c'est-à-dire les textes de référence, en analysant leurs vocabulaires concurrents, posant les bases pour Bonaventure et influençant la scolastique. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : - "Summa de anima" écrit vers  1235 : Traite de l'âme selon les quatre causes aristotéliciennes, distinguant une âme supérieure (spirituelle) et inférieure (corporelle), en débat avec les théories matérialistes. - "Tractatus de divisione potentiarum animae" écrit vers 1233  : Analyse détaillée des divisions de l'âme, intégrant Platon, Aristote, Avicenne et Augustin pour clarifier les sources philosophiques nouvelles. Jean de La Rochelle est en effet l’un des premiers, à Paris, à intégrer dans la théologie la psychologie d’Avicenne, récemment traduite de l’arabe : il distingue avec lui les sens externes, les sens internes, comme l’imagination et la mémoire, et les puissances de l’intellect. Il enseigne avec Alexandre de Hales, dès 1238, la première école franciscaine de l’université de Paris. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_La_Rochelle"  style="color:#6A142A"  title=" Wikipedia"&gt;Jean de La Rochelle&lt;/a&gt; était un philosophe franciscain français disciple direct d'Alexandre de Hales et figure clé de la scolastique parisienne précoce. Il collabore étroitement avec lui à la "Summa theologica", à laquelle il contribue ; maître et disciple meurent tous deux en 1245, et l'ouvrage sera achevé par d'autres franciscains. &lt;/p&gt; &lt;p&gt; Précurseur du franciscanisme intellectuel, il défend la théologie comme sagesse unissant connaissance, sainteté et enseignement, incarnant une approche augustinienne face à l'aristotélisme naissant. &lt;/p&gt; &lt;p&gt;  Innovant en philosophie de l'âme, il organise les  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1964_num_38_4_2400_t1_0422_0000_2" style="color:#88A1E9" title=" Jean de la Rochelle, Tractatus de divisione multiplici potentiarum animae. Texte critique avec introduction, notes et tables, par Pierre Michaud-Quantin, Textes philosophiques du moyen âge XI, 1964 par Persée"&gt;autorités&lt;/a&gt;, c'est-à-dire les textes de référence, en analysant leurs vocabulaires concurrents, posant les bases pour Bonaventure et influençant la scolastique. &lt;/p&gt; &lt;p&gt; Ses oeuvres principales sont : "Summa de anima" écrit vers  1235 : Traite de l'âme selon les quatre causes aristotéliciennes, distinguant une âme supérieure (spirituelle) et inférieure (corporelle), en débat avec les théories matérialistes. "Tractatus de divisione potentiarum animae" écrit vers 1233  : Analyse détaillée des divisions de l'âme, intégrant Platon, Aristote, Avicenne et Augustin pour clarifier les sources philosophiques nouvelles. Jean de La Rochelle est en effet l’un des premiers, à Paris, à intégrer dans la théologie la psychologie d’Avicenne, récemment traduite de l’arabe : il distingue avec lui les sens externes, les sens internes, comme l’imagination et la mémoire, et les puissances de l’intellect. Il enseigne avec Alexandre de Hales, dès 1238, la première école franciscaine de l’université de Paris. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -3460,7 +3432,7 @@
       </c>
       <c r="D44" s="31" t="inlineStr">
         <is>
-          <t>BONNAVENTURE de Bagnorea</t>
+          <t xml:space="preserve">BONAVENTURE de Bagnorea</t>
         </is>
       </c>
       <c r="E44" s="33" t="inlineStr">
@@ -3531,7 +3503,7 @@
       </c>
       <c r="E45" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_de_Gand"   title=" Wikipedia"&gt;Henry de GAND&lt;/a&gt;  était un philosophe et théologien scolastique originaire des anciens Pays-Bas, né à Gand et mort à Tournai. Surnommé le "Doctor Solennis", il fut chanoine de Tournai, maître régent à la faculté de théologie de Paris de 1276 à 1292, et joua un rôle clé dans la condamnation de 219 thèses thomistes et averroïstes par l'évêque Étienne Tempier en 1277. &lt;/p&gt; &lt;p&gt; Platonicien et augustinien, il développa une &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1949_num_47_16_4216" title="A propos de la théorie de la connaissance d'Henri de Gand  par Persée"&gt;pensée influente &lt;/a&gt; entre Thomas d'Aquin et Duns Scot, marquée par une épistémologie centrée sur l'illumination divine et les idées exemplaires pour contrer le scepticisme. &lt;/p&gt; &lt;p&gt; Il insistait sur l'insuffisance de la raison naturelle sans l'illumination divine pour atteindre la vérité, particulièrement pour les idées éternelles. Il distinguait philosophie et théologie par degrés, non par nature : la révélation élève la raison vers Dieu, la volonté prime l'intelligence, et l'amour de la sagesse vise l'union avec le divin.  &lt;a href="https://www.youtube.com/watch?v=n_iDMWExiwI" title="Henry of Ghent: Life, Works, and Philosophy par Philosopher Friends"&gt;Sa métaphysique, &lt;/a&gt;  influencée par Platon et Augustin, mettait l'accent sur la matière, la connaissance et la finalité humaine tournée vers Dieu. &lt;/p&gt; &lt;p&gt; Son oeuvre principale : - "Sa Summa quaestionum ordinariarum" (inachevée, commencée avant 1276) compte 75 articles, dont un traité d'épistémologie en 39 questions sur la possibilité de la connaissance humaine. Il écrivit aussi 15 "Quaestiones quodlibetales" et des commentaires sur Aristote, comme le "De generatione et corruptione". Ces textes explorent la métaphysique, la théologie et l'exemplarisme augustinien. &lt;/p&gt;
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_de_Gand"   title=" Wikipedia"&gt;Henry de GAND&lt;/a&gt;  était un philosophe et théologien scolastique originaire des anciens Pays-Bas, né à Gand et mort à Tournai. Surnommé le "Doctor Solennis", il fut chanoine de Tournai, maître régent à la faculté de théologie de Paris de 1276 à 1292, et joua un rôle clé dans la condamnation de 219 thèses thomistes et averroïstes par l'évêque Étienne Tempier en 1277. &lt;/p&gt; &lt;p&gt; Platonicien et augustinien, il développa une &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1949_num_47_16_4216" title="A propos de la théorie de la connaissance d'Henri de Gand  par Persée"&gt;pensée influente &lt;/a&gt; entre Thomas d'Aquin et Duns Scot, marquée par une épistémologie centrée sur l'illumination divine et les idées exemplaires pour contrer le scepticisme. &lt;/p&gt; &lt;p&gt; Il insistait sur l'insuffisance de la raison naturelle sans l'illumination divine pour atteindre la vérité, particulièrement pour les idées éternelles. Il distinguait philosophie et théologie par degrés, non par nature : la révélation élève la raison vers Dieu, la volonté prime l'intelligence, et l'amour de la sagesse vise l'union avec le divin.  &lt;a href="https://www.youtube.com/watch?v=n_iDMWExiwI" title="Henry of Ghent: Life, Works, and Philosophy par Philosopher Friends"&gt;Sa métaphysique, &lt;/a&gt;  influencée par Platon et Augustin, mettait l'accent sur la matière, la connaissance et la finalité humaine tournée vers Dieu. &lt;/p&gt; &lt;p&gt; Son oeuvre principale : "Sa Summa quaestionum ordinariarum" (inachevée, commencée avant 1276) compte 75 articles, dont un traité d'épistémologie en 39 questions sur la possibilité de la connaissance humaine. Il écrivit aussi 15 "Quaestiones quodlibetales" et des commentaires sur Aristote, comme le "De generatione et corruptione". Ces textes explorent la métaphysique, la théologie et l'exemplarisme augustinien. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -3795,7 +3767,7 @@
       </c>
       <c r="E49" s="35" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_d%27Aquin"  title=" Wikipedia"&gt;Thomas D'AQUIN&lt;/a&gt; est un philosophe et théologien médiéval italien formé à l'école de la pensée &lt;a href="https://www.youtube.com/watch?v=g3GcFwTIVC4" title="La pensée Scolastique par Langue &amp; Poiesis"&gt;"Scolastique"&lt;/a&gt;, qui a dominé la pensée médiévale européenne du XIe au XIVe siècle et qui vise à harmoniser la foi chrétienne et la raison en utilisant une méthode logique et argumentative pour résoudre les questions théologiques et philosophiques. Il s'est éforcé de faire correspondre la pensée grecque d'Aristote avec le Christianisme.&lt;/p&gt; &lt;p&gt; Il y a joué un role clé en y intégrant la philosophie aristotélicienne. Il a soutenu que la raison humaine peut être utilisée pour comprendre la révélation divine, qu'elle peut même être utilisée pour &lt;a href="https://www.youtube.com/watch?v=F3AKuGgzmmQ&amp;ab_channel=CulturePhilo%2FAlainBajom%C3%A9e"  title="Dieu existe par Alain Bajomée"&gt; prouver l'existence de Dieu&lt;/a&gt; et que la foi est nécessaire pour comprendre certaines vérités surnaturelles qui dépassent la portée de la raison humaine.   Son apport le plus célèbre est d’avoir affirmé que foi et raison ne se contredisent pas, parce qu’elles viennent toutes deux de Dieu. Pour lui, la raison humaine peut connaître beaucoup de vérités par elle-même, tandis que la révélation éclaire  &lt;a href="https://www.youtube.com/watch?v=BZ3o_YOmpNE"  title=" Saint Thomas d'Aquin et l’existence de Dieu par Voyage Endormis"&gt; les questions religieuses &lt;/a&gt; plus profondes.  &lt;/p&gt; &lt;p&gt; Son oeuvre,  &lt;a href="https://www.youtube.com/watch?v=9QWMc9htrPY"  title="La Somme Théologique de Saint Thomas d'Aquin par Résumons ça"&gt; la "Somme Théologique"&lt;/a&gt; est considérée comme la plus importante de la scolastique. Il a aborde de nombreux sujets tels que la théologie, la morale, la métaphysique et la philosophie politique. Il a également défendu des enseignements tels que la Trinité, l'Incarnation et la résurrection du Christ, ainsi que la théorie de la juste guerre. &lt;/p&gt; &lt;p&gt; Sa pensée a exercé une influence considérable sur la culture et la pensée occidentales et est largement étudié et admiré dans les milieux catholiques et académiques. Il  a fortement influencé le thomisme, une tradition philosophique et théologique qui continue d’être étudiée aujourd’hui. Sa pensée a aussi nourri des réflexions sur la loi naturelle, l’éthique et la politique.  &lt;/p&gt;    &lt;audio controls title="Retour au Moyen âge: Thomas d'Aquin par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2013/02/s06/NET_FC_e21c4f80-0f51-4360-975a-e46049d94417.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; &lt;p&gt; &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_d%27Aquin"  title=" Wikipedia"&gt;Thomas D'AQUIN&lt;/a&gt; est un philosophe et théologien médiéval italien formé à l'école de la pensée &lt;a href="https://www.youtube.com/watch?v=g3GcFwTIVC4" title="La pensée Scolastique par Langue &amp; Poiesis"&gt;"Scolastique"&lt;/a&gt;, qui a dominé la pensée médiévale européenne du XIe au XIVe siècle et qui vise à harmoniser la foi chrétienne et la raison en utilisant une méthode logique et argumentative pour résoudre les questions théologiques et philosophiques. Il s'est éforcé de faire correspondre la pensée grecque d'Aristote avec le Christianisme.&lt;/p&gt; &lt;p&gt; Il y a joué un role clé en y intégrant la philosophie aristotélicienne. Il a soutenu que la raison humaine peut être utilisée pour comprendre la révélation divine, qu'elle peut même être utilisée pour &lt;a href="https://www.youtube.com/watch?v=F3AKuGgzmmQ&amp;ab_channel=CulturePhilo%2FAlainBajom%C3%A9e"  title="Dieu existe par Alain Bajomée"&gt; prouver l'existence de Dieu&lt;/a&gt; et que la foi est nécessaire pour comprendre certaines vérités surnaturelles qui dépassent la portée de la raison humaine.   Son apport le plus célèbre est d’avoir affirmé que foi et raison ne se contredisent pas, parce qu’elles viennent toutes deux de Dieu. Pour lui, la raison humaine peut connaître beaucoup de vérités par elle-même, tandis que la révélation éclaire  &lt;a href="https://www.youtube.com/watch?v=BZ3o_YOmpNE"  title=" Saint Thomas d'Aquin et l’existence de Dieu par Voyage Endormis"&gt; les questions religieuses &lt;/a&gt; plus profondes.  &lt;/p&gt; &lt;p&gt; Son oeuvre,  &lt;a href="https://www.youtube.com/watch?v=9QWMc9htrPY"  title="La Somme Théologique de Saint Thomas d'Aquin par Résumons ça"&gt; la "Somme Théologique"&lt;/a&gt; est considérée comme la plus importante de la scolastique. Il a aborde de nombreux sujets tels que la théologie, la morale, la métaphysique et la philosophie politique. Il a également défendu des enseignements tels que la Trinité, l'Incarnation et la résurrection du Christ, ainsi que la théorie de la juste guerre. &lt;/p&gt; &lt;p&gt; Sa pensée a exercé une influence considérable sur la culture et la pensée occidentales et est largement étudié et admiré dans les milieux catholiques et académiques. Il  a fortement influencé le thomisme, une tradition philosophique et théologique qui continue d’être étudiée aujourd’hui. Sa pensée a aussi nourri des réflexions sur la loi naturelle, l’éthique et la politique.  &lt;/p&gt;    &lt;audio controls title="Retour au Moyen âge: Thomas d'Aquin par France Culture"&gt; &lt;source src="https://cdn.radiofrance.fr/s3/cruiser-production/static/culture/sons/2013/02/s06/NET_FC_e21c4f80-0f51-4360-975a-e46049d94417.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
         </is>
       </c>
       <c r="F49" s="30" t="inlineStr">
@@ -4059,7 +4031,7 @@
       </c>
       <c r="E53" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Lulle" title=" Wikipedia"&gt;Raymond LULLE&lt;/a&gt; était un philosophe formaliste, théologien, missionnaire, poète et romancier catalan surnommé le  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1963_num_1_2_4030" style="color:#88A1E9" title="Raymond Lulle, le Docteur illuminé par persée"&gt;"Doctor Illuminatus"&lt;/a&gt; et le "Procureur des Infidèles", son œuvre et sa vie sont à l'intersection de trois cultures : arabe, juive et chrétienne. Sa  philosophie est indissociable de son projet missionnaire car son objectif principal était de convaincre les non-chrétiens de la vérité du christianisme par des arguments rationnels, et non par la contrainte. Pour ce faire, il développe une méthode universelle qu'il nomme &lt;a href="https://www.iemed.org/publication/lart-de-raymond-lulle-comme-science-universelle/"  title="  L’Art de Raymond Lulle comme science universelle par IEMed"&gt;"l'Art"&lt;/a&gt; (Ars Magna) dont le principe est le suivant : &lt;/p&gt; &lt;p&gt; - Dignités divines (ou principes absolus) : il identifie neuf attributs divins fondamentaux (Bonté, Grandeur, Éternité, Puissance, Sagesse, Volonté, Vertu, Vérité, Gloire) qui sont les fondements de toute réalité. &lt;/p&gt; &lt;p&gt; - Questions, sujets et vertus/vices : À ces dignités s'ajoutent d'autres catégories comme des questions universelles (Quoi ? Pourquoi ? Comment ?), des sujets (Dieu, ange, homme, etc.), des vertus et vices. &lt;/p&gt; &lt;p&gt; - Combinatoire : L'originalité de l'Art réside dans sa méthode combinatoire car il utilise des figures géométriques (cercles concentriques, carrés) et des lettres pour représenter ces concepts. En faisant pivoter ces figures et en combinant les lettres selon des règles précises, il pensait pouvoir générer toutes les propositions vraies possibles et ainsi démontrer les vérités de la foi. C'est en quelque sorte un précurseur de la logique symbolique et même de l'informatique, certains le considérant comme un "prince de la technologie" pour son approche algorithmique. &lt;/p&gt; &lt;p&gt; Ce n'était pas seulement une spéculation abstraite, mais un outil concret pour le dialogue. Il s'agissait de trouver des principes communs, des "raisons nécessaires" acceptables par tous, pour établir une base de discussion avec les musulmans et les juifs. Il s'opposait à la dialectique scolastique de son temps, jugée inadaptée pour convaincre des non-chrétiens. &lt;/p&gt; &lt;p&gt; Il  fut un  &lt;a href="https://www.youtube.com/watch?v=1KZFxnKPYL0" title=" Llull et ses argumentaires automatiques par histoire de mathématiques"&gt;auteur&lt;/a&gt; extraordinairement prolifique, avec près de 265 œuvres (certains affirment même plus de 400) écrites en catalan, en latin et en arabe. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Lulle" title=" Wikipedia"&gt;Raymond LULLE&lt;/a&gt; était un philosophe formaliste, théologien, missionnaire, poète et romancier catalan surnommé le  &lt;a href="https://www.persee.fr/doc/bude_0004-5527_1963_num_1_2_4030" style="color:#88A1E9" title="Raymond Lulle, le Docteur illuminé par persée"&gt;"Doctor Illuminatus"&lt;/a&gt; et le "Procureur des Infidèles", son œuvre et sa vie sont à l'intersection de trois cultures : arabe, juive et chrétienne. Sa  philosophie est indissociable de son projet missionnaire car son objectif principal était de convaincre les non-chrétiens de la vérité du christianisme par des arguments rationnels, et non par la contrainte. Pour ce faire, il développe une méthode universelle qu'il nomme &lt;a href="https://www.iemed.org/publication/lart-de-raymond-lulle-comme-science-universelle/"  title="  L’Art de Raymond Lulle comme science universelle par IEMed"&gt;"l'Art"&lt;/a&gt; (Ars Magna) dont le principe est le suivant : &lt;/p&gt; &lt;p&gt;Dignités divines (ou principes absolus) : il identifie neuf attributs divins fondamentaux (Bonté, Grandeur, Éternité, Puissance, Sagesse, Volonté, Vertu, Vérité, Gloire) qui sont les fondements de toute réalité. &lt;/p&gt; &lt;p&gt;Questions, sujets et vertus/vices : À ces dignités s'ajoutent d'autres catégories comme des questions universelles (Quoi ? Pourquoi ? Comment ?), des sujets (Dieu, ange, homme, etc.), des vertus et vices. &lt;/p&gt; &lt;p&gt;Combinatoire : L'originalité de l'Art réside dans sa méthode combinatoire car il utilise des figures géométriques (cercles concentriques, carrés) et des lettres pour représenter ces concepts. En faisant pivoter ces figures et en combinant les lettres selon des règles précises, il pensait pouvoir générer toutes les propositions vraies possibles et ainsi démontrer les vérités de la foi. C'est en quelque sorte un précurseur de la logique symbolique et même de l'informatique, certains le considérant comme un "prince de la technologie" pour son approche algorithmique. &lt;/p&gt; &lt;p&gt; Ce n'était pas seulement une spéculation abstraite, mais un outil concret pour le dialogue. Il s'agissait de trouver des principes communs, des "raisons nécessaires" acceptables par tous, pour établir une base de discussion avec les musulmans et les juifs. Il s'opposait à la dialectique scolastique de son temps, jugée inadaptée pour convaincre des non-chrétiens. &lt;/p&gt; &lt;p&gt; Il  fut un  &lt;a href="https://www.youtube.com/watch?v=1KZFxnKPYL0" title=" Llull et ses argumentaires automatiques par histoire de mathématiques"&gt;auteur&lt;/a&gt; extraordinairement prolifique, avec près de 265 œuvres (certains affirment même plus de 400) écrites en catalan, en latin et en arabe. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F53" s="30" t="inlineStr">
@@ -4258,7 +4230,7 @@
       </c>
       <c r="E56" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_d%27Auvergne_(th%C3%A9ologien)"  style="color:#6A142A"  title=" Wikipedia"&gt;Pierre D'AUVERGNE&lt;/a&gt; était un philosophe scolastique français connu comme l’un des grands commentateurs médiévaux d’Aristote. Il est aussi identifié comme Pierre de Croc / de Cros, évêque de Clermont à la toute fin de sa vie. &lt;/p&gt; &lt;p&gt; Il appartient au courant aristotélicien latin et prolonge l’œuvre de Thomas d’Aquin, dont il reprend et complète plusieurs commentaires sur Aristote alors enseignées: logique, physique, métaphysique, psychologie, éthique et politique. Sa production a connu une large diffusion médiévale: on conserve environ cent cinquante   &lt;a href="https://www.persee.fr/doc/mefr_0223-4874_1882_num_2_1_6838" style="color:#88A1E9" title="Extraits des archives du Vatican pour servir à l'histoire littéraire du moyen-âge, première partie par Persée"&gt;manuscrits &lt;/a&gt; de ses œuvres, ce qui témoigne de l’importance de son enseignement à Paris. &lt;/p&gt; &lt;p&gt; On lui doit des commentaires suivis sur de nombreux traités, par exemple : - Du ciel (De caelo), Météorologiques, Politique, où il reprend parfois le texte de Thomas d’Aquin et le continue ainsi que - Des Questions sur la Métaphysique (Quæstiones in Metaphysicam), qui exposent sa lecture de l’“être” chez Aristote. &lt;/p&gt; &lt;p&gt;Il  reste globalement dans la ligne d’un aristotélisme chrétien proche de Thomas d’Aquin, mais il prend parfois des positions originales en métaphysique et en psychologie, par exemple sur la notion d’“être” ou certains problèmes de l’âme. Sa pensée illustre la maturité de la scolastique parisienne à la fin du XIIIᵉ siècle: travail systématique sur Aristote, usage intensif de la disputation, articulation serrée entre philosophie et théologie.&lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pierre_d%27Auvergne_(th%C3%A9ologien)"  style="color:#6A142A"  title=" Wikipedia"&gt;Pierre D'AUVERGNE&lt;/a&gt; était un philosophe scolastique français connu comme l’un des grands commentateurs médiévaux d’Aristote. Il est aussi identifié comme Pierre de Croc / de Cros, évêque de Clermont à la toute fin de sa vie. &lt;/p&gt; &lt;p&gt; Il appartient au courant aristotélicien latin et prolonge l’œuvre de Thomas d’Aquin, dont il reprend et complète plusieurs commentaires sur Aristote alors enseignées: logique, physique, métaphysique, psychologie, éthique et politique. Sa production a connu une large diffusion médiévale: on conserve environ cent cinquante   &lt;a href="https://www.persee.fr/doc/mefr_0223-4874_1882_num_2_1_6838" style="color:#88A1E9" title="Extraits des archives du Vatican pour servir à l'histoire littéraire du moyen-âge, première partie par Persée"&gt;manuscrits &lt;/a&gt; de ses œuvres, ce qui témoigne de l’importance de son enseignement à Paris. &lt;/p&gt; &lt;p&gt; On lui doit des commentaires suivis sur de nombreux traités, par exemple : Du ciel (De caelo), Météorologiques, Politique, où il reprend parfois le texte de Thomas d’Aquin et le continue ainsi que Des Questions sur la Métaphysique (Quæstiones in Metaphysicam), qui exposent sa lecture de l’“être” chez Aristote. &lt;/p&gt; &lt;p&gt;Il  reste globalement dans la ligne d’un aristotélisme chrétien proche de Thomas d’Aquin, mais il prend parfois des positions originales en métaphysique et en psychologie, par exemple sur la notion d’“être” ou certains problèmes de l’âme. Sa pensée illustre la maturité de la scolastique parisienne à la fin du XIIIᵉ siècle: travail systématique sur Aristote, usage intensif de la disputation, articulation serrée entre philosophie et théologie.&lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4523,7 +4495,7 @@
       </c>
       <c r="E60" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_de_Rome"  title=" Wikipedia"&gt;Gilles de ROME&lt;/a&gt; est un théologien augustin italien et philosophe scolastique connu pour son rôle d’interprète d’Aristote, de théoricien du pouvoir princier et de défenseur de la suprématie pontificale. En 1292, il est élu supérieur général de l’ordre augustin, puis, en 1295, le pape Boniface VIII le nomme archevêque de Bourges, charge qu’il exerce tout en restant une figure intellectuelle influente. &lt;/p&gt; &lt;p&gt; Il cherche à concilier Aristote avec la théologie chrétienne, dans un contexte marqué par les condamnations de 1277 à Paris contre certaines thèses aristotéliciennes. Son œuvre couvre la théologie, la philosophie naturelle, la logique et la métaphysique, avec de nombreux commentaires sur Aristote et sur les Sentences de Pierre Lombard. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=Qw-Sbn5MeNs"  title="Giles of Rome: Life, Works, and Influence par Philosoppher Friends"&gt;Son oeuvre &lt;/a&gt; principale est : - "De regimine principum" est un vaste traité en trois livres sur la morale, l’économie domestique et la politique, rédigé pour l’éducation du futur roi Philippe IV le Bel. On lui attribue aussi des textes politiques et ecclésiologiques comme le "De ecclesiastica potestate" et une participation à la bulle "Unam Sanctam", où il défend une vision très forte de la supériorité du pouvoir spirituel sur le pouvoir temporel. &lt;/p&gt; &lt;p&gt; Son traité sur le gouvernement des princes a été largement diffusé et traduit, influençant durablement la pensée politique médiévale et la littérature des "miroirs des princes". &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_de_Rome"  title=" Wikipedia"&gt;Gilles de ROME&lt;/a&gt; est un théologien augustin italien et philosophe scolastique connu pour son rôle d’interprète d’Aristote, de théoricien du pouvoir princier et de défenseur de la suprématie pontificale. En 1292, il est élu supérieur général de l’ordre augustin, puis, en 1295, le pape Boniface VIII le nomme archevêque de Bourges, charge qu’il exerce tout en restant une figure intellectuelle influente. &lt;/p&gt; &lt;p&gt; Il cherche à concilier Aristote avec la théologie chrétienne, dans un contexte marqué par les condamnations de 1277 à Paris contre certaines thèses aristotéliciennes. Son œuvre couvre la théologie, la philosophie naturelle, la logique et la métaphysique, avec de nombreux commentaires sur Aristote et sur les Sentences de Pierre Lombard. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=Qw-Sbn5MeNs"  title="Giles of Rome: Life, Works, and Influence par Philosoppher Friends"&gt;Son oeuvre &lt;/a&gt; principale est : "De regimine principum" est un vaste traité en trois livres sur la morale, l’économie domestique et la politique, rédigé pour l’éducation du futur roi Philippe IV le Bel. On lui attribue aussi des textes politiques et ecclésiologiques comme le "De ecclesiastica potestate" et une participation à la bulle "Unam Sanctam", où il défend une vision très forte de la supériorité du pouvoir spirituel sur le pouvoir temporel. &lt;/p&gt; &lt;p&gt; Son traité sur le gouvernement des princes a été largement diffusé et traduit, influençant durablement la pensée politique médiévale et la littérature des "miroirs des princes". &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
@@ -4656,7 +4628,7 @@
       <c r="E62" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_de_Mediavilla"  style="color:#6A142A"  title=" Wikipedia"&gt;Richard de MEDIAVILLA&lt;/a&gt; était un philosophe franciscain scolastique français surnommé "doctor solidus" pour la solidité de sa pensée.  Il participe aux débats scolastiques entre thomistes et franciscains, critiquant Thomas d'Aquin tout en intégrant des éléments aristotéliciens et avicennisants. Sa postérité a longtemps été éclipsée par Duns Scot et Thomas, mais des éditions récentes révèlent &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2015_num_113_2_8449_t1_0355_0000_2" style="color:#88A1E9" title="        Richard de Mediavilla, Questions disputées par Persée"&gt;son influence pionnière. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Ses Questions disputées et Quodlibets (édités en plusieurs tomes depuis les années 2010) traitent de Dieu, des anges, des démons et de l'homme. Ces textes explorent la physique du mouvement, l'optique et les mathématiques appliquées à la théologie. Il distingue l'infini en acte (Dieu) de l'infini virtuel (créatures), posant le possible comme dimension ontologique de l'être, au-delà de la simple contingence. Il redéfinit la matière comme lieu du possible pour individualiser les anges sans multiplicité d'espèces, anticipant &lt;a href="https://www.youtube.com/watch?v=TxCvg7h9mvg" style="color:#88A1E9" title=" Richard of Middleton , Everything Philosophers par See Hear Say Learn"&gt;l'ecceitas scotiste.&lt;/a&gt; Critique de l'éternité du monde, il articule liberté divine, naturalisme et sciences. &lt;/p&gt; &lt;p&gt; Il débat avec Pierre de Jean Olivi et Henri de Gand, s'opposant à la création éternelle condamnée en 1277. Reconnu comme "le plus thomiste des franciscains", il dépasse les tensions franciscaines par une métaphysique du possible influençant les XIVe-XVe siècles. &lt;/p&gt; 
-&lt;p&gt; &lt;/p&gt;   &lt;audio controls title="La scolastique et les démons de Richard de Mediavilla par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10193-04.04.2011-ITEMA_20277718-2011C3039E0082-ITE_00041542_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;
+   &lt;audio controls title="La scolastique et les démons de Richard de Mediavilla par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10193-04.04.2011-ITEMA_20277718-2011C3039E0082-ITE_00041542_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
       </c>
@@ -4723,7 +4695,7 @@
       </c>
       <c r="E63" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_de_Viterbe"   title=" Wikipedia"&gt;Jacques de VITERBE&lt;/a&gt; était un philosophe augustinien italien célèbre pour son ouvrage majeur sur le gouvernement chrétien et pour son rôle ecclésial à Naples. Il est devenu archevêque de Naples, et son parcours montre une mobilité ecclésiastique notable à l’époque. Cette position lui donne une plateforme pour défendre des &lt;a href="https://www.youtube.com/watch?v=cHRhuvN4t4E&amp;t=84s" title="Blessed James of Viterbo: The Brilliant Augustinian Theologian par St Joseph's Corner"&gt;thèses théocratiques &lt;/a&gt; et pour intervenir dans les débats sur le pouvoir spirituel et temporel. &lt;/p&gt; &lt;p&gt; Son oeuvre majeure : - &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1927_num_7_3_1391_t1_0526_0000_2" title="Le plus ancien traité de l'Église. Jacques de Viterbe. De Regimine Christiano par Persée"&gt;"De regimine Christiano " &lt;/a&gt; écrit entre 1296 et 1303 dans un contexte de conflit entre le pape Boniface VIII et le roi Philippe le Bel. Cette œuvre développe l’idée que l’Église gouverne en théocratie et que le pape possède une autorité sur le pouvoir temporel, réaffirmant des arguments proches de l’orientation hiéroucratique assumant une primauté du pouvoir spirituel. Le livre se structure en deux parties: une sur l’Église et une sur le pouvoir du Christ roi et du vicariat du pape. Cette organisation reflète une réflexion complète sur l’articulation entre la juridiction ecclésiastique et la souveraineté temporelle. &lt;/p&gt; &lt;p&gt; Sur le plan philosophique, ses “Principes de la nature” et ses commentaires sur Aristote (Physique et Métaphysique), montrent un effort pour reconciler la pensée aristotélicienne avec la théologie médiévale, tout en s’ouvrant à un péripatétisme platonisant. Ces éléments indiquent une approche où la théologie et la philosophie s’enrichissent mutuellement plutôt que de s’opposer. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jacques_de_Viterbe"   title=" Wikipedia"&gt;Jacques de VITERBE&lt;/a&gt; était un philosophe augustinien italien célèbre pour son ouvrage majeur sur le gouvernement chrétien et pour son rôle ecclésial à Naples. Il est devenu archevêque de Naples, et son parcours montre une mobilité ecclésiastique notable à l’époque. Cette position lui donne une plateforme pour défendre des &lt;a href="https://www.youtube.com/watch?v=cHRhuvN4t4E&amp;t=84s" title="Blessed James of Viterbo: The Brilliant Augustinian Theologian par St Joseph's Corner"&gt;thèses théocratiques &lt;/a&gt; et pour intervenir dans les débats sur le pouvoir spirituel et temporel. &lt;/p&gt; &lt;p&gt; Son oeuvre majeure : &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1927_num_7_3_1391_t1_0526_0000_2" title="Le plus ancien traité de l'Église. Jacques de Viterbe. De Regimine Christiano par Persée"&gt;"De regimine Christiano " &lt;/a&gt; écrit entre 1296 et 1303 dans un contexte de conflit entre le pape Boniface VIII et le roi Philippe le Bel. Cette œuvre développe l’idée que l’Église gouverne en théocratie et que le pape possède une autorité sur le pouvoir temporel, réaffirmant des arguments proches de l’orientation hiéroucratique assumant une primauté du pouvoir spirituel. Le livre se structure en deux parties: une sur l’Église et une sur le pouvoir du Christ roi et du vicariat du pape. Cette organisation reflète une réflexion complète sur l’articulation entre la juridiction ecclésiastique et la souveraineté temporelle. &lt;/p&gt; &lt;p&gt; Sur le plan philosophique, ses “Principes de la nature” et ses commentaires sur Aristote (Physique et Métaphysique), montrent un effort pour reconciler la pensée aristotélicienne avec la théologie médiévale, tout en s’ouvrant à un péripatétisme platonisant. Ces éléments indiquent une approche où la théologie et la philosophie s’enrichissent mutuellement plutôt que de s’opposer. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4924,8 +4896,7 @@
       </c>
       <c r="E66" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ma%C3%AEtre_Eckhart" title=" Wikipedia"&gt;Maître ECKHART&lt;/a&gt;, de son vrai nom Johannes Eckhart,  était un théologien, philosophe et prédicateur dominicain du saint Empire Germanique dont les enseignements ont profondément marqué la spiritualité occidentale. Il  a vécu à une époque où la pensée scolastique, influencée par des figures comme Thomas d'Aquin, dominait la théologie chrétienne. Cependant, il s'est distingué par son approche plus &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1921_num_23_92_2291" title="Philo de Mtre Eckhart par Persée"&gt;mystique et contemplative&lt;/a&gt;, cherchant à explorer la relation directe entre l'âme humaine et Dieu. &lt;/p&gt; &lt;p&gt;  Ses enseignements se concentrent sur plusieurs thèmes clés : &lt;/p&gt;  &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=oNopoYpvA5c" title="Se quitter soi même par Daniel Brawacki "&gt;La Déité &lt;/a&gt; : Eckhart distingue entre "Dieu" (la conception traditionnelle d'un être personnel) et la "Déité", qu'il décrit comme l'essence ultime et inconnaissable de Dieu, au-delà de toute forme ou attribut. Pour lui, la Déité est un abîme sans fond, une réalité absolue qui transcende toute compréhension humaine.&lt;/p&gt; 
-&lt;p&gt;Le Détachement  : Eckhart insiste sur l'importance du détachement, non seulement des biens matériels, mais aussi des désirs, des pensées et même des images de Dieu. Ce détachement permet à l'âme de se libérer de tout ce qui n'est pas Dieu, afin de s'unir à Lui.&lt;/p&gt; &lt;p&gt;La Naissance de Dieu dans l'âme : L'un de ses concepts le plus célèbre est l'idée que Dieu doit "naître" dans l'âme humaine. Cela signifie que l'expérience de Dieu n'est pas simplement une connaissance intellectuelle, mais une transformation intérieure profonde où l'âme devient un avec Dieu.&lt;/p&gt; &lt;p&gt;Le Fond de l'âme (Grunt der Seele) : il parle d'un "fond" ou d'une "étincelle" dans l'âme qui est éternelle et divine. Ce fond est le lieu où l'âme rencontre Dieu directement, sans intermédiaire. C'est dans ce fond que l'union mystique avec Dieu peut se réaliser.&lt;/p&gt; &lt;p&gt;La Pauvreté en esprit : il interprète la béatitude "Heureux les pauvres en esprit" comme un appel à se dépouiller de tout, y compris de l'idée de soi, pour permettre à Dieu d'être tout en nous. &lt;/p&gt;   &lt;p&gt; Il a laissé un corpus important d'écrits, comprenant des sermons, des traités et des commentaires bibliques. Parmi ses œuvres les plus connues, on trouve : &lt;/p&gt; &lt;dd&gt;- Les Sermons allemands : Ces sermons, prononcés en langue vernaculaire, sont considérés comme l'expression la plus pure de sa pensée mystique. &lt;/dd&gt; &lt;dd&gt;- Le Livre de la Consolation Divine : Un traité qui explore la nature de la consolation spirituelle et la relation entre l'âme et Dieu.&lt;/dd&gt; &lt;p&gt; Maître Eckhart a exercé une influence considérable sur la spiritualité chrétienne, mais aussi sur la philosophie et la littérature. Ses idées ont inspiré des mystiques comme Jean de la Croix et Thérèse d'Avila, ainsi que des philosophes comme Martin Heidegger. En 1329, quelques années après sa mort, certaines de ses propositions ont été condamnées comme hérétiques par le pape Jean XXII, limitant la diffusion de ses écrits pendant plusieurs siècles. &lt;/p&gt; &lt;audio controls title="Maitre ECKHART par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.02.2013-ITEMA_20447137-2013C12410S0037-NET_FC_19A3A611-791B-4BFA-9D91-7F17B53BFD83-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Ma%C3%AEtre_Eckhart" title=" Wikipedia"&gt;Maître ECKHART&lt;/a&gt;, de son vrai nom Johannes Eckhart,  était un théologien, philosophe et prédicateur dominicain du saint Empire Germanique dont les enseignements ont profondément marqué la spiritualité occidentale. Il  a vécu à une époque où la pensée scolastique, influencée par des figures comme Thomas d'Aquin, dominait la théologie chrétienne. Cependant, il s'est distingué par son approche plus &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1921_num_23_92_2291" title="Philo de Mtre Eckhart par Persée"&gt;mystique et contemplative&lt;/a&gt;, cherchant à explorer la relation directe entre l'âme humaine et Dieu. &lt;/p&gt; &lt;p&gt;  Ses enseignements se concentrent sur plusieurs thèmes clés : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=oNopoYpvA5c" title="Se quitter soi même par Daniel Brawacki "&gt;La Déité &lt;/a&gt; : Eckhart distingue entre "Dieu" (la conception traditionnelle d'un être personnel) et la "Déité", qu'il décrit comme l'essence ultime et inconnaissable de Dieu, au-delà de toute forme ou attribut. Pour lui, la Déité est un abîme sans fond, une réalité absolue qui transcende toute compréhension humaine.&lt;/p&gt; &lt;p&gt;Le Détachement  : Eckhart insiste sur l'importance du détachement, non seulement des biens matériels, mais aussi des désirs, des pensées et même des images de Dieu. Ce détachement permet à l'âme de se libérer de tout ce qui n'est pas Dieu, afin de s'unir à Lui.&lt;/p&gt; &lt;p&gt;La Naissance de Dieu dans l'âme : L'un de ses concepts le plus célèbre est l'idée que Dieu doit "naître" dans l'âme humaine. Cela signifie que l'expérience de Dieu n'est pas simplement une connaissance intellectuelle, mais une transformation intérieure profonde où l'âme devient un avec Dieu.&lt;/p&gt; &lt;p&gt;Le Fond de l'âme (Grunt der Seele) : il parle d'un "fond" ou d'une "étincelle" dans l'âme qui est éternelle et divine. Ce fond est le lieu où l'âme rencontre Dieu directement, sans intermédiaire. C'est dans ce fond que l'union mystique avec Dieu peut se réaliser.&lt;/p&gt; &lt;p&gt;La Pauvreté en esprit : il interprète la béatitude "Heureux les pauvres en esprit" comme un appel à se dépouiller de tout, y compris de l'idée de soi, pour permettre à Dieu d'être tout en nous. &lt;/p&gt; &lt;p&gt; Il a laissé un corpus important d'écrits, comprenant des sermons, des traités et des commentaires bibliques. Parmi ses œuvres les plus connues, on trouve : &lt;/p&gt; &lt;p&gt;Les Sermons allemands : Ces sermons, prononcés en langue vernaculaire, sont considérés comme l'expression la plus pure de sa pensée mystique. &lt;/p&gt; &lt;p&gt;Le Livre de la Consolation Divine : Un traité qui explore la nature de la consolation spirituelle et la relation entre l'âme et Dieu.&lt;/p&gt; &lt;p&gt; Maître Eckhart a exercé une influence considérable sur la spiritualité chrétienne, mais aussi sur la philosophie et la littérature. Ses idées ont inspiré des mystiques comme Jean de la Croix et Thérèse d'Avila, ainsi que des philosophes comme Martin Heidegger. En 1329, quelques années après sa mort, certaines de ses propositions ont été condamnées comme hérétiques par le pape Jean XXII, limitant la diffusion de ses écrits pendant plusieurs siècles. &lt;/p&gt; &lt;audio controls title="Maitre ECKHART par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-06.02.2013-ITEMA_20447137-2013C12410S0037-NET_FC_19A3A611-791B-4BFA-9D91-7F17B53BFD83-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;   </t>
         </is>
       </c>
       <c r="F66" s="30" t="inlineStr">
@@ -5323,17 +5294,13 @@
       </c>
       <c r="E72" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_de_Padoue"  title=" Wikipedia"&gt;MARSILE de Pardoue&lt;/a&gt;  était un philosophe, théologien et politologue italien, connu pour son œuvre, &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1954_num_34_3_3377" style="color:#88A1E9" title="Defensor Pacis par Persée "&gt;Defensor Pacis&lt;/a&gt; (Le Défenseur de la Paix), qui a eu un impact considérable sur la pensée politique et religieuse de son époque et des siècles suivants. Il est l'un des précurseurs de la pensée politique moderne, notamment en ce qui concerne la séparation de l'Église et de l'État et la souveraineté populaire. Ses idées principales :&lt;/p&gt;
-&lt;p&gt; - La souveraineté populaire :
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_de_Padoue"  title=" Wikipedia"&gt;MARSILE de Pardoue&lt;/a&gt;  était un philosophe, théologien et politologue italien, connu pour son œuvre, &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1954_num_34_3_3377" style="color:#88A1E9" title="Defensor Pacis par Persée "&gt;Defensor Pacis&lt;/a&gt; (Le Défenseur de la Paix), qui a eu un impact considérable sur la pensée politique et religieuse de son époque et des siècles suivants. Il est l'un des précurseurs de la pensée politique moderne, notamment en ce qui concerne la séparation de l'Église et de l'État et la souveraineté populaire. Ses idées principales :&lt;/p&gt; &lt;p&gt;La souveraineté populaire :
 Il affirme que l'autorité politique ultime réside dans le peuple. C'est une idée révolutionnaire pour l'époque. 
-Le pouvoir des gouvernants vient du consentement des gouvernés, et non de Dieu ou de l'Église. Cette idée annonce les théories modernes du contrat social. &lt;/p&gt;
-&lt;p&gt; - La séparation de l'Église et de l'État :
-Il critique l'ingérence de l'Église dans les affaires politiques et soutient que le pouvoir spirituel et le pouvoir temporel doivent être strictement séparés.&lt;/p&gt;
-&lt;p&gt; -  Le rôle de l'Église :
+Le pouvoir des gouvernants vient du consentement des gouvernés, et non de Dieu ou de l'Église. Cette idée annonce les théories modernes du contrat social. &lt;/p&gt; &lt;p&gt;La séparation de l'Église et de l'État :
+Il critique l'ingérence de l'Église dans les affaires politiques et soutient que le pouvoir spirituel et le pouvoir temporel doivent être strictement séparés.&lt;/p&gt; &lt;p&gt;Le rôle de l'Église :
  l'Église doit se limiter à ses fonctions spirituelles. Il rejette l'idée que le pape ait une autorité suprême sur les rois et les empereurs. 
-Il propose que les conciles généraux, composés de représentants du clergé et des laïcs, soient l'autorité suprême dans les affaires religieuses, et non le pape seul. &lt;/p&gt;
-&lt;p&gt; - La paix comme objectif politique :
-Il considère que la paix est le but ultime de la société. Pour y parvenir, il faut éviter les conflits entre l'Église et l'État et garantir une autorité politique légitime et stable. &lt;/p&gt;   &lt;p&gt; &lt;/p&gt;  &lt;p&gt; Il accuse la papauté d'être une source de division et de conflit et soutient que les lois doivent être l'expression de la volonté du peuple, et non imposées par une autorité extérieure (comme l'Église). Il s'inspire de la philosophie  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1955_num_35_3_3428"  title="Le Rôle de l'aristotélisme dans le « Defensor Paris » par Persée "&gt;politique d'Aristote&lt;/a&gt;, en particulier de son idée que l'homme est un "animal politique" qui ne peut s'épanouir que dans une communauté organisée. &lt;/p&gt;  &lt;p&gt;"" Le Defensor Pacis" est condamné comme hérétique par le pape Jean XXII en 1327. Il est excommunié, et son œuvre est brûlée mais ses idées sur la séparation de l'Église et de l'État et sur l'autorité des conciles influenceront plus tard des réformateurs comme Martin Luther et Jean Calvin. &lt;/p&gt;
+Il propose que les conciles généraux, composés de représentants du clergé et des laïcs, soient l'autorité suprême dans les affaires religieuses, et non le pape seul. &lt;/p&gt; &lt;p&gt;La paix comme objectif politique :
+Il considère que la paix est le but ultime de la société. Pour y parvenir, il faut éviter les conflits entre l'Église et l'État et garantir une autorité politique légitime et stable. &lt;/p&gt; &lt;p&gt; Il accuse la papauté d'être une source de division et de conflit et soutient que les lois doivent être l'expression de la volonté du peuple, et non imposées par une autorité extérieure (comme l'Église). Il s'inspire de la philosophie  &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1955_num_35_3_3428"  title="Le Rôle de l'aristotélisme dans le « Defensor Paris » par Persée "&gt;politique d'Aristote&lt;/a&gt;, en particulier de son idée que l'homme est un "animal politique" qui ne peut s'épanouir que dans une communauté organisée. &lt;/p&gt; &lt;p&gt;"" Le Defensor Pacis" est condamné comme hérétique par le pape Jean XXII en 1327. Il est excommunié, et son œuvre est brûlée mais ses idées sur la séparation de l'Église et de l'État et sur l'autorité des conciles influenceront plus tard des réformateurs comme Martin Luther et Jean Calvin. &lt;/p&gt;
 </t>
         </is>
       </c>
@@ -5532,7 +5499,7 @@
       </c>
       <c r="E75" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Jandun" title=" Wikipedia"&gt;JEAN de Jandun&lt;/a&gt;  était un philosophe, théologien et écrivain politique français, principalement connu pour ses travaux en philosophie naturelle. Il est sans doute le représentant le plus illustre de l’averroïsme parisien du premier quart du xive siècle, mais il est surtout connu par les conflits politico-religieux qui, à côté de Louis de Bavière et Marsile de Padoue, l’ont opposé au pape Jean XXII.. &lt;/p&gt; &lt;p&gt; Il est connu pour son interprétation radicale de la &lt;a href="https://la-philosophie.com/philosophie-aristote" style="color:#88A1E9" title=Philosophie d'Aristote par Philo.com "&gt;philosophie d'Aristote&lt;/a&gt;, qu'il a défendue contre les critiques des théologiens chrétiens. Il a soutenu une forme d'aristotélisme qui mettait l'accent sur la séparation entre la raison et la foi, une position qui l'a souvent mis en conflit avec les autorités ecclésiastiques. &lt;/p&gt; &lt;p&gt; Une des idées les plus controversées associées à Jean de Jandun est la théorie de la "double vérité". Selon cette théorie, une proposition peut être vraie en philosophie tout en étant fausse en théologie, et vice versa. Cette idée a été largement rejetée par les théologiens chrétiens, qui considéraient qu'elle sapait l'autorité de la révélation divine. &lt;/p&gt; &lt;p&gt; Il est également connu pour sa collaboration avec Marsile de Padoue, un autre philosophe et théologien médiéval. Ensemble, ils ont écrit le  &lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1929_num_8_1_6594_t1_0256_0000_2" title="Marsilius of Padua" par Persée "&gt;"Defensor Pacis"&lt;/a&gt; (Défenseur de la Paix), un ouvrage politique majeur qui critique la papauté et défend l'idée d'un gouvernement séculier indépendant de l'autorité ecclésiastique. Le "Defensor Pacis" a été publié en 1324 et a immédiatement suscité la controverse. L'ouvrage soutient que la source ultime de l'autorité politique est le peuple, et non le pape. Il critique également la richesse et le pouvoir temporel de l'Église, arguant que ceux-ci corrompent sa mission spirituelle. &lt;/p&gt;  &lt;p&gt; &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Jandun" title=" Wikipedia"&gt;JEAN de Jandun&lt;/a&gt;  était un philosophe, théologien et écrivain politique français, principalement connu pour ses travaux en philosophie naturelle. Il est sans doute le représentant le plus illustre de l’averroïsme parisien du premier quart du xive siècle, mais il est surtout connu par les conflits politico-religieux qui, à côté de Louis de Bavière et Marsile de Padoue, l’ont opposé au pape Jean XXII.. &lt;/p&gt; &lt;p&gt; Il est connu pour son interprétation radicale de la &lt;a href="https://la-philosophie.com/philosophie-aristote" style="color:#88A1E9" title=Philosophie d'Aristote par Philo.com "&gt;philosophie d'Aristote&lt;/a&gt;, qu'il a défendue contre les critiques des théologiens chrétiens. Il a soutenu une forme d'aristotélisme qui mettait l'accent sur la séparation entre la raison et la foi, une position qui l'a souvent mis en conflit avec les autorités ecclésiastiques. &lt;/p&gt; &lt;p&gt; Une des idées les plus controversées associées à Jean de Jandun est la théorie de la "double vérité". Selon cette théorie, une proposition peut être vraie en philosophie tout en étant fausse en théologie, et vice versa. Cette idée a été largement rejetée par les théologiens chrétiens, qui considéraient qu'elle sapait l'autorité de la révélation divine. &lt;/p&gt; &lt;p&gt; Il est également connu pour sa collaboration avec Marsile de Padoue, un autre philosophe et théologien médiéval. Ensemble, ils ont écrit le  &lt;a href="https://www.persee.fr/doc/rbph_0035-0818_1929_num_8_1_6594_t1_0256_0000_2" title="Marsilius of Padua par Persée"&gt;"Defensor Pacis"&lt;/a&gt; (Défenseur de la Paix), un ouvrage politique majeur qui critique la papauté et défend l'idée d'un gouvernement séculier indépendant de l'autorité ecclésiastique. Le "Defensor Pacis" a été publié en 1324 et a immédiatement suscité la controverse. L'ouvrage soutient que la source ultime de l'autorité politique est le peuple, et non le pape. Il critique également la richesse et le pouvoir temporel de l'Église, arguant que ceux-ci corrompent sa mission spirituelle. &lt;/p&gt;   </t>
         </is>
       </c>
       <c r="F75" s="30" t="inlineStr">
@@ -5733,7 +5700,7 @@
       </c>
       <c r="E78" s="38" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gersonide"  title=" Wikipedia"&gt;GERSONIDE&lt;/a&gt; de son nom complet Lévi ben Gershom, est un des grands penseurs juifs du Moyen Âge, actif dans le sud de la France. Mathématicien, astronome, médecin, exégète biblique, talmudiste et philosophe, il est souvent considéré comme l’un des plus  &lt;a href="https://www.youtube.com/watch?v=zFnektKxZok" title="Levi ben Gerson (gersonides)  par Math Mystique"&gt;grands esprits juifs &lt;/a&gt; entre Maïmonide et la modernité. Il écrit en hébreu et en arabe, mêlant étude des textes religieux, science et philosophie, dans un esprit très critique et original. &lt;/p&gt; &lt;p&gt; Sa philosophie se veut un rapprochement systématique entre la pensée d’Aristote (via Averroès) et la pensée biblique‑talmudique. Dans son œuvre majeure, Milhamot Ha‑Shem (Les Guerres du Seigneur), il cherche à montrer que la raison et la révélation peuvent coexister et s’accorder sur la plupart des vérités importantes. Il adopte une cosmologie largement aristotélicienne tout en restant fidèle à un cadre théiste juif, en méditant par exemple  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1954_num_28_4_2056" title="les idées philosophiques de GERSONIDE par Persée"&gt;la création, la nature de Dieu &lt;/a&gt; et l’ordre du monde. &lt;/p&gt; &lt;p&gt; Parmi ses thèses les plus marquantes figurent sa conception de l’âme et de la prophétie : il soutient que l’âme humaine peut s’identifier à une intelligence universelle ou “raison active” qui unit l’homme à Dieu, et que l’immortalité de l’âme passe par l’acquisition de connaissances rationnelles adéquates. Il défend aussi une vision particulière de la connaissance divine : Dieu connaît toutes les possibilités humaines, mais ne prédétermine pas chaque choix, ce qui laisse une véritable place au libre arbitre humain, en rupture avec une vision toute‑puissante et strictement déterministe. &lt;/p&gt; &lt;p&gt; Il  est remarquable par son a href="https://www.youtube.com/watch?v=sq1YiI6BGVQ" title="medieval  philosopher GERSONIDE par Stay curious radio"&gt;rigoureux rationalisme &lt;/a&gt; et son goût pour les méthodes analytiques proches de la scolastique latine. Il utilise les mathématiques et l’astronomie non seulement comme sciences, mais comme instruments pour mieux comprendre Dieu et le monde créé. Sa tentative de fonder une théologie juive stable sur des bases scientifiques et rationnelles en fait un pont entre la pensée islamique‑aristotélicienne, la scolastique chrétienne et la tradition juive médiévale. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gersonide"  title=" Wikipedia"&gt;GERSONIDE&lt;/a&gt; de son nom complet Lévi ben Gershom, est un des grands penseurs juifs du Moyen Âge, actif dans le sud de la France. Mathématicien, astronome, médecin, exégète biblique, talmudiste et philosophe, il est souvent considéré comme l’un des plus  &lt;a href="https://www.youtube.com/watch?v=zFnektKxZok" title="Levi ben Gerson (gersonides)  par Math Mystique"&gt;grands esprits juifs &lt;/a&gt; entre Maïmonide et la modernité. Il écrit en hébreu et en arabe, mêlant étude des textes religieux, science et philosophie, dans un esprit très critique et original. &lt;/p&gt; &lt;p&gt; Sa philosophie se veut un rapprochement systématique entre la pensée d’Aristote (via Averroès) et la pensée biblique‑talmudique. Dans son œuvre majeure, Milhamot Ha‑Shem (Les Guerres du Seigneur), il cherche à montrer que la raison et la révélation peuvent coexister et s’accorder sur la plupart des vérités importantes. Il adopte une cosmologie largement aristotélicienne tout en restant fidèle à un cadre théiste juif, en méditant par exemple  &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1954_num_28_4_2056" title="les idées philosophiques de GERSONIDE par Persée"&gt;la création, la nature de Dieu &lt;/a&gt; et l’ordre du monde. &lt;/p&gt; &lt;p&gt; Parmi ses thèses les plus marquantes figurent sa conception de l’âme et de la prophétie : il soutient que l’âme humaine peut s’identifier à une intelligence universelle ou “raison active” qui unit l’homme à Dieu, et que l’immortalité de l’âme passe par l’acquisition de connaissances rationnelles adéquates. Il défend aussi une vision particulière de la connaissance divine : Dieu connaît toutes les possibilités humaines, mais ne prédétermine pas chaque choix, ce qui laisse une véritable place au libre arbitre humain, en rupture avec une vision toute‑puissante et strictement déterministe. &lt;/p&gt; &lt;p&gt; Il  est remarquable par son &lt;a href="https://www.youtube.com/watch?v=sq1YiI6BGVQ" title="medieval  philosopher GERSONIDE par Stay curious radio"&gt;rigoureux rationalisme &lt;/a&gt; et son goût pour les méthodes analytiques proches de la scolastique latine. Il utilise les mathématiques et l’astronomie non seulement comme sciences, mais comme instruments pour mieux comprendre Dieu et le monde créé. Sa tentative de fonder une théologie juive stable sur des bases scientifiques et rationnelles en fait un pont entre la pensée islamique‑aristotélicienne, la scolastique chrétienne et la tradition juive médiévale. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -6197,7 +6164,7 @@
       </c>
       <c r="E85" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_d%27Autr%C3%A9court"   title=" Wikipedia"&gt;Nicolas D'AUTRECOURT&lt;/a&gt; était un philosophe et théologien médiéval souvent considéré comme l'un des précurseurs du &lt;a href="https://www.philomag.com/lexique/scepticisme" title="Le septicisme  par Philomag "&gt;scepticisme moderne&lt;/a&gt; et de la pensée critique. Bien que moins connu que d'autres figures de la scolastique médiévale, comme Thomas d'Aquin ou Jean Duns Scot, il a joué un rôle important dans l'histoire de la philosophie en remettant en question certaines des certitudes de son époque. &lt;/p&gt; &lt;p&gt;  Il est surtout connu pour son scepticisme radical, qui l'a amené à remettre en question les fondements de la connaissance et de la métaphysique. Il a critiqué les arguments traditionnels de la scolastique, en particulier ceux basés sur la causalité et la substance. Selon lui, il est impossible de connaître avec certitude les causes des phénomènes ou la nature des substances.&lt;/p&gt; &lt;p&gt;  En 1346, il a été condamné par le pape Clément VI pour ses positions philosophiques jugées dangereuses pour la foi chrétienne. Ses écrits ont été brûlés, et il a été contraint de se rétracter publiquement. Après sa condamnation, il a disparu des archives historiques, et on sait peu de choses sur les dernières années de sa vie.&lt;/p&gt; &lt;p&gt; Malgré la destruction de la plupart de ses écrits, quelques lettres et fragments de ses travaux ont survécu. Parmi ceux-ci, ses Lettres à Bernard d'Arezzo sont particulièrement importantes, car elles exposent ses critiques de la causalité et de la connaissance métaphysique. &lt;/p&gt; &lt;p&gt; Il reste une figure fascinante de l'histoire de la philosophie, car il incarne une rupture avec les certitudes de la &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1911_num_18_70_1977" style="color:#88A1E9" title="La scolastique médiévale" par Persée "&gt;scolastique médiévale&lt;/a&gt;. Son scepticisme radical et sa critique de la causalité préfigurent des débats philosophiques qui prendront toute leur importance à l'époque moderne. Bien que marginalisé de son vivant, il est aujourd'hui reconnu comme un penseur original et audacieux. &lt;/p&gt;  </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_d%27Autr%C3%A9court"   title=" Wikipedia"&gt;Nicolas D'AUTRECOURT&lt;/a&gt; était un philosophe et théologien médiéval souvent considéré comme l'un des précurseurs du &lt;a href="https://www.philomag.com/lexique/scepticisme" title="Le septicisme  par Philomag "&gt;scepticisme moderne&lt;/a&gt; et de la pensée critique. Bien que moins connu que d'autres figures de la scolastique médiévale, comme Thomas d'Aquin ou Jean Duns Scot, il a joué un rôle important dans l'histoire de la philosophie en remettant en question certaines des certitudes de son époque. &lt;/p&gt; &lt;p&gt;  Il est surtout connu pour son scepticisme radical, qui l'a amené à remettre en question les fondements de la connaissance et de la métaphysique. Il a critiqué les arguments traditionnels de la scolastique, en particulier ceux basés sur la causalité et la substance. Selon lui, il est impossible de connaître avec certitude les causes des phénomènes ou la nature des substances.&lt;/p&gt; &lt;p&gt;  En 1346, il a été condamné par le pape Clément VI pour ses positions philosophiques jugées dangereuses pour la foi chrétienne. Ses écrits ont été brûlés, et il a été contraint de se rétracter publiquement. Après sa condamnation, il a disparu des archives historiques, et on sait peu de choses sur les dernières années de sa vie.&lt;/p&gt; &lt;p&gt; Malgré la destruction de la plupart de ses écrits, quelques lettres et fragments de ses travaux ont survécu. Parmi ceux-ci, ses Lettres à Bernard d'Arezzo sont particulièrement importantes, car elles exposent ses critiques de la causalité et de la connaissance métaphysique. &lt;/p&gt; &lt;p&gt; Il reste une figure fascinante de l'histoire de la philosophie, car il incarne une rupture avec les certitudes de la &lt;a href="https://www.persee.fr/doc/phlou_0776-555x_1911_num_18_70_1977" style="color:#88A1E9" title="La scolastique médiévale par Persée"&gt;scolastique médiévale&lt;/a&gt;. Son scepticisme radical et sa critique de la causalité préfigurent des débats philosophiques qui prendront toute leur importance à l'époque moderne. Bien que marginalisé de son vivant, il est aujourd'hui reconnu comme un penseur original et audacieux. &lt;/p&gt;  </t>
         </is>
       </c>
       <c r="F85" s="30" t="inlineStr">
@@ -6855,8 +6822,7 @@
       </c>
       <c r="E95" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Coluccio_Salutati"  title=" Wikipedia"&gt;Coluccio SALUTATI&lt;/a&gt; était un philosophe et homme politique italien considéré comme une figure de référence de la Renaissance culturelle florentine. Il a vécu pendant une période de transition entre le Moyen Âge et la Renaissance, marquée par un regain d'intérêt pour les textes antiques et les valeurs civiques. Il a contribué à poser les bases de l'humanisme florentin. &lt;/p&gt; &lt;p&gt; Il a encouragé la traduction et l'étude des œuvres de Cicéron, Sénèque et d'autres auteurs antiques et a promu l'étude de la grammaire, de la rhétorique, de l'histoire et de la philosophie morale, fondements de l'éducation humaniste. Contrairement à Pétrarque, qui privilégiait la retraite studieuse, il a défendu l'engagement civique et l'action politique comme voie vers la vertu et a toujours cherché à concilier philosophie antique et théologie, préfigurant des penseurs comme Marsile Ficin.  Ses oeuvres majeures : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1956_num_54_44_4898_t1_0629_0000_2" title="Coluccio Salutati, De nobilitate legum et medicinae, De verecundia par Persée"&gt;De nobilitate legum et medicinae &lt;/a&gt; : Défend la supériorité du droit sur la médecine. &lt;/p&gt; 
-&lt;p&gt;&lt;em&gt;De fato, fortuna et casu&lt;/em&gt; : Réflexion sur le libre arbitre. &lt;/p&gt; &lt;p&gt;Il incarne le passage de la culture médiévale à  &lt;a href="https://www.youtube.com/watch?v=UCODGnN8Vck"  title=" Coluccio Salutati: El Humanista que Forjó el Renacimiento en Italia par Revista Literaria"&gt;l'humanisme renaissant&lt;/a&gt;, en mêlant érudition classique, engagement politique et  &lt;a href="https://www.persee.fr/doc/efr_0223-5099_2009_act_423_1_9790#:~:text=%C3%94%20hommes%20au%20milieu%20desquels,peut%20trouver%20la%20vie%20solitaire!" title=" Coluccio Salutati et Santa Maria degli Angeli par Persée"&gt;foi chrétienne&lt;/a&gt;. Son rôle administratif et intellectuel a fait de Florence un foyer culturel essentiel. &lt;/p&gt; Chancelier de la république de Florence de 1375 à sa mort, il rédige des lettres officielles d’une telle éloquence que le duc de Milan les disait plus redoutables qu’un corps de cavalerie. Il fait venir à Florence, en 1397, le savant byzantin Manuel Chrysoloras pour y enseigner le grec. 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Coluccio_Salutati"  title=" Wikipedia"&gt;Coluccio SALUTATI&lt;/a&gt; était un philosophe et homme politique italien considéré comme une figure de référence de la Renaissance culturelle florentine. Il a vécu pendant une période de transition entre le Moyen Âge et la Renaissance, marquée par un regain d'intérêt pour les textes antiques et les valeurs civiques. Il a contribué à poser les bases de l'humanisme florentin. &lt;/p&gt; &lt;p&gt; Il a encouragé la traduction et l'étude des œuvres de Cicéron, Sénèque et d'autres auteurs antiques et a promu l'étude de la grammaire, de la rhétorique, de l'histoire et de la philosophie morale, fondements de l'éducation humaniste. Contrairement à Pétrarque, qui privilégiait la retraite studieuse, il a défendu l'engagement civique et l'action politique comme voie vers la vertu et a toujours cherché à concilier philosophie antique et théologie, préfigurant des penseurs comme Marsile Ficin.  Ses oeuvres majeures : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1956_num_54_44_4898_t1_0629_0000_2" title="Coluccio Salutati, De nobilitate legum et medicinae, De verecundia par Persée"&gt;De nobilitate legum et medicinae &lt;/a&gt; : Défend la supériorité du droit sur la médecine. &lt;/p&gt; &lt;p&gt;&lt;em&gt;De fato, fortuna et casu&lt;/em&gt; : Réflexion sur le libre arbitre. &lt;/p&gt; &lt;p&gt;Il incarne le passage de la culture médiévale à  &lt;a href="https://www.youtube.com/watch?v=UCODGnN8Vck"  title=" Coluccio Salutati: El Humanista que Forjó el Renacimiento en Italia par Revista Literaria"&gt;l'humanisme renaissant&lt;/a&gt;, en mêlant érudition classique, engagement politique et  &lt;a href="https://www.persee.fr/doc/efr_0223-5099_2009_act_423_1_9790#:~:text=%C3%94%20hommes%20au%20milieu%20desquels,peut%20trouver%20la%20vie%20solitaire!" title=" Coluccio Salutati et Santa Maria degli Angeli par Persée"&gt;foi chrétienne&lt;/a&gt;. Son rôle administratif et intellectuel a fait de Florence un foyer culturel essentiel. &lt;/p&gt; Chancelier de la république de Florence de 1375 à sa mort, il rédige des lettres officielles d’une telle éloquence que le duc de Milan les disait plus redoutables qu’un corps de cavalerie. Il fait venir à Florence, en 1397, le savant byzantin Manuel Chrysoloras pour y enseigner le grec. 
 </t>
         </is>
       </c>
@@ -7126,7 +7092,7 @@
       </c>
       <c r="E99" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Gerson"   title=" Wikipedia"&gt;Jean GERSON&lt;/a&gt;,  de son nom complet Jean Charlier de Gerson, est principalement connu pour son rôle de théologien, mystique, réformateur et chancelier de l'Université de Paris. Il a vécu pendant une période tumultueuse de l'histoire européenne, marquée par le &lt;a href="https://www.persee.fr/doc/cafan_0575-061x_2004_act_39_1_1831" style="color:#88A1E9" title="Le grand Schisme par Persée"&gt;Grand Schisme&lt;/a&gt; d'Occident (1378-1417), qui a divisé la chrétienté entre plusieurs papes rivaux. Cette crise a profondément influencé sa pensée et ses actions, notamment son engagement pour l'unité de l'Église et la réforme des institutions ecclésiastiques. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un représentant de la &lt;a href="https://www.universalis.fr/encyclopedie/devotio-moderna/" title="&lt;devotio moderna par Universalis"&gt;devotio moderna&lt;/a&gt;, un mouvement spirituel qui mettait l'accent sur la &lt;a href="https://www.universalis.fr/encyclopedie/piete/"  title="&lt;piété par Universalis"&gt;piété&lt;/a&gt; personnelle et la relation intime avec Dieu. Il a écrit abondamment sur des sujets théologiques et mystiques, cherchant à concilier la rigueur intellectuelle de la scolastique avec une spiritualité plus personnelle et affective. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus célèbres, on trouve: &lt;/p&gt; &lt;dd&gt; -  De mystica theologia, où il explore les voies de la contemplation mystique. &lt;/dd&gt; &lt;dd&gt; - De consolatione theologiae, qui traite de la consolation spirituelle face aux épreuves de la vie.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt;  &lt;p&gt; Il a été un ardent défenseur de la conciliarité, une doctrine qui soutenait que les conciles généraux de l'Église avaient autorité sur le pape, notamment en période de crise comme le Grand Schisme. Il a participé activement au &lt;a href="https://www.youtube.com/watch?v=LzxjFDsma3Y" title="&lt;consille de Constance’occident par Pierre de laurier »&gt;consille de Constance&lt;/a&gt;,  où il a plaidé pour la résolution du schisme et la réforme de l'Église. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Gerson"   title=" Wikipedia"&gt;Jean GERSON&lt;/a&gt;,  de son nom complet Jean Charlier de Gerson, est principalement connu pour son rôle de théologien, mystique, réformateur et chancelier de l'Université de Paris. Il a vécu pendant une période tumultueuse de l'histoire européenne, marquée par le &lt;a href="https://www.persee.fr/doc/cafan_0575-061x_2004_act_39_1_1831" style="color:#88A1E9" title="Le grand Schisme par Persée"&gt;Grand Schisme&lt;/a&gt; d'Occident (1378-1417), qui a divisé la chrétienté entre plusieurs papes rivaux. Cette crise a profondément influencé sa pensée et ses actions, notamment son engagement pour l'unité de l'Église et la réforme des institutions ecclésiastiques. &lt;/p&gt; &lt;p&gt; Il est souvent considéré comme un représentant de la &lt;a href="https://www.universalis.fr/encyclopedie/devotio-moderna/" title="&lt;devotio moderna par Universalis"&gt;devotio moderna&lt;/a&gt;, un mouvement spirituel qui mettait l'accent sur la &lt;a href="https://www.universalis.fr/encyclopedie/piete/"  title="&lt;piété par Universalis"&gt;piété&lt;/a&gt; personnelle et la relation intime avec Dieu. Il a écrit abondamment sur des sujets théologiques et mystiques, cherchant à concilier la rigueur intellectuelle de la scolastique avec une spiritualité plus personnelle et affective. &lt;/p&gt; &lt;p&gt; Parmi ses œuvres les plus célèbres, on trouve: &lt;/p&gt; &lt;p&gt;De mystica theologia, où il explore les voies de la contemplation mystique. &lt;/p&gt; &lt;p&gt;De consolatione theologiae, qui traite de la consolation spirituelle face aux épreuves de la vie.&lt;/p&gt; &lt;p&gt; Il a été un ardent défenseur de la conciliarité, une doctrine qui soutenait que les conciles généraux de l'Église avaient autorité sur le pape, notamment en période de crise comme le Grand Schisme. Il a participé activement au &lt;a href="https://www.youtube.com/watch?v=LzxjFDsma3Y" title="&lt;consille de Constance’occident par Pierre de laurier »&gt;consille de Constance&lt;/a&gt;,  où il a plaidé pour la résolution du schisme et la réforme de l'Église. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F99" s="30" t="inlineStr">
@@ -7192,11 +7158,8 @@
       </c>
       <c r="E100" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christine_de_Pizan"   title=" Wikipedia"&gt;CHRISTINE de Pizan&lt;/a&gt; est  l'une des premières femmes écrivaines professionnelles de l'histoire et une pionnière du féminisme italien. Son œuvre, riche et variée, aborde des thèmes tels que la défense des femmes, la philosophie, la politique et la poésie. Ses principales oeuvres : &lt;/p&gt; &lt;p&gt; -   &lt;a href="https://www.youtube.com/watch?v=AVnqVTo8iJ8" title="La Cité des Dames, XIX (extrait), Christine de Pizans  par Poème"&gt;"La Cité des Dames"&lt;/a&gt; (1405) : Considéré comme l'un des premiers textes féministes. Elle y construit une cité imaginaire peuplée de femmes illustres de l'histoire, de la mythologie et de la Bible, pour contrer les stéréotypes misogynes de son époque. Elle y défend l'idée que les femmes sont capables de grandes réalisations et méritent respect et éducation. &lt;/p&gt; 
-&lt;p&gt; - "Les Trois Vertus" (1405) : Également connu sous le titre "Le Trésor de la Cité des Dames", ce livre est un guide pratique pour les femmes de toutes les classes sociales, leur offrant des conseils sur la manière de vivre vertueusement et de gérer leurs responsabilités. &lt;/p&gt; 
-&lt;p&gt; - &lt;a href="https://www.youtube.com/watch?v=9yTFYRPFYuo" title="Le "Non !" de la Rose, Christine de Pizan et les femmes
- par Lettre UNIL"&gt;"Le Dit de la Rose"&lt;/a&gt;  (1402) : Réponse à la "Roman de la Rose", un texte médiéval qui véhiculait des idées misogynes. Elle y critique la représentation des femmes dans la littérature de son temps. &lt;/p&gt; 
-&lt;p&gt; - "Fais et Bonnes Meurs du Sage Roy Charles V" (1404) : Une biographie de Charles V, commandée par le duc de Bourgogne, qui témoigne de son engagement politique et de sa capacité à naviguer dans les cercles du pouvoir. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; &lt;p&gt; Elle est l'une des premières à  défendre les droits et la dignité des femmes. Elle conteste les idées reçues sur l'infériorité naturelle des femmes et plaide pour leur éducation et leur participation à la vie publique. Elle s'inspire de la philosophie antique et chrétienne pour développer une éthique personnelle et sociale. &lt;/p&gt; &lt;p&gt; Elle a laissé un héritage durable, tant dans le domaine littéraire que dans la pensée féministe. Ses œuvres ont été redécouvertes et réévaluées au cours des siècles, et elle est aujourd'hui reconnue comme une figure pionnière dans la lutte pour l'égalité des sexes. &lt;/p&gt;&lt;p&gt;   &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Christine_de_Pizan"   title=" Wikipedia"&gt;CHRISTINE de Pizan&lt;/a&gt; est  l'une des premières femmes écrivaines professionnelles de l'histoire et une pionnière du féminisme italien. Son œuvre, riche et variée, aborde des thèmes tels que la défense des femmes, la philosophie, la politique et la poésie. Ses principales oeuvres : &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=AVnqVTo8iJ8" title="La Cité des Dames, XIX (extrait), Christine de Pizans  par Poème"&gt;"La Cité des Dames"&lt;/a&gt; (1405) : Considéré comme l'un des premiers textes féministes. Elle y construit une cité imaginaire peuplée de femmes illustres de l'histoire, de la mythologie et de la Bible, pour contrer les stéréotypes misogynes de son époque. Elle y défend l'idée que les femmes sont capables de grandes réalisations et méritent respect et éducation. &lt;/p&gt; &lt;p&gt;"Les Trois Vertus" (1405) : Également connu sous le titre "Le Trésor de la Cité des Dames", ce livre est un guide pratique pour les femmes de toutes les classes sociales, leur offrant des conseils sur la manière de vivre vertueusement et de gérer leurs responsabilités. &lt;/p&gt; &lt;p&gt;&lt;a href="https://www.youtube.com/watch?v=9yTFYRPFYuo" title="Le "Non !" de la Rose, Christine de Pizan et les femmes
+ par Lettre UNIL"&gt;"Le Dit de la Rose"&lt;/a&gt;  (1402) : Réponse à la "Roman de la Rose", un texte médiéval qui véhiculait des idées misogynes. Elle y critique la représentation des femmes dans la littérature de son temps. &lt;/p&gt; &lt;p&gt;"Fais et Bonnes Meurs du Sage Roy Charles V" (1404) : Une biographie de Charles V, commandée par le duc de Bourgogne, qui témoigne de son engagement politique et de sa capacité à naviguer dans les cercles du pouvoir. &lt;/p&gt; &lt;p&gt; Elle est l'une des premières à  défendre les droits et la dignité des femmes. Elle conteste les idées reçues sur l'infériorité naturelle des femmes et plaide pour leur éducation et leur participation à la vie publique. Elle s'inspire de la philosophie antique et chrétienne pour développer une éthique personnelle et sociale. &lt;/p&gt; &lt;p&gt; Elle a laissé un héritage durable, tant dans le domaine littéraire que dans la pensée féministe. Ses œuvres ont été redécouvertes et réévaluées au cours des siècles, et elle est aujourd'hui reconnue comme une figure pionnière dans la lutte pour l'égalité des sexes. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F100" s="30" t="inlineStr">
@@ -7267,9 +7230,7 @@
       </c>
       <c r="E101" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leonardo_Bruni"   title=" Wikipedia"&gt;Léonardo BRUNI&lt;/a&gt; était un  &lt;a href="https://www.youtube.com/watch?v=t4SznS_1W-s" style="color:#88A1E9" title="Leonardo Bruni le stoicien par Michel Onfray "&gt;philosophe stoicien&lt;/a&gt;, humaniste italien et l'une des figures les plus importantes de la Renaissance italienne. Il vécu à une époque charnière, marquée par la transition entre le Moyen Âge et la Renaissance. Cette période a vu un regain d'intérêt pour les textes classiques de l'Antiquité gréco-romaine, ainsi que l'émergence de l'humanisme, un mouvement intellectuel qui mettait l'accent sur l'étude des humanités (littérature, histoire, philosophie) et la valorisation de l'individu. Ses contributions incluent : &lt;/p&gt; &lt;p&gt; - Traductions : Il a traduit de nombreuses œuvres classiques du grec au latin, rendant ainsi accessibles à un public plus large des textes d'auteurs comme Platon, Aristote, et Plutarque. Ses traductions étaient connues pour leur élégance et leur fidélité aux originaux. &lt;/p&gt; 
-&lt;p&gt; - Écrits historiques : Il est connu pour son ouvrage "Historiarum Florentini populi libri XII", une histoire de Florence qui marque une rupture avec les chroniques médiévales. Il a adopté une approche humaniste, en mettant l'accent sur les causes politiques et économiques des événements historiques plutôt que sur les interventions divines. &lt;/p&gt; 
-&lt;p&gt; - Écrits philosophiques et politiques : Il a écrit des traités sur la philosophie morale à la théorie politique. Son ouvrage &lt;a href="https://history.hanover.edu/texts/bruni.html"  title="Leonardo Bruni d'Arezzo par history Hanover "&gt;"De studiis et litteris"&lt;/a&gt; est un plaidoyer pour l'éducation humaniste, soulignant l'importance des études classiques pour la formation d'un citoyen éclairé. &lt;/p&gt; &lt;p&gt;Il a eu une influence profonde sur la Renaissance italienne et au-delà. Ses travaux ont contribué à redéfinir l'historiographie en la basant sur des sources fiables et une analyse critique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leonardo_Bruni"   title=" Wikipedia"&gt;Léonardo BRUNI&lt;/a&gt; était un  &lt;a href="https://www.youtube.com/watch?v=t4SznS_1W-s" style="color:#88A1E9" title="Leonardo Bruni le stoicien par Michel Onfray "&gt;philosophe stoicien&lt;/a&gt;, humaniste italien et l'une des figures les plus importantes de la Renaissance italienne. Il vécu à une époque charnière, marquée par la transition entre le Moyen Âge et la Renaissance. Cette période a vu un regain d'intérêt pour les textes classiques de l'Antiquité gréco-romaine, ainsi que l'émergence de l'humanisme, un mouvement intellectuel qui mettait l'accent sur l'étude des humanités (littérature, histoire, philosophie) et la valorisation de l'individu. Ses contributions incluent : &lt;/p&gt; &lt;p&gt;Traductions : Il a traduit de nombreuses œuvres classiques du grec au latin, rendant ainsi accessibles à un public plus large des textes d'auteurs comme Platon, Aristote, et Plutarque. Ses traductions étaient connues pour leur élégance et leur fidélité aux originaux. &lt;/p&gt; &lt;p&gt;Écrits historiques : Il est connu pour son ouvrage "Historiarum Florentini populi libri XII", une histoire de Florence qui marque une rupture avec les chroniques médiévales. Il a adopté une approche humaniste, en mettant l'accent sur les causes politiques et économiques des événements historiques plutôt que sur les interventions divines. &lt;/p&gt; &lt;p&gt;Écrits philosophiques et politiques : Il a écrit des traités sur la philosophie morale à la théorie politique. Son ouvrage &lt;a href="https://history.hanover.edu/texts/bruni.html"  title="Leonardo Bruni d'Arezzo par history Hanover "&gt;"De studiis et litteris"&lt;/a&gt; est un plaidoyer pour l'éducation humaniste, soulignant l'importance des études classiques pour la formation d'un citoyen éclairé. &lt;/p&gt; &lt;p&gt;Il a eu une influence profonde sur la Renaissance italienne et au-delà. Ses travaux ont contribué à redéfinir l'historiographie en la basant sur des sources fiables et une analyse critique. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F101" s="30" t="inlineStr">
@@ -7734,9 +7695,9 @@
       </c>
       <c r="E108" s="33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Cues"  title=" Wikipedia"&gt;Nicolas de CUES&lt;/a&gt; aussi connu sous le nom de Nicolaus Cusanus, était un philosophe, théologien, mathématicien et cardinal allemand. Il est souvent considéré comme un précurseur de la pensée moderne en raison de ses idées novatrices sur la connaissance, l’infini et la nature de Dieu. &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure,  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2009_num_107_2_8075_t1_0363_0000_2" style="color:#88A1E9" title="De Docta Ignorantia par Persée "&gt;De Docta Ignorantia&lt;/a&gt; (1440), il développe l’idée que Dieu est infini et inconnaissable pour l’homme. Toute tentative de compréhension de Dieu est nécessairement limitée par l’intellect humain. Il introduit une méthode où l’on admet son ignorance comme point de départ pour progresser vers une connaissance plus profonde.
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Nicolas_de_Cues"  title=" Wikipedia"&gt;Nicolas de CUES&lt;/a&gt; aussi connu sous le nom de Nicolaus Cusanus, était un philosophe, théologien, mathématicien et cardinal allemand. Il est souvent considéré comme un précurseur de la pensée moderne en raison de ses idées novatrices sur la connaissance, l’infini et la nature de Dieu. &lt;/p&gt; &lt;p&gt; Dans son œuvre majeure,  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2009_num_107_2_8075_t1_0363_0000_2" style="color:#88A1E9" title="De Docta Ignorantia par Persée "&gt;De Docta Ignorantia&lt;/a&gt; (1440), il développe l’idée que Dieu est infini et inconnaissable pour l’homme. Toute tentative de compréhension de Dieu est nécessairement limitée par l’intellect humain. Il introduit une méthode où l’on admet son ignorance comme point de départ pour progresser vers une connaissance plus profonde.
 Il utilise une analogie mathématique : tout rapport entre un cercle et une ligne droite est incompréhensible pour un esprit fini, tout comme la compréhension de Dieu dépasse les capacités humaines. &lt;/p&gt; &lt;p&gt; Un autre concept central chez lui est la &lt;a href="https://fr.wikipedia.org/wiki/Coincidentia_oppositorum" style="color:#88A1E9" title="coincidentia oppositorum par Wikipedia "&gt;coincidentia oppositorum&lt;/a&gt; : il soutient que dans l’infini (Dieu), les contradictions apparentes se résolvent. Ainsi, des notions opposées comme le mouvement et le repos, le fini et l’infini, se fondent en une unité supérieure. &lt;/p&gt; &lt;p&gt; Il est l’un des premiers penseurs à rompre avec la vision géocentrique d’Aristote et de Ptolémée. Dans De Visione Dei et De docta ignorantia, il remet en question l’idée d’un univers fini et centré sur la Terre, affirmant que l’univers pourrait être infini et que la Terre n’est pas au centre du cosmos.
-Cette idée influencera plus tard Giordano Bruno et Nicolas Copernic dans l’élaboration du modèle héliocentrique. &lt;/p&gt; &lt;p&gt; Son œuvre a influencé les courants mystiques chrétiens et certains penseurs de la Renaissance. Son approche théologique et philosophique anticipe des idées modernes sur l’infini, la relativité et la tolérance religieuse. &lt;/p&gt; &lt;p&gt; &lt;/p&gt;   &lt;p&gt;  &lt;/p&gt; &lt;p&gt; &lt;/p&gt;  &lt;audio controls title="Nicolas de Cues par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.04.2017-ITEMA_21307029-2017C12410S0118-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  &lt;p&gt;  &lt;/p&gt;</t>
+Cette idée influencera plus tard Giordano Bruno et Nicolas Copernic dans l’élaboration du modèle héliocentrique. &lt;/p&gt; &lt;p&gt; Son œuvre a influencé les courants mystiques chrétiens et certains penseurs de la Renaissance. Son approche théologique et philosophique anticipe des idées modernes sur l’infini, la relativité et la tolérance religieuse. &lt;/p&gt;       &lt;audio controls title="Nicolas de Cues par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10467-28.04.2017-ITEMA_21307029-2017C12410S0118-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  </t>
         </is>
       </c>
       <c r="F108" s="30" t="inlineStr">
@@ -7804,7 +7765,7 @@
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leon_Battista_Alberti" title=" Wikipedia"&gt;Léon Battista ALBERTI&lt;/a&gt; était un penseur et un artiste Italien de la Renaissance. Il était un polymathe, c'est-à-dire un savant qui excelle dans de nombreux domaines, y compris l'architecture, la sculpture, les mathématiques, la philosophie et la littérature. &lt;p&gt; &lt;p&gt; Il était un humaniste convaincu, qui croyait que la culture et la connaissance étaient des éléments clés pour améliorer la vie des individus et de la société dans son ensemble. Dans ses dialogues &lt;em&gt;Sur la famille&lt;/em&gt;, il réfléchit à l'éducation des enfants, à l'économie domestique et à l'amitié, et défend la vertu et la responsabilité civique.&lt;/p&gt; &lt;p&gt;  Il est aussi connu pour son traité sur l'architecture, intitulé De re aedificatoria (De la construction), publié en 1452. Ce livre est considéré comme l'un des premiers traités d'architecture modernes et a eu une influence considérable sur l'architecture européenne pendant des siècles.&lt;/p&gt; &lt;p&gt;
 Il a également écrit des traités sur la peinture et la sculpture, dans lesquels il a souligné l'importance de &lt;a href="https://www.youtube.com/watch?v=JnCiwh75D_k&amp;ab_channel=MassimoBrandolini"  title="Leon Battista Alberti par Massimo Brandolini"&gt; la perspective &lt;/a&gt; et de la proportion dans l'art. Il a été l'un des premiers à utiliser la perspective linéaire de manière systématique dans ses peintures et ses dessins, ce qui a permis de donner une impression de profondeur et de réalisme. &lt;/p&gt; Dans &lt;em&gt;De la peinture&lt;/em&gt; (1435) il donne la première théorie de la perspective : le tableau est comme « une fenêtre ouverte » sur le monde. Architecte, il dessine la façade de Santa Maria Novella à Florence et l’église Sant’Andrea de Mantoue. Il incarne l’idéal de l’« homme universel » de la Renaissance, pour qui « les hommes peuvent tout par eux-mêmes, pourvu qu’ils le veuillent ». 
-&lt;p&gt; &lt;/p&gt;</t>
+</t>
         </is>
       </c>
       <c r="F109" s="30" t="inlineStr">
@@ -7871,7 +7832,7 @@
       </c>
       <c r="E110" s="32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Laurent_Valla"   title=" Wikipedia"&gt;Lorenzo VALA&lt;/a&gt; est une figure majeure du début de la Renaissance italienne, connu pour ses contributions à la philosophie, à la philologie, à l'humanisme et à la &lt;a href="https://www.persee.fr/doc/vita_0042-7306_1994_num_134_1_1368"  title="&lt;Plaidoyer pour lorenzo Valla par Persée"&gt;critique historique&lt;/a&gt;. Il est souvent considéré comme l'un des &lt;a href="https://www.persee.fr/doc/vita_0042-7306_1993_num_130_1_900"  title="&lt;Lorenzo Valla par persée"&gt;premiers humanistes&lt;/a&gt; à avoir appliqué une méthode critique rigoureuse aux textes anciens et aux idées reçues de son époque. Son travail de philologie, notamment sa critique de la "Donation de Constantin" (Donatio Constantini), un document médiéval qui prétendait que l'empereur Constantin avait donné au pape Sylvestre Ier une autorité temporelle sur Rome et l'Occident. Valla a démontré que ce document était un faux, en utilisant des arguments linguistiques et historiques. Cette découverte a eu un impact significatif sur la critique historique et a affaibli les prétentions temporelles de la papauté. &lt;/p&gt; &lt;p&gt; Il a également contribué à la philosophie, en particulier dans son ouvrage "De voluptate" (Sur le plaisir), où il défend une éthique épicurienne, soutenant que le plaisir est le bien suprême. Cette position était en contradiction avec la morale chrétienne traditionnelle de son époque, qui privilégiait l'ascétisme et la renonciation. &lt;/p&gt; &lt;p&gt; Il a aussi plaidé pour un retour aux sources antiques et a critiqué la scolastique médiévale et a insisté sur l'importance de l'étude des langues classiques (latin et grec) afin d'améliorer la compréhension des textes anciens. Il a abordé des questions théologiques, notamment dans son "Annotationes in Novum Testamentum", où il a appliqué des méthodes philologiques à l'étude du Nouveau Testament. Il a critiqué la Vulgate, la traduction latine de la Bible, et a plaidé pour un retour aux textes originaux en grec. &lt;/p&gt;  &lt;p&gt; Il est considéré comme un précurseur de la Réforme protestante en raison de sa critique des institutions ecclésiastiques et il a joué un rôle crucial dans la transition entre le Moyen Âge et la Renaissance. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Laurent_Valla"   title=" Wikipedia"&gt;Lorenzo VALA&lt;/a&gt; est une figure majeure du début de la Renaissance italienne, connu pour ses contributions à la philosophie, à la philologie, à l'humanisme et à la &lt;a href="https://www.persee.fr/doc/vita_0042-7306_1994_num_134_1_1368"  title="&lt;Plaidoyer pour lorenzo Valla par Persée"&gt;critique historique&lt;/a&gt;. Il est souvent considéré comme l'un des &lt;a href="https://www.persee.fr/doc/vita_0042-7306_1993_num_130_1_900"  title="&lt;Lorenzo Valla par persée"&gt;premiers humanistes&lt;/a&gt; à avoir appliqué une méthode critique rigoureuse aux textes anciens et aux idées reçues de son époque. Son travail de philologie, notamment sa critique de la "Donation de Constantin" (Donatio Constantini), un document médiéval qui prétendait que l'empereur Constantin avait donné au pape Sylvestre Ier une autorité temporelle sur Rome et l'Occident. Valla a démontré que ce document était un faux, en utilisant des arguments linguistiques et historiques. Cette découverte a eu un impact significatif sur la critique historique et a affaibli les prétentions temporelles de la papauté. &lt;/p&gt; &lt;p&gt; Il a également contribué à la philosophie, en particulier dans son ouvrage "De voluptate" (Sur le plaisir), où il défend une éthique épicurienne, soutenant que le plaisir est le bien suprême. Cette position était en contradiction avec la morale chrétienne traditionnelle de son époque, qui privilégiait l'ascétisme et la renonciation. &lt;/p&gt; &lt;p&gt; Il a aussi plaidé pour un retour aux sources antiques et a critiqué la scolastique médiévale et a insisté sur l'importance de l'étude des langues classiques (latin et grec) afin d'améliorer la compréhension des textes anciens. Il a abordé des questions théologiques, notamment dans son "Annotationes in Novum Testamentum", où il a appliqué des méthodes philologiques à l'étude du Nouveau Testament. Il a critiqué la Vulgate, la traduction latine de la Bible, et a plaidé pour un retour aux textes originaux en grec. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur de la Réforme protestante en raison de sa critique des institutions ecclésiastiques et il a joué un rôle crucial dans la transition entre le Moyen Âge et la Renaissance. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F110" s="30" t="inlineStr">
@@ -8002,7 +7963,7 @@
       </c>
       <c r="E112" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_Ficin" title=" Wikipedia"&gt;Marsile FICIN&lt;/a&gt; était un philosophe, théologien et humaniste italien connu pour avoir joué un rôle clé dans la redécouverte et la diffusion du  &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme par Wikipedia "&gt;néoplatonisme&lt;/a&gt; en Occident. Il dirigea l’Académie néoplatonicienne de Florence, un cercle de penseurs inspirés par Platon, Plotin et d'autres philosophes antiques. &lt;/p&gt; &lt;p&gt;Il fut le premier à traduire intégralement les œuvres de Platon en latin, ce qui permit à toute l’Europe intellectuelle de redécouvrir sa pensée. Il traduisit également les œuvres de Plotin, Porphyre, Jamblique et Proclus, principaux représentants du néoplatonisme.  L’un de ses travaux majeurs fut aussi la traduction du &lt;a href="https://www.youtube.com/watch?v=SGI75n4lMSg&amp;t=538s" title="Hermès Trismégiste - Corpus Hermeticum par Julie Dratwiak "&gt;"Corpus Hermeticum"&lt;/a&gt;, une collection de textes ésotériques attribués à Hermès Trismégiste. Il chercha à réconcilier la philosophie platonicienne avec le christianisme voyant dans Platon une pensée compatible avec la religion chrétienne et considérait que la sagesse antique pouvait enrichir la foi. &lt;/p&gt; &lt;p&gt; Il développa une vision où l’âme humaine occupe une place centrale : elle est un intermédiaire entre le monde matériel et le monde intelligible (spirituel). L’ascension de l’âme vers Dieu passe par la contemplation et l’amour divin, des thèmes repris dans sa principale œuvre philosophique, la "Théologie platonicienne sur l’immortalité des âmes". &lt;/p&gt; &lt;p&gt;  Il influença la vision de l’amour platonique, développée notamment dans son &lt;a href="https://www.actu-philosophia.com/marsile-ficin-commentaire-du-parmenide-de-platon-564/"  title="Commentaire du Parmémide de Platon par Actu Philosophia "&gt;"Commentaire sur le Banquet de Platon"&lt;/a&gt; où il l y expose une conception de l’amour comme élévation spirituelle. &lt;p&gt; &lt;/p&gt; Il fut l’un des penseurs qui permit à la philosophie antique de renaître au sein de la Renaissance italienne. Son influence se fit sentir non seulement en philosophie, mais aussi dans l’esthétique, la théologie et même l’ésotérisme. Son œuvre reste essentielle pour comprendre la pensée humaniste et le renouveau de l’idéal platonicien dans l’Occident chrétien. &lt;/p&gt; &lt;p&gt; &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_Ficin" title=" Wikipedia"&gt;Marsile FICIN&lt;/a&gt; était un philosophe, théologien et humaniste italien connu pour avoir joué un rôle clé dans la redécouverte et la diffusion du  &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme par Wikipedia "&gt;néoplatonisme&lt;/a&gt; en Occident. Il dirigea l’Académie néoplatonicienne de Florence, un cercle de penseurs inspirés par Platon, Plotin et d'autres philosophes antiques. &lt;/p&gt; &lt;p&gt;Il fut le premier à traduire intégralement les œuvres de Platon en latin, ce qui permit à toute l’Europe intellectuelle de redécouvrir sa pensée. Il traduisit également les œuvres de Plotin, Porphyre, Jamblique et Proclus, principaux représentants du néoplatonisme.  L’un de ses travaux majeurs fut aussi la traduction du &lt;a href="https://www.youtube.com/watch?v=SGI75n4lMSg&amp;t=538s" title="Hermès Trismégiste - Corpus Hermeticum par Julie Dratwiak "&gt;"Corpus Hermeticum"&lt;/a&gt;, une collection de textes ésotériques attribués à Hermès Trismégiste. Il chercha à réconcilier la philosophie platonicienne avec le christianisme voyant dans Platon une pensée compatible avec la religion chrétienne et considérait que la sagesse antique pouvait enrichir la foi. &lt;/p&gt; &lt;p&gt; Il développa une vision où l’âme humaine occupe une place centrale : elle est un intermédiaire entre le monde matériel et le monde intelligible (spirituel). L’ascension de l’âme vers Dieu passe par la contemplation et l’amour divin, des thèmes repris dans sa principale œuvre philosophique, la "Théologie platonicienne sur l’immortalité des âmes". &lt;/p&gt; &lt;p&gt;  Il influença la vision de l’amour platonique, développée notamment dans son &lt;a href="https://www.actu-philosophia.com/marsile-ficin-commentaire-du-parmenide-de-platon-564/"  title="Commentaire du Parmémide de Platon par Actu Philosophia "&gt;"Commentaire sur le Banquet de Platon"&lt;/a&gt; où il l y expose une conception de l’amour comme élévation spirituelle.  Il fut l’un des penseurs qui permit à la philosophie antique de renaître au sein de la Renaissance italienne. Son influence se fit sentir non seulement en philosophie, mais aussi dans l’esthétique, la théologie et même l’ésotérisme. Son œuvre reste essentielle pour comprendre la pensée humaniste et le renouveau de l’idéal platonicien dans l’Occident chrétien. &lt;/p&gt;  
 </t>
         </is>
       </c>
@@ -8135,9 +8096,7 @@
       </c>
       <c r="E114" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Leonardo_Bruni"  title=" Wikipedia"&gt;Piétro POMPONAZZI&lt;/a&gt; était un philosophe italien, connu pour ses contributions à la philosophie naturelle, à l'éthique et à la métaphysique ainsi que pour ses réflexions audacieuses sur l'âme humaine, la mortalité et la relation entre la raison et la foi. Ses principales oeuvres :&lt;/p&gt; &lt;p&gt; -  &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2012_num_110_2_8231_t1_0382_0000_2"  title="Pietro Pomponazzi entre traditions et innovations par Persée "&gt;"De immortalitate animae"&lt;/a&gt; :  Dans cet ouvrage, il soutient que l'immortalité de l'âme ne peut pas être démontrée par la raison naturelle. Selon lui, Aristote, correctement interprété, ne soutenait pas l'immortalité de l'âme individuelle, mais plutôt que l'intellect est une faculté immortelle en tant que principe universel, et non en tant que réalité personnelle. &lt;/p&gt; 
-&lt;p&gt; - "De fato, de libero arbitrio et de praedestinatione" : Il a exploré la tension entre la liberté humaine et le déterminisme en soutenant que les êtres humains ont une certaine capacité à agir librement, mais que cette liberté est limitée par des facteurs naturels et sociaux.&lt;/p&gt; 
-&lt;p&gt; - "De naturalium effectuum admirandorum causis" : Il a défendu une  &lt;a href="https://www.youtube.com/watch?v=e_VbEpsgKOM"  title="Pomponazzi, Las Bases Filosoficas de la Revolucion Cientifica Moderna par Resumenes Entelekia "&gt;vision naturaliste&lt;/a&gt; du monde, insistant sur l'importance de la raison et de l'observation pour comprendre la nature et l'homme en rejetant les explications surnaturelles des phénomènes naturels, préférant des explications fondées sur des causes naturelles. &lt;/p&gt; &lt;p&gt; Il était un penseur clé de la Renaissance, dont les idées audacieuses et novatrices ont marqué un tournant dans l'histoire de la philosophie. En défendant une approche naturaliste et rationnelle, il a contribué à redéfinir les relations entre la philosophie, la science et la religion. Son œuvre reste une référence pour quiconque s'intéresse à l'évolution de la pensée occidentale à l'aube de la modernité. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Pietro_Pomponazzi"  title=" Wikipedia"&gt;Pietro POMPONAZZI&lt;/a&gt; était un philosophe italien, connu pour ses contributions à la philosophie naturelle, à l'éthique et à la métaphysique ainsi que pour ses réflexions audacieuses sur l'âme humaine, la mortalité et la relation entre la raison et la foi. Ses principales oeuvres :&lt;/p&gt; &lt;p&gt;&lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2012_num_110_2_8231_t1_0382_0000_2"  title="Pietro Pomponazzi entre traditions et innovations par Persée "&gt;"De immortalitate animae"&lt;/a&gt; :  Dans cet ouvrage, il soutient que l'immortalité de l'âme ne peut pas être démontrée par la raison naturelle. Selon lui, Aristote, correctement interprété, ne soutenait pas l'immortalité de l'âme individuelle, mais plutôt que l'intellect est une faculté immortelle en tant que principe universel, et non en tant que réalité personnelle. &lt;/p&gt; &lt;p&gt;"De fato, de libero arbitrio et de praedestinatione" : Il a exploré la tension entre la liberté humaine et le déterminisme en soutenant que les êtres humains ont une certaine capacité à agir librement, mais que cette liberté est limitée par des facteurs naturels et sociaux.&lt;/p&gt; &lt;p&gt;"De naturalium effectuum admirandorum causis" : Il a défendu une  &lt;a href="https://www.youtube.com/watch?v=e_VbEpsgKOM"  title="Pomponazzi, Las Bases Filosoficas de la Revolucion Cientifica Moderna par Resumenes Entelekia "&gt;vision naturaliste&lt;/a&gt; du monde, insistant sur l'importance de la raison et de l'observation pour comprendre la nature et l'homme en rejetant les explications surnaturelles des phénomènes naturels, préférant des explications fondées sur des causes naturelles. &lt;/p&gt; &lt;p&gt; Il était un penseur clé de la Renaissance, dont les idées audacieuses et novatrices ont marqué un tournant dans l'histoire de la philosophie. En défendant une approche naturaliste et rationnelle, il a contribué à redéfinir les relations entre la philosophie, la science et la religion. Son œuvre reste une référence pour quiconque s'intéresse à l'évolution de la pensée occidentale à l'aube de la modernité. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F114" s="30" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -936,17 +936,17 @@
       </c>
     </row>
     <row r="7" ht="97.5" customHeight="1" s="25">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="30">
         <v>672</v>
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>737</t>
+          <t xml:space="preserve">735</t>
         </is>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>672 - 737</t>
+          <t xml:space="preserve">vers 672 - 735</t>
         </is>
       </c>
       <c r="D7" s="31" t="inlineStr">
@@ -3348,17 +3348,17 @@
       </c>
     </row>
     <row r="43" ht="112.5" customHeight="1" s="25">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="30">
         <v>1215</v>
       </c>
       <c r="B43" s="30" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t xml:space="preserve">1277</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>1215 – 1280</t>
+          <t xml:space="preserve">vers 1215 – 1277</t>
         </is>
       </c>
       <c r="D43" s="31" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="E86" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Mirecourt"   title=" Wikipedia"&gt;Jean de MIRECOURT&lt;/a&gt;  était un philosophe cirtercien français connu pour ses positions nominalistes radicales qui insiste sur la toute-puissance divine et la contingence des lois morales et naturelles. Ses thèses, inspirées de Guillaume d’Ockham, ont été perçues comme dangereuses pour la théologie scolastique dominante. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=wu3EBIPzhlA" title="Who was the philosopher of Mirecourt?  par VIS PHILO"&gt;Sa pensée  &lt;/a&gt; pousse très loin l’idée que seule la volonté de Dieu fonde le bien et le mal, ce qui relativise la capacité de la raison humaine à saisir des vérités morales nécessaires. Son œuvre principale est un commentaire des "Sentences" de Pierre Lombard, genre classique de la théologie scolastique, dans lequel se trouvent les thèses qui ont suscité la censure. &lt;/p&gt; &lt;p&gt; En raison de la radicalité de certaines de ses positions, une série de propositions attribuées à Jean de Mirecourt est examinée puis condamnée à l’université de Paris en 1347, dans la ligne des grandes condamnations doctrinales de l'époque. Cette condamnation vise en particulier sa manière d’expliquer la causalité, le péché et la liberté humaine, jugée incompatible avec la doctrine catholique traditionnelle. &lt;/p&gt; &lt;p&gt; Il illustre un moment où la philosophie médiévale explore les limites de la rationalité théologique : jusqu’où peut-on aller en affirmant la liberté absolue de Dieu sans rendre la morale arbitraire. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_de_Mirecourt"   title=" Wikipedia"&gt;Jean de MIRECOURT&lt;/a&gt;  était un philosophe cistercien français connu pour ses positions nominalistes radicales qui insiste sur la toute-puissance divine et la contingence des lois morales et naturelles. Ses thèses, inspirées de Guillaume d’Ockham, ont été perçues comme dangereuses pour la théologie scolastique dominante. Surnommé le « moine blanc », à cause de son habit, il enseigne vers 1345 au collège cistercien Saint-Bernard, à Paris. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=wu3EBIPzhlA" title="Who was the philosopher of Mirecourt?  par VIS PHILO"&gt;Sa pensée  &lt;/a&gt; pousse très loin l’idée que seule la volonté de Dieu fonde le bien et le mal, ce qui relativise la capacité de la raison humaine à saisir des vérités morales nécessaires. Son œuvre principale est un commentaire des "Sentences" de Pierre Lombard, genre classique de la théologie scolastique, dans lequel se trouvent les thèses qui ont suscité la censure. &lt;/p&gt; &lt;p&gt; En raison de la radicalité de certaines de ses positions, une série de propositions attribuées à Jean de Mirecourt est examinée puis condamnée à l’université de Paris en 1347, dans la ligne des grandes condamnations doctrinales de l'époque. Cette condamnation vise en particulier sa manière d’expliquer la causalité, le péché et la liberté humaine, jugée incompatible avec la doctrine catholique traditionnelle. Il distingue deux degrés de certitude : l’évidence absolue, fondée sur le principe de non-contradiction, et l’évidence naturelle, celle des sens, que Dieu pourrait toujours tromper par sa toute-puissance. &lt;/p&gt; &lt;p&gt; Il illustre un moment où la philosophie médiévale explore les limites de la rationalité théologique : jusqu’où peut-on aller en affirmant la liberté absolue de Dieu sans rendre la morale arbitraire. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F86" s="30" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="E94" s="32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Dondi_dall%27Orologio"  title=" Wikipedia"&gt;Giovanni DONDI&lt;/a&gt;  naît à Chioggia, dans la région de Padoue, au sein d'une famille de savants — son père Jacopo Dondi est lui-même astronome et médecin réputé. Professeur de &lt;a href="https://fr.wikipedia.org/wiki/M%C3%A9decine" title=" Wikipedia"&gt;médecine&lt;/a&gt; à Padoue puis à Pavie, il est l'une des figures les plus polyvalentes de l'Italie du Trecento, à la croisée de la philosophie naturelle, de l'astronomie et de la mécanique. Il fréquente &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9trarque" title=" Wikipedia"&gt;Pétrarque&lt;/a&gt;, qui l'estime hautement et le cite dans ses écrits, signe de son insertion dans les cercles humanistes naissants qui transforment alors la culture italienne.&lt;/p&gt; &lt;p&gt;La réalisation qui assure à Dondi une gloire durable est l'Astrarium, horloge astronomique extraordinaire dont la construction lui demande seize années de travail, achevée vers 1364. Cet instrument, aux sept cadrans représentant les mouvements des planètes connues, est à la fois chef-d'œuvre d'horlogerie mécanique et traité d'&lt;a href="https://fr.wikipedia.org/wiki/Astronomie" title=" Wikipedia"&gt;astronomie&lt;/a&gt; appliquée. Dondi en laissa une description technique détaillée dans son &lt;em&gt;Tractatus Astrarii&lt;/em&gt;, source précieuse pour l'histoire des sciences. Il contribua également à la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_naturelle" title=" Wikipedia"&gt;philosophie naturelle&lt;/a&gt; par des traités sur les eaux thermales et des questions médicales.&lt;/p&gt; &lt;p&gt;Dondi appartient à la tradition aristotélicienne padouane, héritière du grand commentateur &lt;a href="https://fr.wikipedia.org/wiki/Averro%C3%A8s"  title=" Wikipedia"&gt;Averroès&lt;/a&gt;, qui fait de Padoue au XIVe siècle l'un des foyers les plus actifs de la philosophie naturelle en Europe. Cette tradition insiste sur l'observation rigoureuse, l'analyse des causes naturelles et l'usage des mathématiques pour décrire les phénomènes célestes. Son amitié avec Pétrarque le place au confluent de la scolastique héritée et de l'&lt;a href="https://fr.wikipedia.org/wiki/Humanisme_de_la_Renaissance"  title=" Wikipedia"&gt;humanisme&lt;/a&gt; naissant, tension féconde qui caractérise toute la culture italienne du Trecento.&lt;/p&gt; &lt;p&gt;L'héritage de Dondi est multiple : son Astrarium, reconstruit à plusieurs reprises à partir de ses descriptions, est exposé dans des musées de sciences et témoigne du génie technique de la mécanique médiévale. Ses travaux s'inscrivent dans la lignée qui mène à l'astronomie de la Renaissance et aux grandes horloges astronomiques des cathédrales européennes. Son exemple illustre comment, à Padoue, la frontière entre philosophie naturelle, mathématiques et technique s'efface progressivement, préfigurant l'idéal de l'ingénieur-philosophe de la &lt;a href="https://fr.wikipedia.org/wiki/Renaissance"  title=" Wikipedia"&gt;Renaissance&lt;/a&gt;.&lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Giovanni_Dondi"  title=" Wikipedia"&gt;Giovanni DONDI&lt;/a&gt;  naît à Chioggia, dans la région de Padoue, au sein d'une famille de savants — son père Jacopo Dondi est lui-même astronome et médecin réputé. Professeur de &lt;a href="https://fr.wikipedia.org/wiki/M%C3%A9decine" title=" Wikipedia"&gt;médecine&lt;/a&gt; à Padoue puis à Pavie, il est l'une des figures les plus polyvalentes de l'Italie du Trecento, à la croisée de la philosophie naturelle, de l'astronomie et de la mécanique. Il fréquente &lt;a href="https://fr.wikipedia.org/wiki/P%C3%A9trarque" title=" Wikipedia"&gt;Pétrarque&lt;/a&gt;, qui l'estime hautement et le cite dans ses écrits, signe de son insertion dans les cercles humanistes naissants qui transforment alors la culture italienne.&lt;/p&gt; &lt;p&gt;La réalisation qui assure à Dondi une gloire durable est l'Astrarium, horloge astronomique extraordinaire dont la construction lui demande seize années de travail, achevée vers 1364. Cet instrument, aux sept cadrans représentant les mouvements des planètes connues, est à la fois chef-d'œuvre d'horlogerie mécanique et traité d'&lt;a href="https://fr.wikipedia.org/wiki/Astronomie" title=" Wikipedia"&gt;astronomie&lt;/a&gt; appliquée. Dondi en laissa une description technique détaillée dans son &lt;em&gt;Tractatus Astrarii&lt;/em&gt;, source précieuse pour l'histoire des sciences. Il contribua également à la &lt;a href="https://fr.wikipedia.org/wiki/Philosophie_naturelle" title=" Wikipedia"&gt;philosophie naturelle&lt;/a&gt; par des traités sur les eaux thermales et des questions médicales.&lt;/p&gt; &lt;p&gt;Dondi appartient à la tradition aristotélicienne padouane, héritière du grand commentateur &lt;a href="https://fr.wikipedia.org/wiki/Averro%C3%A8s"  title=" Wikipedia"&gt;Averroès&lt;/a&gt;, qui fait de Padoue au XIVe siècle l'un des foyers les plus actifs de la philosophie naturelle en Europe. Cette tradition insiste sur l'observation rigoureuse, l'analyse des causes naturelles et l'usage des mathématiques pour décrire les phénomènes célestes. Son amitié avec Pétrarque le place au confluent de la scolastique héritée et de l'&lt;a href="https://fr.wikipedia.org/wiki/Humanisme_de_la_Renaissance"  title=" Wikipedia"&gt;humanisme&lt;/a&gt; naissant, tension féconde qui caractérise toute la culture italienne du Trecento.&lt;/p&gt; &lt;p&gt;L'héritage de Dondi est multiple : son Astrarium, reconstruit à plusieurs reprises à partir de ses descriptions, est exposé dans des musées de sciences et témoigne du génie technique de la mécanique médiévale. Ses travaux s'inscrivent dans la lignée qui mène à l'astronomie de la Renaissance et aux grandes horloges astronomiques des cathédrales européennes. Son exemple illustre comment, à Padoue, la frontière entre philosophie naturelle, mathématiques et technique s'efface progressivement, préfigurant l'idéal de l'ingénieur-philosophe de la &lt;a href="https://fr.wikipedia.org/wiki/Renaissance"  title=" Wikipedia"&gt;Renaissance&lt;/a&gt;.&lt;/p&gt;</t>
         </is>
       </c>
       <c r="F94" s="30" t="inlineStr">
@@ -7628,8 +7628,8 @@
       </c>
       <c r="E107" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Sebon"  title=" Wikipedia"&gt;Raymond SEBOND&lt;/a&gt;  était un philosophe catalan  actif principalement à Toulouse. Il est surtout célèbre pour son ouvrage "Theologia naturalis sive Liber creaturarum", une tentative audacieuse de démontrer les vérités de la foi chrétienne par la raison naturelle seule, sans recourir aux Écritures. &lt;/p&gt; &lt;p&gt; Né à Barcelone, il étudie et enseigne la médecine avant de se tourner vers la théologie à l'université de Toulouse. Son livre, publié posthumément, distingue le "livre de la nature" (accessible par l'observation rationnelle du monde) du "livre révélé" (la Bible), visant à réfuter les athées et le pélagianisme sur le terrain de la raison pure. &lt;/p&gt; &lt;p&gt; Dans sa Théologie naturelle, il progresse de l'analyse des créatures (minéral, végétal, animal) à la connaissance de Dieu, en insistant sur l'humilité humaine face à la transcendance divine. Influencé par Thomas d'Aquin et Aristote, il argue que la science profane peut mener à la foi, mais reste limitée par rapport à la révélation. &lt;/p&gt; &lt;p&gt; Montaigne traduira l'ouvrage en français vers 1568  à la demande de son père et lui consacre  &lt;a href="https://www.youtube.com/watch?v=kpyXQoRATWA" style="color:#88A1E9" title="
-Chapitre 12, livre ll: Apologie de Raimond Sebond  par Michel Piccoli "&gt;l'"Apologie de Raymond Sebond", &lt;/a&gt; le plus long chapitre de ses Essais. Montaigne critique toutefois son ambition rationaliste excessive, introduisant le doute sceptique et l'idée que la raison humaine ne suffit pas à saisir le divin. &lt;p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Raymond_Sebon"  title=" Wikipedia"&gt;Raymond SEBOND&lt;/a&gt;  était un philosophe catalan  actif principalement à Toulouse. Il est surtout célèbre pour son ouvrage "Theologia naturalis sive Liber creaturarum", une tentative audacieuse de démontrer les vérités de la foi chrétienne par la raison naturelle seule, sans recourir aux Écritures. Il meurt à Toulouse en 1436, l’année même où il achève son livre. &lt;/p&gt; &lt;p&gt; Né à Barcelone, il étudie et enseigne la médecine avant de se tourner vers la théologie à l'université de Toulouse. Son livre, publié posthumément, distingue le "livre de la nature" (accessible par l'observation rationnelle du monde) du "livre révélé" (la Bible), visant à réfuter les athées sur le terrain de la raison pure. &lt;/p&gt; &lt;p&gt; Dans sa Théologie naturelle, il progresse de l'analyse des créatures (minéral, végétal, animal) à la connaissance de Dieu, en insistant sur l'humilité humaine face à la transcendance divine. Influencé par Raymond Lulle, il argue que la science profane peut mener à la foi, mais reste limitée par rapport à la révélation. Son prologue, qui semble placer le livre de la nature au-dessus de la Bible, sera mis à l’Index en 1564. &lt;/p&gt; &lt;p&gt; Montaigne traduira l'ouvrage en français à la demande de son père (la traduction paraît en 1569) et lui consacre  &lt;a href="https://www.youtube.com/watch?v=kpyXQoRATWA" style="color:#88A1E9" title="
+Chapitre 12, livre ll: Apologie de Raimond Sebond  par Michel Piccoli "&gt;l'"Apologie de Raymond Sebond", &lt;/a&gt; le plus long chapitre de ses Essais. Montaigne critique toutefois son ambition rationaliste excessive, introduisant le doute sceptique et l'idée que la raison humaine ne suffit pas à saisir le divin. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F107" s="30" t="inlineStr">
@@ -8435,7 +8435,7 @@
     </row>
     <row r="120" ht="99.75" customHeight="1" s="25">
       <c r="A120" s="30">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="B120" s="30" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="C120" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">724 - 804</t>
+          <t xml:space="preserve">vers 735 - 804</t>
         </is>
       </c>
       <c r="D120" s="31" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2966,7 +2966,7 @@
       </c>
       <c r="E37" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_de_Hales"    title=" Wikipedia"&gt;Alexandre de HALES&lt;/a&gt; était un philosophe scolastique anglais considéré comme le premier grand maître franciscain à l'Université de Paris et surnommé "Doctor irrefragabilis admodum". Maître des arts dès 1209-1210 à Paris, il enseigne la philosophie avant les interdictions temporaires des textes aristotéliciens. &lt;/p&gt; &lt;p&gt; Précurseur du scotisme et du  &lt;a href="https://fr.wikipedia.org/wiki/Histoire_des_ordres_franciscains" title=" ordres des franciscains  par Wikipedia"&gt;franciscanisme &lt;/a&gt; intellectuel, il intègre Aristote avec Augustin, développant des doctrines comme le caractère indélébile des sacrements et le trésor des mérites des saints. Il défend une vision augustinienne de l'illumination divine et pose les bases théologiques pour l'ordre franciscain, notamment dans l'interprétation de la règle de saint François. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=lfzyS3RdRl0&amp;t=174s"  title=" Alexandre de Hales Biographies Fr par Christopher Santos Côté"&gt;Ses oeuvres  &lt;/a&gt; principales sont : "Sa Summa theologica"  achevée par ses élèves comme Jean de la Rochelle et Guillaume de Melitona, est la première somme théologique systématique franciscaine, structurée en thèse-antithèse-synthèse avec citations variées (Bible, Pères, philosophes arabes et grecs). Elle traite de Dieu et ses attributs (livre I), de la Création et du péché (II), de la rédemption (III), et des sacrements (IV), influençant profondément la scolastique. &lt;/p&gt; &lt;p&gt; Son œuvre, imprimée dès 1475, marque la transition vers la grande scolastique du XIIIe siècle et reste une référence pour la théologie franciscaine. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Alexandre_de_Hales"    title=" Wikipedia"&gt;Alexandre de HALES&lt;/a&gt; était un philosophe scolastique anglais considéré comme le premier grand maître franciscain à l'Université de Paris et surnommé "Doctor irrefragabilis admodum". Maître des arts dès 1209-1210 à Paris, il enseigne la philosophie avant les interdictions temporaires des textes aristotéliciens. En 1236, déjà maître réputé en théologie, il entre chez les franciscains : sa chaire devient la première chaire franciscaine de l’université de Paris. &lt;/p&gt; &lt;p&gt; Précurseur du scotisme et du  &lt;a href="https://fr.wikipedia.org/wiki/Histoire_des_ordres_franciscains" title=" ordres des franciscains  par Wikipedia"&gt;franciscanisme &lt;/a&gt; intellectuel, il intègre Aristote avec Augustin, développant des doctrines comme le caractère indélébile des sacrements et le trésor des mérites des saints. Il défend une vision augustinienne de l'illumination divine et pose les bases théologiques pour l'ordre franciscain, notamment dans l'interprétation de la règle de saint François. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=lfzyS3RdRl0&amp;t=174s"  title=" Alexandre de Hales Biographies Fr par Christopher Santos Côté"&gt;Ses oeuvres  &lt;/a&gt; principales sont : la &lt;em&gt;Summa theologica&lt;/em&gt;  achevée par ses élèves comme Jean de la Rochelle et Guillaume de Melitona, est la première somme théologique systématique franciscaine, organisée en questions, avec arguments pour et contre et citations variées (Bible, Pères, philosophes arabes et grecs). Elle traite de Dieu et ses attributs (livre I), de la Création et du péché (II), de la rédemption (III), et des sacrements (IV), influençant profondément la scolastique. &lt;/p&gt; &lt;p&gt; Son œuvre, imprimée dès 1475, marque la transition vers la grande scolastique du XIIIe siècle et reste une référence pour la théologie franciscaine. Il fut aussi le premier à prendre les &lt;em&gt;Sentences&lt;/em&gt; de Pierre Lombard comme manuel de l’enseignement théologique, et compta Bonaventure parmi ses élèves. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F37" s="30" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E16" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/B%C3%A9renger_de_Tours"   title=" Wikipedia"&gt; BERENGER de Tours&lt;/a&gt;  est une figure importante de l'histoire intellectuelle et religieuse du Moyen Âge surtout connu pour ses positions théologiques controversées, en particulier sur la question de la présence réelle du Christ dans &lt;a href="https://shs.cairn.info/revue-des-sciences-philosophiques-et-theologiques-2011-2-page-303?lang=fr"  title="Querelle eucharistique par Cairn "&gt;l'Eucharistie.  &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Au XIe siècle, la doctrine de la transsubstantiation, qui affirme que le pain et le vin deviennent réellement le corps et le sang du Christ lors de la consécration, commençait à se formaliser. Pour lui, le pain et le vin conservaient leur substance matérielle après la consécration, et la présence du Christ était spirituelle plutôt que physique. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur du rationalisme théologique, un courant qui cherche à concilier la foi chrétienne avec la raison et la logique. Il s'appuie sur des arguments rationnels pour interpréter les Écritures et les doctrines de l'Église, plutôt que de se contenter d'une acceptation littérale ou traditionnelle. &lt;/p&gt;&lt;p&gt;Bérenger utilise la dialectique, une méthode de raisonnement et de débat, pour défendre ses positions théologiques. Cette approche méthodique et logique préfigure la méthode scolastique, qui deviendra dominante dans les universités médiévales à partir du XIIe siècle. La scolastique cherche à résoudre les contradictions apparentes entre la foi et la raison en utilisant des arguments logiques et philosophiques. &lt;/p&gt;</t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/B%C3%A9renger_de_Tours"   title=" Wikipedia"&gt; BERENGER de Tours&lt;/a&gt;  est une figure importante de l'histoire intellectuelle et religieuse du Moyen Âge surtout connu pour ses positions théologiques controversées, en particulier sur la question de la présence réelle du Christ dans &lt;a href="https://shs.cairn.info/revue-des-sciences-philosophiques-et-theologiques-2011-2-page-303?lang=fr"  title="Querelle eucharistique par Cairn "&gt;l'Eucharistie.  &lt;/a&gt; Il enseigne à l’école Saint-Martin de Tours et s’oppose à Lanfranc, abbé du Bec. &lt;/p&gt; &lt;p&gt; Au XIe siècle, la doctrine de la transsubstantiation, qui affirme que le pain et le vin deviennent réellement le corps et le sang du Christ lors de la consécration, commençait à se formaliser. Pour lui, le pain et le vin conservaient leur substance matérielle après la consécration, et la présence du Christ était spirituelle plutôt que physique. Condamné par plusieurs conciles, il doit se rétracter à Rome en 1059, puis de nouveau en 1079 devant Grégoire VII, avant de finir ses jours en ermite sur l’île de Saint-Cosme, près de Tours. &lt;/p&gt; &lt;p&gt; Il est considéré comme un précurseur du rationalisme théologique, un courant qui cherche à concilier la foi chrétienne avec la raison et la logique. Il s'appuie sur des arguments rationnels pour interpréter les Écritures et les doctrines de l'Église, plutôt que de se contenter d'une acceptation littérale ou traditionnelle. &lt;/p&gt;&lt;p&gt;Bérenger utilise la dialectique, une méthode de raisonnement et de débat, pour défendre ses positions théologiques. Cette approche méthodique et logique préfigure la méthode scolastique, qui deviendra dominante dans les universités médiévales à partir du XIIe siècle. La scolastique cherche à résoudre les contradictions apparentes entre la foi et la raison en utilisant des arguments logiques et philosophiques. &lt;/p&gt;</t>
         </is>
       </c>
       <c r="F16" s="30" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E24" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilbert_de_La_Porr%C3%A9e" title=" Wikipedia"&gt;GILBERT de la Porrée&lt;/a&gt; était un grand penseur, à la fois philosophe, théologien et évêque de Poitiers. Il appartient à l’école de Chartres et compte parmi les figures importantes de la scolastique naissante. &lt;/p&gt; &lt;p&gt; Sa philosophie est marquée par &lt;a href="https://www.youtube.com/watch?v=1aU99SspzLA" title="gilbert of poitiers on individuation par history of philosophy"&gt;un réalisme modéré &lt;/a&gt; dans le débat sur les universaux. Il soutient qu’aux concepts généraux de notre esprit correspondent dans les choses des natures semblables, sans confondre pour autant l’idée générale et l’individu concret. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est son commentaire du De Trinitate de Boèce. C’est là qu’il développe ses analyses métaphysiques sur la forme, l’essence et l’individualité, avec un langage souvent très technique et parfois difficile à lire. &lt;/p&gt; &lt;p&gt; Ses positions sur la Trinité lui ont valu des accusations d’hérésie au concile de Reims en 1148. Le cœur du problème venait de certaines formulations jugées trop séparatrices entre l’essence divine et les personnes divines, mais Gilbert finit par accepter les formules proposées par ses adversaires. &lt;/p&gt; &lt;p&gt; Son intérêt principal est de clarifier la structure du réel par l’analyse logique et métaphysique. Il cherche à montrer comment les notions générales, les essences et les individus s’articulent, ce qui fait de lui  &lt;a href="https://gloss-e.irht.cnrs.fr/php/page.php?id=5" title=" commentaires sur les psaumes pauliniens par gloss"&gt;un auteur important &lt;/a&gt;  pour comprendre la transition entre la pensée antique et la scolastique médiévale. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilbert_de_La_Porr%C3%A9e" title=" Wikipedia"&gt;GILBERT de la Porrée&lt;/a&gt; était un grand penseur, à la fois philosophe, théologien et évêque de Poitiers. Il appartient à l’école de Chartres et compte parmi les figures importantes de la scolastique naissante. Élève de Bernard de Chartres et d’Anselme de Laon, il enseigne à Chartres puis à Paris, avant de devenir évêque de sa ville natale en 1142. &lt;/p&gt; &lt;p&gt; Sa philosophie est marquée par &lt;a href="https://www.youtube.com/watch?v=1aU99SspzLA" title="gilbert of poitiers on individuation par history of philosophy"&gt;un réalisme modéré &lt;/a&gt; dans le débat sur les universaux. Il soutient qu’aux concepts généraux de notre esprit correspondent dans les choses des natures semblables, sans confondre pour autant l’idée générale et l’individu concret. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est son commentaire du De Trinitate de Boèce. C’est là qu’il développe ses analyses métaphysiques sur la forme, l’essence et l’individualité, avec un langage souvent très technique et parfois difficile à lire. &lt;/p&gt; &lt;p&gt; Ses positions sur la Trinité lui ont valu des accusations d’hérésie au concile de Reims en 1148. Son principal accusateur était Bernard de Clairvaux. Le cœur du problème venait de certaines formulations jugées trop séparatrices entre l’essence divine et les personnes divines, mais Gilbert finit par accepter les formules proposées par ses adversaires. &lt;/p&gt; &lt;p&gt; Son intérêt principal est de clarifier la structure du réel par l’analyse logique et métaphysique. Il cherche à montrer comment les notions générales, les essences et les individus s’articulent, ce qui fait de lui  &lt;a href="https://gloss-e.irht.cnrs.fr/php/page.php?id=5" title=" commentaires sur les psaumes pauliniens par gloss"&gt;un auteur important &lt;/a&gt;  pour comprendre la transition entre la pensée antique et la scolastique médiévale. Ses disciples, les « porrétains », prolongent son enseignement jusqu’à la fin du XIIe siècle. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="E58" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_de_Freiberg"  title=" Wikipedia"&gt;Thierry de FREIBERG&lt;/a&gt;,  aussi appelé Dietrich de Freiberg, était un théologien dominicain, philosophe et scientifique allemand  connu pour son opposition au thomisme et ses réflexions novatrices en optique et en métaphysique.  Il enseigne dans plusieurs couvents allemands et devient provincial des dominicains de Teutonie vers 1300-1307. Ses écrits, influencés par Albert le Grand et Proclus, critiquent Thomas d'Aquin tout en développant une hylémorphisme audacieux. &lt;/p&gt; &lt;p&gt; Dans  &lt;a href="https://www.youtube.com/watch?v=BwgBLnWfv-g" title="Dietrich of Freiberg | Life, Works, and Philosophy par Philosopher Friends"&gt;son oeuvre &lt;/a&gt; " De ente et essentiae, il défend une ontologie réaliste où l'être premier est Dieu, distinct de l'essence, et où la forme substantialise la matière sans nécessiter une multiplicité d'individus par formes séparées. Il explore la connaissance de soi comme acte intellectif abstrait, et les objets intentionnels comme constitués par l'intellect agent. Anti-thomiste, il rejette l'univocité de l'être au profit d'une analogie stricte. &lt;/p&gt; &lt;p&gt; Il  excelle en optique expérimentale avec son traité De iride (Sur l'arc-en-ciel), où il explique la formation des couleurs primaires et secondaires par réfraction et réflexion dans les gouttes d'eau, dépassant les modèles purement qualitatifs d'Aristote et Alhazen. Il distingue lumière et couleur comme réalités distinctes et propose une théorie des medios transparents. Ses travaux préfigurent la perspective scientifique moderne. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thierry_de_Freiberg"  title=" Wikipedia"&gt;Thierry de FREIBERG&lt;/a&gt;,  aussi appelé Dietrich de Freiberg, était un théologien dominicain, philosophe et scientifique allemand  connu pour son opposition au thomisme et ses réflexions novatrices en optique et en métaphysique.  Il enseigne dans plusieurs couvents allemands et devient provincial des dominicains de Teutonie vers 1300-1307. Ses écrits, influencés par Albert le Grand et Proclus, critiquent Thomas d'Aquin tout en développant un hylémorphisme audacieux. &lt;/p&gt; &lt;p&gt; Dans  &lt;a href="https://www.youtube.com/watch?v=BwgBLnWfv-g" title="Dietrich of Freiberg | Life, Works, and Philosophy par Philosopher Friends"&gt;son oeuvre &lt;/a&gt; &lt;em&gt;De ente et essentia&lt;/em&gt;, il rejette la distinction réelle entre l’être et l’essence des créatures, défendue par Thomas d’Aquin. Il explore la connaissance de soi comme acte intellectif abstrait, et les objets intentionnels comme constitués par l'intellect agent. Pour lui, l’intellect agent est une substance qui se connaît elle-même et connaît toutes choses en connaissant son principe, une thèse qui marquera Maître Eckhart. &lt;/p&gt; &lt;p&gt; Il  excelle en optique expérimentale avec son traité De iride (Sur l'arc-en-ciel), où il explique la formation des arcs-en-ciel primaire et secondaire par réfraction et réflexion dans les gouttes d'eau, grâce à des expériences menées avec des globes de verre remplis d’eau, qui jouent le rôle de gouttes agrandies, dépassant les modèles purement qualitatifs d'Aristote et Alhazen. Il distingue lumière et couleur comme réalités distinctes et propose une théorie des milieux transparents. Ses travaux préfigurent la perspective scientifique moderne. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F58" s="30" t="inlineStr">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="E60" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_de_Rome"  title=" Wikipedia"&gt;Gilles de ROME&lt;/a&gt; est un théologien augustin italien et philosophe scolastique connu pour son rôle d’interprète d’Aristote, de théoricien du pouvoir princier et de défenseur de la suprématie pontificale. En 1292, il est élu supérieur général de l’ordre augustin, puis, en 1295, le pape Boniface VIII le nomme archevêque de Bourges, charge qu’il exerce tout en restant une figure intellectuelle influente. &lt;/p&gt; &lt;p&gt; Il cherche à concilier Aristote avec la théologie chrétienne, dans un contexte marqué par les condamnations de 1277 à Paris contre certaines thèses aristotéliciennes. Son œuvre couvre la théologie, la philosophie naturelle, la logique et la métaphysique, avec de nombreux commentaires sur Aristote et sur les Sentences de Pierre Lombard. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=Qw-Sbn5MeNs"  title="Giles of Rome: Life, Works, and Influence par Philosoppher Friends"&gt;Son oeuvre &lt;/a&gt; principale est : "De regimine principum" est un vaste traité en trois livres sur la morale, l’économie domestique et la politique, rédigé pour l’éducation du futur roi Philippe IV le Bel. On lui attribue aussi des textes politiques et ecclésiologiques comme le "De ecclesiastica potestate" et une participation à la bulle "Unam Sanctam", où il défend une vision très forte de la supériorité du pouvoir spirituel sur le pouvoir temporel. &lt;/p&gt; &lt;p&gt; Son traité sur le gouvernement des princes a été largement diffusé et traduit, influençant durablement la pensée politique médiévale et la littérature des "miroirs des princes". &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gilles_de_Rome"  title=" Wikipedia"&gt;Gilles de ROME&lt;/a&gt; est un théologien augustin italien et philosophe scolastique connu pour son rôle d’interprète d’Aristote, de théoricien du pouvoir princier et de défenseur de la suprématie pontificale. En 1292, il est élu supérieur général de l’ordre augustin, puis, en 1295, le pape Boniface VIII le nomme archevêque de Bourges, charge qu’il exerce tout en restant une figure intellectuelle influente. Élève de Thomas d’Aquin à Paris, il perd le droit d’enseigner en 1277 pour avoir refusé de désavouer certaines thèses, avant d’être réhabilité en 1285 ; son ordre fait ensuite de sa doctrine l’enseignement officiel. &lt;/p&gt; &lt;p&gt; Il cherche à concilier Aristote avec la théologie chrétienne, dans un contexte marqué par les condamnations de 1277 à Paris contre certaines thèses aristotéliciennes. Son œuvre couvre la théologie, la philosophie naturelle, la logique et la métaphysique, avec de nombreux commentaires sur Aristote et sur les Sentences de Pierre Lombard. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=Qw-Sbn5MeNs"  title="Giles of Rome: Life, Works, and Influence par Philosoppher Friends"&gt;Son oeuvre &lt;/a&gt; principale est : "De regimine principum" est un vaste traité en trois livres sur la morale, l’économie domestique et la politique, rédigé pour l’éducation du futur roi Philippe IV le Bel. On lui attribue aussi des textes politiques et ecclésiologiques comme le "De ecclesiastica potestate" et une participation à la bulle "Unam Sanctam", où il défend une vision très forte de la supériorité du pouvoir spirituel sur le pouvoir temporel. &lt;/p&gt; &lt;p&gt; Son traité sur le gouvernement des princes a été largement diffusé et traduit, influençant durablement la pensée politique médiévale et la littérature des "miroirs des princes". &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F60" s="30" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="E62" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_de_Mediavilla"  style="color:#6A142A"  title=" Wikipedia"&gt;Richard de MEDIAVILLA&lt;/a&gt; était un philosophe franciscain scolastique français surnommé "doctor solidus" pour la solidité de sa pensée.  Il participe aux débats scolastiques entre thomistes et franciscains, critiquant Thomas d'Aquin tout en intégrant des éléments aristotéliciens et avicennisants. Sa postérité a longtemps été éclipsée par Duns Scot et Thomas, mais des éditions récentes révèlent &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2015_num_113_2_8449_t1_0355_0000_2" style="color:#88A1E9" title="        Richard de Mediavilla, Questions disputées par Persée"&gt;son influence pionnière. &lt;/a&gt;&lt;/p&gt; &lt;p&gt; Ses Questions disputées et Quodlibets (édités en plusieurs tomes depuis les années 2010) traitent de Dieu, des anges, des démons et de l'homme. Ces textes explorent la physique du mouvement, l'optique et les mathématiques appliquées à la théologie. Il distingue l'infini en acte (Dieu) de l'infini virtuel (créatures), posant le possible comme dimension ontologique de l'être, au-delà de la simple contingence. Il redéfinit la matière comme lieu du possible pour individualiser les anges sans multiplicité d'espèces, anticipant &lt;a href="https://www.youtube.com/watch?v=TxCvg7h9mvg" style="color:#88A1E9" title=" Richard of Middleton , Everything Philosophers par See Hear Say Learn"&gt;l'ecceitas scotiste.&lt;/a&gt; Critique de l'éternité du monde, il articule liberté divine, naturalisme et sciences. &lt;/p&gt; &lt;p&gt; Il débat avec Pierre de Jean Olivi et Henri de Gand, s'opposant à la création éternelle condamnée en 1277. Reconnu comme "le plus thomiste des franciscains", il dépasse les tensions franciscaines par une métaphysique du possible influençant les XIVe-XVe siècles. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Richard_de_Mediavilla"  style="color:#6A142A"  title=" Wikipedia"&gt;Richard de MEDIAVILLA&lt;/a&gt; était un philosophe franciscain scolastique français surnommé "doctor solidus" pour la solidité de sa pensée.  Il participe aux débats scolastiques entre thomistes et franciscains, critiquant Thomas d'Aquin tout en intégrant des éléments aristotéliciens et avicennisants. Sa postérité a longtemps été éclipsée par Duns Scot et Thomas, mais des éditions récentes révèlent &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_2015_num_113_2_8449_t1_0355_0000_2" style="color:#88A1E9" title="        Richard de Mediavilla, Questions disputées par Persée"&gt;son influence pionnière. &lt;/a&gt; Maître en théologie à Paris vers 1284, il est ensuite à Naples le précepteur de Louis d’Anjou, fils du roi Charles II, le futur saint Louis de Toulouse.&lt;/p&gt; &lt;p&gt; Ses Questions disputées et Quodlibets (édités en plusieurs tomes depuis les années 2010) traitent de Dieu, des anges, des démons et de l'homme. Ces textes explorent la physique du mouvement, l'optique et les mathématiques appliquées à la théologie. Il distingue l'infini en acte (Dieu) de l'infini virtuel (créatures), posant le possible comme dimension ontologique de l'être, au-delà de la simple contingence. Il redéfinit la matière comme lieu du possible pour individualiser les anges sans multiplicité d'espèces, anticipant &lt;a href="https://www.youtube.com/watch?v=TxCvg7h9mvg" style="color:#88A1E9" title=" Richard of Middleton , Everything Philosophers par See Hear Say Learn"&gt;l'ecceitas scotiste.&lt;/a&gt; Critique de l'éternité du monde, il articule liberté divine, naturalisme et sciences. &lt;/p&gt; &lt;p&gt; Il débat avec Pierre de Jean Olivi et Henri de Gand, s'opposant à la création éternelle condamnée en 1277. Reconnu comme "le plus thomiste des franciscains", il dépasse les tensions franciscaines par une métaphysique du possible influençant les XIVe-XVe siècles. Son commentaire des &lt;em&gt;Sentences&lt;/em&gt; de Pierre Lombard, imprimé dès la fin du XVe siècle, a été lu jusqu’à l’époque moderne. &lt;/p&gt; 
    &lt;audio controls title="La scolastique et les démons de Richard de Mediavilla par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/10193-04.04.2011-ITEMA_20277718-2011C3039E0082-ITE_00041542_RSCE-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt;  
 </t>
         </is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="E80" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Bradwardine"  title=" Wikipedia"&gt;Thomas BRADWARDINE&lt;/a&gt;  était un philosophe anglais surnommé "le Docteur Profond". Archevêque de Canterbury et confesseur du roi Édouard III, il a marqué son époque par ses contributions à la théologie augustinienne et aux sciences naturelles. &lt;/p&gt; &lt;p&gt; Né probablement à Hartfield dans le Sussex, il étudie à Oxford puis au Merton College, où il excelle en  &lt;a href="https://www.youtube.com/watch?v=G05snIT5bRo&amp;t=58s" title="Thomas Bradwardine: The Mathematician-Philosopher Who Bridged Medieval Thought and Early Science  par Math Mystique"&gt;théologie et en mathématiques&lt;/a&gt;. Il devient chancelier de l'université d'Oxford, chanoine de Lincoln, chancelier de la cathédrale Saint-Paul de Londres, et suit Édouard III lors de ses campagnes en France en tant que chapelain. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "De causa Dei contra Pelagium" paru vers 1344, combat le pélagianisme en défendant la toute-puissance divine et la prédestination, tout en intégrant une approche mathématique à la théologie.   &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1960_num_40_2_3617"  title="Thomas Bradwardine, un précurseur de Luther ?  par Persée"&gt;Thomiste rigoureux, &lt;/a&gt;  il insiste sur la concurrence divine avec la volonté humaine, influençant plus tard des réformateurs comme Wycliffe. &lt;/p&gt; &lt;p&gt; Dans "Tractatus de proportionibus velocitatum in motibus" paru en  1328, il développe une théorie des proportions géométriques pour les vitesses, anticipant la croissance exponentielle et critiquant les idées aristotéliciennes sur le mouvement. Associé aux "Calculateurs d'Oxford", il contribue au théorème de la vitesse moyenne et à la cinématique, préfigurant des découvertes comme la loi des corps tombants. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Thomas_Bradwardine"  title=" Wikipedia"&gt;Thomas BRADWARDINE&lt;/a&gt;  était un philosophe anglais surnommé "le Docteur Profond". Archevêque de Canterbury et confesseur du roi Édouard III, il a marqué son époque par ses contributions à la théologie augustinienne et aux sciences naturelles. &lt;/p&gt; &lt;p&gt; Né probablement à Hartfield dans le Sussex, il étudie à Oxford puis au Merton College, où il excelle en  &lt;a href="https://www.youtube.com/watch?v=G05snIT5bRo&amp;t=58s" title="Thomas Bradwardine: The Mathematician-Philosopher Who Bridged Medieval Thought and Early Science  par Math Mystique"&gt;théologie et en mathématiques&lt;/a&gt;. Il devient chancelier de l'université d'Oxford, chanoine de Lincoln, chancelier de la cathédrale Saint-Paul de Londres, et suit Édouard III lors de ses campagnes en France en tant que chapelain. Élu archevêque de Canterbury en 1349, il meurt de la peste noire quelques semaines après sa consécration. &lt;/p&gt; &lt;p&gt; Son œuvre majeure "De causa Dei contra Pelagium" paru vers 1344, combat le pélagianisme en défendant la toute-puissance divine et la prédestination, tout en intégrant une approche mathématique à la théologie.   &lt;a href="https://www.persee.fr/doc/rhpr_0035-2403_1960_num_40_2_3617"  title="Thomas Bradwardine, un précurseur de Luther ?  par Persée"&gt;Augustinien rigoureux, &lt;/a&gt;  il insiste sur le concours divin avec la volonté humaine, influençant plus tard des réformateurs comme Wycliffe. Chaucer le cite dans les &lt;em&gt;Contes de Canterbury&lt;/em&gt;, aux côtés d’Augustin et de Boèce, à propos de la prédestination. &lt;/p&gt; &lt;p&gt; Dans "Tractatus de proportionibus velocitatum in motibus" paru en  1328, il développe une théorie des proportions géométriques pour les vitesses, anticipant la croissance exponentielle et critiquant les idées aristotéliciennes sur le mouvement. Associé aux "Calculateurs d'Oxford", il contribue au théorème de la vitesse moyenne et à la cinématique, préfigurant des découvertes comme la loi des corps tombants. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F80" s="30" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="E90" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_de_Saxe_(philosophe)"   title=" Wikipedia"&gt;ALBERT de Saxe&lt;/a&gt;  était un philosophe allemand  élève de Jean Buridan et l’un des principaux représentants du nominalisme tard-médiéval. Il travaille en logique, philosophie naturelle (physique), métaphysique, mais aussi en mathématiques, astronomie et parfois géologie et appartient à la tradition parisienne dite "nominaliste", aux côtés de Jean Buridan et Marsile d’Inghen, et commente de nombreux textes d’Aristote. &lt;/p&gt; &lt;p&gt; Ses  &lt;a href="https://www.youtube.com/watch?v=Iu7jX1SXekM"  title="Albert of Saxony (philosopher) par WikiWikiup"&gt;œuvres logiques &lt;/a&gt; (comme la Perutilis Logica et ses Quaestiones circa logicam) développent une logique très technique, influencée par Guillaume d’Ockham, portant sur les termes, les conséquences, les sophismes et les obligations. Il insiste sur la distinction entre ce qui est absolument impossible et ce qui est impossible seulement "dans le cours ordinaire de la nature", ouvrant la voie à des scénarios hypothétiques fondés sur la toute-puissance divine. &lt;/p&gt; &lt;p&gt; Comme philosophe naturel, il prolonge la réflexion de Buridan sur la théorie de l’"impetus" : il décrit le mouvement d’un projectile en trois phases, depuis l’impulsion initiale rectiligne jusqu’à la chute verticale lorsque l’impetus est entièrement dissipé. Cette analyse du mouvement est souvent vue comme un précurseur de la notion d’inertie dans la physique moderne, même si elle reste formulée dans le cadre aristotélicien médiéval. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Albert_de_Saxe_(philosophe)"   title=" Wikipedia"&gt;ALBERT de Saxe&lt;/a&gt;  était un philosophe allemand  élève de Jean Buridan et l’un des principaux représentants du nominalisme tard-médiéval. Il travaille en logique, philosophie naturelle (physique), métaphysique, mais aussi en mathématiques, astronomie et parfois géologie et appartient à la tradition parisienne dite "nominaliste", aux côtés de Jean Buridan et Marsile d’Inghen, et commente de nombreux textes d’Aristote. Recteur de l’université de Paris en 1353, il devient en 1365 le premier recteur de la nouvelle université de Vienne, puis évêque de Halberstadt en 1366. &lt;/p&gt; &lt;p&gt; Ses  &lt;a href="https://www.youtube.com/watch?v=Iu7jX1SXekM"  title="Albert of Saxony (philosopher) par WikiWikiup"&gt;œuvres logiques &lt;/a&gt; (comme la Perutilis Logica et ses Quaestiones circa logicam) développent une logique très technique, influencée par Guillaume d’Ockham, portant sur les termes, les conséquences, les sophismes et les obligations. Il insiste sur la distinction entre ce qui est absolument impossible et ce qui est impossible seulement "dans le cours ordinaire de la nature", ouvrant la voie à des scénarios hypothétiques fondés sur la toute-puissance divine. &lt;/p&gt; &lt;p&gt; Comme philosophe naturel, il prolonge la réflexion de Buridan sur la théorie de l’"impetus" : il décrit le mouvement d’un projectile en trois phases, depuis l’impulsion initiale rectiligne jusqu’à la chute verticale lorsque l’impetus est entièrement dissipé. Cette analyse du mouvement est souvent vue comme un précurseur de la notion d’inertie dans la physique moderne, même si elle reste formulée dans le cadre aristotélicien médiéval. Il explique aussi le relief par l’érosion et le déplacement du centre de gravité de la Terre, une idée que Léonard de Vinci a lue et reprise. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F90" s="30" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="E98" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9miste_Pl%C3%A9thon"  title=" Wikipedia"&gt;Gémiste PLÉTHON&lt;/a&gt; était  un philosophe byzantin et un fervent néoplatonicien, hostile à l’aristotélisme dominant dans la scolastique médiévale. &lt;/p&gt; &lt;p&gt; Il écrivit "De Differentiis" (Sur les différences entre Platon et Aristote), où il défendait la &lt;a href="https://www.youtube.com/watch?v=uvXgnbYMzRg&amp;t=11s" style="color:#88A1E9" title="Gemistus Pletho: Neoplatonist and Pagan during the Renaissance par Kings and Kings "&gt;supériorité de Platon&lt;/a&gt;, notamment sur des questions de l’immortalité de l’âme (Platon la conçoit comme éternelle, contrairement à Aristote) ainsi que sur  la théorie des Idées (Pléthon soutenait la réalité des formes intelligibles). &lt;/p&gt; &lt;p&gt; Dans son œuvre secrète "Les Lois" (inspirée de Platon), il proposa une religion philosophique syncrétique, mêlant platonisme, zoroastrisme et polythéisme antique. Ce texte fut brûlé après sa mort pour hérésie (seuls des fragments subsistent).  Il développa une &lt;a href="https://www.persee.fr/doc/metis_1105-2201_1987_num_2_1_887" title="Pléthon lecteur des oracles par Persée "&gt;vision hiérarchique&lt;/a&gt; de l’univers, avec un Dieu suprême entouré de divinités subalternes (influence païenne). &lt;/p&gt; &lt;p&gt; Son syncrétisme philosophico-religieux en fait un penseur à part, entre paganisme et christianisme. On le voit, aujourd'hui comme un  &lt;a href="https://www.persee.fr/doc/bude_1247-6862_1950_num_9_9_4946" title="Gémiste Pléthon et son souvenir par Persée "&gt;passeur culturel&lt;/a&gt; entre Byzance et l’Europe. Il  incarne la dernière flambée de la pensée néoplatonicienne byzantine, à la fois mystique et politique. Son rôle dans la renaissance du platonisme en Occident en fait une figure clé de l’histoire des idées. Si certains le considèrent comme un "païen chrétien", d’autres y voient un visionnaire cherchant à unifier sagesse antique et spiritualité moderne. &lt;/p&gt; 
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/G%C3%A9miste_Pl%C3%A9thon"  title=" Wikipedia"&gt;Gémiste PLÉTHON&lt;/a&gt; était  un philosophe byzantin et un fervent néoplatonicien, hostile à l’aristotélisme dominant dans la scolastique médiévale. Il enseigne à Mistra, dans le Péloponnèse. En 1439, au concile de Florence, ses leçons sur Platon inspirent à Cosme de Médicis, selon Marsile Ficin, l’idée d’une Académie platonicienne. &lt;/p&gt; &lt;p&gt; Il écrivit "De Differentiis" (Sur les différences entre Platon et Aristote), où il défendait la &lt;a href="https://www.youtube.com/watch?v=uvXgnbYMzRg&amp;t=11s" style="color:#88A1E9" title="Gemistus Pletho: Neoplatonist and Pagan during the Renaissance par Kings and Kings "&gt;supériorité de Platon&lt;/a&gt;, notamment sur des questions de l’immortalité de l’âme (Platon la conçoit comme éternelle, contrairement à Aristote) ainsi que sur  la théorie des Idées (Pléthon soutenait la réalité des formes intelligibles). &lt;/p&gt; &lt;p&gt; Dans son œuvre secrète "Les Lois" (inspirée de Platon), il proposa une religion philosophique syncrétique, mêlant platonisme, zoroastrisme et polythéisme antique. Ce texte fut brûlé après sa mort par le patriarche Gennade Scholarios (seuls des fragments subsistent).  Il développa une &lt;a href="https://www.persee.fr/doc/metis_1105-2201_1987_num_2_1_887" title="Pléthon lecteur des oracles par Persée "&gt;vision hiérarchique&lt;/a&gt; de l’univers, avec un Dieu suprême entouré de divinités subalternes (influence païenne). &lt;/p&gt; &lt;p&gt; Son syncrétisme philosophico-religieux en fait un penseur à part, entre paganisme et christianisme. On le voit, aujourd'hui comme un  &lt;a href="https://www.persee.fr/doc/bude_1247-6862_1950_num_9_9_4946" title="Gémiste Pléthon et son souvenir par Persée "&gt;passeur culturel&lt;/a&gt; entre Byzance et l’Europe. Il  incarne la dernière flambée de la pensée néoplatonicienne byzantine, à la fois mystique et politique. Son rôle dans la renaissance du platonisme en Occident en fait une figure clé de l’histoire des idées. Si certains le considèrent comme un "païen chrétien", d’autres y voient un visionnaire cherchant à unifier sagesse antique et spiritualité moderne. &lt;/p&gt; 
 </t>
         </is>
       </c>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E102" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Hus"  title=" Wikipedia"&gt;Jan HUS&lt;/a&gt;  était  un théologien, philosophe et réformateur religieux tchèque né en Bohême et mort brûlé vif en 1415 à Constance, il est considéré comme un précurseur de la  &lt;a href="https://www.youtube.com/watch?v=_EazQEm9KMo" style="color:#88A1E9" title="Le réformateur de Bohême.  par Il Est Ecrit"&gt;Réforme protestante, &lt;/a&gt; influencé par John Wyclif.  Il obtient sa maîtrise ès arts en 1396, puis devient prêtre en 1400. Il prêche à la chapelle de Bethléem à Prague dès 1402, en langue tchèque, attirant des foules importantes par son appel à une réforme morale de l'Église. &lt;/p&gt; &lt;p&gt;Il critique la corruption cléricale, le simoniaque et l'indulgence, prônant un retour aux Écritures et à la pauvreté évangélique comme Wyclif. Il défend l'égalité linguistique (prédication en vernaculaire) et une eucharistie symbolique (utranquiste), remettant en cause l'autorité papale au profit du Christ comme juge suprême. Sa pensée mêle réalisme philosophique et réformisme radical, influençant l'identité tchèque naissante. &lt;/p&gt; &lt;p&gt; Excommunié en 1411 pour ses écrits, il refuse de se rétracter et se rend au concile de Constance en 1414 sous sauf-conduit impérial, mais y est arrêté. Condamné pour hérésie le 6 juillet 1415, il est  &lt;a href="https://www.youtube.com/watch?v=RMmjwFotg3M" title="Jan Hus : POURQUOI a-t-il été BRÛLÉ ?   par Echo de l'Histoire"&gt;brûlé vif, &lt;/a&gt;  son exécution déclenchant les guerres hussites en Bohême. Sa mort inspire l'hussitisme, une révolution religieuse et nationale, et préfigure Luther un siècle plus tard, avec des échos dans le protestantisme. Héros national tchèque, il symbolise la lutte pour la liberté religieuse et linguistique. &lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Hus"  title=" Wikipedia"&gt;Jan HUS&lt;/a&gt;  était  un théologien, philosophe et réformateur religieux tchèque né en Bohême et mort brûlé vif en 1415 à Constance, il est considéré comme un précurseur de la  &lt;a href="https://www.youtube.com/watch?v=_EazQEm9KMo" style="color:#88A1E9" title="Le réformateur de Bohême.  par Il Est Ecrit"&gt;Réforme protestante, &lt;/a&gt; influencé par John Wyclif.  Il obtient sa maîtrise ès arts en 1396, puis devient prêtre en 1400. Il prêche à la chapelle de Bethléem à Prague dès 1402, en langue tchèque, attirant des foules importantes par son appel à une réforme morale de l'Église. &lt;/p&gt; &lt;p&gt;Il critique la corruption cléricale, la simonie et l'indulgence, prônant un retour aux Écritures et à la pauvreté évangélique comme Wyclif. Il défend l'égalité linguistique (prédication en vernaculaire) et, à la fin de sa vie, la communion au calice pour tous les fidèles, que réclameront ses disciples utraquistes, remettant en cause l'autorité papale au profit du Christ comme juge suprême. Sa pensée mêle réalisme philosophique et réformisme radical, influençant l'identité tchèque naissante. Recteur de l’université de Prague en 1409, il expose dans le &lt;em&gt;De ecclesia&lt;/em&gt; (1413) sa conception de l’Église, dont le Christ seul est la tête. &lt;/p&gt; &lt;p&gt; Excommunié en 1411 pour ses écrits, il refuse de se rétracter et se rend au concile de Constance en 1414 sous sauf-conduit impérial, mais y est arrêté. Condamné pour hérésie le 6 juillet 1415, il est  &lt;a href="https://www.youtube.com/watch?v=RMmjwFotg3M" title="Jan Hus : POURQUOI a-t-il été BRÛLÉ ?   par Echo de l'Histoire"&gt;brûlé vif, &lt;/a&gt;  son exécution déclenchant les guerres hussites en Bohême. Sa mort inspire l'hussitisme, une révolution religieuse et nationale, et préfigure Luther un siècle plus tard, avec des échos dans le protestantisme. Héros national tchèque, il symbolise la lutte pour la liberté religieuse et linguistique. &lt;/p&gt; </t>
         </is>
       </c>
       <c r="F102" s="30" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E36" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Grosset%C3%AAte"  title=" Wikipedia"&gt;Robert GROSSETESTE&lt;/a&gt; était un philosophe érudit anglais, passerelle entre la pensée médiévale et l'émergence de la science moderne. Il a commenté les Écritures (Psaumes, Épîtres de Paul) et a joué un rôle important dans le développement de la pensée franciscaine à &lt;a href="https://www.youtube.com/watch?v=Rm-sK0v5JDc"  title=" Robert Grosseteste: The Founder of Scientific Thought in Oxford par InfinoSphere"&gt; Oxford&lt;/a&gt;. &lt;/p&gt; &lt;p&gt;   Il a traduit et commenté de nombreuses œuvres, notamment celles d'Aristote (comme l'Éthique à Nicomaque), intégrant également des éléments néoplatoniciens et augustiniens. Ses commentaires sur Aristote ont durablement marqué la pensée occidentale. &lt;/p&gt; &lt;p&gt;  C'est peut-être là qu'il est le plus original pour son époque. Il a écrit des traités sur l'optique, la lumière, l'astronomie, les comètes, les arcs-en-ciel, et même sur les marées. Son œuvre la plus célèbre en philosophie naturelle est sans doute De Luce (Sur la Lumière) où il développe une &lt;a href="https://www.youtube.com/watch?v=kipiRbWux60" title=" The medieval Cosmos par Gilles Gasper"&gt; cosmologie fascinante &lt;/a&gt; où la lumière est le principe fondamental de l'existence. C'est la "première forme corporelle" à être créée, et elle se propage à partir d'un point originel, s'auto-multipliant pour former la matière et structurer l'univers en sphères concentriques. &lt;/p&gt; &lt;p&gt; Il  a été l'un des premiers penseurs latins à étudier en profondeur et à intégrer les œuvres d'Aristote (souvent via des traductions arabes), tout en restant profondément ancré dans la tradition augustinienne, notamment l'idée de l'illumination divine pour l'acquisition de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1977_num_75_25_5920" style="color:#88A1E9" title=" La connaissance individuelle selon Robert Grosseteste  par Persée"&gt; la connaissance&lt;/a&gt;. Son approche était un mélange éclectique mais cohérent. &lt;/p&gt; &lt;p&gt;  Son œuvre témoigne d'une tentative audacieuse d'intégrer la raison et la foi, la philosophie et la science, dans une vision cohérente du cosmos et de la place de l'homme en son sein.&lt;/p&gt; </t>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Robert_Grosset%C3%AAte"  title=" Wikipedia"&gt;Robert GROSSETESTE&lt;/a&gt; était un philosophe érudit anglais, passerelle entre la pensée médiévale et l'émergence de la science moderne. Il a commenté les Écritures (Psaumes, Épîtres de Paul) et a joué un rôle important dans le développement de la pensée franciscaine à  Oxford. &lt;/p&gt; &lt;p&gt;   Il a traduit et commenté de nombreuses œuvres, notamment celles d'Aristote (comme l'Éthique à Nicomaque), intégrant également des éléments néoplatoniciens et augustiniens. Ses commentaires sur Aristote ont durablement marqué la pensée occidentale. &lt;/p&gt; &lt;p&gt;  C'est peut-être là qu'il est le plus original pour son époque. Il a écrit des traités sur l'optique, la lumière, l'astronomie, les comètes, les arcs-en-ciel, et même sur les marées. Son œuvre la plus célèbre en philosophie naturelle est sans doute De Luce (Sur la Lumière) où il développe une &lt;a href="https://www.youtube.com/watch?v=kipiRbWux60" title=" The medieval Cosmos par Gilles Gasper"&gt; cosmologie fascinante &lt;/a&gt; où la lumière est le principe fondamental de l'existence. C'est la "première forme corporelle" à être créée, et elle se propage à partir d'un point originel, s'auto-multipliant pour former la matière et structurer l'univers en sphères concentriques. &lt;/p&gt; &lt;p&gt; Il  a été l'un des premiers penseurs latins à étudier en profondeur et à intégrer les œuvres d'Aristote (souvent via des traductions arabes), tout en restant profondément ancré dans la tradition augustinienne, notamment l'idée de l'illumination divine pour l'acquisition de &lt;a href="https://www.persee.fr/doc/phlou_0035-3841_1977_num_75_25_5920" style="color:#88A1E9" title=" La connaissance individuelle selon Robert Grosseteste  par Persée"&gt; la connaissance&lt;/a&gt;. Son approche était un mélange éclectique mais cohérent. &lt;/p&gt; &lt;p&gt;  Son œuvre témoigne d'une tentative audacieuse d'intégrer la raison et la foi, la philosophie et la science, dans une vision cohérente du cosmos et de la place de l'homme en son sein.&lt;/p&gt; </t>
         </is>
       </c>
       <c r="F36" s="30" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M43" s="24" t="inlineStr">
         <is>
-          <t>philosophe espagnol auteur des "Summulae logicales", manuel scolastique.</t>
+          <t xml:space="preserve">philosophe portugais auteur des "Summulae logicales", manuel scolastique.</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="E112" s="32" t="inlineStr">
         <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_Ficin" title=" Wikipedia"&gt;Marsile FICIN&lt;/a&gt; était un philosophe, théologien et humaniste italien connu pour avoir joué un rôle clé dans la redécouverte et la diffusion du  &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme par Wikipedia "&gt;néoplatonisme&lt;/a&gt; en Occident. Il dirigea l’Académie néoplatonicienne de Florence, un cercle de penseurs inspirés par Platon, Plotin et d'autres philosophes antiques. &lt;/p&gt; &lt;p&gt;Il fut le premier à traduire intégralement les œuvres de Platon en latin, ce qui permit à toute l’Europe intellectuelle de redécouvrir sa pensée. Il traduisit également les œuvres de Plotin, Porphyre, Jamblique et Proclus, principaux représentants du néoplatonisme.  L’un de ses travaux majeurs fut aussi la traduction du &lt;a href="https://www.youtube.com/watch?v=SGI75n4lMSg&amp;t=538s" title="Hermès Trismégiste - Corpus Hermeticum par Julie Dratwiak "&gt;"Corpus Hermeticum"&lt;/a&gt;, une collection de textes ésotériques attribués à Hermès Trismégiste. Il chercha à réconcilier la philosophie platonicienne avec le christianisme voyant dans Platon une pensée compatible avec la religion chrétienne et considérait que la sagesse antique pouvait enrichir la foi. &lt;/p&gt; &lt;p&gt; Il développa une vision où l’âme humaine occupe une place centrale : elle est un intermédiaire entre le monde matériel et le monde intelligible (spirituel). L’ascension de l’âme vers Dieu passe par la contemplation et l’amour divin, des thèmes repris dans sa principale œuvre philosophique, la "Théologie platonicienne sur l’immortalité des âmes". &lt;/p&gt; &lt;p&gt;  Il influença la vision de l’amour platonique, développée notamment dans son &lt;a href="https://www.actu-philosophia.com/marsile-ficin-commentaire-du-parmenide-de-platon-564/"  title="Commentaire du Parmémide de Platon par Actu Philosophia "&gt;"Commentaire sur le Banquet de Platon"&lt;/a&gt; où il l y expose une conception de l’amour comme élévation spirituelle.  Il fut l’un des penseurs qui permit à la philosophie antique de renaître au sein de la Renaissance italienne. Son influence se fit sentir non seulement en philosophie, mais aussi dans l’esthétique, la théologie et même l’ésotérisme. Son œuvre reste essentielle pour comprendre la pensée humaniste et le renouveau de l’idéal platonicien dans l’Occident chrétien. &lt;/p&gt;  
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Marsile_Ficin" title=" Wikipedia"&gt;Marsile FICIN&lt;/a&gt; était un philosophe, théologien et humaniste italien connu pour avoir joué un rôle clé dans la redécouverte et la diffusion du  &lt;a href="https://fr.wikipedia.org/wiki/N%C3%A9oplatonisme" title="Néoplatonisme par Wikipedia "&gt;néoplatonisme&lt;/a&gt; en Occident. Il dirigea l’Académie néoplatonicienne de Florence, un cercle de penseurs inspirés par Platon, Plotin et d'autres philosophes antiques. &lt;/p&gt; &lt;p&gt;Il fut le premier à traduire intégralement les œuvres de Platon en latin, ce qui permit à toute l’Europe intellectuelle de redécouvrir sa pensée. Il traduisit également les œuvres de Plotin, Porphyre, Jamblique et Proclus, principaux représentants du néoplatonisme.  L’un de ses travaux majeurs fut aussi la traduction du "Corpus Hermeticum", une collection de textes ésotériques attribués à Hermès Trismégiste. Il chercha à réconcilier la philosophie platonicienne avec le christianisme voyant dans Platon une pensée compatible avec la religion chrétienne et considérait que la sagesse antique pouvait enrichir la foi. &lt;/p&gt; &lt;p&gt; Il développa une vision où l’âme humaine occupe une place centrale : elle est un intermédiaire entre le monde matériel et le monde intelligible (spirituel). L’ascension de l’âme vers Dieu passe par la contemplation et l’amour divin, des thèmes repris dans sa principale œuvre philosophique, la "Théologie platonicienne sur l’immortalité des âmes". &lt;/p&gt; &lt;p&gt;  Il influença la vision de l’amour platonique, développée notamment dans son &lt;a href="https://www.actu-philosophia.com/marsile-ficin-commentaire-du-parmenide-de-platon-564/"  title="Commentaire du Parmémide de Platon par Actu Philosophia "&gt;"Commentaire sur le Banquet de Platon"&lt;/a&gt; où il l y expose une conception de l’amour comme élévation spirituelle.  Il fut l’un des penseurs qui permit à la philosophie antique de renaître au sein de la Renaissance italienne. Son influence se fit sentir non seulement en philosophie, mais aussi dans l’esthétique, la théologie et même l’ésotérisme. Son œuvre reste essentielle pour comprendre la pensée humaniste et le renouveau de l’idéal platonicien dans l’Occident chrétien. &lt;/p&gt;  
 </t>
         </is>
       </c>

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2880,17 +2880,17 @@
       </c>
     </row>
     <row r="36" ht="116.25" customHeight="1" s="25">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="30">
         <v>1175</v>
       </c>
       <c r="B36" s="30" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t xml:space="preserve">1253</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>1175 -1224</t>
+          <t xml:space="preserve">1175 – 1253</t>
         </is>
       </c>
       <c r="D36" s="31" t="inlineStr">
@@ -6936,17 +6936,17 @@
       </c>
     </row>
     <row r="97" ht="152.25" customHeight="1" s="25">
-      <c r="A97" s="30" t="n">
+      <c r="A97" s="30">
         <v>1351</v>
       </c>
       <c r="B97" s="30" t="inlineStr">
         <is>
-          <t>1411</t>
+          <t xml:space="preserve">1420</t>
         </is>
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>1351 – 1411</t>
+          <t xml:space="preserve">1351 – 1420</t>
         </is>
       </c>
       <c r="D97" s="31" t="inlineStr">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -2277,196 +2277,196 @@
     </row>
     <row r="27" ht="217.5" customHeight="1" s="25">
       <c r="A27" s="30" t="n">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B27" s="30" t="n">
+        <v>1141</v>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>1096 – 1141</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>HUGUES de St Victor</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugues_de_Saint-Victor"  style=  title=" Wikipedia"&gt;HUGUES de Saint Victor&lt;/a&gt; était à la fois philosophe, théologien et pédagogue, souvent présenté comme une figure majeure de l’école   &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1960_num_34_1_2248" title="les origines de huges de st victor par persée  "&gt;de Saint-Victor à Paris&lt;/a&gt;. Sa philosophie cherche à organiser tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance n’est pas une fin en soi : elle prépare l’âme à une vie spirituelle plus haute. C’est pourquoi il accorde une grande importance aux arts libéraux, à la lecture, à l’étude méthodique et à l’éducation intellectuelle, dans &lt;a href="https://www.youtube.com/watch?v=A65kiTkbMNU" title="hugh of st victor’s Didascalicon par Cut the Fluff "&gt;son Didascalicon. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Un point central de sa pensée est l’union entre raison et foi. Il ne méprise pas la raison, mais il estime qu’elle a ses limites et qu’elle doit servir à comprendre ce que la foi révèle. Il se méfie d’une dialectique trop querelleuse et préfère une démarche plus ordonnée, plus humble et plus tournée vers l’édification intérieure. &lt;/p&gt; &lt;p&gt; Sa philosophie est aussi profondément spirituelle et mystique. Il décrit l’ascension de l’âme vers Dieu à travers un mouvement en plusieurs étapes, souvent résumé par la progression de la pensée, de la méditation et de la contemplation. Chez lui, la contemplation n’est pas une fuite du monde, mais l’aboutissement d’un travail patient sur soi, sur le savoir et sur la prière. &lt;/p&gt; &lt;p&gt; Il a marqué durablement la pensée médiévale parce qu’il veut tout relier : savoirs, morale, vie intérieure et histoire du salut. Il incarne une philosophie de l’ordre, de l’apprentissage total et de la montée graduelle vers la vérité, ce qui lui a valu une grande influence au Moyen Âge. &lt;/p&gt; 
+</t>
+        </is>
+      </c>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>pgLBmxrfyRY</t>
+        </is>
+      </c>
+      <c r="G27" s="33" t="inlineStr">
+        <is>
+          <t>Hugh of St Victor par Wikipedia tts</t>
+        </is>
+      </c>
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/hsvictor-mini.webp</t>
+        </is>
+      </c>
+      <c r="I27" s="33" t="n"/>
+      <c r="J27" s="23" t="inlineStr">
+        <is>
+          <t>Française</t>
+        </is>
+      </c>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>spiritualite</t>
+        </is>
+      </c>
+      <c r="L27" s="24" t="inlineStr">
+        <is>
+          <t>Mysticisme ; Scolastique</t>
+        </is>
+      </c>
+      <c r="M27" s="24" t="inlineStr">
+        <is>
+          <t>philosophe français qui organisa tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="179.25" customHeight="1" s="25">
+      <c r="A28" s="30" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>1179</v>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>1098 – 1179</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>HILDEGARDE de Bingen</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hildegarde_de_Bingen"  style=  title=" Wikipedia"&gt;HILDEGARDE de Bingen&lt;/a&gt; était une grande figure du Moyen Âge,originaire du Saint Empire germanique et à la fois mystique, abbesse, musicienne, médecin et penseuse.  &lt;a href="https://www.youtube.com/watch?v=-kf9N7UKzvA" title="hildegarde de bingen une vie une œuvre par Eclair Brut  "&gt;Sa philosophie &lt;/a&gt;  ne se présente pas comme un système abstrait, mais comme une vision du monde unifiée, où Dieu, la nature, le corps et l’âme forment un tout cohérent. &lt;/p&gt; &lt;p&gt; Pour elle, l’univers est vivant et ordonné par une harmonie profonde. L’être humain y occupe une place centrale, comme un microcosme qui reflète le macrocosme : ce qui se passe dans l’âme répond aux mouvements du monde, et inversement. &lt;/p&gt; &lt;p&gt; Un concept essentiel chez elle est la viriditas, souvent traduite par « verdeur » ou « force de vie ». Cette idée désigne l’énergie vitale, la fécondité, la santé spirituelle et corporelle, ainsi que la capacité de croître dans le bien et dans la foi. La nature n’est donc pas seulement un décor, mais un signe de la présence divine. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=AoQE_GQGZK4" title="hildegarde de bingen guérisseuse par France Culture "&gt;Sa pensée insiste &lt;/a&gt;  aussi sur l’unité entre le corps et l’âme. Elle ne les oppose pas radicalement : elle considère qu’une vie juste suppose un équilibre entre la dimension spirituelle, les émotions, la santé physique et la relation à Dieu. C’est ce qui explique son intérêt pour la médecine, les plantes, les remèdes et les rythmes de vie. &lt;/p&gt; &lt;p&gt; Sa philosophie a une forte dimension morale et spirituelle. Elle invite à la conversion, à la simplicité, à l’écoute intérieure et à la responsabilité envers la création. Elle voit le monde comme une symphonie où chaque être a sa place, et où l’être humain est appelé à retrouver l’harmonie perdue. &lt;/p&gt;  &lt;audio controls title="Hildegarde de Bingen, l’insoumise par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-22.12.2013-ITEMA_20564951-2013C14958E0046-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
+        </is>
+      </c>
+      <c r="F28" s="30" t="inlineStr">
+        <is>
+          <t>LJZEQoBEnZc</t>
+        </is>
+      </c>
+      <c r="G28" s="33" t="inlineStr">
+        <is>
+          <t>Hildegarde de Bingen la visionnaire par Sanctuaire des Martyrs</t>
+        </is>
+      </c>
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>https://www.laphilo.fr/pho/hildegarde-mini.webp</t>
+        </is>
+      </c>
+      <c r="I28" s="33" t="n"/>
+      <c r="J28" s="23" t="inlineStr">
+        <is>
+          <t>Allemande</t>
+        </is>
+      </c>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L28" s="24" t="inlineStr">
+        <is>
+          <t>Mysticisme</t>
+        </is>
+      </c>
+      <c r="M28" s="24" t="inlineStr">
+        <is>
+          <t>abbesse, mystique et visionnaire du Moyen Âge.</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="217.5" customHeight="1" s="25">
+      <c r="A29" s="30">
+        <v>1101</v>
+      </c>
+      <c r="B29" s="30" t="n">
         <v>1164</v>
       </c>
-      <c r="C27" s="30" t="inlineStr">
-        <is>
-          <t>1092 – 1164</t>
-        </is>
-      </c>
-      <c r="D27" s="31" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101 – 1164</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
         <is>
           <t>HÉLOÏSE</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E29" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/H%C3%A9lo%C3%AFse_(abbesse)"  style=  title=" Wikipedia"&gt;Héloïse &lt;/a&gt; était l’une des femmes les plus remarquables du Moyen Âge : penseuse, correspondante épistolaire, et abbesse du monastère du Paraclet en Champagne. Elle est d’abord connue pour sa relation passionnelle et intellectuellement profonde avec Pierre Abélard, son professeur, mais elle mérite aussi d’être étudiée pour sa propre pensée et son rôle de dirigeante religieuse. &lt;/p&gt; &lt;p&gt;  &lt;a href="https://www.youtube.com/watch?v=CRHz0jQ5GJ0" title="Héloise et Habélard par Radio Classique "&gt;Éduquée parmi les bénédictines &lt;/a&gt; d’Argenteuil, Héloïse reçoit une formation rare pour une femme de son époque, notamment dans les arts libéraux, ce qui lui permet de maîtriser le latin et de dialoguer d’égal à égal avec les grands intellectuels de son temps. Elle devient rapidement l’une des rares femmes savantes d’Occident, capable de poser des questions exégétiques complexes sur la Bible et d’exiger une compréhension plus fine des textes sacrés. &lt;/p&gt; &lt;p&gt; Sa philosophie se distingue par une éthique de l’intention : pour elle, la valeur morale d’une action ne réside pas dans l’acte extérieur, mais dans l’intention qui l’anime. Elle écrit ainsi qu’il faut évaluer « non les choses que nous faisons, mais l’âme avec laquelle nous les faisons ». Cette approche lui permet de défendre la légitimité de sa passion pour Abélard en affirmant qu’elle peut être innocente malgré le péché apparent, car son amour n’est pas né d’une intention perverse. &lt;/p&gt; &lt;p&gt; En tant qu’abbesse du Paraclet, Héloïse montre une grande autonomie de conscience et une capacité organisationnelle remarquable, faisant prospérer le monastère tout en maintenant une vie spirituelle exigeante. Elle promut l’étude du grec et de l’hébreu pour mieux comprendre les Écritures, encourage ses moniales à développer leur esprit critique, et défend la positivité de l’expérience matrimoniale dans une perspective chrétienne. &lt;/p&gt; &lt;p&gt; Elle  incarne ainsi une figure rare de femme philosophe et religieuse au XIIᵉ siècle, alliant passion, intelligence et responsabilité spirituelle. Sa pensée, à la fois théologique et éthique, invite à une foi vivante, centrée sur la conscience, l’intention et la dignité de la personne humaine, y compris dans sa dimension féminine. &lt;/p&gt; 
  &lt;audio controls title="Les voluptés charnelles  par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/18722-29.02.2020-ITEMA_22295307-2.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; 
 </t>
         </is>
       </c>
-      <c r="F27" s="30" t="inlineStr">
+      <c r="F29" s="30" t="inlineStr">
         <is>
           <t>tLTjrrLxg_Q</t>
         </is>
       </c>
-      <c r="G27" s="33" t="inlineStr">
+      <c r="G29" s="33" t="inlineStr">
         <is>
           <t>Héloise et Habélard par Jean Luc Dubart</t>
         </is>
       </c>
-      <c r="H27" s="32" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>https://www.laphilo.fr/pho/heloise-mini.webp</t>
-        </is>
-      </c>
-      <c r="I27" s="33" t="n"/>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K27" s="24" t="inlineStr">
-        <is>
-          <t>ethique ; spiritualite</t>
-        </is>
-      </c>
-      <c r="L27" s="24" t="inlineStr">
-        <is>
-          <t>Scolastique</t>
-        </is>
-      </c>
-      <c r="M27" s="24" t="inlineStr">
-        <is>
-          <t>abbesse et intellectuelle française connue pour sa relation avec Pierre Abélard.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="217.5" customHeight="1" s="25">
-      <c r="A28" s="30" t="n">
-        <v>1096</v>
-      </c>
-      <c r="B28" s="30" t="n">
-        <v>1141</v>
-      </c>
-      <c r="C28" s="30" t="inlineStr">
-        <is>
-          <t>1096 – 1141</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>HUGUES de St Victor</t>
-        </is>
-      </c>
-      <c r="E28" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hugues_de_Saint-Victor"  style=  title=" Wikipedia"&gt;HUGUES de Saint Victor&lt;/a&gt; était à la fois philosophe, théologien et pédagogue, souvent présenté comme une figure majeure de l’école   &lt;a href="https://www.persee.fr/doc/rscir_0035-2217_1960_num_34_1_2248" title="les origines de huges de st victor par persée  "&gt;de Saint-Victor à Paris&lt;/a&gt;. Sa philosophie cherche à organiser tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu. &lt;/p&gt; &lt;p&gt; Pour lui, la connaissance n’est pas une fin en soi : elle prépare l’âme à une vie spirituelle plus haute. C’est pourquoi il accorde une grande importance aux arts libéraux, à la lecture, à l’étude méthodique et à l’éducation intellectuelle, dans &lt;a href="https://www.youtube.com/watch?v=A65kiTkbMNU" title="hugh of st victor’s Didascalicon par Cut the Fluff "&gt;son Didascalicon. &lt;/a&gt; &lt;/p&gt; &lt;p&gt; Un point central de sa pensée est l’union entre raison et foi. Il ne méprise pas la raison, mais il estime qu’elle a ses limites et qu’elle doit servir à comprendre ce que la foi révèle. Il se méfie d’une dialectique trop querelleuse et préfère une démarche plus ordonnée, plus humble et plus tournée vers l’édification intérieure. &lt;/p&gt; &lt;p&gt; Sa philosophie est aussi profondément spirituelle et mystique. Il décrit l’ascension de l’âme vers Dieu à travers un mouvement en plusieurs étapes, souvent résumé par la progression de la pensée, de la méditation et de la contemplation. Chez lui, la contemplation n’est pas une fuite du monde, mais l’aboutissement d’un travail patient sur soi, sur le savoir et sur la prière. &lt;/p&gt; &lt;p&gt; Il a marqué durablement la pensée médiévale parce qu’il veut tout relier : savoirs, morale, vie intérieure et histoire du salut. Il incarne une philosophie de l’ordre, de l’apprentissage total et de la montée graduelle vers la vérité, ce qui lui a valu une grande influence au Moyen Âge. &lt;/p&gt; 
-</t>
-        </is>
-      </c>
-      <c r="F28" s="30" t="inlineStr">
-        <is>
-          <t>pgLBmxrfyRY</t>
-        </is>
-      </c>
-      <c r="G28" s="33" t="inlineStr">
-        <is>
-          <t>Hugh of St Victor par Wikipedia tts</t>
-        </is>
-      </c>
-      <c r="H28" s="32" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/hsvictor-mini.webp</t>
-        </is>
-      </c>
-      <c r="I28" s="33" t="n"/>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>Française</t>
-        </is>
-      </c>
-      <c r="K28" s="24" t="inlineStr">
-        <is>
-          <t>spiritualite</t>
-        </is>
-      </c>
-      <c r="L28" s="24" t="inlineStr">
-        <is>
-          <t>Mysticisme ; Scolastique</t>
-        </is>
-      </c>
-      <c r="M28" s="24" t="inlineStr">
-        <is>
-          <t>philosophe français qui organisa tous les savoirs pour les orienter vers la sagesse et, en dernier ressort, vers Dieu.</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">occident</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="179.25" customHeight="1" s="25">
-      <c r="A29" s="30" t="n">
-        <v>1098</v>
-      </c>
-      <c r="B29" s="30" t="n">
-        <v>1179</v>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>1098 – 1179</t>
-        </is>
-      </c>
-      <c r="D29" s="31" t="inlineStr">
-        <is>
-          <t>HILDEGARDE de Bingen</t>
-        </is>
-      </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Hildegarde_de_Bingen"  style=  title=" Wikipedia"&gt;HILDEGARDE de Bingen&lt;/a&gt; était une grande figure du Moyen Âge,originaire du Saint Empire germanique et à la fois mystique, abbesse, musicienne, médecin et penseuse.  &lt;a href="https://www.youtube.com/watch?v=-kf9N7UKzvA" title="hildegarde de bingen une vie une œuvre par Eclair Brut  "&gt;Sa philosophie &lt;/a&gt;  ne se présente pas comme un système abstrait, mais comme une vision du monde unifiée, où Dieu, la nature, le corps et l’âme forment un tout cohérent. &lt;/p&gt; &lt;p&gt; Pour elle, l’univers est vivant et ordonné par une harmonie profonde. L’être humain y occupe une place centrale, comme un microcosme qui reflète le macrocosme : ce qui se passe dans l’âme répond aux mouvements du monde, et inversement. &lt;/p&gt; &lt;p&gt; Un concept essentiel chez elle est la viriditas, souvent traduite par « verdeur » ou « force de vie ». Cette idée désigne l’énergie vitale, la fécondité, la santé spirituelle et corporelle, ainsi que la capacité de croître dans le bien et dans la foi. La nature n’est donc pas seulement un décor, mais un signe de la présence divine. &lt;/p&gt; &lt;p&gt; &lt;a href="https://www.youtube.com/watch?v=AoQE_GQGZK4" title="hildegarde de bingen guérisseuse par France Culture "&gt;Sa pensée insiste &lt;/a&gt;  aussi sur l’unité entre le corps et l’âme. Elle ne les oppose pas radicalement : elle considère qu’une vie juste suppose un équilibre entre la dimension spirituelle, les émotions, la santé physique et la relation à Dieu. C’est ce qui explique son intérêt pour la médecine, les plantes, les remèdes et les rythmes de vie. &lt;/p&gt; &lt;p&gt; Sa philosophie a une forte dimension morale et spirituelle. Elle invite à la conversion, à la simplicité, à l’écoute intérieure et à la responsabilité envers la création. Elle voit le monde comme une symphonie où chaque être a sa place, et où l’être humain est appelé à retrouver l’harmonie perdue. &lt;/p&gt;  &lt;audio controls title="Hildegarde de Bingen, l’insoumise par France Culture"&gt; &lt;source src="https://media.radiofrance-podcast.net/podcast09/11200-22.12.2013-ITEMA_20564951-2013C14958E0046-21.mp3" type="audio/mpeg" align="center"&gt; &lt;/audio&gt; </t>
-        </is>
-      </c>
-      <c r="F29" s="30" t="inlineStr">
-        <is>
-          <t>LJZEQoBEnZc</t>
-        </is>
-      </c>
-      <c r="G29" s="33" t="inlineStr">
-        <is>
-          <t>Hildegarde de Bingen la visionnaire par Sanctuaire des Martyrs</t>
-        </is>
-      </c>
-      <c r="H29" s="32" t="inlineStr">
-        <is>
-          <t>https://www.laphilo.fr/pho/hildegarde-mini.webp</t>
         </is>
       </c>
       <c r="I29" s="33" t="n"/>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>Allemande</t>
+          <t>Française</t>
         </is>
       </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
-          <t>spiritualite ; metaphysique</t>
+          <t>ethique ; spiritualite</t>
         </is>
       </c>
       <c r="L29" s="24" t="inlineStr">
         <is>
-          <t>Mysticisme</t>
+          <t>Scolastique</t>
         </is>
       </c>
       <c r="M29" s="24" t="inlineStr">
         <is>
-          <t>abbesse, mystique et visionnaire du Moyen Âge.</t>
+          <t>abbesse et intellectuelle française connue pour sa relation avec Pierre Abélard.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -8513,9 +8513,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Gilbert_de_La_Porr%C3%A9e&quot; title=&quot; Wikipedia&quot;&gt;GILBERT de la Porrée&lt;/a&gt; était un grand penseur, à la fois philosophe, théologien et évêque de Poitiers. Il appartient à l’école de Chartres et compte parmi les figures importantes de la scolastique naissante. &lt;/p&gt; &lt;p&gt; Sa philosophie est marquée par &lt;a href=&quot;https://www.youtube.com/watch?v=1aU99SspzLA&quot; title=&quot;gilbert of poitiers on individuation par history of philosophy&quot;&gt;un réalisme modéré &lt;/a&gt; dans le débat sur les universaux. Il soutient qu’aux concepts généraux de notre esprit correspondent dans les choses des natures semblables, sans confondre pour autant l’idée générale et l’individu concret. &lt;/p&gt; &lt;p&gt; Son œuvre la plus célèbre est son commentaire du De Trinitate de Boèce. C’est là qu’il développe ses analyses métaphysiques sur la forme, l’essence et l’individualité, avec un langage souvent très technique et parfois difficile à lire. &lt;/p&gt; &lt;p&gt; Ses positions sur la Trinité lui ont valu des accusations d’hérésie au concile de Reims en 1148. Le cœur du problème venait de certaines formulations jugées trop séparatrices entre l’essence divine et les personnes divines, mais Gilbert finit par accepter les formules proposées par ses adversaires. &lt;/p&gt; &lt;p&gt; Son intérêt principal est de clarifier la structure du réel par l’analyse logique et métaphysique. Il cherche à montrer comment les notions générales, les essences et les individus s’articulent, ce qui fait de lui  &lt;a href=&quot;https://gloss-e.irht.cnrs.fr/php/page.php?id=5&quot; title=&quot; commentaires sur les psaumes pauliniens par gloss&quot;&gt;un auteur important &lt;/a&gt;  pour comprendre la transition entre la pensée antique et la scolastique médiévale. &lt;/p&gt; &#10;" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" display="https://www.laphilo.fr/pho/gdlporree-mini.webp" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Bernard_de_Clairvaux&quot;  style=  title=&quot; Wikipedia&quot;&gt;BERNARD de Clairvaux&lt;/a&gt; est une figure marquante du XIIe siècle, tant sur le plan religieux que politique. Moine cistercien, mystique, réformateur, théologien et conseiller influent, il a joué un rôle central dans l'Église catholique et dans la société médiévale. &lt;/p&gt; &lt;p&gt; Il est un ardent et très influent défenseur de la réforme Grégorienne de l'Église et il s'oppose fermement à la corruption et à l'accumulation de richesses par le clergé. Il critique également les excès de la scolastique naissante, privilégiant une approche plus mystique et contemplative de la foi. &lt;/p&gt; &lt;p&gt; Il est l'auteur de nombreux traités théologiques et spirituels, dont les plus célèbres sont : &lt;/p&gt;&#10;&lt;dd&gt;&quot;De l'amour de Dieu&quot; (De diligendo Deo), où il explore la nature de l'amour divin et son rôle dans la vie spirituelle. &lt;/dd&gt;&#10;&lt;dd&gt;&lt;a href=&quot;https://www.youtube.com/watch?v=uo94zAU5RnU&quot;  title=&quot;Sermons sur le Cantique par Sanctus&quot;&gt;&quot;Sermons sur le Cantique des Cantiques&quot; &lt;/a&gt;, une œuvre mystique qui interprète ce livre biblique comme une allégorie de l'union de l'âme avec Dieu.&lt;/dd&gt;&#10;&lt;dd&gt;&quot;De la grâce et du libre arbitre&quot;, où il aborde les questions de la prédestination et de la liberté humaine.&lt;/dd&gt; &lt;p&gt; &lt;/p&gt;&#10;&lt;p&gt; Il fut co-fondateur de l'ordre des Templiers et le premier investigateur du le lancement de la &lt;a href=&quot;https://www.youtube.com/watch?v=jvRDaQ81vZc&quot; title=&quot;Bernard de Clairvaux , la 2ème croisade par Coursitou &quot;&gt;deuxième croissade . &lt;/a&gt; &lt;/p&gt;  &lt;p&gt; Canonisé en 1174, il est déclaré docteur de l'Église en 1830. Il a contribué à l'expansion de l'ordre cistercien et ses écrits ont profondément marqué la spiritualité chrétienne, inspirant des figures comme saint François d'Assise et saint Thomas d'Aquin.  Il est considéré comme l'un des grands mystiques du christianisme, ayant approfondi la compréhension de l'amour divin et de la relation entre l'homme et Dieu. &lt;/p&gt;    &lt;audio controls title=&quot;Saint Bertrand de Clairvaux par France Culture&quot;&gt; &lt;source src=&quot;https://media.radiofrance-podcast.net/podcast09/22636-10.04.2022-ITEMA_22990601-2022B45498S0100-21.mp3&quot; type=&quot;audio/mpeg&quot; align=&quot;center&quot;&gt; &lt;/audio&gt; " r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" display="https://www.laphilo.fr/pho/heloise-mini.webp" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" display="https://www.laphilo.fr/pho/hsvictor-mini.webp" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" display="https://www.laphilo.fr/pho/hildegarde-mini.webp" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" display="https://www.laphilo.fr/pho/heloise-mini.webp" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" display="https://www.laphilo.fr/pho/hsvictor-mini.webp" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" display="https://www.laphilo.fr/pho/hildegarde-mini.webp" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Pierre_le_Chantre&quot; title=&quot; Wikipedia&quot;&gt;Pierre le Chantre&lt;/a&gt; était  un théologien et maître parisien, plus qu’un philosophe au sens moderne du terme. Il appartient à la scolastique médiévale et a surtout travaillé sur l’interprétation de la Bible, la morale chrétienne et le droit canonique. Sa pensée est d’abord celle d’un enseignant. Il a formulé une &lt;a href=&quot;https://www.persee.fr/doc/rbph_0035-0818_1995_num_73_4_6951_t1_1144_0000_2&quot;  title=&quot; Glossae super Genesim  de pierre le Chantre par persée&quot;&gt;idée très importante &lt;/a&gt;  sur le métier de maître en théologie : lire l’Écriture, discuter rationnellement les questions qu’elle pose, puis prêcher pour transmettre ce savoir. &lt;/p&gt; &lt;p&gt; Il accorde aussi une grande place à la cohérence de la foi. Dans ses commentaires bibliques, il cherche à résoudre les contradictions apparentes entre les textes sacrés, ce qui montre une méthode intellectuelle très ordonnée et soucieuse d’harmoniser raison et révélation. &lt;/p&gt; &lt;p&gt; Sur le plan moral, il insiste sur la réforme du clergé, la vertu des moines et la discipline ecclésiastique. Son &lt;a href=&quot;https://www.persee.fr/doc/jds_0021-8103_1916_num_14_7_4589&quot;  title=&quot; Les manuscrits de pierre le Chantre par persée&quot;&gt;Verbum abbreviatum &lt;/a&gt; critique les abus religieux et défend une vie plus stricte, plus conforme à l’idéal chrétien.  Sa pensée est marquée par une réflexion sur la justice face à l’hérésie. À propos des cathares, il refuse l’idée de mise à mort systématique et préfère l’enfermement, ce qui montre une position plus juridique que purement répressive, et un souci de limiter la violence. &lt;/p&gt; &lt;p&gt; Il fut une figure essentielle de la pensée religieuse du XIIe siècle : un maître de la méthode scolastique, un moraliste exigeant et un témoin des débats intellectuels et institutionnels de son temps. &lt;/p&gt; &#10;&#10;" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" display="https://www.laphilo.fr/pho/plchantre-mini.webp" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" display="&lt;p&gt;&lt;a href=&quot;https://fr.wikipedia.org/wiki/Albert_le_Grand&quot;   title=&quot; Wikipedia&quot;&gt;ALBERT le Grand&lt;/a&gt; était un érudit, philosophe, théologien, et scientifique dont les travaux ont eu une influence profonde sur la pensée médiévale et moderne. Il est souvent considéré comme le &lt;a href=&quot;https://www.youtube.com/watch?v=DvQXZaFwB5k&quot; title=Albert le Grand par Pier Aujourd'hui &quot;&gt;précurseur&lt;/a&gt; de la synthèse entre la philosophie aristotélicienne et la théologie chrétienne, les rendant accessibles au monde chrétien. Ses travaux ont jeté les bases pour la synthèse philosophico-théologique que Thomas d'Aquin développera plus tard. Il était également un scientifique passionné et a écrit des traités sur une variété de sujets, y compris la biologie, la zoologie, la botanique, la minéralogie, et l'alchimie. Ses observations empiriques et ses expériences ont marqué un tournant dans l'approche médiévale des sciences naturelles. &lt;/p&gt; &lt;p&gt; Ses Œuvres Majeures : &lt;/p&gt;&#10;&lt;p&gt; De Mineralibus (Sur les Minéraux)  ,  De Animalibus (Sur les Animaux)  , &lt;a href=&quot;https://www.youtube.com/watch?v=PwYmEVkmqlo&amp;t=27s&quot; style=&quot;color:#88A1E9&quot; title=Le silence :Albert le Grand par la caverne du pelerins &quot;&gt;Summa Theologiae&lt;/a&gt; (une synthèse de théologie)  , Commentaires sur Aristote (y compris sur la Physique, la Métaphysique, et l'Éthique à Nicomaque)  ,  Canonisation et Héritage &lt;/p&gt; &#10;&lt;p&gt; Il  a été canonisé par le pape Pie XI en 1931 et déclaré Docteur de l'Église. Son héritage intellectuel est immense, influençant non seulement la théologie et la philosophie, mais aussi les sciences naturelles. Il est souvent considéré comme un modèle de l'érudition médiévale, capable de synthétiser la foi et la raison. &lt;/p&gt; &#10;&#10;&#10;&#10;" r:id="rId15"/>

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P120"/>
+  <dimension ref="A1:P123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -8507,6 +8507,176 @@
           <t xml:space="preserve">occident</t>
         </is>
       </c>
+    </row>
+    <row r="121" ht="99.75" customHeight="1" s="25">
+      <c r="A121" s="30">
+        <v>1018</v>
+      </c>
+      <c r="B121" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1078</t>
+        </is>
+      </c>
+      <c r="C121" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1018 – vers 1078</t>
+        </is>
+      </c>
+      <c r="D121" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michel PSELLOS</t>
+        </is>
+      </c>
+      <c r="E121" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Psellos" title=" Wikipedia"&gt;Michel PSELLOS&lt;/a&gt; est un philosophe, historien et homme politique byzantin. Né à Constantinople en 1018, dans une famille modeste, il reçoit une formation brillante et entre au service de l’empereur. Sous Constantin IX, il devient l’un des personnages les plus influents de la cour et reçoit le titre de « consul des philosophes » : il dirige l’enseignement de la philosophie dans la capitale. Il se fait moine en 1054 sous le nom de Michel, mais revient vite à la cour, où il conseille plusieurs empereurs. Il meurt vers 1078.&lt;/p&gt; &lt;p&gt;Esprit encyclopédique, il écrit sur la philosophie, la théologie, la rhétorique, la médecine, les mathématiques et l’astronomie. Il fait renaître à Byzance l’étude de Platon et des néoplatoniciens, surtout Plotin et Proclus, et commente Aristote. Il s’intéresse aussi aux &lt;em&gt;Oracles chaldaïques&lt;/em&gt; et aux traditions occultes. Pour lui, la philosophie grecque n’est pas l’ennemie de la foi chrétienne : bien comprise, elle y prépare, et le chrétien cultivé doit en connaître les trésors. Cette admiration pour les païens lui vaut d’être soupçonné d’hérésie, et il doit à plusieurs reprises affirmer son orthodoxie.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Chronographie&lt;/em&gt;, histoire des empereurs de 976 à 1078 dont il a souvent été le témoin direct, est un chef-d’œuvre de la littérature byzantine, plein de portraits vivants. Il a préparé la renaissance du &lt;a href="https://fr.wikipedia.org/wiki/Platonisme" title=" Wikipedia"&gt;platonisme&lt;/a&gt; qui, avec Pléthon, gagnera l’Italie au XVe siècle.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H121" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/psellos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J121" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Byzantine</t>
+        </is>
+      </c>
+      <c r="K121" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L121" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme ; Platonisme</t>
+        </is>
+      </c>
+      <c r="M121" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe, historien et homme de cour byzantin, qui fit renaître l’étude de Platon à Constantinople.</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" ht="99.75" customHeight="1" s="25">
+      <c r="A122" s="30">
+        <v>1025</v>
+      </c>
+      <c r="B122" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1082</t>
+        </is>
+      </c>
+      <c r="C122" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1025 – après 1082</t>
+        </is>
+      </c>
+      <c r="D122" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jean ITALOS</t>
+        </is>
+      </c>
+      <c r="E122" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Italos" title=" Wikipedia"&gt;Jean ITALOS&lt;/a&gt; est un philosophe byzantin. Né vers 1025 en Italie du Sud, fils d’un soldat, il gagne Constantinople vers 1049, où il devient l’élève de Michel Psellos. Il lui succède vers 1055 à la tête de l’enseignement de la philosophie, avec le titre de « consul des philosophes ». Il est apprécié de l’empereur Michel VII, qui lui confie des missions diplomatiques en Italie. Ses élèves l’admirent pour sa rigueur, ses adversaires lui reprochent sa rudesse et son grec à l’accent étranger.&lt;/p&gt; &lt;p&gt;Il commente la logique d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt; et rassemble ses leçons dans un recueil de &lt;em&gt;Questions et réponses&lt;/em&gt; sur la philosophie, la logique et la théologie. Plus audacieux que son maître, il applique le raisonnement philosophique aux questions religieuses et accorde une grande autorité à Platon et aux néoplatoniciens. Il passe pour défendre des thèses contraires à la foi : l’éternité du monde, l’existence réelle des Idées de Platon, la migration des âmes d’un corps à l’autre.&lt;/p&gt; &lt;p&gt;En 1082, sous l’empereur Alexis Ier Comnène, il est jugé par un synode et condamné. Onze anathèmes sont ajoutés au &lt;em&gt;Synodikon de l’Orthodoxie&lt;/em&gt;, que l’on lit chaque année dans les églises : ils condamnent ceux qui étudient la philosophie grecque non pour s’instruire, mais pour l’adopter. Italos doit se rétracter et finit ses jours dans un monastère. Son procès marque la méfiance de l’Église byzantine envers la philosophie.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H122" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/italos-mini.webp</t>
+        </is>
+      </c>
+      <c r="J122" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Byzantine</t>
+        </is>
+      </c>
+      <c r="K122" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metaphysique ; logique</t>
+        </is>
+      </c>
+      <c r="L122" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Néoplatonisme ; Aristotélisme</t>
+        </is>
+      </c>
+      <c r="M122" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">philosophe byzantin d’origine italienne, élève de Psellos, condamné pour avoir trop aimé la philosophie grecque.</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P122"/>
+    </row>
+    <row r="123" ht="99.75" customHeight="1" s="25">
+      <c r="A123" s="30">
+        <v>1346</v>
+      </c>
+      <c r="B123" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1409</t>
+        </is>
+      </c>
+      <c r="C123" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1346 – 1409</t>
+        </is>
+      </c>
+      <c r="D123" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GRÉGOIRE de Tatev</t>
+        </is>
+      </c>
+      <c r="E123" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Tatev" title=" Wikipedia"&gt;GRÉGOIRE de Tatev&lt;/a&gt; est un théologien, philosophe, enseignant et peintre arménien, appelé dans sa langue Grigor Tatevatsi. Né en 1346, dans une Arménie ravagée par les guerres, il est envoyé jeune au monastère de Tatev, dans le sud du pays, où il étudie auprès du maître Hovhannès Vorotnetsi. Il en devient le supérieur et y dirige une célèbre école, sorte d’université médiévale où l’on enseigne la philosophie, la théologie, la musique et la peinture. Malgré les invasions de Tamerlan, qui l’obligent souvent à fuir avec ses élèves, il maintient son enseignement jusqu’à sa mort en 1409.&lt;/p&gt; &lt;p&gt;Il est l’auteur d’une œuvre considérable, dont le &lt;em&gt;Livre des questions&lt;/em&gt; (1397), une vaste encyclopédie de la théologie et de la philosophie, et deux grands recueils de sermons. Nourri d’Aristote, des Pères de l’Église et de la &lt;a href="https://fr.wikipedia.org/wiki/Scolastique" title=" Wikipedia"&gt;scolastique&lt;/a&gt; occidentale, il distingue nettement la philosophie, qui s’appuie sur la raison, et la théologie, qui s’appuie sur la révélation : ce sont deux chemins vers une même vérité. Les historiens soviétiques ont souligné ses positions proches du nominalisme, pour qui les idées générales n’existent que dans l’esprit.&lt;/p&gt; &lt;p&gt;Il défend avec vigueur l’indépendance de l’Église apostolique arménienne contre les missionnaires catholiques qui voulaient la rattacher à Rome, en retournant contre eux leurs propres méthodes. Peintre de talent, il enlumine des Évangiles aux couleurs éclatantes. Il est vénéré comme un saint par l’Église arménienne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H123" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/gregoiretatev-mini.webp</t>
+        </is>
+      </c>
+      <c r="J123" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arménienne</t>
+        </is>
+      </c>
+      <c r="K123" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spiritualite ; metaphysique</t>
+        </is>
+      </c>
+      <c r="L123" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nominalisme ; Scolastique</t>
+        </is>
+      </c>
+      <c r="M123" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">théologien, philosophe et peintre arménien, maître de l’école de Tatev et saint de l’Église arménienne.</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P123"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -598,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P123"/>
+  <dimension ref="A1:P124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6.81" customWidth="1" style="23" min="1" max="1"/>
@@ -8677,6 +8677,62 @@
         </is>
       </c>
       <c r="P123"/>
+    </row>
+    <row r="124" ht="99.75" customHeight="1" s="25">
+      <c r="A124" s="30">
+        <v>1290</v>
+      </c>
+      <c r="B124" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1348</t>
+        </is>
+      </c>
+      <c r="C124" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vers 1290 – 1348</t>
+        </is>
+      </c>
+      <c r="D124" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BARLAAM de Calabre</t>
+        </is>
+      </c>
+      <c r="E124" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Barlaam_le_Calabrais" title=" Wikipedia"&gt;BARLAAM de Calabre&lt;/a&gt; est un moine, philosophe et savant de langue grecque. Né vers 1290 à Seminara, en Calabre, une région de l’Italie du Sud où vivaient encore des communautés grecques, il devient moine de rite grec. Vers 1330, il gagne Constantinople, où il est bien accueilli par l’empereur Andronic III. Il y enseigne la philosophie, commente Euclide et écrit sur l’astronomie et la musique. L’empereur l’envoie en 1339 à Avignon, auprès du pape, pour négocier l’union des Églises d’Orient et d’Occident.&lt;/p&gt; &lt;p&gt;Contre les théologiens latins, il soutient qu’on ne peut rien démontrer sur Dieu, qui dépasse toute raison : les raisonnements théologiques ne sont que probables. Cette position heurte le moine Grégoire Palamas. La querelle s’envenime quand Barlaam s’attaque aux moines de l’Athos, les hésychastes, qui pratiquent une prière continue liée à la respiration et affirment voir la lumière divine qui transfigura le Christ sur le mont Thabor. Pour Barlaam, savant formé à Aristote, cette lumière ne peut être que créée, et leurs pratiques relèvent de la superstition.&lt;/p&gt; &lt;p&gt;Il est condamné par un concile à Constantinople en 1341, et l’Église orthodoxe donne raison à Palamas. Barlaam retourne alors en Italie, rejoint l’Église latine et devient évêque de Gerace, en Calabre. Il enseigne le grec à Pétrarque et contribue ainsi aux débuts de l’&lt;a href="https://fr.wikipedia.org/wiki/Humanisme" title=" Wikipedia"&gt;humanisme&lt;/a&gt; italien. Il meurt à Avignon en 1348.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="H124" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.laphilo.fr/pho/barlaam-mini.webp</t>
+        </is>
+      </c>
+      <c r="J124" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Byzantine</t>
+        </is>
+      </c>
+      <c r="K124" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">epistemologie ; spiritualite</t>
+        </is>
+      </c>
+      <c r="L124" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristotélisme ; Humanisme</t>
+        </is>
+      </c>
+      <c r="M124" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moine et savant gréco-italien, adversaire de Grégoire Palamas et maître de grec de Pétrarque.</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">occident</t>
+        </is>
+      </c>
+      <c r="P124"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/frise-philosophes-medievaux.xlsx
+++ b/data/frise-philosophes-medievaux.xlsx
@@ -8297,6 +8297,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Ioane_Petritsi" title=" Wikipedia (en)"&gt;Ioane PETRITSI&lt;/a&gt; est le plus important philosophe géorgien du Moyen Âge. Né dans une famille aristocratique de la province de Samtskhé, dans le sud de la Géorgie, il étudie à Constantinople auprès des plus grands maîtres byzantins de son temps, Michel Psellos et Jean Italos, qui renouvellent l’étude de Platon et des néoplatoniciens. Après la condamnation de Jean Italos pour hérésie, il se réfugie, semble-t-il, au monastère géorgien de Petritsoni, en Bulgarie, dont il tire son surnom.&lt;/p&gt; &lt;p&gt;Traducteur infatigable, il fait passer en géorgien des œuvres d’Aristote, de &lt;a href="https://fr.wikipedia.org/wiki/Proclus" title=" Wikipedia"&gt;Proclus&lt;/a&gt;, de Némésius et d’Ammonius, ainsi que des textes bibliques et des vies de saints. Il veut montrer que la philosophie grecque et la foi chrétienne peuvent s’accorder. Son œuvre maîtresse est sa traduction des &lt;em&gt;Éléments de théologie&lt;/em&gt; de Proclus, accompagnée d’un long commentaire : l’Un, principe premier au-delà de tout ce qui existe, y est rapproché du Dieu chrétien, et la procession des êtres à partir de l’Un est relue à la lumière de la Création.&lt;/p&gt; &lt;p&gt;Ses idées le mettent en conflit avec les gardiens de l’orthodoxie géorgienne, jusqu’à ce que le roi David IV le Bâtisseur l’installe à l’académie de Gelati, grand centre d’enseignement fondé par le souverain. Il compose aussi des hymnes et de la poésie mystique. Son influence sur la pensée et la langue philosophique géorgiennes a été durable, et elle connaît un renouveau au XVIIIe siècle. Il est aujourd’hui considéré comme le philosophe géorgien le plus lu.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CJSD5ZlSnlM</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"HoP 319 - Georgia on My Mind - Petritsi and the Proclus Revival" par History of Philosophy Without Any Gaps Podcast</t>
+        </is>
+      </c>
       <c r="H117" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/petritsi-mini.webp</t>
@@ -8355,6 +8365,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Henri_Suso" title=" Wikipedia"&gt;Henri SUSO&lt;/a&gt; (Heinrich Seuse en allemand) est un religieux dominicain allemand, l’une des grandes figures de la &lt;a href="https://fr.wikipedia.org/wiki/Mystique_rh%C3%A9nane" title=" Wikipedia"&gt;mystique rhénane&lt;/a&gt;. Né vers 1295 au bord du lac de Constance, il entre à treize ans au couvent des dominicains de Constance. Vers dix-huit ans, une expérience intérieure le convertit : il se livre alors pendant des années à des pénitences extrêmes, avant de comprendre qu’il doit renoncer à ces mortifications extérieures pour une ascèse tout intérieure.&lt;/p&gt; &lt;p&gt;Envoyé étudier à Cologne en 1323, il y suit l’enseignement de &lt;a href="https://fr.wikipedia.org/wiki/Ma%C3%AEtre_Eckhart" title=" Wikipedia"&gt;Maître Eckhart&lt;/a&gt;, dont il devient l’un des disciples les plus fidèles. Après la condamnation de son maître, il écrit pour le défendre le &lt;em&gt;Petit Livre de la vérité&lt;/em&gt;, ce qui lui vaut des ennuis avec son ordre. Mais là où Eckhart pense en métaphysicien, Suso parle en poète et en amoureux. Dans le &lt;em&gt;Petit Livre de la Sagesse éternelle&lt;/em&gt;, sous forme de dialogue, il célèbre la Sagesse divine, qu’il aime comme un chevalier aime sa dame. Sa version latine, l’&lt;em&gt;Horloge de la Sagesse&lt;/em&gt;, devient l’un des livres de dévotion les plus lus de la fin du Moyen Âge. Le détachement eckhartien devient chez lui un chemin de l’âme qui passe par la souffrance acceptée, l’imitation du Christ et la tendresse.&lt;/p&gt; &lt;p&gt;Prédicateur et directeur spirituel de nombreuses religieuses, il raconte sa vie à l’une d’elles, Elsbeth Stagel, qui la met par écrit : c’est l’une des premières autobiographies spirituelles en langue allemande, illustrée de dessins symboliques. Il meurt à Ulm en 1366. Il a été proclamé bienheureux en 1831.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cpk-raT8EQE</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Histoires mystiques rhénanes (3/3) Tauler et Suso, héritiers d'Eckhart" par Résonance[s]</t>
+        </is>
+      </c>
       <c r="H118" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/suso-mini.webp</t>
@@ -8411,6 +8431,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jan_Van_Ruysbroeck_%28religieux%29" title=" Wikipedia"&gt;Jan van RUUSBROEC&lt;/a&gt; (ou Ruysbroeck, dit « l’Admirable ») est un prêtre et mystique brabançon, le grand maître de la mystique flamande, branche de la &lt;a href="https://fr.wikipedia.org/wiki/Mystique_rh%C3%A9nane" title=" Wikipedia"&gt;mystique rhénane&lt;/a&gt;. Né en 1293 près de Bruxelles, il étudie auprès d’un oncle chanoine, devient prêtre et chapelain de la collégiale Sainte-Gudule, où il reste jusqu’à cinquante ans. Il écrit en moyen néerlandais, la langue du peuple, et non en latin.&lt;/p&gt; &lt;p&gt;En 1343, il se retire avec quelques compagnons dans la forêt de Soignes, à Groenendael, la « vallée verte », où il fonde une communauté qui adopte la règle des chanoines de saint Augustin. Son chef-d’œuvre, &lt;em&gt;Les Noces spirituelles&lt;/em&gt;, décrit l’ascension de l’âme vers Dieu en trois étapes : la vie active, faite de vertus et de charité ; la vie intérieure, où l’âme se recueille et désire Dieu ; enfin la vie contemplative, où elle s’unit à Dieu sans se confondre avec lui. Car, à la différence de certains mystiques de son temps, Ruusbroec maintient toujours la distinction entre la créature et le Créateur, et ne sépare jamais la contemplation des sacrements de l’Église ni de l’amour du prochain. Il s’oppose vivement aux « Frères du libre esprit », qui prétendaient qu’une âme unie à Dieu n’était plus tenue par aucune loi morale.&lt;/p&gt; &lt;p&gt;Sa renommée dépasse vite le Brabant. Gérard Groote, le fondateur de la &lt;a href="https://fr.wikipedia.org/wiki/Devotio_moderna" title=" Wikipedia"&gt;Devotio moderna&lt;/a&gt;, lui rend visite, et ce mouvement, d’où sortira l’&lt;em&gt;Imitation de Jésus-Christ&lt;/em&gt;, prolonge son esprit. Il meurt à Groenendael en 1381, presque nonagénaire. Maurice Maeterlinck a traduit et fait connaître son œuvre en France. Il a été proclamé bienheureux en 1908.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8AFJOWf3V0E</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Jan van Ruusbroec - Life and works, Part 1 with Rob Faesen, SJ #chapter27" par Xaverian Brothers</t>
+        </is>
+      </c>
       <c r="H119" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/ruusbroec-mini.webp</t>
@@ -8532,6 +8562,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Michel_Psellos" title=" Wikipedia"&gt;Michel PSELLOS&lt;/a&gt; est un philosophe, historien et homme politique byzantin. Né à Constantinople en 1018, dans une famille modeste, il reçoit une formation brillante et entre au service de l’empereur. Sous Constantin IX, il devient l’un des personnages les plus influents de la cour et reçoit le titre de « consul des philosophes » : il dirige l’enseignement de la philosophie dans la capitale. Il se fait moine en 1054 sous le nom de Michel, mais revient vite à la cour, où il conseille plusieurs empereurs. Il meurt vers 1078.&lt;/p&gt; &lt;p&gt;Esprit encyclopédique, il écrit sur la philosophie, la théologie, la rhétorique, la médecine, les mathématiques et l’astronomie. Il fait renaître à Byzance l’étude de Platon et des néoplatoniciens, surtout Plotin et Proclus, et commente Aristote. Il s’intéresse aussi aux &lt;em&gt;Oracles chaldaïques&lt;/em&gt; et aux traditions occultes. Pour lui, la philosophie grecque n’est pas l’ennemie de la foi chrétienne : bien comprise, elle y prépare, et le chrétien cultivé doit en connaître les trésors. Cette admiration pour les païens lui vaut d’être soupçonné d’hérésie, et il doit à plusieurs reprises affirmer son orthodoxie.&lt;/p&gt; &lt;p&gt;Sa &lt;em&gt;Chronographie&lt;/em&gt;, histoire des empereurs de 976 à 1078 dont il a souvent été le témoin direct, est un chef-d’œuvre de la littérature byzantine, plein de portraits vivants. Il a préparé la renaissance du &lt;a href="https://fr.wikipedia.org/wiki/Platonisme" title=" Wikipedia"&gt;platonisme&lt;/a&gt; qui, avec Pléthon, gagnera l’Italie au XVe siècle.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">QB1UIYZ3p8A</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Le système théologique des Oracles chaldaïques selon Michel Psellos et sa source proclienne" par Les Platonismes de l'Antiquité Tardive</t>
+        </is>
+      </c>
       <c r="H121" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/psellos-mini.webp</t>
@@ -8590,6 +8630,16 @@
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Jean_Italos" title=" Wikipedia"&gt;Jean ITALOS&lt;/a&gt; est un philosophe byzantin. Né vers 1025 en Italie du Sud, fils d’un soldat, il gagne Constantinople vers 1049, où il devient l’élève de Michel Psellos. Il lui succède vers 1055 à la tête de l’enseignement de la philosophie, avec le titre de « consul des philosophes ». Il est apprécié de l’empereur Michel VII, qui lui confie des missions diplomatiques en Italie. Ses élèves l’admirent pour sa rigueur, ses adversaires lui reprochent sa rudesse et son grec à l’accent étranger.&lt;/p&gt; &lt;p&gt;Il commente la logique d’&lt;a href="https://fr.wikipedia.org/wiki/Aristote" title=" Wikipedia"&gt;Aristote&lt;/a&gt; et rassemble ses leçons dans un recueil de &lt;em&gt;Questions et réponses&lt;/em&gt; sur la philosophie, la logique et la théologie. Plus audacieux que son maître, il applique le raisonnement philosophique aux questions religieuses et accorde une grande autorité à Platon et aux néoplatoniciens. Il passe pour défendre des thèses contraires à la foi : l’éternité du monde, l’existence réelle des Idées de Platon, la migration des âmes d’un corps à l’autre.&lt;/p&gt; &lt;p&gt;En 1082, sous l’empereur Alexis Ier Comnène, il est jugé par un synode et condamné. Onze anathèmes sont ajoutés au &lt;em&gt;Synodikon de l’Orthodoxie&lt;/em&gt;, que l’on lit chaque année dans les églises : ils condamnent ceux qui étudient la philosophie grecque non pour s’instruire, mais pour l’adopter. Italos doit se rétracter et finit ses jours dans un monastère. Son procès marque la méfiance de l’Église byzantine envers la philosophie.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rCt8aepKo80</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Néoplatonisme ? Transmigration des âmes ? Salut universel ? (Les Chapitres contre Jean Italos)" par Foi Patristique</t>
+        </is>
+      </c>
       <c r="H122" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.laphilo.fr/pho/italos-mini.webp</t>
@@ -8644,6 +8694,16 @@
       <c r="E123" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;p&gt;&lt;a href="https://fr.wikipedia.org/wiki/Gr%C3%A9goire_de_Tatev" title=" Wikipedia"&gt;GRÉGOIRE de Tatev&lt;/a&gt; est un théologien, philosophe, enseignant et peintre arménien, appelé dans sa langue Grigor Tatevatsi. Né en 1346, dans une Arménie ravagée par les guerres, il est envoyé jeune au monastère de Tatev, dans le sud du pays, où il étudie auprès du maître Hovhannès Vorotnetsi. Il en devient le supérieur et y dirige une célèbre école, sorte d’université médiévale où l’on enseigne la philosophie, la théologie, la musique et la peinture. Malgré les invasions de Tamerlan, qui l’obligent souvent à fuir avec ses élèves, il maintient son enseignement jusqu’à sa mort en 1409.&lt;/p&gt; &lt;p&gt;Il est l’auteur d’une œuvre considérable, dont le &lt;em&gt;Livre des questions&lt;/em&gt; (1397), une vaste encyclopédie de la théologie et de la philosophie, et deux grands recueils de sermons. Nourri d’Aristote, des Pères de l’Église et de la &lt;a href="https://fr.wikipedia.org/wiki/Scolastique" title=" Wikipedia"&gt;scolastique&lt;/a&gt; occidentale, il distingue nettement la philosophie, qui s’appuie sur la raison, et la théologie, qui s’appuie sur la révélation : ce sont deux chemins vers une même vérité. Les historiens soviétiques ont souligné ses positions proches du nominalisme, pour qui les idées générales n’existent que dans l’esprit.&lt;/p&gt; &lt;p&gt;Il défend avec vigueur l’indépendance de l’Église apostolique arménienne contre les missionnaires catholiques qui voulaient la rattacher à Rome, en retournant contre eux leurs propres méthodes. Peintre de talent, il enlumine des Évangiles aux couleurs éclatantes. Il est vénéré comme un saint par l’Église arménienne.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EypZhSHcgJc</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Saint Grégoire de Tatev, 14 Questions contre les Dyophysites, Livre des Questions." par Saint Tatevatsi</t>
         </is>
       </c>
       <c r="H123" s="33" t="inlineStr">
